--- a/BASE_KEMPARTS.xlsx
+++ b/BASE_KEMPARTS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dash_kp_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45BC4A76-966E-4727-B3B3-BBC4CC33B9D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{902177DB-F828-4D2A-AAFF-1F8EEF583922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{0A1F9BA2-0B75-4EBC-AAED-2636C969E57C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{034ED65E-4C5C-4047-81C4-E67EF536DEAB}"/>
   </bookViews>
   <sheets>
     <sheet name="FSP" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6897" uniqueCount="1230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7147" uniqueCount="1258">
   <si>
     <t/>
   </si>
@@ -3036,6 +3036,90 @@
   </si>
   <si>
     <t>173793</t>
+  </si>
+  <si>
+    <t>000015529</t>
+  </si>
+  <si>
+    <t>COO648</t>
+  </si>
+  <si>
+    <t>POLLIBOX INDUSTRIA</t>
+  </si>
+  <si>
+    <t>2024.103.03.Q240613</t>
+  </si>
+  <si>
+    <t>Q240613</t>
+  </si>
+  <si>
+    <t>2024.103.03.</t>
+  </si>
+  <si>
+    <t>152747</t>
+  </si>
+  <si>
+    <t>000015530</t>
+  </si>
+  <si>
+    <t>2026.429.02.936752</t>
+  </si>
+  <si>
+    <t>936752</t>
+  </si>
+  <si>
+    <t>2026.429.02.</t>
+  </si>
+  <si>
+    <t>173780</t>
+  </si>
+  <si>
+    <t>000015533</t>
+  </si>
+  <si>
+    <t>150974</t>
+  </si>
+  <si>
+    <t>000015534</t>
+  </si>
+  <si>
+    <t>C01139</t>
+  </si>
+  <si>
+    <t>NEOSENSE FRAGRANCIAS LTDA</t>
+  </si>
+  <si>
+    <t>150268</t>
+  </si>
+  <si>
+    <t>2025.732.01.0000410888</t>
+  </si>
+  <si>
+    <t>0000410888</t>
+  </si>
+  <si>
+    <t>2025.732.01.</t>
+  </si>
+  <si>
+    <t>2025.732.01.0000404968</t>
+  </si>
+  <si>
+    <t>0000404968</t>
+  </si>
+  <si>
+    <t>2024.772.03.2024.1002HH1016</t>
+  </si>
+  <si>
+    <t>1002HH1016</t>
+  </si>
+  <si>
+    <t>2024.772.03.2024.</t>
+  </si>
+  <si>
+    <t>2025.732.01.0000406221</t>
+  </si>
+  <si>
+    <t>0000406221</t>
   </si>
   <si>
     <t>GASTOS GERAIS</t>
@@ -4657,46 +4741,45 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F2ADB9-C618-4B85-A55D-86323D7CFBEC}">
-  <dimension ref="A1:AJ209"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BC32493-C966-4678-BA2F-91D43E76D569}">
+  <dimension ref="A1:AJ219"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="59.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="59.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="64.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="72" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="42.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="48" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="24.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -27687,6 +27770,1106 @@
       </c>
       <c r="AJ209" s="8">
         <v>1959.2873999999999</v>
+      </c>
+    </row>
+    <row r="210" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A210" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D210" s="4">
+        <v>46087</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G210" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H210" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I210" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J210" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K210" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="L210" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="M210" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="N210" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="O210" s="5">
+        <v>1</v>
+      </c>
+      <c r="P210" s="5">
+        <v>10</v>
+      </c>
+      <c r="Q210" s="6">
+        <v>10</v>
+      </c>
+      <c r="R210" s="6">
+        <v>0</v>
+      </c>
+      <c r="S210" s="6">
+        <v>10</v>
+      </c>
+      <c r="T210" s="6">
+        <v>0</v>
+      </c>
+      <c r="U210" s="6">
+        <v>0</v>
+      </c>
+      <c r="V210" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="W210" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="X210" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y210" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="Z210" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA210" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB210" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC210" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="AD210" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="AE210" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="AF210" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="AG210" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH210" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI210" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ210" s="5">
+        <v>7.5035699999999999</v>
+      </c>
+    </row>
+    <row r="211" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A211" s="3" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D211" s="7">
+        <v>46087</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F211" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G211" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="H211" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="I211" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J211" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K211" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="L211" s="3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="M211" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N211" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="O211" s="8">
+        <v>2040</v>
+      </c>
+      <c r="P211" s="8">
+        <v>24.98</v>
+      </c>
+      <c r="Q211" s="9">
+        <v>50959.199999999997</v>
+      </c>
+      <c r="R211" s="9">
+        <v>1656.17</v>
+      </c>
+      <c r="S211" s="9">
+        <v>52615.37</v>
+      </c>
+      <c r="T211" s="9">
+        <v>50959.199999999997</v>
+      </c>
+      <c r="U211" s="9">
+        <v>2038.37</v>
+      </c>
+      <c r="V211" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="W211" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="X211" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y211" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="Z211" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA211" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB211" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC211" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="AD211" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE211" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF211" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG211" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH211" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI211" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ211" s="8">
+        <v>21548.356800000001</v>
+      </c>
+    </row>
+    <row r="212" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A212" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D212" s="4">
+        <v>46087</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F212" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G212" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="H212" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="I212" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J212" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K212" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="L212" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="M212" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="N212" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="O212" s="5">
+        <v>1</v>
+      </c>
+      <c r="P212" s="5">
+        <v>10</v>
+      </c>
+      <c r="Q212" s="6">
+        <v>10</v>
+      </c>
+      <c r="R212" s="6">
+        <v>0</v>
+      </c>
+      <c r="S212" s="6">
+        <v>10</v>
+      </c>
+      <c r="T212" s="6">
+        <v>0</v>
+      </c>
+      <c r="U212" s="6">
+        <v>0</v>
+      </c>
+      <c r="V212" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="W212" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="X212" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y212" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="Z212" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA212" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB212" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC212" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="AD212" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="AE212" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="AF212" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="AG212" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH212" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI212" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ212" s="5">
+        <v>33.119909999999997</v>
+      </c>
+    </row>
+    <row r="213" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A213" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D213" s="7">
+        <v>46087</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F213" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G213" s="3" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H213" s="3" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I213" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J213" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="K213" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="L213" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="M213" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="N213" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="O213" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="P213" s="8">
+        <v>10</v>
+      </c>
+      <c r="Q213" s="9">
+        <v>3</v>
+      </c>
+      <c r="R213" s="9">
+        <v>0</v>
+      </c>
+      <c r="S213" s="9">
+        <v>3</v>
+      </c>
+      <c r="T213" s="9">
+        <v>0</v>
+      </c>
+      <c r="U213" s="9">
+        <v>0</v>
+      </c>
+      <c r="V213" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="W213" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="X213" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y213" s="3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="Z213" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA213" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB213" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC213" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD213" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="AE213" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="AF213" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AG213" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH213" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI213" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ213" s="8">
+        <v>5.8336399999999999</v>
+      </c>
+    </row>
+    <row r="214" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A214" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D214" s="4">
+        <v>46087</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F214" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G214" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H214" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I214" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J214" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K214" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="L214" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M214" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="N214" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="O214" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="P214" s="5">
+        <v>10</v>
+      </c>
+      <c r="Q214" s="6">
+        <v>3</v>
+      </c>
+      <c r="R214" s="6">
+        <v>0</v>
+      </c>
+      <c r="S214" s="6">
+        <v>3</v>
+      </c>
+      <c r="T214" s="6">
+        <v>0</v>
+      </c>
+      <c r="U214" s="6">
+        <v>0</v>
+      </c>
+      <c r="V214" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="W214" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="X214" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y214" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="Z214" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA214" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB214" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC214" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD214" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="AE214" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="AF214" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="AG214" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH214" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI214" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ214" s="5">
+        <v>11.511559999999999</v>
+      </c>
+    </row>
+    <row r="215" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A215" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D215" s="7">
+        <v>46087</v>
+      </c>
+      <c r="E215" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F215" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G215" s="3" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H215" s="3" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I215" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J215" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="K215" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="L215" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="M215" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="N215" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="O215" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="P215" s="8">
+        <v>10</v>
+      </c>
+      <c r="Q215" s="9">
+        <v>3</v>
+      </c>
+      <c r="R215" s="9">
+        <v>0</v>
+      </c>
+      <c r="S215" s="9">
+        <v>3</v>
+      </c>
+      <c r="T215" s="9">
+        <v>0</v>
+      </c>
+      <c r="U215" s="9">
+        <v>0</v>
+      </c>
+      <c r="V215" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="W215" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="X215" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y215" s="3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="Z215" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA215" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB215" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC215" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD215" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="AE215" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="AF215" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AG215" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH215" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI215" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ215" s="8">
+        <v>4.2570499999999996</v>
+      </c>
+    </row>
+    <row r="216" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A216" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D216" s="4">
+        <v>46087</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F216" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G216" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H216" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I216" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J216" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K216" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="L216" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="M216" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="N216" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="O216" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="P216" s="5">
+        <v>10</v>
+      </c>
+      <c r="Q216" s="6">
+        <v>3</v>
+      </c>
+      <c r="R216" s="6">
+        <v>0</v>
+      </c>
+      <c r="S216" s="6">
+        <v>3</v>
+      </c>
+      <c r="T216" s="6">
+        <v>0</v>
+      </c>
+      <c r="U216" s="6">
+        <v>0</v>
+      </c>
+      <c r="V216" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="W216" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="X216" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y216" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="Z216" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA216" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB216" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC216" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD216" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="AE216" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="AF216" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="AG216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH216" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ216" s="5">
+        <v>5.5413300000000003</v>
+      </c>
+    </row>
+    <row r="217" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A217" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D217" s="7">
+        <v>46087</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G217" s="3" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H217" s="3" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I217" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J217" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="K217" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="L217" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="M217" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="N217" s="3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="O217" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="P217" s="8">
+        <v>10</v>
+      </c>
+      <c r="Q217" s="9">
+        <v>3</v>
+      </c>
+      <c r="R217" s="9">
+        <v>0</v>
+      </c>
+      <c r="S217" s="9">
+        <v>3</v>
+      </c>
+      <c r="T217" s="9">
+        <v>0</v>
+      </c>
+      <c r="U217" s="9">
+        <v>0</v>
+      </c>
+      <c r="V217" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="W217" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="X217" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y217" s="3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="Z217" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA217" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB217" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC217" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD217" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="AE217" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="AF217" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AG217" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH217" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI217" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ217" s="8">
+        <v>9.1377699999999997</v>
+      </c>
+    </row>
+    <row r="218" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A218" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D218" s="4">
+        <v>46087</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F218" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G218" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H218" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I218" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J218" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K218" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="L218" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="M218" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="N218" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="O218" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="P218" s="5">
+        <v>10</v>
+      </c>
+      <c r="Q218" s="6">
+        <v>3</v>
+      </c>
+      <c r="R218" s="6">
+        <v>0</v>
+      </c>
+      <c r="S218" s="6">
+        <v>3</v>
+      </c>
+      <c r="T218" s="6">
+        <v>0</v>
+      </c>
+      <c r="U218" s="6">
+        <v>0</v>
+      </c>
+      <c r="V218" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="W218" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="X218" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y218" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="Z218" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA218" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB218" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC218" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD218" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="AE218" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="AF218" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="AG218" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH218" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI218" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ218" s="5">
+        <v>6.1189999999999998</v>
+      </c>
+    </row>
+    <row r="219" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A219" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D219" s="7">
+        <v>46087</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G219" s="3" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H219" s="3" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I219" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J219" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="K219" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="L219" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="M219" s="3" t="s">
+        <v>1032</v>
+      </c>
+      <c r="N219" s="3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="O219" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="P219" s="8">
+        <v>10</v>
+      </c>
+      <c r="Q219" s="9">
+        <v>3</v>
+      </c>
+      <c r="R219" s="9">
+        <v>0</v>
+      </c>
+      <c r="S219" s="9">
+        <v>3</v>
+      </c>
+      <c r="T219" s="9">
+        <v>0</v>
+      </c>
+      <c r="U219" s="9">
+        <v>0</v>
+      </c>
+      <c r="V219" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="W219" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="X219" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y219" s="3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="Z219" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA219" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB219" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC219" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD219" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="AE219" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="AF219" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AG219" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH219" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI219" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ219" s="8">
+        <v>13.0503</v>
       </c>
     </row>
   </sheetData>
@@ -27695,45 +28878,44 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF97C886-AD47-4F2D-975B-017666E22EED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A0FB20-CDDD-4477-B867-5F1CAAB1D4C5}">
   <dimension ref="A1:AJ66"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="56.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="43.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="42.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="64.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="50.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="48" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="25.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -27848,13 +29030,13 @@
     </row>
     <row r="2" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>1229</v>
+        <v>1257</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1229</v>
+        <v>1257</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D2" s="4">
         <v>46024</v>
@@ -27866,10 +29048,10 @@
         <v>40</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1010</v>
+        <v>1038</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>1009</v>
+        <v>1037</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>43</v>
@@ -27881,13 +29063,13 @@
         <v>440</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>1078</v>
+        <v>1106</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>1077</v>
+        <v>1105</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>1076</v>
+        <v>1104</v>
       </c>
       <c r="O2" s="5">
         <v>50</v>
@@ -27911,16 +29093,16 @@
         <v>39.06</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>1075</v>
+        <v>1103</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>1074</v>
+        <v>1102</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>1228</v>
+        <v>1256</v>
       </c>
       <c r="Z2" s="2" t="s">
         <v>0</v>
@@ -27958,13 +29140,13 @@
     </row>
     <row r="3" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>1227</v>
+        <v>1255</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1227</v>
+        <v>1255</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D3" s="7">
         <v>46027</v>
@@ -27976,10 +29158,10 @@
         <v>61</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1093</v>
+        <v>1121</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1092</v>
+        <v>1120</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>163</v>
@@ -27991,13 +29173,13 @@
         <v>632</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1091</v>
+        <v>1119</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>648</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>1090</v>
+        <v>1118</v>
       </c>
       <c r="O3" s="8">
         <v>1001</v>
@@ -28030,7 +29212,7 @@
         <v>51</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>1226</v>
+        <v>1254</v>
       </c>
       <c r="Z3" s="3" t="s">
         <v>0</v>
@@ -28068,13 +29250,13 @@
     </row>
     <row r="4" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>1225</v>
+        <v>1253</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1225</v>
+        <v>1253</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D4" s="4">
         <v>46027</v>
@@ -28086,10 +29268,10 @@
         <v>61</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1224</v>
+        <v>1252</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1223</v>
+        <v>1251</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>152</v>
@@ -28101,13 +29283,13 @@
         <v>342</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1222</v>
+        <v>1250</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1221</v>
+        <v>1249</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1220</v>
+        <v>1248</v>
       </c>
       <c r="O4" s="5">
         <v>600</v>
@@ -28131,16 +29313,16 @@
         <v>355.68</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>1219</v>
+        <v>1247</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>1218</v>
+        <v>1246</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>1217</v>
+        <v>1245</v>
       </c>
       <c r="Z4" s="2" t="s">
         <v>0</v>
@@ -28178,13 +29360,13 @@
     </row>
     <row r="5" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>1216</v>
+        <v>1244</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1216</v>
+        <v>1244</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D5" s="7">
         <v>46029</v>
@@ -28196,10 +29378,10 @@
         <v>212</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>1134</v>
+        <v>1162</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>139</v>
@@ -28208,7 +29390,7 @@
         <v>140</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>1215</v>
+        <v>1243</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>0</v>
@@ -28250,7 +29432,7 @@
         <v>87</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>1214</v>
+        <v>1242</v>
       </c>
       <c r="Z5" s="3" t="s">
         <v>0</v>
@@ -28288,13 +29470,13 @@
     </row>
     <row r="6" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>1216</v>
+        <v>1244</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1216</v>
+        <v>1244</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D6" s="4">
         <v>46029</v>
@@ -28306,10 +29488,10 @@
         <v>212</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1134</v>
+        <v>1162</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>139</v>
@@ -28318,7 +29500,7 @@
         <v>140</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>1215</v>
+        <v>1243</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>0</v>
@@ -28360,7 +29542,7 @@
         <v>87</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>1214</v>
+        <v>1242</v>
       </c>
       <c r="Z6" s="2" t="s">
         <v>0</v>
@@ -28398,13 +29580,13 @@
     </row>
     <row r="7" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>1213</v>
+        <v>1241</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1213</v>
+        <v>1241</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D7" s="7">
         <v>46029</v>
@@ -28422,22 +29604,22 @@
         <v>386</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>1097</v>
+        <v>1125</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>1096</v>
+        <v>1124</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>1040</v>
+        <v>1068</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>1212</v>
+        <v>1240</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>1211</v>
+        <v>1239</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>1210</v>
+        <v>1238</v>
       </c>
       <c r="O7" s="8">
         <v>1000</v>
@@ -28470,7 +29652,7 @@
         <v>51</v>
       </c>
       <c r="Y7" s="3" t="s">
-        <v>1209</v>
+        <v>1237</v>
       </c>
       <c r="Z7" s="3" t="s">
         <v>0</v>
@@ -28508,13 +29690,13 @@
     </row>
     <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>1208</v>
+        <v>1236</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1208</v>
+        <v>1236</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D8" s="4">
         <v>46036</v>
@@ -28526,10 +29708,10 @@
         <v>61</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1093</v>
+        <v>1121</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>1092</v>
+        <v>1120</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>163</v>
@@ -28541,13 +29723,13 @@
         <v>632</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>1091</v>
+        <v>1119</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1090</v>
+        <v>1118</v>
       </c>
       <c r="O8" s="5">
         <v>1001</v>
@@ -28580,7 +29762,7 @@
         <v>51</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>1207</v>
+        <v>1235</v>
       </c>
       <c r="Z8" s="2" t="s">
         <v>0</v>
@@ -28618,13 +29800,13 @@
     </row>
     <row r="9" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>1206</v>
+        <v>1234</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1206</v>
+        <v>1234</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D9" s="7">
         <v>46037</v>
@@ -28636,10 +29818,10 @@
         <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>1106</v>
+        <v>1134</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1105</v>
+        <v>1133</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>163</v>
@@ -28651,13 +29833,13 @@
         <v>417</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>1205</v>
+        <v>1233</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>1204</v>
+        <v>1232</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>1102</v>
+        <v>1130</v>
       </c>
       <c r="O9" s="8">
         <v>1000</v>
@@ -28690,7 +29872,7 @@
         <v>51</v>
       </c>
       <c r="Y9" s="3" t="s">
-        <v>1203</v>
+        <v>1231</v>
       </c>
       <c r="Z9" s="3" t="s">
         <v>0</v>
@@ -28728,13 +29910,13 @@
     </row>
     <row r="10" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>1202</v>
+        <v>1230</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1202</v>
+        <v>1230</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D10" s="4">
         <v>46037</v>
@@ -28746,10 +29928,10 @@
         <v>40</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1054</v>
+        <v>1082</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1053</v>
+        <v>1081</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>139</v>
@@ -28761,13 +29943,13 @@
         <v>784</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>1052</v>
+        <v>1080</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1051</v>
+        <v>1079</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1050</v>
+        <v>1078</v>
       </c>
       <c r="O10" s="5">
         <v>300</v>
@@ -28800,7 +29982,7 @@
         <v>51</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>1201</v>
+        <v>1229</v>
       </c>
       <c r="Z10" s="2" t="s">
         <v>0</v>
@@ -28838,13 +30020,13 @@
     </row>
     <row r="11" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>1200</v>
+        <v>1228</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1200</v>
+        <v>1228</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D11" s="7">
         <v>46037</v>
@@ -28856,10 +30038,10 @@
         <v>40</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>1144</v>
+        <v>1172</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1143</v>
+        <v>1171</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>43</v>
@@ -28871,13 +30053,13 @@
         <v>300</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>1199</v>
+        <v>1227</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>1198</v>
+        <v>1226</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>1197</v>
+        <v>1225</v>
       </c>
       <c r="O11" s="8">
         <v>25</v>
@@ -28910,7 +30092,7 @@
         <v>51</v>
       </c>
       <c r="Y11" s="3" t="s">
-        <v>1196</v>
+        <v>1224</v>
       </c>
       <c r="Z11" s="3" t="s">
         <v>0</v>
@@ -28948,13 +30130,13 @@
     </row>
     <row r="12" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>1195</v>
+        <v>1223</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1195</v>
+        <v>1223</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D12" s="4">
         <v>46041</v>
@@ -28966,10 +30148,10 @@
         <v>212</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1134</v>
+        <v>1162</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>139</v>
@@ -28978,7 +30160,7 @@
         <v>140</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>1026</v>
+        <v>1054</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>0</v>
@@ -29020,7 +30202,7 @@
         <v>87</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>1194</v>
+        <v>1222</v>
       </c>
       <c r="Z12" s="2" t="s">
         <v>0</v>
@@ -29035,10 +30217,10 @@
         <v>55</v>
       </c>
       <c r="AD12" s="2" t="s">
-        <v>1021</v>
+        <v>1049</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>1020</v>
+        <v>1048</v>
       </c>
       <c r="AF12" s="2" t="s">
         <v>442</v>
@@ -29058,13 +30240,13 @@
     </row>
     <row r="13" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>1193</v>
+        <v>1221</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1193</v>
+        <v>1221</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D13" s="7">
         <v>46042</v>
@@ -29082,22 +30264,22 @@
         <v>386</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>1097</v>
+        <v>1125</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>1096</v>
+        <v>1124</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>446</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>1100</v>
+        <v>1128</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>1099</v>
+        <v>1127</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>1065</v>
+        <v>1093</v>
       </c>
       <c r="O13" s="8">
         <v>2000</v>
@@ -29130,7 +30312,7 @@
         <v>51</v>
       </c>
       <c r="Y13" s="3" t="s">
-        <v>1192</v>
+        <v>1220</v>
       </c>
       <c r="Z13" s="3" t="s">
         <v>0</v>
@@ -29168,13 +30350,13 @@
     </row>
     <row r="14" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>1191</v>
+        <v>1219</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1191</v>
+        <v>1219</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D14" s="4">
         <v>46042</v>
@@ -29198,16 +30380,16 @@
         <v>294</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>1026</v>
+        <v>1054</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>1159</v>
+        <v>1187</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1158</v>
+        <v>1186</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1023</v>
+        <v>1051</v>
       </c>
       <c r="O14" s="5">
         <v>6000</v>
@@ -29231,16 +30413,16 @@
         <v>12873.6</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>1190</v>
+        <v>1218</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>1189</v>
+        <v>1217</v>
       </c>
       <c r="X14" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>1188</v>
+        <v>1216</v>
       </c>
       <c r="Z14" s="2" t="s">
         <v>0</v>
@@ -29255,10 +30437,10 @@
         <v>298</v>
       </c>
       <c r="AD14" s="2" t="s">
-        <v>1021</v>
+        <v>1049</v>
       </c>
       <c r="AE14" s="2" t="s">
-        <v>1020</v>
+        <v>1048</v>
       </c>
       <c r="AF14" s="2" t="s">
         <v>77</v>
@@ -29278,13 +30460,13 @@
     </row>
     <row r="15" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>1187</v>
+        <v>1215</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1187</v>
+        <v>1215</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D15" s="7">
         <v>46042</v>
@@ -29296,10 +30478,10 @@
         <v>212</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>1134</v>
+        <v>1162</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>139</v>
@@ -29350,7 +30532,7 @@
         <v>87</v>
       </c>
       <c r="Y15" s="3" t="s">
-        <v>1186</v>
+        <v>1214</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>0</v>
@@ -29371,7 +30553,7 @@
         <v>518</v>
       </c>
       <c r="AF15" s="3" t="s">
-        <v>1154</v>
+        <v>1182</v>
       </c>
       <c r="AG15" s="9">
         <v>0</v>
@@ -29388,13 +30570,13 @@
     </row>
     <row r="16" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>1187</v>
+        <v>1215</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1187</v>
+        <v>1215</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D16" s="4">
         <v>46042</v>
@@ -29406,10 +30588,10 @@
         <v>212</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1134</v>
+        <v>1162</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>139</v>
@@ -29460,7 +30642,7 @@
         <v>87</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>1186</v>
+        <v>1214</v>
       </c>
       <c r="Z16" s="2" t="s">
         <v>0</v>
@@ -29481,7 +30663,7 @@
         <v>518</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>1154</v>
+        <v>1182</v>
       </c>
       <c r="AG16" s="6">
         <v>0</v>
@@ -29498,13 +30680,13 @@
     </row>
     <row r="17" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>1185</v>
+        <v>1213</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1185</v>
+        <v>1213</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D17" s="7">
         <v>46043</v>
@@ -29531,13 +30713,13 @@
         <v>417</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>1104</v>
+        <v>1132</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>1103</v>
+        <v>1131</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>1102</v>
+        <v>1130</v>
       </c>
       <c r="O17" s="8">
         <v>1000</v>
@@ -29570,7 +30752,7 @@
         <v>51</v>
       </c>
       <c r="Y17" s="3" t="s">
-        <v>1184</v>
+        <v>1212</v>
       </c>
       <c r="Z17" s="3" t="s">
         <v>0</v>
@@ -29608,28 +30790,28 @@
     </row>
     <row r="18" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>1172</v>
+        <v>1200</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1172</v>
+        <v>1200</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D18" s="4">
         <v>46045</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1171</v>
+        <v>1199</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1170</v>
+        <v>1198</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1110</v>
+        <v>1138</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>1109</v>
+        <v>1137</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>139</v>
@@ -29641,13 +30823,13 @@
         <v>628</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>1183</v>
+        <v>1211</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1182</v>
+        <v>1210</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1181</v>
+        <v>1209</v>
       </c>
       <c r="O18" s="5">
         <v>2000</v>
@@ -29671,16 +30853,16 @@
         <v>0</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>1166</v>
+        <v>1194</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="X18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>1165</v>
+        <v>1193</v>
       </c>
       <c r="Z18" s="2" t="s">
         <v>0</v>
@@ -29718,28 +30900,28 @@
     </row>
     <row r="19" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>1172</v>
+        <v>1200</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>1172</v>
+        <v>1200</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D19" s="7">
         <v>46045</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>1171</v>
+        <v>1199</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>1170</v>
+        <v>1198</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>1110</v>
+        <v>1138</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>1109</v>
+        <v>1137</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>139</v>
@@ -29751,13 +30933,13 @@
         <v>631</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>1180</v>
+        <v>1208</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>1179</v>
+        <v>1207</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>1167</v>
+        <v>1195</v>
       </c>
       <c r="O19" s="8">
         <v>11725</v>
@@ -29781,16 +30963,16 @@
         <v>0</v>
       </c>
       <c r="V19" s="3" t="s">
-        <v>1166</v>
+        <v>1194</v>
       </c>
       <c r="W19" s="3" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="X19" s="3" t="s">
         <v>87</v>
       </c>
       <c r="Y19" s="3" t="s">
-        <v>1165</v>
+        <v>1193</v>
       </c>
       <c r="Z19" s="3" t="s">
         <v>0</v>
@@ -29828,28 +31010,28 @@
     </row>
     <row r="20" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>1172</v>
+        <v>1200</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1172</v>
+        <v>1200</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D20" s="4">
         <v>46045</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1171</v>
+        <v>1199</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1170</v>
+        <v>1198</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1110</v>
+        <v>1138</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1109</v>
+        <v>1137</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>139</v>
@@ -29861,13 +31043,13 @@
         <v>632</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>1091</v>
+        <v>1119</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1090</v>
+        <v>1118</v>
       </c>
       <c r="O20" s="5">
         <v>2925</v>
@@ -29891,16 +31073,16 @@
         <v>0</v>
       </c>
       <c r="V20" s="2" t="s">
-        <v>1166</v>
+        <v>1194</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="X20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>1165</v>
+        <v>1193</v>
       </c>
       <c r="Z20" s="2" t="s">
         <v>0</v>
@@ -29938,28 +31120,28 @@
     </row>
     <row r="21" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>1172</v>
+        <v>1200</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>1172</v>
+        <v>1200</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D21" s="7">
         <v>46045</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>1171</v>
+        <v>1199</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>1170</v>
+        <v>1198</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>1110</v>
+        <v>1138</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>1109</v>
+        <v>1137</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>139</v>
@@ -29971,13 +31153,13 @@
         <v>633</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>1034</v>
+        <v>1062</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>652</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>1033</v>
+        <v>1061</v>
       </c>
       <c r="O21" s="8">
         <v>2925</v>
@@ -30001,16 +31183,16 @@
         <v>0</v>
       </c>
       <c r="V21" s="3" t="s">
-        <v>1166</v>
+        <v>1194</v>
       </c>
       <c r="W21" s="3" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>87</v>
       </c>
       <c r="Y21" s="3" t="s">
-        <v>1165</v>
+        <v>1193</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>0</v>
@@ -30048,28 +31230,28 @@
     </row>
     <row r="22" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>1172</v>
+        <v>1200</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1172</v>
+        <v>1200</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D22" s="4">
         <v>46045</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1171</v>
+        <v>1199</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1170</v>
+        <v>1198</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1110</v>
+        <v>1138</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1109</v>
+        <v>1137</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>139</v>
@@ -30081,13 +31263,13 @@
         <v>465</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1178</v>
+        <v>1206</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1177</v>
+        <v>1205</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1176</v>
+        <v>1204</v>
       </c>
       <c r="O22" s="5">
         <v>2400</v>
@@ -30111,16 +31293,16 @@
         <v>0</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>1166</v>
+        <v>1194</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="X22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>1165</v>
+        <v>1193</v>
       </c>
       <c r="Z22" s="2" t="s">
         <v>0</v>
@@ -30158,28 +31340,28 @@
     </row>
     <row r="23" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>1172</v>
+        <v>1200</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>1172</v>
+        <v>1200</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D23" s="7">
         <v>46045</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>1171</v>
+        <v>1199</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>1170</v>
+        <v>1198</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>1110</v>
+        <v>1138</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>1109</v>
+        <v>1137</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>139</v>
@@ -30191,13 +31373,13 @@
         <v>465</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>1175</v>
+        <v>1203</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>1174</v>
+        <v>1202</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>1173</v>
+        <v>1201</v>
       </c>
       <c r="O23" s="8">
         <v>1800</v>
@@ -30221,16 +31403,16 @@
         <v>0</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>1166</v>
+        <v>1194</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>87</v>
       </c>
       <c r="Y23" s="3" t="s">
-        <v>1165</v>
+        <v>1193</v>
       </c>
       <c r="Z23" s="3" t="s">
         <v>0</v>
@@ -30268,28 +31450,28 @@
     </row>
     <row r="24" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>1172</v>
+        <v>1200</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1172</v>
+        <v>1200</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D24" s="4">
         <v>46045</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1171</v>
+        <v>1199</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1170</v>
+        <v>1198</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1110</v>
+        <v>1138</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1109</v>
+        <v>1137</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>139</v>
@@ -30301,13 +31483,13 @@
         <v>634</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>1169</v>
+        <v>1197</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1168</v>
+        <v>1196</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1167</v>
+        <v>1195</v>
       </c>
       <c r="O24" s="5">
         <v>1400</v>
@@ -30331,16 +31513,16 @@
         <v>0</v>
       </c>
       <c r="V24" s="2" t="s">
-        <v>1166</v>
+        <v>1194</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="X24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>1165</v>
+        <v>1193</v>
       </c>
       <c r="Z24" s="2" t="s">
         <v>0</v>
@@ -30378,13 +31560,13 @@
     </row>
     <row r="25" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>1164</v>
+        <v>1192</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>1164</v>
+        <v>1192</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D25" s="7">
         <v>46048</v>
@@ -30411,13 +31593,13 @@
         <v>417</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>1116</v>
+        <v>1144</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>1115</v>
+        <v>1143</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>1114</v>
+        <v>1142</v>
       </c>
       <c r="O25" s="8">
         <v>5000</v>
@@ -30441,16 +31623,16 @@
         <v>2354</v>
       </c>
       <c r="V25" s="3" t="s">
-        <v>1044</v>
+        <v>1072</v>
       </c>
       <c r="W25" s="3" t="s">
-        <v>1043</v>
+        <v>1071</v>
       </c>
       <c r="X25" s="3" t="s">
         <v>51</v>
       </c>
       <c r="Y25" s="3" t="s">
-        <v>1163</v>
+        <v>1191</v>
       </c>
       <c r="Z25" s="3" t="s">
         <v>0</v>
@@ -30488,13 +31670,13 @@
     </row>
     <row r="26" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>1162</v>
+        <v>1190</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1162</v>
+        <v>1190</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D26" s="4">
         <v>46048</v>
@@ -30506,10 +31688,10 @@
         <v>40</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1054</v>
+        <v>1082</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1053</v>
+        <v>1081</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>139</v>
@@ -30521,13 +31703,13 @@
         <v>784</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>1052</v>
+        <v>1080</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1051</v>
+        <v>1079</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1050</v>
+        <v>1078</v>
       </c>
       <c r="O26" s="5">
         <v>300</v>
@@ -30560,7 +31742,7 @@
         <v>51</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>1161</v>
+        <v>1189</v>
       </c>
       <c r="Z26" s="2" t="s">
         <v>0</v>
@@ -30598,13 +31780,13 @@
     </row>
     <row r="27" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>1160</v>
+        <v>1188</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>1160</v>
+        <v>1188</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D27" s="7">
         <v>46048</v>
@@ -30616,10 +31798,10 @@
         <v>61</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>1093</v>
+        <v>1121</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>1092</v>
+        <v>1120</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>163</v>
@@ -30631,13 +31813,13 @@
         <v>632</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>1091</v>
+        <v>1119</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>648</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>1090</v>
+        <v>1118</v>
       </c>
       <c r="O27" s="8">
         <v>611</v>
@@ -30670,7 +31852,7 @@
         <v>51</v>
       </c>
       <c r="Y27" s="3" t="s">
-        <v>1157</v>
+        <v>1185</v>
       </c>
       <c r="Z27" s="3" t="s">
         <v>0</v>
@@ -30708,13 +31890,13 @@
     </row>
     <row r="28" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>1160</v>
+        <v>1188</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1160</v>
+        <v>1188</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D28" s="4">
         <v>46048</v>
@@ -30726,10 +31908,10 @@
         <v>61</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1093</v>
+        <v>1121</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1092</v>
+        <v>1120</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>163</v>
@@ -30738,16 +31920,16 @@
         <v>164</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>1026</v>
+        <v>1054</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>1159</v>
+        <v>1187</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1158</v>
+        <v>1186</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1023</v>
+        <v>1051</v>
       </c>
       <c r="O28" s="5">
         <v>700</v>
@@ -30780,7 +31962,7 @@
         <v>51</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>1157</v>
+        <v>1185</v>
       </c>
       <c r="Z28" s="2" t="s">
         <v>0</v>
@@ -30795,10 +31977,10 @@
         <v>55</v>
       </c>
       <c r="AD28" s="2" t="s">
-        <v>1021</v>
+        <v>1049</v>
       </c>
       <c r="AE28" s="2" t="s">
-        <v>1020</v>
+        <v>1048</v>
       </c>
       <c r="AF28" s="2" t="s">
         <v>77</v>
@@ -30818,13 +32000,13 @@
     </row>
     <row r="29" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>1156</v>
+        <v>1184</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>1156</v>
+        <v>1184</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D29" s="7">
         <v>46048</v>
@@ -30836,10 +32018,10 @@
         <v>212</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>1134</v>
+        <v>1162</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>139</v>
@@ -30890,7 +32072,7 @@
         <v>87</v>
       </c>
       <c r="Y29" s="3" t="s">
-        <v>1155</v>
+        <v>1183</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>0</v>
@@ -30911,7 +32093,7 @@
         <v>57</v>
       </c>
       <c r="AF29" s="3" t="s">
-        <v>1154</v>
+        <v>1182</v>
       </c>
       <c r="AG29" s="9">
         <v>0</v>
@@ -30928,13 +32110,13 @@
     </row>
     <row r="30" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>1153</v>
+        <v>1181</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1153</v>
+        <v>1181</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D30" s="4">
         <v>46049</v>
@@ -30946,10 +32128,10 @@
         <v>212</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1134</v>
+        <v>1162</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>139</v>
@@ -31000,7 +32182,7 @@
         <v>87</v>
       </c>
       <c r="Y30" s="2" t="s">
-        <v>1152</v>
+        <v>1180</v>
       </c>
       <c r="Z30" s="2" t="s">
         <v>0</v>
@@ -31038,13 +32220,13 @@
     </row>
     <row r="31" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>1153</v>
+        <v>1181</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>1153</v>
+        <v>1181</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D31" s="7">
         <v>46049</v>
@@ -31056,10 +32238,10 @@
         <v>212</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>1134</v>
+        <v>1162</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>139</v>
@@ -31110,7 +32292,7 @@
         <v>87</v>
       </c>
       <c r="Y31" s="3" t="s">
-        <v>1152</v>
+        <v>1180</v>
       </c>
       <c r="Z31" s="3" t="s">
         <v>0</v>
@@ -31148,13 +32330,13 @@
     </row>
     <row r="32" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>1149</v>
+        <v>1177</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1149</v>
+        <v>1177</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D32" s="4">
         <v>46050</v>
@@ -31172,22 +32354,22 @@
         <v>386</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>1097</v>
+        <v>1125</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>1096</v>
+        <v>1124</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>446</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>1151</v>
+        <v>1179</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>448</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1150</v>
+        <v>1178</v>
       </c>
       <c r="O32" s="5">
         <v>1000</v>
@@ -31220,7 +32402,7 @@
         <v>51</v>
       </c>
       <c r="Y32" s="2" t="s">
-        <v>1148</v>
+        <v>1176</v>
       </c>
       <c r="Z32" s="2" t="s">
         <v>0</v>
@@ -31258,13 +32440,13 @@
     </row>
     <row r="33" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>1149</v>
+        <v>1177</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>1149</v>
+        <v>1177</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D33" s="7">
         <v>46050</v>
@@ -31282,22 +32464,22 @@
         <v>386</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>1097</v>
+        <v>1125</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>1096</v>
+        <v>1124</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>446</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>1100</v>
+        <v>1128</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>1099</v>
+        <v>1127</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>1065</v>
+        <v>1093</v>
       </c>
       <c r="O33" s="8">
         <v>1000</v>
@@ -31330,7 +32512,7 @@
         <v>51</v>
       </c>
       <c r="Y33" s="3" t="s">
-        <v>1148</v>
+        <v>1176</v>
       </c>
       <c r="Z33" s="3" t="s">
         <v>0</v>
@@ -31368,13 +32550,13 @@
     </row>
     <row r="34" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>1147</v>
+        <v>1175</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1147</v>
+        <v>1175</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D34" s="4">
         <v>46050</v>
@@ -31386,10 +32568,10 @@
         <v>212</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1134</v>
+        <v>1162</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>139</v>
@@ -31440,7 +32622,7 @@
         <v>87</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>1146</v>
+        <v>1174</v>
       </c>
       <c r="Z34" s="2" t="s">
         <v>0</v>
@@ -31478,13 +32660,13 @@
     </row>
     <row r="35" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>1145</v>
+        <v>1173</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>1145</v>
+        <v>1173</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D35" s="7">
         <v>46051</v>
@@ -31496,10 +32678,10 @@
         <v>40</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>1144</v>
+        <v>1172</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>1143</v>
+        <v>1171</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>43</v>
@@ -31511,13 +32693,13 @@
         <v>632</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>1091</v>
+        <v>1119</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>648</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>1090</v>
+        <v>1118</v>
       </c>
       <c r="O35" s="8">
         <v>26</v>
@@ -31550,7 +32732,7 @@
         <v>51</v>
       </c>
       <c r="Y35" s="3" t="s">
-        <v>1142</v>
+        <v>1170</v>
       </c>
       <c r="Z35" s="3" t="s">
         <v>0</v>
@@ -31588,13 +32770,13 @@
     </row>
     <row r="36" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>1141</v>
+        <v>1169</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>1141</v>
+        <v>1169</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D36" s="4">
         <v>46052</v>
@@ -31606,10 +32788,10 @@
         <v>61</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1093</v>
+        <v>1121</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>1092</v>
+        <v>1120</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>163</v>
@@ -31621,13 +32803,13 @@
         <v>632</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>1091</v>
+        <v>1119</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1090</v>
+        <v>1118</v>
       </c>
       <c r="O36" s="5">
         <v>507</v>
@@ -31660,7 +32842,7 @@
         <v>51</v>
       </c>
       <c r="Y36" s="2" t="s">
-        <v>1140</v>
+        <v>1168</v>
       </c>
       <c r="Z36" s="2" t="s">
         <v>0</v>
@@ -31698,13 +32880,13 @@
     </row>
     <row r="37" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>1139</v>
+        <v>1167</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>1139</v>
+        <v>1167</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D37" s="7">
         <v>46052</v>
@@ -31728,16 +32910,16 @@
         <v>164</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>1031</v>
+        <v>1059</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>1059</v>
+        <v>1087</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>1058</v>
+        <v>1086</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>1028</v>
+        <v>1056</v>
       </c>
       <c r="O37" s="8">
         <v>500</v>
@@ -31770,7 +32952,7 @@
         <v>51</v>
       </c>
       <c r="Y37" s="3" t="s">
-        <v>1138</v>
+        <v>1166</v>
       </c>
       <c r="Z37" s="3" t="s">
         <v>0</v>
@@ -31808,13 +32990,13 @@
     </row>
     <row r="38" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>1137</v>
+        <v>1165</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1137</v>
+        <v>1165</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D38" s="4">
         <v>46052</v>
@@ -31826,10 +33008,10 @@
         <v>40</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>1054</v>
+        <v>1082</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>1053</v>
+        <v>1081</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>139</v>
@@ -31841,13 +33023,13 @@
         <v>784</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>1052</v>
+        <v>1080</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>1051</v>
+        <v>1079</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>1050</v>
+        <v>1078</v>
       </c>
       <c r="O38" s="5">
         <v>300</v>
@@ -31880,7 +33062,7 @@
         <v>51</v>
       </c>
       <c r="Y38" s="2" t="s">
-        <v>1136</v>
+        <v>1164</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>0</v>
@@ -31918,13 +33100,13 @@
     </row>
     <row r="39" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>1135</v>
+        <v>1163</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>1135</v>
+        <v>1163</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D39" s="7">
         <v>46055</v>
@@ -31936,10 +33118,10 @@
         <v>212</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>1134</v>
+        <v>1162</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>139</v>
@@ -31948,7 +33130,7 @@
         <v>140</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>1132</v>
+        <v>1160</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>0</v>
@@ -31990,7 +33172,7 @@
         <v>87</v>
       </c>
       <c r="Y39" s="3" t="s">
-        <v>1131</v>
+        <v>1159</v>
       </c>
       <c r="Z39" s="3" t="s">
         <v>0</v>
@@ -32028,13 +33210,13 @@
     </row>
     <row r="40" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>1130</v>
+        <v>1158</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1130</v>
+        <v>1158</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D40" s="4">
         <v>46057</v>
@@ -32046,10 +33228,10 @@
         <v>61</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1093</v>
+        <v>1121</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>1092</v>
+        <v>1120</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>163</v>
@@ -32061,13 +33243,13 @@
         <v>632</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>1091</v>
+        <v>1119</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>1090</v>
+        <v>1118</v>
       </c>
       <c r="O40" s="5">
         <v>507</v>
@@ -32100,7 +33282,7 @@
         <v>51</v>
       </c>
       <c r="Y40" s="2" t="s">
-        <v>1129</v>
+        <v>1157</v>
       </c>
       <c r="Z40" s="2" t="s">
         <v>0</v>
@@ -32138,13 +33320,13 @@
     </row>
     <row r="41" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>1128</v>
+        <v>1156</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>1128</v>
+        <v>1156</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D41" s="7">
         <v>46057</v>
@@ -32162,22 +33344,22 @@
         <v>386</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>1097</v>
+        <v>1125</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>1096</v>
+        <v>1124</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>446</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>1100</v>
+        <v>1128</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>1099</v>
+        <v>1127</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>1065</v>
+        <v>1093</v>
       </c>
       <c r="O41" s="8">
         <v>2000</v>
@@ -32210,7 +33392,7 @@
         <v>51</v>
       </c>
       <c r="Y41" s="3" t="s">
-        <v>1095</v>
+        <v>1123</v>
       </c>
       <c r="Z41" s="3" t="s">
         <v>0</v>
@@ -32248,13 +33430,13 @@
     </row>
     <row r="42" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>1127</v>
+        <v>1155</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1127</v>
+        <v>1155</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D42" s="4">
         <v>46058</v>
@@ -32266,10 +33448,10 @@
         <v>61</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1093</v>
+        <v>1121</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>1092</v>
+        <v>1120</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>163</v>
@@ -32281,13 +33463,13 @@
         <v>632</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>1091</v>
+        <v>1119</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>1090</v>
+        <v>1118</v>
       </c>
       <c r="O42" s="5">
         <v>507</v>
@@ -32320,7 +33502,7 @@
         <v>51</v>
       </c>
       <c r="Y42" s="2" t="s">
-        <v>1126</v>
+        <v>1154</v>
       </c>
       <c r="Z42" s="2" t="s">
         <v>0</v>
@@ -32358,13 +33540,13 @@
     </row>
     <row r="43" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>1125</v>
+        <v>1153</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>1125</v>
+        <v>1153</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D43" s="7">
         <v>46058</v>
@@ -32376,10 +33558,10 @@
         <v>61</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>1062</v>
+        <v>1090</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>1061</v>
+        <v>1089</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>163</v>
@@ -32391,13 +33573,13 @@
         <v>417</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>1116</v>
+        <v>1144</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>1115</v>
+        <v>1143</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>1114</v>
+        <v>1142</v>
       </c>
       <c r="O43" s="8">
         <v>1800</v>
@@ -32430,7 +33612,7 @@
         <v>51</v>
       </c>
       <c r="Y43" s="3" t="s">
-        <v>1124</v>
+        <v>1152</v>
       </c>
       <c r="Z43" s="3" t="s">
         <v>0</v>
@@ -32468,13 +33650,13 @@
     </row>
     <row r="44" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>1123</v>
+        <v>1151</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>1123</v>
+        <v>1151</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D44" s="4">
         <v>46059</v>
@@ -32486,10 +33668,10 @@
         <v>40</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1122</v>
+        <v>1150</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>1121</v>
+        <v>1149</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>43</v>
@@ -32501,13 +33683,13 @@
         <v>784</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>1052</v>
+        <v>1080</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>1051</v>
+        <v>1079</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>1050</v>
+        <v>1078</v>
       </c>
       <c r="O44" s="5">
         <v>500</v>
@@ -32540,7 +33722,7 @@
         <v>51</v>
       </c>
       <c r="Y44" s="2" t="s">
-        <v>1120</v>
+        <v>1148</v>
       </c>
       <c r="Z44" s="2" t="s">
         <v>0</v>
@@ -32578,13 +33760,13 @@
     </row>
     <row r="45" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>1119</v>
+        <v>1147</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>1119</v>
+        <v>1147</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D45" s="7">
         <v>46059</v>
@@ -32596,10 +33778,10 @@
         <v>40</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>1118</v>
+        <v>1146</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>1117</v>
+        <v>1145</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>43</v>
@@ -32611,13 +33793,13 @@
         <v>417</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>1116</v>
+        <v>1144</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>1115</v>
+        <v>1143</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>1114</v>
+        <v>1142</v>
       </c>
       <c r="O45" s="8">
         <v>200</v>
@@ -32650,7 +33832,7 @@
         <v>51</v>
       </c>
       <c r="Y45" s="3" t="s">
-        <v>1113</v>
+        <v>1141</v>
       </c>
       <c r="Z45" s="3" t="s">
         <v>0</v>
@@ -32688,28 +33870,28 @@
     </row>
     <row r="46" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>1112</v>
+        <v>1140</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1112</v>
+        <v>1140</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D46" s="4">
         <v>46063</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1111</v>
+        <v>1139</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>267</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1110</v>
+        <v>1138</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>1109</v>
+        <v>1137</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>139</v>
@@ -32718,7 +33900,7 @@
         <v>140</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>1008</v>
+        <v>1036</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>0</v>
@@ -32760,7 +33942,7 @@
         <v>0</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>1108</v>
+        <v>1136</v>
       </c>
       <c r="Z46" s="2" t="s">
         <v>0</v>
@@ -32775,10 +33957,10 @@
         <v>74</v>
       </c>
       <c r="AD46" s="2" t="s">
-        <v>1006</v>
+        <v>1034</v>
       </c>
       <c r="AE46" s="2" t="s">
-        <v>1005</v>
+        <v>1033</v>
       </c>
       <c r="AF46" s="2" t="s">
         <v>0</v>
@@ -32798,13 +33980,13 @@
     </row>
     <row r="47" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>1107</v>
+        <v>1135</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>1107</v>
+        <v>1135</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D47" s="7">
         <v>46064</v>
@@ -32816,10 +33998,10 @@
         <v>61</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>1106</v>
+        <v>1134</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>1105</v>
+        <v>1133</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>139</v>
@@ -32831,13 +34013,13 @@
         <v>417</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>1104</v>
+        <v>1132</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>1103</v>
+        <v>1131</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>1102</v>
+        <v>1130</v>
       </c>
       <c r="O47" s="8">
         <v>1000</v>
@@ -32870,7 +34052,7 @@
         <v>51</v>
       </c>
       <c r="Y47" s="3" t="s">
-        <v>1101</v>
+        <v>1129</v>
       </c>
       <c r="Z47" s="3" t="s">
         <v>0</v>
@@ -32908,13 +34090,13 @@
     </row>
     <row r="48" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>1098</v>
+        <v>1126</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1098</v>
+        <v>1126</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D48" s="4">
         <v>46064</v>
@@ -32932,22 +34114,22 @@
         <v>386</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>1097</v>
+        <v>1125</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>1096</v>
+        <v>1124</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>446</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>1100</v>
+        <v>1128</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>1099</v>
+        <v>1127</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>1065</v>
+        <v>1093</v>
       </c>
       <c r="O48" s="5">
         <v>1000</v>
@@ -32980,7 +34162,7 @@
         <v>51</v>
       </c>
       <c r="Y48" s="2" t="s">
-        <v>1095</v>
+        <v>1123</v>
       </c>
       <c r="Z48" s="2" t="s">
         <v>0</v>
@@ -33018,13 +34200,13 @@
     </row>
     <row r="49" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>1098</v>
+        <v>1126</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>1098</v>
+        <v>1126</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D49" s="7">
         <v>46064</v>
@@ -33042,22 +34224,22 @@
         <v>386</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>1097</v>
+        <v>1125</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>1096</v>
+        <v>1124</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>446</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>1067</v>
+        <v>1095</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>1066</v>
+        <v>1094</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>1065</v>
+        <v>1093</v>
       </c>
       <c r="O49" s="8">
         <v>1000</v>
@@ -33090,7 +34272,7 @@
         <v>51</v>
       </c>
       <c r="Y49" s="3" t="s">
-        <v>1095</v>
+        <v>1123</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>0</v>
@@ -33128,13 +34310,13 @@
     </row>
     <row r="50" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>1094</v>
+        <v>1122</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>1094</v>
+        <v>1122</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D50" s="4">
         <v>46066</v>
@@ -33146,10 +34328,10 @@
         <v>61</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1093</v>
+        <v>1121</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>1092</v>
+        <v>1120</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>163</v>
@@ -33161,13 +34343,13 @@
         <v>632</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>1091</v>
+        <v>1119</v>
       </c>
       <c r="M50" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>1090</v>
+        <v>1118</v>
       </c>
       <c r="O50" s="5">
         <v>507</v>
@@ -33200,7 +34382,7 @@
         <v>51</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>1089</v>
+        <v>1117</v>
       </c>
       <c r="Z50" s="2" t="s">
         <v>0</v>
@@ -33238,13 +34420,13 @@
     </row>
     <row r="51" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>1088</v>
+        <v>1116</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>1088</v>
+        <v>1116</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D51" s="7">
         <v>46071</v>
@@ -33268,16 +34450,16 @@
         <v>164</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>1026</v>
+        <v>1054</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>1087</v>
+        <v>1115</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>1086</v>
+        <v>1114</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>1085</v>
+        <v>1113</v>
       </c>
       <c r="O51" s="8">
         <v>500</v>
@@ -33310,7 +34492,7 @@
         <v>51</v>
       </c>
       <c r="Y51" s="3" t="s">
-        <v>1084</v>
+        <v>1112</v>
       </c>
       <c r="Z51" s="3" t="s">
         <v>0</v>
@@ -33325,10 +34507,10 @@
         <v>111</v>
       </c>
       <c r="AD51" s="3" t="s">
-        <v>1021</v>
+        <v>1049</v>
       </c>
       <c r="AE51" s="3" t="s">
-        <v>1020</v>
+        <v>1048</v>
       </c>
       <c r="AF51" s="3" t="s">
         <v>77</v>
@@ -33348,13 +34530,13 @@
     </row>
     <row r="52" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>1083</v>
+        <v>1111</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1083</v>
+        <v>1111</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D52" s="4">
         <v>46071</v>
@@ -33366,10 +34548,10 @@
         <v>61</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1082</v>
+        <v>1110</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>1081</v>
+        <v>1109</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>139</v>
@@ -33381,13 +34563,13 @@
         <v>446</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>1067</v>
+        <v>1095</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>1066</v>
+        <v>1094</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>1065</v>
+        <v>1093</v>
       </c>
       <c r="O52" s="5">
         <v>200</v>
@@ -33420,7 +34602,7 @@
         <v>51</v>
       </c>
       <c r="Y52" s="2" t="s">
-        <v>1080</v>
+        <v>1108</v>
       </c>
       <c r="Z52" s="2" t="s">
         <v>0</v>
@@ -33458,13 +34640,13 @@
     </row>
     <row r="53" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>1079</v>
+        <v>1107</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>1079</v>
+        <v>1107</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D53" s="7">
         <v>46072</v>
@@ -33476,10 +34658,10 @@
         <v>40</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>1010</v>
+        <v>1038</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>1009</v>
+        <v>1037</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>43</v>
@@ -33491,13 +34673,13 @@
         <v>440</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>1078</v>
+        <v>1106</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>1077</v>
+        <v>1105</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>1076</v>
+        <v>1104</v>
       </c>
       <c r="O53" s="8">
         <v>50</v>
@@ -33521,16 +34703,16 @@
         <v>0</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>1075</v>
+        <v>1103</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>1074</v>
+        <v>1102</v>
       </c>
       <c r="X53" s="3" t="s">
         <v>51</v>
       </c>
       <c r="Y53" s="3" t="s">
-        <v>1073</v>
+        <v>1101</v>
       </c>
       <c r="Z53" s="3" t="s">
         <v>0</v>
@@ -33568,13 +34750,13 @@
     </row>
     <row r="54" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>1072</v>
+        <v>1100</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1072</v>
+        <v>1100</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D54" s="4">
         <v>46072</v>
@@ -33586,10 +34768,10 @@
         <v>61</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1062</v>
+        <v>1090</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>1061</v>
+        <v>1089</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>163</v>
@@ -33601,13 +34783,13 @@
         <v>417</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>1047</v>
+        <v>1075</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>1046</v>
+        <v>1074</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>1045</v>
+        <v>1073</v>
       </c>
       <c r="O54" s="5">
         <v>1600</v>
@@ -33640,7 +34822,7 @@
         <v>51</v>
       </c>
       <c r="Y54" s="2" t="s">
-        <v>1071</v>
+        <v>1099</v>
       </c>
       <c r="Z54" s="2" t="s">
         <v>0</v>
@@ -33678,13 +34860,13 @@
     </row>
     <row r="55" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>1070</v>
+        <v>1098</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>1070</v>
+        <v>1098</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D55" s="7">
         <v>46072</v>
@@ -33696,10 +34878,10 @@
         <v>40</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>1069</v>
+        <v>1097</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>1068</v>
+        <v>1096</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>43</v>
@@ -33711,13 +34893,13 @@
         <v>446</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>1067</v>
+        <v>1095</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>1066</v>
+        <v>1094</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>1065</v>
+        <v>1093</v>
       </c>
       <c r="O55" s="8">
         <v>500</v>
@@ -33750,7 +34932,7 @@
         <v>51</v>
       </c>
       <c r="Y55" s="3" t="s">
-        <v>1064</v>
+        <v>1092</v>
       </c>
       <c r="Z55" s="3" t="s">
         <v>0</v>
@@ -33788,13 +34970,13 @@
     </row>
     <row r="56" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>1063</v>
+        <v>1091</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1063</v>
+        <v>1091</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D56" s="4">
         <v>46076</v>
@@ -33806,10 +34988,10 @@
         <v>61</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1062</v>
+        <v>1090</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>1061</v>
+        <v>1089</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>163</v>
@@ -33821,13 +35003,13 @@
         <v>417</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>1047</v>
+        <v>1075</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>1046</v>
+        <v>1074</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>1045</v>
+        <v>1073</v>
       </c>
       <c r="O56" s="5">
         <v>1700</v>
@@ -33860,7 +35042,7 @@
         <v>51</v>
       </c>
       <c r="Y56" s="2" t="s">
-        <v>1060</v>
+        <v>1088</v>
       </c>
       <c r="Z56" s="2" t="s">
         <v>0</v>
@@ -33898,13 +35080,13 @@
     </row>
     <row r="57" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>1057</v>
+        <v>1085</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>1057</v>
+        <v>1085</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D57" s="7">
         <v>46077</v>
@@ -33928,16 +35110,16 @@
         <v>164</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>1031</v>
+        <v>1059</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>1059</v>
+        <v>1087</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>1058</v>
+        <v>1086</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>1028</v>
+        <v>1056</v>
       </c>
       <c r="O57" s="8">
         <v>500</v>
@@ -33970,7 +35152,7 @@
         <v>51</v>
       </c>
       <c r="Y57" s="3" t="s">
-        <v>1056</v>
+        <v>1084</v>
       </c>
       <c r="Z57" s="3" t="s">
         <v>0</v>
@@ -34008,13 +35190,13 @@
     </row>
     <row r="58" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>1057</v>
+        <v>1085</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1057</v>
+        <v>1085</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D58" s="4">
         <v>46077</v>
@@ -34038,16 +35220,16 @@
         <v>164</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>1026</v>
+        <v>1054</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>1025</v>
+        <v>1053</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>1024</v>
+        <v>1052</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>1023</v>
+        <v>1051</v>
       </c>
       <c r="O58" s="5">
         <v>500</v>
@@ -34080,7 +35262,7 @@
         <v>51</v>
       </c>
       <c r="Y58" s="2" t="s">
-        <v>1056</v>
+        <v>1084</v>
       </c>
       <c r="Z58" s="2" t="s">
         <v>0</v>
@@ -34095,10 +35277,10 @@
         <v>111</v>
       </c>
       <c r="AD58" s="2" t="s">
-        <v>1021</v>
+        <v>1049</v>
       </c>
       <c r="AE58" s="2" t="s">
-        <v>1020</v>
+        <v>1048</v>
       </c>
       <c r="AF58" s="2" t="s">
         <v>77</v>
@@ -34118,13 +35300,13 @@
     </row>
     <row r="59" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>1055</v>
+        <v>1083</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>1055</v>
+        <v>1083</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D59" s="7">
         <v>46078</v>
@@ -34136,10 +35318,10 @@
         <v>40</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>1054</v>
+        <v>1082</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>1053</v>
+        <v>1081</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>139</v>
@@ -34151,13 +35333,13 @@
         <v>784</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>1052</v>
+        <v>1080</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>1051</v>
+        <v>1079</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>1050</v>
+        <v>1078</v>
       </c>
       <c r="O59" s="8">
         <v>225</v>
@@ -34190,7 +35372,7 @@
         <v>51</v>
       </c>
       <c r="Y59" s="3" t="s">
-        <v>1049</v>
+        <v>1077</v>
       </c>
       <c r="Z59" s="3" t="s">
         <v>0</v>
@@ -34228,13 +35410,13 @@
     </row>
     <row r="60" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>1048</v>
+        <v>1076</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1048</v>
+        <v>1076</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D60" s="4">
         <v>46079</v>
@@ -34261,13 +35443,13 @@
         <v>417</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>1047</v>
+        <v>1075</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>1046</v>
+        <v>1074</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>1045</v>
+        <v>1073</v>
       </c>
       <c r="O60" s="5">
         <v>5000</v>
@@ -34291,16 +35473,16 @@
         <v>2354</v>
       </c>
       <c r="V60" s="2" t="s">
-        <v>1044</v>
+        <v>1072</v>
       </c>
       <c r="W60" s="2" t="s">
-        <v>1043</v>
+        <v>1071</v>
       </c>
       <c r="X60" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Y60" s="2" t="s">
-        <v>1042</v>
+        <v>1070</v>
       </c>
       <c r="Z60" s="2" t="s">
         <v>0</v>
@@ -34338,13 +35520,13 @@
     </row>
     <row r="61" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>1041</v>
+        <v>1069</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>1041</v>
+        <v>1069</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D61" s="7">
         <v>46079</v>
@@ -34368,16 +35550,16 @@
         <v>912</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>1040</v>
+        <v>1068</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>1039</v>
+        <v>1067</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>1038</v>
+        <v>1066</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>1037</v>
+        <v>1065</v>
       </c>
       <c r="O61" s="8">
         <v>12000</v>
@@ -34410,7 +35592,7 @@
         <v>51</v>
       </c>
       <c r="Y61" s="3" t="s">
-        <v>1036</v>
+        <v>1064</v>
       </c>
       <c r="Z61" s="3" t="s">
         <v>0</v>
@@ -34448,13 +35630,13 @@
     </row>
     <row r="62" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>1035</v>
+        <v>1063</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1035</v>
+        <v>1063</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D62" s="4">
         <v>46085</v>
@@ -34481,13 +35663,13 @@
         <v>633</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>1034</v>
+        <v>1062</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>652</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>1033</v>
+        <v>1061</v>
       </c>
       <c r="O62" s="5">
         <v>5005</v>
@@ -34520,7 +35702,7 @@
         <v>51</v>
       </c>
       <c r="Y62" s="2" t="s">
-        <v>1032</v>
+        <v>1060</v>
       </c>
       <c r="Z62" s="2" t="s">
         <v>0</v>
@@ -34558,13 +35740,13 @@
     </row>
     <row r="63" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>1027</v>
+        <v>1055</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>1027</v>
+        <v>1055</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D63" s="7">
         <v>46085</v>
@@ -34588,16 +35770,16 @@
         <v>164</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>1031</v>
+        <v>1059</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>1030</v>
+        <v>1058</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>1029</v>
+        <v>1057</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>1028</v>
+        <v>1056</v>
       </c>
       <c r="O63" s="8">
         <v>500</v>
@@ -34630,7 +35812,7 @@
         <v>51</v>
       </c>
       <c r="Y63" s="3" t="s">
-        <v>1022</v>
+        <v>1050</v>
       </c>
       <c r="Z63" s="3" t="s">
         <v>0</v>
@@ -34668,13 +35850,13 @@
     </row>
     <row r="64" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>1027</v>
+        <v>1055</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1027</v>
+        <v>1055</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D64" s="4">
         <v>46085</v>
@@ -34698,16 +35880,16 @@
         <v>164</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>1026</v>
+        <v>1054</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>1025</v>
+        <v>1053</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>1024</v>
+        <v>1052</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>1023</v>
+        <v>1051</v>
       </c>
       <c r="O64" s="5">
         <v>500</v>
@@ -34740,7 +35922,7 @@
         <v>51</v>
       </c>
       <c r="Y64" s="2" t="s">
-        <v>1022</v>
+        <v>1050</v>
       </c>
       <c r="Z64" s="2" t="s">
         <v>0</v>
@@ -34755,10 +35937,10 @@
         <v>111</v>
       </c>
       <c r="AD64" s="2" t="s">
-        <v>1021</v>
+        <v>1049</v>
       </c>
       <c r="AE64" s="2" t="s">
-        <v>1020</v>
+        <v>1048</v>
       </c>
       <c r="AF64" s="2" t="s">
         <v>77</v>
@@ -34778,13 +35960,13 @@
     </row>
     <row r="65" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>1019</v>
+        <v>1047</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>1019</v>
+        <v>1047</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D65" s="7">
         <v>46085</v>
@@ -34796,10 +35978,10 @@
         <v>40</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>1018</v>
+        <v>1046</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>1017</v>
+        <v>1045</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>163</v>
@@ -34811,13 +35993,13 @@
         <v>154</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>1016</v>
+        <v>1044</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>1015</v>
+        <v>1043</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>1014</v>
+        <v>1042</v>
       </c>
       <c r="O65" s="8">
         <v>3700</v>
@@ -34850,7 +36032,7 @@
         <v>51</v>
       </c>
       <c r="Y65" s="3" t="s">
-        <v>1013</v>
+        <v>1041</v>
       </c>
       <c r="Z65" s="3" t="s">
         <v>0</v>
@@ -34888,13 +36070,13 @@
     </row>
     <row r="66" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>1012</v>
+        <v>1040</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1012</v>
+        <v>1040</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="D66" s="4">
         <v>46085</v>
@@ -34906,10 +36088,10 @@
         <v>40</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1010</v>
+        <v>1038</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>1009</v>
+        <v>1037</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>139</v>
@@ -34918,7 +36100,7 @@
         <v>140</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>1008</v>
+        <v>1036</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>0</v>
@@ -34960,7 +36142,7 @@
         <v>0</v>
       </c>
       <c r="Y66" s="2" t="s">
-        <v>1007</v>
+        <v>1035</v>
       </c>
       <c r="Z66" s="2" t="s">
         <v>0</v>
@@ -34975,10 +36157,10 @@
         <v>298</v>
       </c>
       <c r="AD66" s="2" t="s">
-        <v>1006</v>
+        <v>1034</v>
       </c>
       <c r="AE66" s="2" t="s">
-        <v>1005</v>
+        <v>1033</v>
       </c>
       <c r="AF66" s="2" t="s">
         <v>0</v>

--- a/BASE_KEMPARTS.xlsx
+++ b/BASE_KEMPARTS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dash_kp_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{902177DB-F828-4D2A-AAFF-1F8EEF583922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCDF60A6-0241-4C84-A5C9-0B6398B4F075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{034ED65E-4C5C-4047-81C4-E67EF536DEAB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{6FEA2588-5565-4B12-8C5E-E6FBB7E9CDF0}"/>
   </bookViews>
   <sheets>
     <sheet name="FSP" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7147" uniqueCount="1258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7397" uniqueCount="1288">
   <si>
     <t/>
   </si>
@@ -3122,6 +3122,102 @@
     <t>0000406221</t>
   </si>
   <si>
+    <t>000015536</t>
+  </si>
+  <si>
+    <t>173798</t>
+  </si>
+  <si>
+    <t>000015537</t>
+  </si>
+  <si>
+    <t>173800</t>
+  </si>
+  <si>
+    <t>000015538</t>
+  </si>
+  <si>
+    <t>173804</t>
+  </si>
+  <si>
+    <t>000015539</t>
+  </si>
+  <si>
+    <t>C00305</t>
+  </si>
+  <si>
+    <t>RAIOLUX INDUSTRIA E COM DE TINTAS LTDA</t>
+  </si>
+  <si>
+    <t>TRAN.24.004.12.24121017</t>
+  </si>
+  <si>
+    <t>24121017</t>
+  </si>
+  <si>
+    <t>173806</t>
+  </si>
+  <si>
+    <t>000015540</t>
+  </si>
+  <si>
+    <t>C00616</t>
+  </si>
+  <si>
+    <t>AGROPLASTIC COMERCIAL DE PLASTICOS LTDA</t>
+  </si>
+  <si>
+    <t>T00282</t>
+  </si>
+  <si>
+    <t>MEG DE SOUZA COUTINHO TRANSPORTES - EPP</t>
+  </si>
+  <si>
+    <t>173820</t>
+  </si>
+  <si>
+    <t>000015541</t>
+  </si>
+  <si>
+    <t>173824</t>
+  </si>
+  <si>
+    <t>000015542</t>
+  </si>
+  <si>
+    <t>173826</t>
+  </si>
+  <si>
+    <t>000015543</t>
+  </si>
+  <si>
+    <t>173828</t>
+  </si>
+  <si>
+    <t>000015545</t>
+  </si>
+  <si>
+    <t>C00102</t>
+  </si>
+  <si>
+    <t>POLI-COR INDUSTRIA DE TINTAS E VERNIZES</t>
+  </si>
+  <si>
+    <t>HHQ 100 (YL 90)</t>
+  </si>
+  <si>
+    <t>TRAN.25.357.04.250416</t>
+  </si>
+  <si>
+    <t>250416</t>
+  </si>
+  <si>
+    <t>TRAN.25.357.04.</t>
+  </si>
+  <si>
+    <t>153266</t>
+  </si>
+  <si>
     <t>GASTOS GERAIS</t>
   </si>
   <si>
@@ -3227,9 +3323,6 @@
     <t>2025.357.07.251014</t>
   </si>
   <si>
-    <t>HHQ 100 (YL 90)</t>
-  </si>
-  <si>
     <t>000002500</t>
   </si>
   <si>
@@ -3717,9 +3810,6 @@
   </si>
   <si>
     <t>003209</t>
-  </si>
-  <si>
-    <t>24121017</t>
   </si>
   <si>
     <t>2024.004.13.24121017</t>
@@ -4741,8 +4831,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BC32493-C966-4678-BA2F-91D43E76D569}">
-  <dimension ref="A1:AJ219"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{318A57C2-A3D9-48EA-BD6D-8BF7B0CE2ED1}">
+  <dimension ref="A1:AJ229"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -28872,13 +28962,1113 @@
         <v>13.0503</v>
       </c>
     </row>
+    <row r="220" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A220" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D220" s="4">
+        <v>46090</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F220" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G220" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H220" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I220" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="J220" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K220" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L220" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="M220" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="N220" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="O220" s="5">
+        <v>740</v>
+      </c>
+      <c r="P220" s="5">
+        <v>37.32</v>
+      </c>
+      <c r="Q220" s="6">
+        <v>27616.799999999999</v>
+      </c>
+      <c r="R220" s="6">
+        <v>897.55</v>
+      </c>
+      <c r="S220" s="6">
+        <v>28514.35</v>
+      </c>
+      <c r="T220" s="6">
+        <v>27616.799999999999</v>
+      </c>
+      <c r="U220" s="6">
+        <v>4971.0200000000004</v>
+      </c>
+      <c r="V220" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="W220" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="X220" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y220" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="Z220" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA220" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB220" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC220" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD220" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE220" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF220" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG220" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH220" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI220" s="6">
+        <v>18</v>
+      </c>
+      <c r="AJ220" s="5">
+        <v>9825.6164000000008</v>
+      </c>
+    </row>
+    <row r="221" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A221" s="3" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D221" s="7">
+        <v>46090</v>
+      </c>
+      <c r="E221" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G221" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="H221" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="I221" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J221" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K221" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="L221" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="M221" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="N221" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="O221" s="8">
+        <v>2220</v>
+      </c>
+      <c r="P221" s="8">
+        <v>24.6</v>
+      </c>
+      <c r="Q221" s="9">
+        <v>54612</v>
+      </c>
+      <c r="R221" s="9">
+        <v>1774.89</v>
+      </c>
+      <c r="S221" s="9">
+        <v>56386.89</v>
+      </c>
+      <c r="T221" s="9">
+        <v>54612</v>
+      </c>
+      <c r="U221" s="9">
+        <v>2184.48</v>
+      </c>
+      <c r="V221" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="W221" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="X221" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y221" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="Z221" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA221" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB221" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC221" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="AD221" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE221" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF221" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG221" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH221" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI221" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ221" s="8">
+        <v>31058.3328</v>
+      </c>
+    </row>
+    <row r="222" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A222" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D222" s="4">
+        <v>46090</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F222" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G222" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="H222" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="I222" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J222" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K222" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L222" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="M222" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="N222" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="O222" s="5">
+        <v>2000</v>
+      </c>
+      <c r="P222" s="5">
+        <v>11.98</v>
+      </c>
+      <c r="Q222" s="6">
+        <v>23960</v>
+      </c>
+      <c r="R222" s="6">
+        <v>778.7</v>
+      </c>
+      <c r="S222" s="6">
+        <v>24738.7</v>
+      </c>
+      <c r="T222" s="6">
+        <v>23960</v>
+      </c>
+      <c r="U222" s="6">
+        <v>4312.8</v>
+      </c>
+      <c r="V222" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="W222" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="X222" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y222" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="Z222" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA222" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB222" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC222" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD222" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="AE222" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="AF222" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG222" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH222" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI222" s="6">
+        <v>18</v>
+      </c>
+      <c r="AJ222" s="5">
+        <v>17704.900000000001</v>
+      </c>
+    </row>
+    <row r="223" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A223" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D223" s="7">
+        <v>46090</v>
+      </c>
+      <c r="E223" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F223" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G223" s="3" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H223" s="3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="I223" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="J223" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="K223" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="L223" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="M223" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="N223" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="O223" s="8">
+        <v>1000</v>
+      </c>
+      <c r="P223" s="8">
+        <v>17.46</v>
+      </c>
+      <c r="Q223" s="9">
+        <v>17460</v>
+      </c>
+      <c r="R223" s="9">
+        <v>567.45000000000005</v>
+      </c>
+      <c r="S223" s="9">
+        <v>18027.45</v>
+      </c>
+      <c r="T223" s="9">
+        <v>17460</v>
+      </c>
+      <c r="U223" s="9">
+        <v>3142.8</v>
+      </c>
+      <c r="V223" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="W223" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="X223" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y223" s="3" t="s">
+        <v>1044</v>
+      </c>
+      <c r="Z223" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA223" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB223" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC223" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD223" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE223" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF223" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG223" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH223" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI223" s="9">
+        <v>18</v>
+      </c>
+      <c r="AJ223" s="8">
+        <v>9897.6</v>
+      </c>
+    </row>
+    <row r="224" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A224" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D224" s="4">
+        <v>46090</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F224" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G224" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="H224" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="I224" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J224" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K224" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L224" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="M224" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="N224" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="O224" s="5">
+        <v>185</v>
+      </c>
+      <c r="P224" s="5">
+        <v>24.78</v>
+      </c>
+      <c r="Q224" s="6">
+        <v>4584.3</v>
+      </c>
+      <c r="R224" s="6">
+        <v>148.99</v>
+      </c>
+      <c r="S224" s="6">
+        <v>4733.29</v>
+      </c>
+      <c r="T224" s="6">
+        <v>4584.3</v>
+      </c>
+      <c r="U224" s="6">
+        <v>183.37</v>
+      </c>
+      <c r="V224" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="W224" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="X224" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y224" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="Z224" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA224" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB224" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AC224" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="AD224" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE224" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF224" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG224" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH224" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI224" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ224" s="5">
+        <v>2456.4041000000002</v>
+      </c>
+    </row>
+    <row r="225" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A225" s="3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D225" s="7">
+        <v>46090</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G225" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="H225" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="I225" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J225" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K225" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="L225" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M225" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N225" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="O225" s="8">
+        <v>1870</v>
+      </c>
+      <c r="P225" s="8">
+        <v>24.59273</v>
+      </c>
+      <c r="Q225" s="9">
+        <v>45988.41</v>
+      </c>
+      <c r="R225" s="9">
+        <v>1494.62</v>
+      </c>
+      <c r="S225" s="9">
+        <v>47483.03</v>
+      </c>
+      <c r="T225" s="9">
+        <v>45988.41</v>
+      </c>
+      <c r="U225" s="9">
+        <v>8277.91</v>
+      </c>
+      <c r="V225" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="W225" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="X225" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y225" s="3" t="s">
+        <v>1052</v>
+      </c>
+      <c r="Z225" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA225" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB225" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC225" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD225" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE225" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF225" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG225" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH225" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI225" s="9">
+        <v>18</v>
+      </c>
+      <c r="AJ225" s="8">
+        <v>21765.603200000001</v>
+      </c>
+    </row>
+    <row r="226" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A226" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D226" s="4">
+        <v>46090</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F226" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G226" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="H226" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="I226" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="J226" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="K226" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="L226" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="M226" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="N226" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O226" s="5">
+        <v>370</v>
+      </c>
+      <c r="P226" s="5">
+        <v>21.5</v>
+      </c>
+      <c r="Q226" s="6">
+        <v>7955</v>
+      </c>
+      <c r="R226" s="6">
+        <v>258.54000000000002</v>
+      </c>
+      <c r="S226" s="6">
+        <v>8213.5400000000009</v>
+      </c>
+      <c r="T226" s="6">
+        <v>7955</v>
+      </c>
+      <c r="U226" s="6">
+        <v>318.2</v>
+      </c>
+      <c r="V226" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="W226" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="X226" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y226" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="Z226" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA226" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB226" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AC226" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="AD226" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE226" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF226" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG226" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH226" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI226" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ226" s="5">
+        <v>5176.3887999999997</v>
+      </c>
+    </row>
+    <row r="227" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A227" s="3" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D227" s="7">
+        <v>46090</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G227" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="H227" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="I227" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J227" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K227" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="L227" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M227" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N227" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="O227" s="8">
+        <v>170</v>
+      </c>
+      <c r="P227" s="8">
+        <v>26.89</v>
+      </c>
+      <c r="Q227" s="9">
+        <v>4571.3</v>
+      </c>
+      <c r="R227" s="9">
+        <v>148.57</v>
+      </c>
+      <c r="S227" s="9">
+        <v>4719.87</v>
+      </c>
+      <c r="T227" s="9">
+        <v>4571.3</v>
+      </c>
+      <c r="U227" s="9">
+        <v>822.83</v>
+      </c>
+      <c r="V227" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="W227" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="X227" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y227" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="Z227" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA227" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB227" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC227" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD227" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE227" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF227" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG227" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH227" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI227" s="9">
+        <v>18</v>
+      </c>
+      <c r="AJ227" s="8">
+        <v>1978.6912</v>
+      </c>
+    </row>
+    <row r="228" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A228" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D228" s="4">
+        <v>46090</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F228" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G228" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="H228" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="I228" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J228" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K228" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="L228" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="M228" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="N228" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="O228" s="5">
+        <v>1</v>
+      </c>
+      <c r="P228" s="5">
+        <v>10</v>
+      </c>
+      <c r="Q228" s="6">
+        <v>10</v>
+      </c>
+      <c r="R228" s="6">
+        <v>0</v>
+      </c>
+      <c r="S228" s="6">
+        <v>10</v>
+      </c>
+      <c r="T228" s="6">
+        <v>0</v>
+      </c>
+      <c r="U228" s="6">
+        <v>0</v>
+      </c>
+      <c r="V228" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="W228" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="X228" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y228" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="Z228" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA228" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB228" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC228" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD228" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE228" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF228" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="AG228" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH228" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI228" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ228" s="5">
+        <v>9.1311099999999996</v>
+      </c>
+    </row>
+    <row r="229" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A229" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D229" s="7">
+        <v>46090</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G229" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="H229" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="I229" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J229" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="K229" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="L229" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="M229" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="N229" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="O229" s="8">
+        <v>1</v>
+      </c>
+      <c r="P229" s="8">
+        <v>10</v>
+      </c>
+      <c r="Q229" s="9">
+        <v>10</v>
+      </c>
+      <c r="R229" s="9">
+        <v>0</v>
+      </c>
+      <c r="S229" s="9">
+        <v>10</v>
+      </c>
+      <c r="T229" s="9">
+        <v>0</v>
+      </c>
+      <c r="U229" s="9">
+        <v>0</v>
+      </c>
+      <c r="V229" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="W229" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="X229" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y229" s="3" t="s">
+        <v>1064</v>
+      </c>
+      <c r="Z229" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA229" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB229" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC229" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD229" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE229" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF229" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AG229" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH229" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI229" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ229" s="8">
+        <v>9.8148</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A0FB20-CDDD-4477-B867-5F1CAAB1D4C5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11535412-83B7-4F7D-A32C-87312564DCEE}">
   <dimension ref="A1:AJ66"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -29030,13 +30220,13 @@
     </row>
     <row r="2" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>1257</v>
+        <v>1287</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1257</v>
+        <v>1287</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D2" s="4">
         <v>46024</v>
@@ -29048,10 +30238,10 @@
         <v>40</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1038</v>
+        <v>1070</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>1037</v>
+        <v>1069</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>43</v>
@@ -29063,13 +30253,13 @@
         <v>440</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>1106</v>
+        <v>1137</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>1105</v>
+        <v>1136</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>1104</v>
+        <v>1135</v>
       </c>
       <c r="O2" s="5">
         <v>50</v>
@@ -29093,16 +30283,16 @@
         <v>39.06</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>1103</v>
+        <v>1134</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>1102</v>
+        <v>1133</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>1256</v>
+        <v>1286</v>
       </c>
       <c r="Z2" s="2" t="s">
         <v>0</v>
@@ -29140,13 +30330,13 @@
     </row>
     <row r="3" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>1255</v>
+        <v>1285</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1255</v>
+        <v>1285</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D3" s="7">
         <v>46027</v>
@@ -29158,10 +30348,10 @@
         <v>61</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1121</v>
+        <v>1152</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1120</v>
+        <v>1151</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>163</v>
@@ -29173,13 +30363,13 @@
         <v>632</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1119</v>
+        <v>1150</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>648</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>1118</v>
+        <v>1149</v>
       </c>
       <c r="O3" s="8">
         <v>1001</v>
@@ -29212,7 +30402,7 @@
         <v>51</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>1254</v>
+        <v>1284</v>
       </c>
       <c r="Z3" s="3" t="s">
         <v>0</v>
@@ -29250,13 +30440,13 @@
     </row>
     <row r="4" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>1253</v>
+        <v>1283</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1253</v>
+        <v>1283</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D4" s="4">
         <v>46027</v>
@@ -29268,10 +30458,10 @@
         <v>61</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1252</v>
+        <v>1282</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1251</v>
+        <v>1281</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>152</v>
@@ -29283,13 +30473,13 @@
         <v>342</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1250</v>
+        <v>1280</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1249</v>
+        <v>1279</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1248</v>
+        <v>1278</v>
       </c>
       <c r="O4" s="5">
         <v>600</v>
@@ -29313,16 +30503,16 @@
         <v>355.68</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>1247</v>
+        <v>1277</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>1246</v>
+        <v>1276</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>1245</v>
+        <v>1275</v>
       </c>
       <c r="Z4" s="2" t="s">
         <v>0</v>
@@ -29360,13 +30550,13 @@
     </row>
     <row r="5" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>1244</v>
+        <v>1274</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1244</v>
+        <v>1274</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D5" s="7">
         <v>46029</v>
@@ -29378,10 +30568,10 @@
         <v>212</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>1162</v>
+        <v>1193</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1161</v>
+        <v>1192</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>139</v>
@@ -29390,7 +30580,7 @@
         <v>140</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>1243</v>
+        <v>1273</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>0</v>
@@ -29432,7 +30622,7 @@
         <v>87</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>1242</v>
+        <v>1272</v>
       </c>
       <c r="Z5" s="3" t="s">
         <v>0</v>
@@ -29470,13 +30660,13 @@
     </row>
     <row r="6" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>1244</v>
+        <v>1274</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1244</v>
+        <v>1274</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D6" s="4">
         <v>46029</v>
@@ -29488,10 +30678,10 @@
         <v>212</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1162</v>
+        <v>1193</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1161</v>
+        <v>1192</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>139</v>
@@ -29500,7 +30690,7 @@
         <v>140</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>1243</v>
+        <v>1273</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>0</v>
@@ -29542,7 +30732,7 @@
         <v>87</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>1242</v>
+        <v>1272</v>
       </c>
       <c r="Z6" s="2" t="s">
         <v>0</v>
@@ -29580,13 +30770,13 @@
     </row>
     <row r="7" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>1241</v>
+        <v>1271</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1241</v>
+        <v>1271</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D7" s="7">
         <v>46029</v>
@@ -29604,22 +30794,22 @@
         <v>386</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>1125</v>
+        <v>1156</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>1124</v>
+        <v>1155</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>1068</v>
+        <v>1060</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>1240</v>
+        <v>1270</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>1239</v>
+        <v>1269</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>1238</v>
+        <v>1268</v>
       </c>
       <c r="O7" s="8">
         <v>1000</v>
@@ -29652,7 +30842,7 @@
         <v>51</v>
       </c>
       <c r="Y7" s="3" t="s">
-        <v>1237</v>
+        <v>1267</v>
       </c>
       <c r="Z7" s="3" t="s">
         <v>0</v>
@@ -29690,13 +30880,13 @@
     </row>
     <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>1236</v>
+        <v>1266</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1236</v>
+        <v>1266</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D8" s="4">
         <v>46036</v>
@@ -29708,10 +30898,10 @@
         <v>61</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1121</v>
+        <v>1152</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>1120</v>
+        <v>1151</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>163</v>
@@ -29723,13 +30913,13 @@
         <v>632</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>1119</v>
+        <v>1150</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1118</v>
+        <v>1149</v>
       </c>
       <c r="O8" s="5">
         <v>1001</v>
@@ -29762,7 +30952,7 @@
         <v>51</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>1235</v>
+        <v>1265</v>
       </c>
       <c r="Z8" s="2" t="s">
         <v>0</v>
@@ -29800,13 +30990,13 @@
     </row>
     <row r="9" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>1234</v>
+        <v>1264</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1234</v>
+        <v>1264</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D9" s="7">
         <v>46037</v>
@@ -29818,10 +31008,10 @@
         <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>1134</v>
+        <v>1165</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1133</v>
+        <v>1164</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>163</v>
@@ -29833,13 +31023,13 @@
         <v>417</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>1233</v>
+        <v>1263</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>1232</v>
+        <v>1043</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>1130</v>
+        <v>1161</v>
       </c>
       <c r="O9" s="8">
         <v>1000</v>
@@ -29872,7 +31062,7 @@
         <v>51</v>
       </c>
       <c r="Y9" s="3" t="s">
-        <v>1231</v>
+        <v>1262</v>
       </c>
       <c r="Z9" s="3" t="s">
         <v>0</v>
@@ -29910,13 +31100,13 @@
     </row>
     <row r="10" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>1230</v>
+        <v>1261</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1230</v>
+        <v>1261</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D10" s="4">
         <v>46037</v>
@@ -29928,10 +31118,10 @@
         <v>40</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1082</v>
+        <v>1113</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1081</v>
+        <v>1112</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>139</v>
@@ -29943,13 +31133,13 @@
         <v>784</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>1080</v>
+        <v>1111</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1079</v>
+        <v>1110</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1078</v>
+        <v>1109</v>
       </c>
       <c r="O10" s="5">
         <v>300</v>
@@ -29982,7 +31172,7 @@
         <v>51</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>1229</v>
+        <v>1260</v>
       </c>
       <c r="Z10" s="2" t="s">
         <v>0</v>
@@ -30020,13 +31210,13 @@
     </row>
     <row r="11" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>1228</v>
+        <v>1259</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1228</v>
+        <v>1259</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D11" s="7">
         <v>46037</v>
@@ -30038,10 +31228,10 @@
         <v>40</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>1172</v>
+        <v>1203</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1171</v>
+        <v>1202</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>43</v>
@@ -30053,13 +31243,13 @@
         <v>300</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>1227</v>
+        <v>1258</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>1226</v>
+        <v>1257</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>1225</v>
+        <v>1256</v>
       </c>
       <c r="O11" s="8">
         <v>25</v>
@@ -30092,7 +31282,7 @@
         <v>51</v>
       </c>
       <c r="Y11" s="3" t="s">
-        <v>1224</v>
+        <v>1255</v>
       </c>
       <c r="Z11" s="3" t="s">
         <v>0</v>
@@ -30130,13 +31320,13 @@
     </row>
     <row r="12" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>1223</v>
+        <v>1254</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1223</v>
+        <v>1254</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D12" s="4">
         <v>46041</v>
@@ -30148,10 +31338,10 @@
         <v>212</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1162</v>
+        <v>1193</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1161</v>
+        <v>1192</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>139</v>
@@ -30160,7 +31350,7 @@
         <v>140</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>1054</v>
+        <v>1086</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>0</v>
@@ -30202,7 +31392,7 @@
         <v>87</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>1222</v>
+        <v>1253</v>
       </c>
       <c r="Z12" s="2" t="s">
         <v>0</v>
@@ -30217,10 +31407,10 @@
         <v>55</v>
       </c>
       <c r="AD12" s="2" t="s">
-        <v>1049</v>
+        <v>1081</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>1048</v>
+        <v>1080</v>
       </c>
       <c r="AF12" s="2" t="s">
         <v>442</v>
@@ -30240,13 +31430,13 @@
     </row>
     <row r="13" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>1221</v>
+        <v>1252</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1221</v>
+        <v>1252</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D13" s="7">
         <v>46042</v>
@@ -30264,22 +31454,22 @@
         <v>386</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>1125</v>
+        <v>1156</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>1124</v>
+        <v>1155</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>446</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>1128</v>
+        <v>1159</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>1127</v>
+        <v>1158</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>1093</v>
+        <v>1124</v>
       </c>
       <c r="O13" s="8">
         <v>2000</v>
@@ -30312,7 +31502,7 @@
         <v>51</v>
       </c>
       <c r="Y13" s="3" t="s">
-        <v>1220</v>
+        <v>1251</v>
       </c>
       <c r="Z13" s="3" t="s">
         <v>0</v>
@@ -30350,13 +31540,13 @@
     </row>
     <row r="14" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>1219</v>
+        <v>1250</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1219</v>
+        <v>1250</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D14" s="4">
         <v>46042</v>
@@ -30380,16 +31570,16 @@
         <v>294</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>1054</v>
+        <v>1086</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>1187</v>
+        <v>1218</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1186</v>
+        <v>1217</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1051</v>
+        <v>1083</v>
       </c>
       <c r="O14" s="5">
         <v>6000</v>
@@ -30413,16 +31603,16 @@
         <v>12873.6</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>1218</v>
+        <v>1249</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>1217</v>
+        <v>1248</v>
       </c>
       <c r="X14" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>1216</v>
+        <v>1247</v>
       </c>
       <c r="Z14" s="2" t="s">
         <v>0</v>
@@ -30437,10 +31627,10 @@
         <v>298</v>
       </c>
       <c r="AD14" s="2" t="s">
-        <v>1049</v>
+        <v>1081</v>
       </c>
       <c r="AE14" s="2" t="s">
-        <v>1048</v>
+        <v>1080</v>
       </c>
       <c r="AF14" s="2" t="s">
         <v>77</v>
@@ -30460,13 +31650,13 @@
     </row>
     <row r="15" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>1215</v>
+        <v>1246</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1215</v>
+        <v>1246</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D15" s="7">
         <v>46042</v>
@@ -30478,10 +31668,10 @@
         <v>212</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>1162</v>
+        <v>1193</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>1161</v>
+        <v>1192</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>139</v>
@@ -30532,7 +31722,7 @@
         <v>87</v>
       </c>
       <c r="Y15" s="3" t="s">
-        <v>1214</v>
+        <v>1245</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>0</v>
@@ -30553,7 +31743,7 @@
         <v>518</v>
       </c>
       <c r="AF15" s="3" t="s">
-        <v>1182</v>
+        <v>1213</v>
       </c>
       <c r="AG15" s="9">
         <v>0</v>
@@ -30570,13 +31760,13 @@
     </row>
     <row r="16" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>1215</v>
+        <v>1246</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1215</v>
+        <v>1246</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D16" s="4">
         <v>46042</v>
@@ -30588,10 +31778,10 @@
         <v>212</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1162</v>
+        <v>1193</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1161</v>
+        <v>1192</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>139</v>
@@ -30642,7 +31832,7 @@
         <v>87</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>1214</v>
+        <v>1245</v>
       </c>
       <c r="Z16" s="2" t="s">
         <v>0</v>
@@ -30663,7 +31853,7 @@
         <v>518</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>1182</v>
+        <v>1213</v>
       </c>
       <c r="AG16" s="6">
         <v>0</v>
@@ -30680,13 +31870,13 @@
     </row>
     <row r="17" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>1213</v>
+        <v>1244</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1213</v>
+        <v>1244</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D17" s="7">
         <v>46043</v>
@@ -30713,13 +31903,13 @@
         <v>417</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>1132</v>
+        <v>1163</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>1131</v>
+        <v>1162</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>1130</v>
+        <v>1161</v>
       </c>
       <c r="O17" s="8">
         <v>1000</v>
@@ -30752,7 +31942,7 @@
         <v>51</v>
       </c>
       <c r="Y17" s="3" t="s">
-        <v>1212</v>
+        <v>1243</v>
       </c>
       <c r="Z17" s="3" t="s">
         <v>0</v>
@@ -30790,28 +31980,28 @@
     </row>
     <row r="18" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>1200</v>
+        <v>1231</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1200</v>
+        <v>1231</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D18" s="4">
         <v>46045</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1199</v>
+        <v>1230</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1198</v>
+        <v>1229</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1138</v>
+        <v>1169</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>1137</v>
+        <v>1168</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>139</v>
@@ -30823,13 +32013,13 @@
         <v>628</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>1211</v>
+        <v>1242</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1210</v>
+        <v>1241</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1209</v>
+        <v>1240</v>
       </c>
       <c r="O18" s="5">
         <v>2000</v>
@@ -30853,16 +32043,16 @@
         <v>0</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>1194</v>
+        <v>1225</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>1161</v>
+        <v>1192</v>
       </c>
       <c r="X18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>1193</v>
+        <v>1224</v>
       </c>
       <c r="Z18" s="2" t="s">
         <v>0</v>
@@ -30900,28 +32090,28 @@
     </row>
     <row r="19" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>1200</v>
+        <v>1231</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>1200</v>
+        <v>1231</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D19" s="7">
         <v>46045</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>1199</v>
+        <v>1230</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>1198</v>
+        <v>1229</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>1138</v>
+        <v>1169</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>1137</v>
+        <v>1168</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>139</v>
@@ -30933,13 +32123,13 @@
         <v>631</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>1208</v>
+        <v>1239</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>1207</v>
+        <v>1238</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>1195</v>
+        <v>1226</v>
       </c>
       <c r="O19" s="8">
         <v>11725</v>
@@ -30963,16 +32153,16 @@
         <v>0</v>
       </c>
       <c r="V19" s="3" t="s">
-        <v>1194</v>
+        <v>1225</v>
       </c>
       <c r="W19" s="3" t="s">
-        <v>1161</v>
+        <v>1192</v>
       </c>
       <c r="X19" s="3" t="s">
         <v>87</v>
       </c>
       <c r="Y19" s="3" t="s">
-        <v>1193</v>
+        <v>1224</v>
       </c>
       <c r="Z19" s="3" t="s">
         <v>0</v>
@@ -31010,28 +32200,28 @@
     </row>
     <row r="20" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>1200</v>
+        <v>1231</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1200</v>
+        <v>1231</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D20" s="4">
         <v>46045</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1199</v>
+        <v>1230</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1198</v>
+        <v>1229</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1138</v>
+        <v>1169</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1137</v>
+        <v>1168</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>139</v>
@@ -31043,13 +32233,13 @@
         <v>632</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>1119</v>
+        <v>1150</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1118</v>
+        <v>1149</v>
       </c>
       <c r="O20" s="5">
         <v>2925</v>
@@ -31073,16 +32263,16 @@
         <v>0</v>
       </c>
       <c r="V20" s="2" t="s">
-        <v>1194</v>
+        <v>1225</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>1161</v>
+        <v>1192</v>
       </c>
       <c r="X20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>1193</v>
+        <v>1224</v>
       </c>
       <c r="Z20" s="2" t="s">
         <v>0</v>
@@ -31120,28 +32310,28 @@
     </row>
     <row r="21" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>1200</v>
+        <v>1231</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>1200</v>
+        <v>1231</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D21" s="7">
         <v>46045</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>1199</v>
+        <v>1230</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>1198</v>
+        <v>1229</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>1138</v>
+        <v>1169</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>1137</v>
+        <v>1168</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>139</v>
@@ -31153,13 +32343,13 @@
         <v>633</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>1062</v>
+        <v>1094</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>652</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>1061</v>
+        <v>1093</v>
       </c>
       <c r="O21" s="8">
         <v>2925</v>
@@ -31183,16 +32373,16 @@
         <v>0</v>
       </c>
       <c r="V21" s="3" t="s">
-        <v>1194</v>
+        <v>1225</v>
       </c>
       <c r="W21" s="3" t="s">
-        <v>1161</v>
+        <v>1192</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>87</v>
       </c>
       <c r="Y21" s="3" t="s">
-        <v>1193</v>
+        <v>1224</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>0</v>
@@ -31230,28 +32420,28 @@
     </row>
     <row r="22" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>1200</v>
+        <v>1231</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1200</v>
+        <v>1231</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D22" s="4">
         <v>46045</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1199</v>
+        <v>1230</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1198</v>
+        <v>1229</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1138</v>
+        <v>1169</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1137</v>
+        <v>1168</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>139</v>
@@ -31263,13 +32453,13 @@
         <v>465</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1206</v>
+        <v>1237</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1205</v>
+        <v>1236</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1204</v>
+        <v>1235</v>
       </c>
       <c r="O22" s="5">
         <v>2400</v>
@@ -31293,16 +32483,16 @@
         <v>0</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>1194</v>
+        <v>1225</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>1161</v>
+        <v>1192</v>
       </c>
       <c r="X22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>1193</v>
+        <v>1224</v>
       </c>
       <c r="Z22" s="2" t="s">
         <v>0</v>
@@ -31340,28 +32530,28 @@
     </row>
     <row r="23" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>1200</v>
+        <v>1231</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>1200</v>
+        <v>1231</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D23" s="7">
         <v>46045</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>1199</v>
+        <v>1230</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>1198</v>
+        <v>1229</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>1138</v>
+        <v>1169</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>1137</v>
+        <v>1168</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>139</v>
@@ -31373,13 +32563,13 @@
         <v>465</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>1203</v>
+        <v>1234</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>1202</v>
+        <v>1233</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>1201</v>
+        <v>1232</v>
       </c>
       <c r="O23" s="8">
         <v>1800</v>
@@ -31403,16 +32593,16 @@
         <v>0</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>1194</v>
+        <v>1225</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>1161</v>
+        <v>1192</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>87</v>
       </c>
       <c r="Y23" s="3" t="s">
-        <v>1193</v>
+        <v>1224</v>
       </c>
       <c r="Z23" s="3" t="s">
         <v>0</v>
@@ -31450,28 +32640,28 @@
     </row>
     <row r="24" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>1200</v>
+        <v>1231</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1200</v>
+        <v>1231</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D24" s="4">
         <v>46045</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1199</v>
+        <v>1230</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1198</v>
+        <v>1229</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1138</v>
+        <v>1169</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1137</v>
+        <v>1168</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>139</v>
@@ -31483,13 +32673,13 @@
         <v>634</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>1197</v>
+        <v>1228</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1196</v>
+        <v>1227</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1195</v>
+        <v>1226</v>
       </c>
       <c r="O24" s="5">
         <v>1400</v>
@@ -31513,16 +32703,16 @@
         <v>0</v>
       </c>
       <c r="V24" s="2" t="s">
-        <v>1194</v>
+        <v>1225</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>1161</v>
+        <v>1192</v>
       </c>
       <c r="X24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>1193</v>
+        <v>1224</v>
       </c>
       <c r="Z24" s="2" t="s">
         <v>0</v>
@@ -31560,13 +32750,13 @@
     </row>
     <row r="25" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>1192</v>
+        <v>1223</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>1192</v>
+        <v>1223</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D25" s="7">
         <v>46048</v>
@@ -31593,13 +32783,13 @@
         <v>417</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>1144</v>
+        <v>1175</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>1143</v>
+        <v>1174</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>1142</v>
+        <v>1173</v>
       </c>
       <c r="O25" s="8">
         <v>5000</v>
@@ -31623,16 +32813,16 @@
         <v>2354</v>
       </c>
       <c r="V25" s="3" t="s">
-        <v>1072</v>
+        <v>1103</v>
       </c>
       <c r="W25" s="3" t="s">
-        <v>1071</v>
+        <v>1102</v>
       </c>
       <c r="X25" s="3" t="s">
         <v>51</v>
       </c>
       <c r="Y25" s="3" t="s">
-        <v>1191</v>
+        <v>1222</v>
       </c>
       <c r="Z25" s="3" t="s">
         <v>0</v>
@@ -31670,13 +32860,13 @@
     </row>
     <row r="26" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>1190</v>
+        <v>1221</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1190</v>
+        <v>1221</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D26" s="4">
         <v>46048</v>
@@ -31688,10 +32878,10 @@
         <v>40</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1082</v>
+        <v>1113</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1081</v>
+        <v>1112</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>139</v>
@@ -31703,13 +32893,13 @@
         <v>784</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>1080</v>
+        <v>1111</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1079</v>
+        <v>1110</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1078</v>
+        <v>1109</v>
       </c>
       <c r="O26" s="5">
         <v>300</v>
@@ -31742,7 +32932,7 @@
         <v>51</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>1189</v>
+        <v>1220</v>
       </c>
       <c r="Z26" s="2" t="s">
         <v>0</v>
@@ -31780,13 +32970,13 @@
     </row>
     <row r="27" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>1188</v>
+        <v>1219</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>1188</v>
+        <v>1219</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D27" s="7">
         <v>46048</v>
@@ -31798,10 +32988,10 @@
         <v>61</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>1121</v>
+        <v>1152</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>1120</v>
+        <v>1151</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>163</v>
@@ -31813,13 +33003,13 @@
         <v>632</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>1119</v>
+        <v>1150</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>648</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>1118</v>
+        <v>1149</v>
       </c>
       <c r="O27" s="8">
         <v>611</v>
@@ -31852,7 +33042,7 @@
         <v>51</v>
       </c>
       <c r="Y27" s="3" t="s">
-        <v>1185</v>
+        <v>1216</v>
       </c>
       <c r="Z27" s="3" t="s">
         <v>0</v>
@@ -31890,13 +33080,13 @@
     </row>
     <row r="28" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>1188</v>
+        <v>1219</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1188</v>
+        <v>1219</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D28" s="4">
         <v>46048</v>
@@ -31908,10 +33098,10 @@
         <v>61</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1121</v>
+        <v>1152</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1120</v>
+        <v>1151</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>163</v>
@@ -31920,16 +33110,16 @@
         <v>164</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>1054</v>
+        <v>1086</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>1187</v>
+        <v>1218</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1186</v>
+        <v>1217</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1051</v>
+        <v>1083</v>
       </c>
       <c r="O28" s="5">
         <v>700</v>
@@ -31962,7 +33152,7 @@
         <v>51</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>1185</v>
+        <v>1216</v>
       </c>
       <c r="Z28" s="2" t="s">
         <v>0</v>
@@ -31977,10 +33167,10 @@
         <v>55</v>
       </c>
       <c r="AD28" s="2" t="s">
-        <v>1049</v>
+        <v>1081</v>
       </c>
       <c r="AE28" s="2" t="s">
-        <v>1048</v>
+        <v>1080</v>
       </c>
       <c r="AF28" s="2" t="s">
         <v>77</v>
@@ -32000,13 +33190,13 @@
     </row>
     <row r="29" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>1184</v>
+        <v>1215</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>1184</v>
+        <v>1215</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D29" s="7">
         <v>46048</v>
@@ -32018,10 +33208,10 @@
         <v>212</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>1162</v>
+        <v>1193</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>1161</v>
+        <v>1192</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>139</v>
@@ -32072,7 +33262,7 @@
         <v>87</v>
       </c>
       <c r="Y29" s="3" t="s">
-        <v>1183</v>
+        <v>1214</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>0</v>
@@ -32093,7 +33283,7 @@
         <v>57</v>
       </c>
       <c r="AF29" s="3" t="s">
-        <v>1182</v>
+        <v>1213</v>
       </c>
       <c r="AG29" s="9">
         <v>0</v>
@@ -32110,13 +33300,13 @@
     </row>
     <row r="30" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>1181</v>
+        <v>1212</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1181</v>
+        <v>1212</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D30" s="4">
         <v>46049</v>
@@ -32128,10 +33318,10 @@
         <v>212</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1162</v>
+        <v>1193</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1161</v>
+        <v>1192</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>139</v>
@@ -32182,7 +33372,7 @@
         <v>87</v>
       </c>
       <c r="Y30" s="2" t="s">
-        <v>1180</v>
+        <v>1211</v>
       </c>
       <c r="Z30" s="2" t="s">
         <v>0</v>
@@ -32220,13 +33410,13 @@
     </row>
     <row r="31" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>1181</v>
+        <v>1212</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>1181</v>
+        <v>1212</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D31" s="7">
         <v>46049</v>
@@ -32238,10 +33428,10 @@
         <v>212</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>1162</v>
+        <v>1193</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>1161</v>
+        <v>1192</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>139</v>
@@ -32292,7 +33482,7 @@
         <v>87</v>
       </c>
       <c r="Y31" s="3" t="s">
-        <v>1180</v>
+        <v>1211</v>
       </c>
       <c r="Z31" s="3" t="s">
         <v>0</v>
@@ -32330,13 +33520,13 @@
     </row>
     <row r="32" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>1177</v>
+        <v>1208</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1177</v>
+        <v>1208</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D32" s="4">
         <v>46050</v>
@@ -32354,22 +33544,22 @@
         <v>386</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>1125</v>
+        <v>1156</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>1124</v>
+        <v>1155</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>446</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>1179</v>
+        <v>1210</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>448</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1178</v>
+        <v>1209</v>
       </c>
       <c r="O32" s="5">
         <v>1000</v>
@@ -32402,7 +33592,7 @@
         <v>51</v>
       </c>
       <c r="Y32" s="2" t="s">
-        <v>1176</v>
+        <v>1207</v>
       </c>
       <c r="Z32" s="2" t="s">
         <v>0</v>
@@ -32440,13 +33630,13 @@
     </row>
     <row r="33" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>1177</v>
+        <v>1208</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>1177</v>
+        <v>1208</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D33" s="7">
         <v>46050</v>
@@ -32464,22 +33654,22 @@
         <v>386</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>1125</v>
+        <v>1156</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>1124</v>
+        <v>1155</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>446</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>1128</v>
+        <v>1159</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>1127</v>
+        <v>1158</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>1093</v>
+        <v>1124</v>
       </c>
       <c r="O33" s="8">
         <v>1000</v>
@@ -32512,7 +33702,7 @@
         <v>51</v>
       </c>
       <c r="Y33" s="3" t="s">
-        <v>1176</v>
+        <v>1207</v>
       </c>
       <c r="Z33" s="3" t="s">
         <v>0</v>
@@ -32550,13 +33740,13 @@
     </row>
     <row r="34" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>1175</v>
+        <v>1206</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1175</v>
+        <v>1206</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D34" s="4">
         <v>46050</v>
@@ -32568,10 +33758,10 @@
         <v>212</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1162</v>
+        <v>1193</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>1161</v>
+        <v>1192</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>139</v>
@@ -32622,7 +33812,7 @@
         <v>87</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>1174</v>
+        <v>1205</v>
       </c>
       <c r="Z34" s="2" t="s">
         <v>0</v>
@@ -32660,13 +33850,13 @@
     </row>
     <row r="35" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>1173</v>
+        <v>1204</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>1173</v>
+        <v>1204</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D35" s="7">
         <v>46051</v>
@@ -32678,10 +33868,10 @@
         <v>40</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>1172</v>
+        <v>1203</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>1171</v>
+        <v>1202</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>43</v>
@@ -32693,13 +33883,13 @@
         <v>632</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>1119</v>
+        <v>1150</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>648</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>1118</v>
+        <v>1149</v>
       </c>
       <c r="O35" s="8">
         <v>26</v>
@@ -32732,7 +33922,7 @@
         <v>51</v>
       </c>
       <c r="Y35" s="3" t="s">
-        <v>1170</v>
+        <v>1201</v>
       </c>
       <c r="Z35" s="3" t="s">
         <v>0</v>
@@ -32770,13 +33960,13 @@
     </row>
     <row r="36" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>1169</v>
+        <v>1200</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>1169</v>
+        <v>1200</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D36" s="4">
         <v>46052</v>
@@ -32788,10 +33978,10 @@
         <v>61</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1121</v>
+        <v>1152</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>1120</v>
+        <v>1151</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>163</v>
@@ -32803,13 +33993,13 @@
         <v>632</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>1119</v>
+        <v>1150</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1118</v>
+        <v>1149</v>
       </c>
       <c r="O36" s="5">
         <v>507</v>
@@ -32842,7 +34032,7 @@
         <v>51</v>
       </c>
       <c r="Y36" s="2" t="s">
-        <v>1168</v>
+        <v>1199</v>
       </c>
       <c r="Z36" s="2" t="s">
         <v>0</v>
@@ -32880,13 +34070,13 @@
     </row>
     <row r="37" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>1167</v>
+        <v>1198</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>1167</v>
+        <v>1198</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D37" s="7">
         <v>46052</v>
@@ -32910,16 +34100,16 @@
         <v>164</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>1059</v>
+        <v>1091</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>1087</v>
+        <v>1118</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>1086</v>
+        <v>1117</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>1056</v>
+        <v>1088</v>
       </c>
       <c r="O37" s="8">
         <v>500</v>
@@ -32952,7 +34142,7 @@
         <v>51</v>
       </c>
       <c r="Y37" s="3" t="s">
-        <v>1166</v>
+        <v>1197</v>
       </c>
       <c r="Z37" s="3" t="s">
         <v>0</v>
@@ -32990,13 +34180,13 @@
     </row>
     <row r="38" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>1165</v>
+        <v>1196</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1165</v>
+        <v>1196</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D38" s="4">
         <v>46052</v>
@@ -33008,10 +34198,10 @@
         <v>40</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>1082</v>
+        <v>1113</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>1081</v>
+        <v>1112</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>139</v>
@@ -33023,13 +34213,13 @@
         <v>784</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>1080</v>
+        <v>1111</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>1079</v>
+        <v>1110</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>1078</v>
+        <v>1109</v>
       </c>
       <c r="O38" s="5">
         <v>300</v>
@@ -33062,7 +34252,7 @@
         <v>51</v>
       </c>
       <c r="Y38" s="2" t="s">
-        <v>1164</v>
+        <v>1195</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>0</v>
@@ -33100,13 +34290,13 @@
     </row>
     <row r="39" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>1163</v>
+        <v>1194</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>1163</v>
+        <v>1194</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D39" s="7">
         <v>46055</v>
@@ -33118,10 +34308,10 @@
         <v>212</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>1162</v>
+        <v>1193</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>1161</v>
+        <v>1192</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>139</v>
@@ -33130,7 +34320,7 @@
         <v>140</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>1160</v>
+        <v>1191</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>0</v>
@@ -33172,7 +34362,7 @@
         <v>87</v>
       </c>
       <c r="Y39" s="3" t="s">
-        <v>1159</v>
+        <v>1190</v>
       </c>
       <c r="Z39" s="3" t="s">
         <v>0</v>
@@ -33210,13 +34400,13 @@
     </row>
     <row r="40" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>1158</v>
+        <v>1189</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1158</v>
+        <v>1189</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D40" s="4">
         <v>46057</v>
@@ -33228,10 +34418,10 @@
         <v>61</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1121</v>
+        <v>1152</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>1120</v>
+        <v>1151</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>163</v>
@@ -33243,13 +34433,13 @@
         <v>632</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>1119</v>
+        <v>1150</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>1118</v>
+        <v>1149</v>
       </c>
       <c r="O40" s="5">
         <v>507</v>
@@ -33282,7 +34472,7 @@
         <v>51</v>
       </c>
       <c r="Y40" s="2" t="s">
-        <v>1157</v>
+        <v>1188</v>
       </c>
       <c r="Z40" s="2" t="s">
         <v>0</v>
@@ -33320,13 +34510,13 @@
     </row>
     <row r="41" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>1156</v>
+        <v>1187</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>1156</v>
+        <v>1187</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D41" s="7">
         <v>46057</v>
@@ -33344,22 +34534,22 @@
         <v>386</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>1125</v>
+        <v>1156</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>1124</v>
+        <v>1155</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>446</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>1128</v>
+        <v>1159</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>1127</v>
+        <v>1158</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>1093</v>
+        <v>1124</v>
       </c>
       <c r="O41" s="8">
         <v>2000</v>
@@ -33392,7 +34582,7 @@
         <v>51</v>
       </c>
       <c r="Y41" s="3" t="s">
-        <v>1123</v>
+        <v>1154</v>
       </c>
       <c r="Z41" s="3" t="s">
         <v>0</v>
@@ -33430,13 +34620,13 @@
     </row>
     <row r="42" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>1155</v>
+        <v>1186</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1155</v>
+        <v>1186</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D42" s="4">
         <v>46058</v>
@@ -33448,10 +34638,10 @@
         <v>61</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1121</v>
+        <v>1152</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>1120</v>
+        <v>1151</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>163</v>
@@ -33463,13 +34653,13 @@
         <v>632</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>1119</v>
+        <v>1150</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>1118</v>
+        <v>1149</v>
       </c>
       <c r="O42" s="5">
         <v>507</v>
@@ -33502,7 +34692,7 @@
         <v>51</v>
       </c>
       <c r="Y42" s="2" t="s">
-        <v>1154</v>
+        <v>1185</v>
       </c>
       <c r="Z42" s="2" t="s">
         <v>0</v>
@@ -33540,13 +34730,13 @@
     </row>
     <row r="43" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>1153</v>
+        <v>1184</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>1153</v>
+        <v>1184</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D43" s="7">
         <v>46058</v>
@@ -33558,10 +34748,10 @@
         <v>61</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>1090</v>
+        <v>1121</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>1089</v>
+        <v>1120</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>163</v>
@@ -33573,13 +34763,13 @@
         <v>417</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>1144</v>
+        <v>1175</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>1143</v>
+        <v>1174</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>1142</v>
+        <v>1173</v>
       </c>
       <c r="O43" s="8">
         <v>1800</v>
@@ -33612,7 +34802,7 @@
         <v>51</v>
       </c>
       <c r="Y43" s="3" t="s">
-        <v>1152</v>
+        <v>1183</v>
       </c>
       <c r="Z43" s="3" t="s">
         <v>0</v>
@@ -33650,13 +34840,13 @@
     </row>
     <row r="44" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>1151</v>
+        <v>1182</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>1151</v>
+        <v>1182</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D44" s="4">
         <v>46059</v>
@@ -33668,10 +34858,10 @@
         <v>40</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1150</v>
+        <v>1181</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>1149</v>
+        <v>1180</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>43</v>
@@ -33683,13 +34873,13 @@
         <v>784</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>1080</v>
+        <v>1111</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>1079</v>
+        <v>1110</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>1078</v>
+        <v>1109</v>
       </c>
       <c r="O44" s="5">
         <v>500</v>
@@ -33722,7 +34912,7 @@
         <v>51</v>
       </c>
       <c r="Y44" s="2" t="s">
-        <v>1148</v>
+        <v>1179</v>
       </c>
       <c r="Z44" s="2" t="s">
         <v>0</v>
@@ -33760,13 +34950,13 @@
     </row>
     <row r="45" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>1147</v>
+        <v>1178</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>1147</v>
+        <v>1178</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D45" s="7">
         <v>46059</v>
@@ -33778,10 +34968,10 @@
         <v>40</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>1146</v>
+        <v>1177</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>1145</v>
+        <v>1176</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>43</v>
@@ -33793,13 +34983,13 @@
         <v>417</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>1144</v>
+        <v>1175</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>1143</v>
+        <v>1174</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>1142</v>
+        <v>1173</v>
       </c>
       <c r="O45" s="8">
         <v>200</v>
@@ -33832,7 +35022,7 @@
         <v>51</v>
       </c>
       <c r="Y45" s="3" t="s">
-        <v>1141</v>
+        <v>1172</v>
       </c>
       <c r="Z45" s="3" t="s">
         <v>0</v>
@@ -33870,28 +35060,28 @@
     </row>
     <row r="46" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>1140</v>
+        <v>1171</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1140</v>
+        <v>1171</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D46" s="4">
         <v>46063</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1139</v>
+        <v>1170</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>267</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1138</v>
+        <v>1169</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>1137</v>
+        <v>1168</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>139</v>
@@ -33900,7 +35090,7 @@
         <v>140</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>1036</v>
+        <v>1068</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>0</v>
@@ -33942,7 +35132,7 @@
         <v>0</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>1136</v>
+        <v>1167</v>
       </c>
       <c r="Z46" s="2" t="s">
         <v>0</v>
@@ -33957,10 +35147,10 @@
         <v>74</v>
       </c>
       <c r="AD46" s="2" t="s">
-        <v>1034</v>
+        <v>1066</v>
       </c>
       <c r="AE46" s="2" t="s">
-        <v>1033</v>
+        <v>1065</v>
       </c>
       <c r="AF46" s="2" t="s">
         <v>0</v>
@@ -33980,13 +35170,13 @@
     </row>
     <row r="47" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>1135</v>
+        <v>1166</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>1135</v>
+        <v>1166</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D47" s="7">
         <v>46064</v>
@@ -33998,10 +35188,10 @@
         <v>61</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>1134</v>
+        <v>1165</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>1133</v>
+        <v>1164</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>139</v>
@@ -34013,13 +35203,13 @@
         <v>417</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>1132</v>
+        <v>1163</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>1131</v>
+        <v>1162</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>1130</v>
+        <v>1161</v>
       </c>
       <c r="O47" s="8">
         <v>1000</v>
@@ -34052,7 +35242,7 @@
         <v>51</v>
       </c>
       <c r="Y47" s="3" t="s">
-        <v>1129</v>
+        <v>1160</v>
       </c>
       <c r="Z47" s="3" t="s">
         <v>0</v>
@@ -34090,13 +35280,13 @@
     </row>
     <row r="48" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>1126</v>
+        <v>1157</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1126</v>
+        <v>1157</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D48" s="4">
         <v>46064</v>
@@ -34114,22 +35304,22 @@
         <v>386</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>1125</v>
+        <v>1156</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>1124</v>
+        <v>1155</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>446</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>1128</v>
+        <v>1159</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>1127</v>
+        <v>1158</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>1093</v>
+        <v>1124</v>
       </c>
       <c r="O48" s="5">
         <v>1000</v>
@@ -34162,7 +35352,7 @@
         <v>51</v>
       </c>
       <c r="Y48" s="2" t="s">
-        <v>1123</v>
+        <v>1154</v>
       </c>
       <c r="Z48" s="2" t="s">
         <v>0</v>
@@ -34200,13 +35390,13 @@
     </row>
     <row r="49" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>1126</v>
+        <v>1157</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>1126</v>
+        <v>1157</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D49" s="7">
         <v>46064</v>
@@ -34224,22 +35414,22 @@
         <v>386</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>1125</v>
+        <v>1156</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>1124</v>
+        <v>1155</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>446</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>1095</v>
+        <v>1126</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>1094</v>
+        <v>1125</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>1093</v>
+        <v>1124</v>
       </c>
       <c r="O49" s="8">
         <v>1000</v>
@@ -34272,7 +35462,7 @@
         <v>51</v>
       </c>
       <c r="Y49" s="3" t="s">
-        <v>1123</v>
+        <v>1154</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>0</v>
@@ -34310,13 +35500,13 @@
     </row>
     <row r="50" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>1122</v>
+        <v>1153</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>1122</v>
+        <v>1153</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D50" s="4">
         <v>46066</v>
@@ -34328,10 +35518,10 @@
         <v>61</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1121</v>
+        <v>1152</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>1120</v>
+        <v>1151</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>163</v>
@@ -34343,13 +35533,13 @@
         <v>632</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>1119</v>
+        <v>1150</v>
       </c>
       <c r="M50" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>1118</v>
+        <v>1149</v>
       </c>
       <c r="O50" s="5">
         <v>507</v>
@@ -34382,7 +35572,7 @@
         <v>51</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>1117</v>
+        <v>1148</v>
       </c>
       <c r="Z50" s="2" t="s">
         <v>0</v>
@@ -34420,13 +35610,13 @@
     </row>
     <row r="51" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>1116</v>
+        <v>1147</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>1116</v>
+        <v>1147</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D51" s="7">
         <v>46071</v>
@@ -34450,16 +35640,16 @@
         <v>164</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>1054</v>
+        <v>1086</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>1115</v>
+        <v>1146</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>1114</v>
+        <v>1145</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>1113</v>
+        <v>1144</v>
       </c>
       <c r="O51" s="8">
         <v>500</v>
@@ -34492,7 +35682,7 @@
         <v>51</v>
       </c>
       <c r="Y51" s="3" t="s">
-        <v>1112</v>
+        <v>1143</v>
       </c>
       <c r="Z51" s="3" t="s">
         <v>0</v>
@@ -34507,10 +35697,10 @@
         <v>111</v>
       </c>
       <c r="AD51" s="3" t="s">
-        <v>1049</v>
+        <v>1081</v>
       </c>
       <c r="AE51" s="3" t="s">
-        <v>1048</v>
+        <v>1080</v>
       </c>
       <c r="AF51" s="3" t="s">
         <v>77</v>
@@ -34530,13 +35720,13 @@
     </row>
     <row r="52" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>1111</v>
+        <v>1142</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1111</v>
+        <v>1142</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D52" s="4">
         <v>46071</v>
@@ -34548,10 +35738,10 @@
         <v>61</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1110</v>
+        <v>1141</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>1109</v>
+        <v>1140</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>139</v>
@@ -34563,13 +35753,13 @@
         <v>446</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>1095</v>
+        <v>1126</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>1094</v>
+        <v>1125</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>1093</v>
+        <v>1124</v>
       </c>
       <c r="O52" s="5">
         <v>200</v>
@@ -34602,7 +35792,7 @@
         <v>51</v>
       </c>
       <c r="Y52" s="2" t="s">
-        <v>1108</v>
+        <v>1139</v>
       </c>
       <c r="Z52" s="2" t="s">
         <v>0</v>
@@ -34640,13 +35830,13 @@
     </row>
     <row r="53" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>1107</v>
+        <v>1138</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>1107</v>
+        <v>1138</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D53" s="7">
         <v>46072</v>
@@ -34658,10 +35848,10 @@
         <v>40</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>1038</v>
+        <v>1070</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>1037</v>
+        <v>1069</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>43</v>
@@ -34673,13 +35863,13 @@
         <v>440</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>1106</v>
+        <v>1137</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>1105</v>
+        <v>1136</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>1104</v>
+        <v>1135</v>
       </c>
       <c r="O53" s="8">
         <v>50</v>
@@ -34703,16 +35893,16 @@
         <v>0</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>1103</v>
+        <v>1134</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>1102</v>
+        <v>1133</v>
       </c>
       <c r="X53" s="3" t="s">
         <v>51</v>
       </c>
       <c r="Y53" s="3" t="s">
-        <v>1101</v>
+        <v>1132</v>
       </c>
       <c r="Z53" s="3" t="s">
         <v>0</v>
@@ -34750,13 +35940,13 @@
     </row>
     <row r="54" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>1100</v>
+        <v>1131</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1100</v>
+        <v>1131</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D54" s="4">
         <v>46072</v>
@@ -34768,10 +35958,10 @@
         <v>61</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1090</v>
+        <v>1121</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>1089</v>
+        <v>1120</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>163</v>
@@ -34783,13 +35973,13 @@
         <v>417</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>1075</v>
+        <v>1106</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>1074</v>
+        <v>1105</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>1073</v>
+        <v>1104</v>
       </c>
       <c r="O54" s="5">
         <v>1600</v>
@@ -34822,7 +36012,7 @@
         <v>51</v>
       </c>
       <c r="Y54" s="2" t="s">
-        <v>1099</v>
+        <v>1130</v>
       </c>
       <c r="Z54" s="2" t="s">
         <v>0</v>
@@ -34860,13 +36050,13 @@
     </row>
     <row r="55" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>1098</v>
+        <v>1129</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>1098</v>
+        <v>1129</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D55" s="7">
         <v>46072</v>
@@ -34878,10 +36068,10 @@
         <v>40</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>1097</v>
+        <v>1128</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>1096</v>
+        <v>1127</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>43</v>
@@ -34893,13 +36083,13 @@
         <v>446</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>1095</v>
+        <v>1126</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>1094</v>
+        <v>1125</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>1093</v>
+        <v>1124</v>
       </c>
       <c r="O55" s="8">
         <v>500</v>
@@ -34932,7 +36122,7 @@
         <v>51</v>
       </c>
       <c r="Y55" s="3" t="s">
-        <v>1092</v>
+        <v>1123</v>
       </c>
       <c r="Z55" s="3" t="s">
         <v>0</v>
@@ -34970,13 +36160,13 @@
     </row>
     <row r="56" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>1091</v>
+        <v>1122</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1091</v>
+        <v>1122</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D56" s="4">
         <v>46076</v>
@@ -34988,10 +36178,10 @@
         <v>61</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1090</v>
+        <v>1121</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>1089</v>
+        <v>1120</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>163</v>
@@ -35003,13 +36193,13 @@
         <v>417</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>1075</v>
+        <v>1106</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>1074</v>
+        <v>1105</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>1073</v>
+        <v>1104</v>
       </c>
       <c r="O56" s="5">
         <v>1700</v>
@@ -35042,7 +36232,7 @@
         <v>51</v>
       </c>
       <c r="Y56" s="2" t="s">
-        <v>1088</v>
+        <v>1119</v>
       </c>
       <c r="Z56" s="2" t="s">
         <v>0</v>
@@ -35080,13 +36270,13 @@
     </row>
     <row r="57" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>1085</v>
+        <v>1116</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>1085</v>
+        <v>1116</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D57" s="7">
         <v>46077</v>
@@ -35110,16 +36300,16 @@
         <v>164</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>1059</v>
+        <v>1091</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>1087</v>
+        <v>1118</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>1086</v>
+        <v>1117</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>1056</v>
+        <v>1088</v>
       </c>
       <c r="O57" s="8">
         <v>500</v>
@@ -35152,7 +36342,7 @@
         <v>51</v>
       </c>
       <c r="Y57" s="3" t="s">
-        <v>1084</v>
+        <v>1115</v>
       </c>
       <c r="Z57" s="3" t="s">
         <v>0</v>
@@ -35190,13 +36380,13 @@
     </row>
     <row r="58" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>1085</v>
+        <v>1116</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1085</v>
+        <v>1116</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D58" s="4">
         <v>46077</v>
@@ -35220,16 +36410,16 @@
         <v>164</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>1054</v>
+        <v>1086</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>1053</v>
+        <v>1085</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>1052</v>
+        <v>1084</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>1051</v>
+        <v>1083</v>
       </c>
       <c r="O58" s="5">
         <v>500</v>
@@ -35262,7 +36452,7 @@
         <v>51</v>
       </c>
       <c r="Y58" s="2" t="s">
-        <v>1084</v>
+        <v>1115</v>
       </c>
       <c r="Z58" s="2" t="s">
         <v>0</v>
@@ -35277,10 +36467,10 @@
         <v>111</v>
       </c>
       <c r="AD58" s="2" t="s">
-        <v>1049</v>
+        <v>1081</v>
       </c>
       <c r="AE58" s="2" t="s">
-        <v>1048</v>
+        <v>1080</v>
       </c>
       <c r="AF58" s="2" t="s">
         <v>77</v>
@@ -35300,13 +36490,13 @@
     </row>
     <row r="59" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>1083</v>
+        <v>1114</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>1083</v>
+        <v>1114</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D59" s="7">
         <v>46078</v>
@@ -35318,10 +36508,10 @@
         <v>40</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>1082</v>
+        <v>1113</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>1081</v>
+        <v>1112</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>139</v>
@@ -35333,13 +36523,13 @@
         <v>784</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>1080</v>
+        <v>1111</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>1079</v>
+        <v>1110</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>1078</v>
+        <v>1109</v>
       </c>
       <c r="O59" s="8">
         <v>225</v>
@@ -35372,7 +36562,7 @@
         <v>51</v>
       </c>
       <c r="Y59" s="3" t="s">
-        <v>1077</v>
+        <v>1108</v>
       </c>
       <c r="Z59" s="3" t="s">
         <v>0</v>
@@ -35410,13 +36600,13 @@
     </row>
     <row r="60" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>1076</v>
+        <v>1107</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1076</v>
+        <v>1107</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D60" s="4">
         <v>46079</v>
@@ -35443,13 +36633,13 @@
         <v>417</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>1075</v>
+        <v>1106</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>1074</v>
+        <v>1105</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>1073</v>
+        <v>1104</v>
       </c>
       <c r="O60" s="5">
         <v>5000</v>
@@ -35473,16 +36663,16 @@
         <v>2354</v>
       </c>
       <c r="V60" s="2" t="s">
-        <v>1072</v>
+        <v>1103</v>
       </c>
       <c r="W60" s="2" t="s">
-        <v>1071</v>
+        <v>1102</v>
       </c>
       <c r="X60" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Y60" s="2" t="s">
-        <v>1070</v>
+        <v>1101</v>
       </c>
       <c r="Z60" s="2" t="s">
         <v>0</v>
@@ -35520,13 +36710,13 @@
     </row>
     <row r="61" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>1069</v>
+        <v>1100</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>1069</v>
+        <v>1100</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D61" s="7">
         <v>46079</v>
@@ -35550,16 +36740,16 @@
         <v>912</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>1068</v>
+        <v>1060</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>1067</v>
+        <v>1099</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>1066</v>
+        <v>1098</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>1065</v>
+        <v>1097</v>
       </c>
       <c r="O61" s="8">
         <v>12000</v>
@@ -35592,7 +36782,7 @@
         <v>51</v>
       </c>
       <c r="Y61" s="3" t="s">
-        <v>1064</v>
+        <v>1096</v>
       </c>
       <c r="Z61" s="3" t="s">
         <v>0</v>
@@ -35630,13 +36820,13 @@
     </row>
     <row r="62" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>1063</v>
+        <v>1095</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1063</v>
+        <v>1095</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D62" s="4">
         <v>46085</v>
@@ -35663,13 +36853,13 @@
         <v>633</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>1062</v>
+        <v>1094</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>652</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>1061</v>
+        <v>1093</v>
       </c>
       <c r="O62" s="5">
         <v>5005</v>
@@ -35702,7 +36892,7 @@
         <v>51</v>
       </c>
       <c r="Y62" s="2" t="s">
-        <v>1060</v>
+        <v>1092</v>
       </c>
       <c r="Z62" s="2" t="s">
         <v>0</v>
@@ -35740,13 +36930,13 @@
     </row>
     <row r="63" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>1055</v>
+        <v>1087</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>1055</v>
+        <v>1087</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D63" s="7">
         <v>46085</v>
@@ -35770,16 +36960,16 @@
         <v>164</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>1059</v>
+        <v>1091</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>1058</v>
+        <v>1090</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>1057</v>
+        <v>1089</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>1056</v>
+        <v>1088</v>
       </c>
       <c r="O63" s="8">
         <v>500</v>
@@ -35812,7 +37002,7 @@
         <v>51</v>
       </c>
       <c r="Y63" s="3" t="s">
-        <v>1050</v>
+        <v>1082</v>
       </c>
       <c r="Z63" s="3" t="s">
         <v>0</v>
@@ -35850,13 +37040,13 @@
     </row>
     <row r="64" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>1055</v>
+        <v>1087</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1055</v>
+        <v>1087</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D64" s="4">
         <v>46085</v>
@@ -35880,16 +37070,16 @@
         <v>164</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>1054</v>
+        <v>1086</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>1053</v>
+        <v>1085</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>1052</v>
+        <v>1084</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>1051</v>
+        <v>1083</v>
       </c>
       <c r="O64" s="5">
         <v>500</v>
@@ -35922,7 +37112,7 @@
         <v>51</v>
       </c>
       <c r="Y64" s="2" t="s">
-        <v>1050</v>
+        <v>1082</v>
       </c>
       <c r="Z64" s="2" t="s">
         <v>0</v>
@@ -35937,10 +37127,10 @@
         <v>111</v>
       </c>
       <c r="AD64" s="2" t="s">
-        <v>1049</v>
+        <v>1081</v>
       </c>
       <c r="AE64" s="2" t="s">
-        <v>1048</v>
+        <v>1080</v>
       </c>
       <c r="AF64" s="2" t="s">
         <v>77</v>
@@ -35960,13 +37150,13 @@
     </row>
     <row r="65" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>1047</v>
+        <v>1079</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>1047</v>
+        <v>1079</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D65" s="7">
         <v>46085</v>
@@ -35978,10 +37168,10 @@
         <v>40</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>1046</v>
+        <v>1078</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>1045</v>
+        <v>1077</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>163</v>
@@ -35993,13 +37183,13 @@
         <v>154</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>1044</v>
+        <v>1076</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>1043</v>
+        <v>1075</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>1042</v>
+        <v>1074</v>
       </c>
       <c r="O65" s="8">
         <v>3700</v>
@@ -36032,7 +37222,7 @@
         <v>51</v>
       </c>
       <c r="Y65" s="3" t="s">
-        <v>1041</v>
+        <v>1073</v>
       </c>
       <c r="Z65" s="3" t="s">
         <v>0</v>
@@ -36070,13 +37260,13 @@
     </row>
     <row r="66" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>1040</v>
+        <v>1072</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1040</v>
+        <v>1072</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="D66" s="4">
         <v>46085</v>
@@ -36088,10 +37278,10 @@
         <v>40</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1038</v>
+        <v>1070</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>1037</v>
+        <v>1069</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>139</v>
@@ -36100,7 +37290,7 @@
         <v>140</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>1036</v>
+        <v>1068</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>0</v>
@@ -36142,7 +37332,7 @@
         <v>0</v>
       </c>
       <c r="Y66" s="2" t="s">
-        <v>1035</v>
+        <v>1067</v>
       </c>
       <c r="Z66" s="2" t="s">
         <v>0</v>
@@ -36157,10 +37347,10 @@
         <v>298</v>
       </c>
       <c r="AD66" s="2" t="s">
-        <v>1034</v>
+        <v>1066</v>
       </c>
       <c r="AE66" s="2" t="s">
-        <v>1033</v>
+        <v>1065</v>
       </c>
       <c r="AF66" s="2" t="s">
         <v>0</v>

--- a/BASE_KEMPARTS.xlsx
+++ b/BASE_KEMPARTS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dash_kp_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCDF60A6-0241-4C84-A5C9-0B6398B4F075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97583B37-DC83-4DD0-9F4C-6CDFE6B33DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{6FEA2588-5565-4B12-8C5E-E6FBB7E9CDF0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{CB469FB5-CC63-49DF-8F0A-CC2C928DC074}"/>
   </bookViews>
   <sheets>
     <sheet name="FSP" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7397" uniqueCount="1288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7547" uniqueCount="1305">
   <si>
     <t/>
   </si>
@@ -3218,6 +3218,84 @@
     <t>153266</t>
   </si>
   <si>
+    <t>000015547</t>
+  </si>
+  <si>
+    <t>173837</t>
+  </si>
+  <si>
+    <t>000015548</t>
+  </si>
+  <si>
+    <t>C00113</t>
+  </si>
+  <si>
+    <t>EVERCOL INDUSTRIA E COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>173818</t>
+  </si>
+  <si>
+    <t>000015551</t>
+  </si>
+  <si>
+    <t>TRAN.24.004.10.24081025</t>
+  </si>
+  <si>
+    <t>24081025</t>
+  </si>
+  <si>
+    <t>TRAN.24.004.10.</t>
+  </si>
+  <si>
+    <t>153309</t>
+  </si>
+  <si>
+    <t>003301</t>
+  </si>
+  <si>
+    <t>2024.357.03.</t>
+  </si>
+  <si>
+    <t>240707</t>
+  </si>
+  <si>
+    <t>2024.357.03.240707</t>
+  </si>
+  <si>
+    <t>ALV INDUSTRIA E COMERCIO DE TINTAS LTDA</t>
+  </si>
+  <si>
+    <t>C00341</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>000002510</t>
+  </si>
+  <si>
+    <t>003293</t>
+  </si>
+  <si>
+    <t>TRANSPORTADORA NIMEC LT</t>
+  </si>
+  <si>
+    <t>T00213</t>
+  </si>
+  <si>
+    <t>2025.004.01.</t>
+  </si>
+  <si>
+    <t>25021048</t>
+  </si>
+  <si>
+    <t>2025.004.01.25021048</t>
+  </si>
+  <si>
+    <t>000002509</t>
+  </si>
+  <si>
     <t>GASTOS GERAIS</t>
   </si>
   <si>
@@ -3236,9 +3314,6 @@
     <t>C00591</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>000002508</t>
   </si>
   <si>
@@ -3329,15 +3404,6 @@
     <t>003169</t>
   </si>
   <si>
-    <t>TRANSPORTADORA NIMEC LT</t>
-  </si>
-  <si>
-    <t>T00213</t>
-  </si>
-  <si>
-    <t>2025.004.01.</t>
-  </si>
-  <si>
     <t>25021046</t>
   </si>
   <si>
@@ -3348,21 +3414,6 @@
   </si>
   <si>
     <t>003283</t>
-  </si>
-  <si>
-    <t>2024.357.03.</t>
-  </si>
-  <si>
-    <t>240707</t>
-  </si>
-  <si>
-    <t>2024.357.03.240707</t>
-  </si>
-  <si>
-    <t>ALV INDUSTRIA E COMERCIO DE TINTAS LTDA</t>
-  </si>
-  <si>
-    <t>C00341</t>
   </si>
   <si>
     <t>000002498</t>
@@ -4831,8 +4882,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{318A57C2-A3D9-48EA-BD6D-8BF7B0CE2ED1}">
-  <dimension ref="A1:AJ229"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B26A77ED-7CEE-4E89-8BE8-34DC8758E529}">
+  <dimension ref="A1:AJ233"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -30062,14 +30113,454 @@
         <v>9.8148</v>
       </c>
     </row>
+    <row r="230" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A230" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D230" s="4">
+        <v>46091</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F230" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G230" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="H230" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="I230" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J230" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="K230" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="L230" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="M230" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="N230" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="O230" s="5">
+        <v>1000</v>
+      </c>
+      <c r="P230" s="5">
+        <v>25.2</v>
+      </c>
+      <c r="Q230" s="6">
+        <v>25200</v>
+      </c>
+      <c r="R230" s="6">
+        <v>819</v>
+      </c>
+      <c r="S230" s="6">
+        <v>26019</v>
+      </c>
+      <c r="T230" s="6">
+        <v>25200</v>
+      </c>
+      <c r="U230" s="6">
+        <v>4536</v>
+      </c>
+      <c r="V230" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="W230" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="X230" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y230" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="Z230" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA230" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB230" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC230" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD230" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="AE230" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="AF230" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG230" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH230" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI230" s="6">
+        <v>18</v>
+      </c>
+      <c r="AJ230" s="5">
+        <v>7503.57</v>
+      </c>
+    </row>
+    <row r="231" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A231" s="3" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D231" s="7">
+        <v>46091</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G231" s="3" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H231" s="3" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I231" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J231" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="K231" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="L231" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M231" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N231" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="O231" s="8">
+        <v>1700</v>
+      </c>
+      <c r="P231" s="8">
+        <v>22.98</v>
+      </c>
+      <c r="Q231" s="9">
+        <v>39066</v>
+      </c>
+      <c r="R231" s="9">
+        <v>1269.6500000000001</v>
+      </c>
+      <c r="S231" s="9">
+        <v>40335.65</v>
+      </c>
+      <c r="T231" s="9">
+        <v>39066</v>
+      </c>
+      <c r="U231" s="9">
+        <v>7031.88</v>
+      </c>
+      <c r="V231" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="W231" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="X231" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y231" s="3" t="s">
+        <v>1070</v>
+      </c>
+      <c r="Z231" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA231" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB231" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC231" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD231" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE231" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF231" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG231" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH231" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI231" s="9">
+        <v>18</v>
+      </c>
+      <c r="AJ231" s="8">
+        <v>19786.912</v>
+      </c>
+    </row>
+    <row r="232" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A232" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D232" s="4">
+        <v>46091</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G232" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="H232" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="I232" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J232" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K232" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="L232" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="M232" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="N232" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="O232" s="5">
+        <v>1</v>
+      </c>
+      <c r="P232" s="5">
+        <v>10</v>
+      </c>
+      <c r="Q232" s="6">
+        <v>10</v>
+      </c>
+      <c r="R232" s="6">
+        <v>0</v>
+      </c>
+      <c r="S232" s="6">
+        <v>10</v>
+      </c>
+      <c r="T232" s="6">
+        <v>0</v>
+      </c>
+      <c r="U232" s="6">
+        <v>0</v>
+      </c>
+      <c r="V232" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="W232" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="X232" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y232" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="Z232" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA232" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB232" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC232" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD232" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE232" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF232" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="AG232" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH232" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI232" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ232" s="5">
+        <v>9.8976000000000006</v>
+      </c>
+    </row>
+    <row r="233" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A233" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D233" s="7">
+        <v>46091</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="H233" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="I233" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J233" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="K233" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="L233" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="M233" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="N233" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="O233" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P233" s="8">
+        <v>10</v>
+      </c>
+      <c r="Q233" s="9">
+        <v>5</v>
+      </c>
+      <c r="R233" s="9">
+        <v>0</v>
+      </c>
+      <c r="S233" s="9">
+        <v>5</v>
+      </c>
+      <c r="T233" s="9">
+        <v>0</v>
+      </c>
+      <c r="U233" s="9">
+        <v>0</v>
+      </c>
+      <c r="V233" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="W233" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="X233" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y233" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="Z233" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA233" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB233" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC233" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD233" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="AE233" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="AF233" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AG233" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH233" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI233" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ233" s="8">
+        <v>9.8208099999999998</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11535412-83B7-4F7D-A32C-87312564DCEE}">
-  <dimension ref="A1:AJ66"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49746817-01A4-4A9C-9061-C45AA702B917}">
+  <dimension ref="A1:AJ68"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -30220,13 +30711,13 @@
     </row>
     <row r="2" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>1287</v>
+        <v>1304</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1287</v>
+        <v>1304</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D2" s="4">
         <v>46024</v>
@@ -30238,10 +30729,10 @@
         <v>40</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1070</v>
+        <v>1096</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>1069</v>
+        <v>1095</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>43</v>
@@ -30253,13 +30744,13 @@
         <v>440</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>1137</v>
+        <v>1154</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>1136</v>
+        <v>1153</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>1135</v>
+        <v>1152</v>
       </c>
       <c r="O2" s="5">
         <v>50</v>
@@ -30283,16 +30774,16 @@
         <v>39.06</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>1134</v>
+        <v>1151</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>1133</v>
+        <v>1150</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>1286</v>
+        <v>1303</v>
       </c>
       <c r="Z2" s="2" t="s">
         <v>0</v>
@@ -30330,13 +30821,13 @@
     </row>
     <row r="3" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>1285</v>
+        <v>1302</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1285</v>
+        <v>1302</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D3" s="7">
         <v>46027</v>
@@ -30348,10 +30839,10 @@
         <v>61</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1152</v>
+        <v>1169</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1151</v>
+        <v>1168</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>163</v>
@@ -30363,13 +30854,13 @@
         <v>632</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1150</v>
+        <v>1167</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>648</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>1149</v>
+        <v>1166</v>
       </c>
       <c r="O3" s="8">
         <v>1001</v>
@@ -30402,7 +30893,7 @@
         <v>51</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>1284</v>
+        <v>1301</v>
       </c>
       <c r="Z3" s="3" t="s">
         <v>0</v>
@@ -30440,13 +30931,13 @@
     </row>
     <row r="4" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>1283</v>
+        <v>1300</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1283</v>
+        <v>1300</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D4" s="4">
         <v>46027</v>
@@ -30458,10 +30949,10 @@
         <v>61</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1282</v>
+        <v>1299</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1281</v>
+        <v>1298</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>152</v>
@@ -30473,13 +30964,13 @@
         <v>342</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1280</v>
+        <v>1297</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1279</v>
+        <v>1296</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1278</v>
+        <v>1295</v>
       </c>
       <c r="O4" s="5">
         <v>600</v>
@@ -30503,16 +30994,16 @@
         <v>355.68</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>1277</v>
+        <v>1294</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>1276</v>
+        <v>1293</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>1275</v>
+        <v>1292</v>
       </c>
       <c r="Z4" s="2" t="s">
         <v>0</v>
@@ -30550,13 +31041,13 @@
     </row>
     <row r="5" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>1274</v>
+        <v>1291</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1274</v>
+        <v>1291</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D5" s="7">
         <v>46029</v>
@@ -30568,10 +31059,10 @@
         <v>212</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>1193</v>
+        <v>1210</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1192</v>
+        <v>1209</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>139</v>
@@ -30580,7 +31071,7 @@
         <v>140</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>1273</v>
+        <v>1290</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>0</v>
@@ -30622,7 +31113,7 @@
         <v>87</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>1272</v>
+        <v>1289</v>
       </c>
       <c r="Z5" s="3" t="s">
         <v>0</v>
@@ -30660,13 +31151,13 @@
     </row>
     <row r="6" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>1274</v>
+        <v>1291</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1274</v>
+        <v>1291</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D6" s="4">
         <v>46029</v>
@@ -30678,10 +31169,10 @@
         <v>212</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1193</v>
+        <v>1210</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1192</v>
+        <v>1209</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>139</v>
@@ -30690,7 +31181,7 @@
         <v>140</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>1273</v>
+        <v>1290</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>0</v>
@@ -30732,7 +31223,7 @@
         <v>87</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>1272</v>
+        <v>1289</v>
       </c>
       <c r="Z6" s="2" t="s">
         <v>0</v>
@@ -30770,13 +31261,13 @@
     </row>
     <row r="7" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>1271</v>
+        <v>1288</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1271</v>
+        <v>1288</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D7" s="7">
         <v>46029</v>
@@ -30794,22 +31285,22 @@
         <v>386</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>1155</v>
+        <v>1172</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>1060</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>1270</v>
+        <v>1287</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>1269</v>
+        <v>1286</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>1268</v>
+        <v>1285</v>
       </c>
       <c r="O7" s="8">
         <v>1000</v>
@@ -30842,7 +31333,7 @@
         <v>51</v>
       </c>
       <c r="Y7" s="3" t="s">
-        <v>1267</v>
+        <v>1284</v>
       </c>
       <c r="Z7" s="3" t="s">
         <v>0</v>
@@ -30880,13 +31371,13 @@
     </row>
     <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>1266</v>
+        <v>1283</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1266</v>
+        <v>1283</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D8" s="4">
         <v>46036</v>
@@ -30898,10 +31389,10 @@
         <v>61</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1152</v>
+        <v>1169</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>1151</v>
+        <v>1168</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>163</v>
@@ -30913,13 +31404,13 @@
         <v>632</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>1150</v>
+        <v>1167</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1149</v>
+        <v>1166</v>
       </c>
       <c r="O8" s="5">
         <v>1001</v>
@@ -30952,7 +31443,7 @@
         <v>51</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="Z8" s="2" t="s">
         <v>0</v>
@@ -30990,13 +31481,13 @@
     </row>
     <row r="9" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>1264</v>
+        <v>1281</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1264</v>
+        <v>1281</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D9" s="7">
         <v>46037</v>
@@ -31008,10 +31499,10 @@
         <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>1165</v>
+        <v>1182</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1164</v>
+        <v>1181</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>163</v>
@@ -31023,13 +31514,13 @@
         <v>417</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>1263</v>
+        <v>1280</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>1043</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="O9" s="8">
         <v>1000</v>
@@ -31062,7 +31553,7 @@
         <v>51</v>
       </c>
       <c r="Y9" s="3" t="s">
-        <v>1262</v>
+        <v>1279</v>
       </c>
       <c r="Z9" s="3" t="s">
         <v>0</v>
@@ -31100,13 +31591,13 @@
     </row>
     <row r="10" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>1261</v>
+        <v>1278</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1261</v>
+        <v>1278</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D10" s="4">
         <v>46037</v>
@@ -31118,10 +31609,10 @@
         <v>40</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1113</v>
+        <v>1081</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1112</v>
+        <v>1080</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>139</v>
@@ -31133,13 +31624,13 @@
         <v>784</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>1111</v>
+        <v>1079</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1110</v>
+        <v>1078</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1109</v>
+        <v>1077</v>
       </c>
       <c r="O10" s="5">
         <v>300</v>
@@ -31172,7 +31663,7 @@
         <v>51</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>1260</v>
+        <v>1277</v>
       </c>
       <c r="Z10" s="2" t="s">
         <v>0</v>
@@ -31210,13 +31701,13 @@
     </row>
     <row r="11" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>1259</v>
+        <v>1276</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1259</v>
+        <v>1276</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D11" s="7">
         <v>46037</v>
@@ -31228,10 +31719,10 @@
         <v>40</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>1203</v>
+        <v>1220</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1202</v>
+        <v>1219</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>43</v>
@@ -31243,13 +31734,13 @@
         <v>300</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>1258</v>
+        <v>1275</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>1257</v>
+        <v>1274</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>1256</v>
+        <v>1273</v>
       </c>
       <c r="O11" s="8">
         <v>25</v>
@@ -31282,7 +31773,7 @@
         <v>51</v>
       </c>
       <c r="Y11" s="3" t="s">
-        <v>1255</v>
+        <v>1272</v>
       </c>
       <c r="Z11" s="3" t="s">
         <v>0</v>
@@ -31320,13 +31811,13 @@
     </row>
     <row r="12" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>1254</v>
+        <v>1271</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1254</v>
+        <v>1271</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D12" s="4">
         <v>46041</v>
@@ -31338,10 +31829,10 @@
         <v>212</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1193</v>
+        <v>1210</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1192</v>
+        <v>1209</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>139</v>
@@ -31350,7 +31841,7 @@
         <v>140</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>1086</v>
+        <v>1111</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>0</v>
@@ -31392,7 +31883,7 @@
         <v>87</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>1253</v>
+        <v>1270</v>
       </c>
       <c r="Z12" s="2" t="s">
         <v>0</v>
@@ -31407,10 +31898,10 @@
         <v>55</v>
       </c>
       <c r="AD12" s="2" t="s">
-        <v>1081</v>
+        <v>1106</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>1080</v>
+        <v>1105</v>
       </c>
       <c r="AF12" s="2" t="s">
         <v>442</v>
@@ -31430,13 +31921,13 @@
     </row>
     <row r="13" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>1252</v>
+        <v>1269</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1252</v>
+        <v>1269</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D13" s="7">
         <v>46042</v>
@@ -31454,22 +31945,22 @@
         <v>386</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>1155</v>
+        <v>1172</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>446</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>1159</v>
+        <v>1176</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>1158</v>
+        <v>1175</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>1124</v>
+        <v>1141</v>
       </c>
       <c r="O13" s="8">
         <v>2000</v>
@@ -31502,7 +31993,7 @@
         <v>51</v>
       </c>
       <c r="Y13" s="3" t="s">
-        <v>1251</v>
+        <v>1268</v>
       </c>
       <c r="Z13" s="3" t="s">
         <v>0</v>
@@ -31540,13 +32031,13 @@
     </row>
     <row r="14" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>1250</v>
+        <v>1267</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1250</v>
+        <v>1267</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D14" s="4">
         <v>46042</v>
@@ -31570,16 +32061,16 @@
         <v>294</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>1086</v>
+        <v>1111</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>1218</v>
+        <v>1235</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1217</v>
+        <v>1234</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1083</v>
+        <v>1108</v>
       </c>
       <c r="O14" s="5">
         <v>6000</v>
@@ -31603,16 +32094,16 @@
         <v>12873.6</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>1249</v>
+        <v>1266</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>1248</v>
+        <v>1265</v>
       </c>
       <c r="X14" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>1247</v>
+        <v>1264</v>
       </c>
       <c r="Z14" s="2" t="s">
         <v>0</v>
@@ -31627,10 +32118,10 @@
         <v>298</v>
       </c>
       <c r="AD14" s="2" t="s">
-        <v>1081</v>
+        <v>1106</v>
       </c>
       <c r="AE14" s="2" t="s">
-        <v>1080</v>
+        <v>1105</v>
       </c>
       <c r="AF14" s="2" t="s">
         <v>77</v>
@@ -31650,13 +32141,13 @@
     </row>
     <row r="15" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>1246</v>
+        <v>1263</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1246</v>
+        <v>1263</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D15" s="7">
         <v>46042</v>
@@ -31668,10 +32159,10 @@
         <v>212</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>1193</v>
+        <v>1210</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>1192</v>
+        <v>1209</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>139</v>
@@ -31722,7 +32213,7 @@
         <v>87</v>
       </c>
       <c r="Y15" s="3" t="s">
-        <v>1245</v>
+        <v>1262</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>0</v>
@@ -31743,7 +32234,7 @@
         <v>518</v>
       </c>
       <c r="AF15" s="3" t="s">
-        <v>1213</v>
+        <v>1230</v>
       </c>
       <c r="AG15" s="9">
         <v>0</v>
@@ -31760,13 +32251,13 @@
     </row>
     <row r="16" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>1246</v>
+        <v>1263</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1246</v>
+        <v>1263</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D16" s="4">
         <v>46042</v>
@@ -31778,10 +32269,10 @@
         <v>212</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1193</v>
+        <v>1210</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1192</v>
+        <v>1209</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>139</v>
@@ -31832,7 +32323,7 @@
         <v>87</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>1245</v>
+        <v>1262</v>
       </c>
       <c r="Z16" s="2" t="s">
         <v>0</v>
@@ -31853,7 +32344,7 @@
         <v>518</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>1213</v>
+        <v>1230</v>
       </c>
       <c r="AG16" s="6">
         <v>0</v>
@@ -31870,13 +32361,13 @@
     </row>
     <row r="17" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>1244</v>
+        <v>1261</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1244</v>
+        <v>1261</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D17" s="7">
         <v>46043</v>
@@ -31903,13 +32394,13 @@
         <v>417</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>1163</v>
+        <v>1180</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>1162</v>
+        <v>1179</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="O17" s="8">
         <v>1000</v>
@@ -31942,7 +32433,7 @@
         <v>51</v>
       </c>
       <c r="Y17" s="3" t="s">
-        <v>1243</v>
+        <v>1260</v>
       </c>
       <c r="Z17" s="3" t="s">
         <v>0</v>
@@ -31980,28 +32471,28 @@
     </row>
     <row r="18" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>1231</v>
+        <v>1248</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1231</v>
+        <v>1248</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D18" s="4">
         <v>46045</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1230</v>
+        <v>1247</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1229</v>
+        <v>1246</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1169</v>
+        <v>1186</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>1168</v>
+        <v>1185</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>139</v>
@@ -32013,13 +32504,13 @@
         <v>628</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>1242</v>
+        <v>1259</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1241</v>
+        <v>1258</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1240</v>
+        <v>1257</v>
       </c>
       <c r="O18" s="5">
         <v>2000</v>
@@ -32043,16 +32534,16 @@
         <v>0</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>1225</v>
+        <v>1242</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>1192</v>
+        <v>1209</v>
       </c>
       <c r="X18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>1224</v>
+        <v>1241</v>
       </c>
       <c r="Z18" s="2" t="s">
         <v>0</v>
@@ -32090,28 +32581,28 @@
     </row>
     <row r="19" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>1231</v>
+        <v>1248</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>1231</v>
+        <v>1248</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D19" s="7">
         <v>46045</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>1230</v>
+        <v>1247</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>1229</v>
+        <v>1246</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>1169</v>
+        <v>1186</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>1168</v>
+        <v>1185</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>139</v>
@@ -32123,13 +32614,13 @@
         <v>631</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>1239</v>
+        <v>1256</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>1238</v>
+        <v>1255</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>1226</v>
+        <v>1243</v>
       </c>
       <c r="O19" s="8">
         <v>11725</v>
@@ -32153,16 +32644,16 @@
         <v>0</v>
       </c>
       <c r="V19" s="3" t="s">
-        <v>1225</v>
+        <v>1242</v>
       </c>
       <c r="W19" s="3" t="s">
-        <v>1192</v>
+        <v>1209</v>
       </c>
       <c r="X19" s="3" t="s">
         <v>87</v>
       </c>
       <c r="Y19" s="3" t="s">
-        <v>1224</v>
+        <v>1241</v>
       </c>
       <c r="Z19" s="3" t="s">
         <v>0</v>
@@ -32200,28 +32691,28 @@
     </row>
     <row r="20" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>1231</v>
+        <v>1248</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1231</v>
+        <v>1248</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D20" s="4">
         <v>46045</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1230</v>
+        <v>1247</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1229</v>
+        <v>1246</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1169</v>
+        <v>1186</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1168</v>
+        <v>1185</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>139</v>
@@ -32233,13 +32724,13 @@
         <v>632</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>1150</v>
+        <v>1167</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1149</v>
+        <v>1166</v>
       </c>
       <c r="O20" s="5">
         <v>2925</v>
@@ -32263,16 +32754,16 @@
         <v>0</v>
       </c>
       <c r="V20" s="2" t="s">
-        <v>1225</v>
+        <v>1242</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>1192</v>
+        <v>1209</v>
       </c>
       <c r="X20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>1224</v>
+        <v>1241</v>
       </c>
       <c r="Z20" s="2" t="s">
         <v>0</v>
@@ -32310,28 +32801,28 @@
     </row>
     <row r="21" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>1231</v>
+        <v>1248</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>1231</v>
+        <v>1248</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D21" s="7">
         <v>46045</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>1230</v>
+        <v>1247</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>1229</v>
+        <v>1246</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>1169</v>
+        <v>1186</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>1168</v>
+        <v>1185</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>139</v>
@@ -32343,13 +32834,13 @@
         <v>633</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>1094</v>
+        <v>1119</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>652</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>1093</v>
+        <v>1118</v>
       </c>
       <c r="O21" s="8">
         <v>2925</v>
@@ -32373,16 +32864,16 @@
         <v>0</v>
       </c>
       <c r="V21" s="3" t="s">
-        <v>1225</v>
+        <v>1242</v>
       </c>
       <c r="W21" s="3" t="s">
-        <v>1192</v>
+        <v>1209</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>87</v>
       </c>
       <c r="Y21" s="3" t="s">
-        <v>1224</v>
+        <v>1241</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>0</v>
@@ -32420,28 +32911,28 @@
     </row>
     <row r="22" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>1231</v>
+        <v>1248</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1231</v>
+        <v>1248</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D22" s="4">
         <v>46045</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1230</v>
+        <v>1247</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1229</v>
+        <v>1246</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1169</v>
+        <v>1186</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1168</v>
+        <v>1185</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>139</v>
@@ -32453,13 +32944,13 @@
         <v>465</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1237</v>
+        <v>1254</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1236</v>
+        <v>1253</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1235</v>
+        <v>1252</v>
       </c>
       <c r="O22" s="5">
         <v>2400</v>
@@ -32483,16 +32974,16 @@
         <v>0</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>1225</v>
+        <v>1242</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>1192</v>
+        <v>1209</v>
       </c>
       <c r="X22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>1224</v>
+        <v>1241</v>
       </c>
       <c r="Z22" s="2" t="s">
         <v>0</v>
@@ -32530,28 +33021,28 @@
     </row>
     <row r="23" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>1231</v>
+        <v>1248</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>1231</v>
+        <v>1248</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D23" s="7">
         <v>46045</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>1230</v>
+        <v>1247</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>1229</v>
+        <v>1246</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>1169</v>
+        <v>1186</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>1168</v>
+        <v>1185</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>139</v>
@@ -32563,13 +33054,13 @@
         <v>465</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>1234</v>
+        <v>1251</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>1233</v>
+        <v>1250</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>1232</v>
+        <v>1249</v>
       </c>
       <c r="O23" s="8">
         <v>1800</v>
@@ -32593,16 +33084,16 @@
         <v>0</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>1225</v>
+        <v>1242</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>1192</v>
+        <v>1209</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>87</v>
       </c>
       <c r="Y23" s="3" t="s">
-        <v>1224</v>
+        <v>1241</v>
       </c>
       <c r="Z23" s="3" t="s">
         <v>0</v>
@@ -32640,28 +33131,28 @@
     </row>
     <row r="24" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>1231</v>
+        <v>1248</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1231</v>
+        <v>1248</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D24" s="4">
         <v>46045</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1230</v>
+        <v>1247</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1229</v>
+        <v>1246</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1169</v>
+        <v>1186</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1168</v>
+        <v>1185</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>139</v>
@@ -32673,13 +33164,13 @@
         <v>634</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>1228</v>
+        <v>1245</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1227</v>
+        <v>1244</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1226</v>
+        <v>1243</v>
       </c>
       <c r="O24" s="5">
         <v>1400</v>
@@ -32703,16 +33194,16 @@
         <v>0</v>
       </c>
       <c r="V24" s="2" t="s">
-        <v>1225</v>
+        <v>1242</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>1192</v>
+        <v>1209</v>
       </c>
       <c r="X24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>1224</v>
+        <v>1241</v>
       </c>
       <c r="Z24" s="2" t="s">
         <v>0</v>
@@ -32750,13 +33241,13 @@
     </row>
     <row r="25" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>1223</v>
+        <v>1240</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>1223</v>
+        <v>1240</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D25" s="7">
         <v>46048</v>
@@ -32783,13 +33274,13 @@
         <v>417</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>1175</v>
+        <v>1192</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>1174</v>
+        <v>1191</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>1173</v>
+        <v>1190</v>
       </c>
       <c r="O25" s="8">
         <v>5000</v>
@@ -32813,16 +33304,16 @@
         <v>2354</v>
       </c>
       <c r="V25" s="3" t="s">
-        <v>1103</v>
+        <v>1086</v>
       </c>
       <c r="W25" s="3" t="s">
-        <v>1102</v>
+        <v>1085</v>
       </c>
       <c r="X25" s="3" t="s">
         <v>51</v>
       </c>
       <c r="Y25" s="3" t="s">
-        <v>1222</v>
+        <v>1239</v>
       </c>
       <c r="Z25" s="3" t="s">
         <v>0</v>
@@ -32860,13 +33351,13 @@
     </row>
     <row r="26" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>1221</v>
+        <v>1238</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1221</v>
+        <v>1238</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D26" s="4">
         <v>46048</v>
@@ -32878,10 +33369,10 @@
         <v>40</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1113</v>
+        <v>1081</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1112</v>
+        <v>1080</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>139</v>
@@ -32893,13 +33384,13 @@
         <v>784</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>1111</v>
+        <v>1079</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1110</v>
+        <v>1078</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1109</v>
+        <v>1077</v>
       </c>
       <c r="O26" s="5">
         <v>300</v>
@@ -32932,7 +33423,7 @@
         <v>51</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>1220</v>
+        <v>1237</v>
       </c>
       <c r="Z26" s="2" t="s">
         <v>0</v>
@@ -32970,13 +33461,13 @@
     </row>
     <row r="27" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>1219</v>
+        <v>1236</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>1219</v>
+        <v>1236</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D27" s="7">
         <v>46048</v>
@@ -32988,10 +33479,10 @@
         <v>61</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>1152</v>
+        <v>1169</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>1151</v>
+        <v>1168</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>163</v>
@@ -33003,13 +33494,13 @@
         <v>632</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>1150</v>
+        <v>1167</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>648</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>1149</v>
+        <v>1166</v>
       </c>
       <c r="O27" s="8">
         <v>611</v>
@@ -33042,7 +33533,7 @@
         <v>51</v>
       </c>
       <c r="Y27" s="3" t="s">
-        <v>1216</v>
+        <v>1233</v>
       </c>
       <c r="Z27" s="3" t="s">
         <v>0</v>
@@ -33080,13 +33571,13 @@
     </row>
     <row r="28" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>1219</v>
+        <v>1236</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1219</v>
+        <v>1236</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D28" s="4">
         <v>46048</v>
@@ -33098,10 +33589,10 @@
         <v>61</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1152</v>
+        <v>1169</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1151</v>
+        <v>1168</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>163</v>
@@ -33110,16 +33601,16 @@
         <v>164</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>1086</v>
+        <v>1111</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>1218</v>
+        <v>1235</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1217</v>
+        <v>1234</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1083</v>
+        <v>1108</v>
       </c>
       <c r="O28" s="5">
         <v>700</v>
@@ -33152,7 +33643,7 @@
         <v>51</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>1216</v>
+        <v>1233</v>
       </c>
       <c r="Z28" s="2" t="s">
         <v>0</v>
@@ -33167,10 +33658,10 @@
         <v>55</v>
       </c>
       <c r="AD28" s="2" t="s">
-        <v>1081</v>
+        <v>1106</v>
       </c>
       <c r="AE28" s="2" t="s">
-        <v>1080</v>
+        <v>1105</v>
       </c>
       <c r="AF28" s="2" t="s">
         <v>77</v>
@@ -33190,13 +33681,13 @@
     </row>
     <row r="29" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>1215</v>
+        <v>1232</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>1215</v>
+        <v>1232</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D29" s="7">
         <v>46048</v>
@@ -33208,10 +33699,10 @@
         <v>212</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>1193</v>
+        <v>1210</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>1192</v>
+        <v>1209</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>139</v>
@@ -33262,7 +33753,7 @@
         <v>87</v>
       </c>
       <c r="Y29" s="3" t="s">
-        <v>1214</v>
+        <v>1231</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>0</v>
@@ -33283,7 +33774,7 @@
         <v>57</v>
       </c>
       <c r="AF29" s="3" t="s">
-        <v>1213</v>
+        <v>1230</v>
       </c>
       <c r="AG29" s="9">
         <v>0</v>
@@ -33300,13 +33791,13 @@
     </row>
     <row r="30" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>1212</v>
+        <v>1229</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1212</v>
+        <v>1229</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D30" s="4">
         <v>46049</v>
@@ -33318,10 +33809,10 @@
         <v>212</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1193</v>
+        <v>1210</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1192</v>
+        <v>1209</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>139</v>
@@ -33372,7 +33863,7 @@
         <v>87</v>
       </c>
       <c r="Y30" s="2" t="s">
-        <v>1211</v>
+        <v>1228</v>
       </c>
       <c r="Z30" s="2" t="s">
         <v>0</v>
@@ -33410,13 +33901,13 @@
     </row>
     <row r="31" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>1212</v>
+        <v>1229</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>1212</v>
+        <v>1229</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D31" s="7">
         <v>46049</v>
@@ -33428,10 +33919,10 @@
         <v>212</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>1193</v>
+        <v>1210</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>1192</v>
+        <v>1209</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>139</v>
@@ -33482,7 +33973,7 @@
         <v>87</v>
       </c>
       <c r="Y31" s="3" t="s">
-        <v>1211</v>
+        <v>1228</v>
       </c>
       <c r="Z31" s="3" t="s">
         <v>0</v>
@@ -33520,13 +34011,13 @@
     </row>
     <row r="32" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>1208</v>
+        <v>1225</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1208</v>
+        <v>1225</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D32" s="4">
         <v>46050</v>
@@ -33544,22 +34035,22 @@
         <v>386</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>1155</v>
+        <v>1172</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>446</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>1210</v>
+        <v>1227</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>448</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1209</v>
+        <v>1226</v>
       </c>
       <c r="O32" s="5">
         <v>1000</v>
@@ -33592,7 +34083,7 @@
         <v>51</v>
       </c>
       <c r="Y32" s="2" t="s">
-        <v>1207</v>
+        <v>1224</v>
       </c>
       <c r="Z32" s="2" t="s">
         <v>0</v>
@@ -33630,13 +34121,13 @@
     </row>
     <row r="33" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>1208</v>
+        <v>1225</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>1208</v>
+        <v>1225</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D33" s="7">
         <v>46050</v>
@@ -33654,22 +34145,22 @@
         <v>386</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>1155</v>
+        <v>1172</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>446</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>1159</v>
+        <v>1176</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>1158</v>
+        <v>1175</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>1124</v>
+        <v>1141</v>
       </c>
       <c r="O33" s="8">
         <v>1000</v>
@@ -33702,7 +34193,7 @@
         <v>51</v>
       </c>
       <c r="Y33" s="3" t="s">
-        <v>1207</v>
+        <v>1224</v>
       </c>
       <c r="Z33" s="3" t="s">
         <v>0</v>
@@ -33740,13 +34231,13 @@
     </row>
     <row r="34" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>1206</v>
+        <v>1223</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1206</v>
+        <v>1223</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D34" s="4">
         <v>46050</v>
@@ -33758,10 +34249,10 @@
         <v>212</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1193</v>
+        <v>1210</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>1192</v>
+        <v>1209</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>139</v>
@@ -33812,7 +34303,7 @@
         <v>87</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>1205</v>
+        <v>1222</v>
       </c>
       <c r="Z34" s="2" t="s">
         <v>0</v>
@@ -33850,13 +34341,13 @@
     </row>
     <row r="35" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>1204</v>
+        <v>1221</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>1204</v>
+        <v>1221</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D35" s="7">
         <v>46051</v>
@@ -33868,10 +34359,10 @@
         <v>40</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>1203</v>
+        <v>1220</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>1202</v>
+        <v>1219</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>43</v>
@@ -33883,13 +34374,13 @@
         <v>632</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>1150</v>
+        <v>1167</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>648</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>1149</v>
+        <v>1166</v>
       </c>
       <c r="O35" s="8">
         <v>26</v>
@@ -33922,7 +34413,7 @@
         <v>51</v>
       </c>
       <c r="Y35" s="3" t="s">
-        <v>1201</v>
+        <v>1218</v>
       </c>
       <c r="Z35" s="3" t="s">
         <v>0</v>
@@ -33960,13 +34451,13 @@
     </row>
     <row r="36" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>1200</v>
+        <v>1217</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>1200</v>
+        <v>1217</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D36" s="4">
         <v>46052</v>
@@ -33978,10 +34469,10 @@
         <v>61</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1152</v>
+        <v>1169</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>1151</v>
+        <v>1168</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>163</v>
@@ -33993,13 +34484,13 @@
         <v>632</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>1150</v>
+        <v>1167</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1149</v>
+        <v>1166</v>
       </c>
       <c r="O36" s="5">
         <v>507</v>
@@ -34032,7 +34523,7 @@
         <v>51</v>
       </c>
       <c r="Y36" s="2" t="s">
-        <v>1199</v>
+        <v>1216</v>
       </c>
       <c r="Z36" s="2" t="s">
         <v>0</v>
@@ -34070,13 +34561,13 @@
     </row>
     <row r="37" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>1198</v>
+        <v>1215</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>1198</v>
+        <v>1215</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D37" s="7">
         <v>46052</v>
@@ -34100,16 +34591,16 @@
         <v>164</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>1091</v>
+        <v>1116</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>1118</v>
+        <v>1135</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>1117</v>
+        <v>1134</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>1088</v>
+        <v>1113</v>
       </c>
       <c r="O37" s="8">
         <v>500</v>
@@ -34142,7 +34633,7 @@
         <v>51</v>
       </c>
       <c r="Y37" s="3" t="s">
-        <v>1197</v>
+        <v>1214</v>
       </c>
       <c r="Z37" s="3" t="s">
         <v>0</v>
@@ -34180,13 +34671,13 @@
     </row>
     <row r="38" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>1196</v>
+        <v>1213</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1196</v>
+        <v>1213</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D38" s="4">
         <v>46052</v>
@@ -34198,10 +34689,10 @@
         <v>40</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>1113</v>
+        <v>1081</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>1112</v>
+        <v>1080</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>139</v>
@@ -34213,13 +34704,13 @@
         <v>784</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>1111</v>
+        <v>1079</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>1110</v>
+        <v>1078</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>1109</v>
+        <v>1077</v>
       </c>
       <c r="O38" s="5">
         <v>300</v>
@@ -34252,7 +34743,7 @@
         <v>51</v>
       </c>
       <c r="Y38" s="2" t="s">
-        <v>1195</v>
+        <v>1212</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>0</v>
@@ -34290,13 +34781,13 @@
     </row>
     <row r="39" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>1194</v>
+        <v>1211</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>1194</v>
+        <v>1211</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D39" s="7">
         <v>46055</v>
@@ -34308,10 +34799,10 @@
         <v>212</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>1193</v>
+        <v>1210</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>1192</v>
+        <v>1209</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>139</v>
@@ -34320,7 +34811,7 @@
         <v>140</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>1191</v>
+        <v>1208</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>0</v>
@@ -34362,7 +34853,7 @@
         <v>87</v>
       </c>
       <c r="Y39" s="3" t="s">
-        <v>1190</v>
+        <v>1207</v>
       </c>
       <c r="Z39" s="3" t="s">
         <v>0</v>
@@ -34400,13 +34891,13 @@
     </row>
     <row r="40" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>1189</v>
+        <v>1206</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1189</v>
+        <v>1206</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D40" s="4">
         <v>46057</v>
@@ -34418,10 +34909,10 @@
         <v>61</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1152</v>
+        <v>1169</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>1151</v>
+        <v>1168</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>163</v>
@@ -34433,13 +34924,13 @@
         <v>632</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>1150</v>
+        <v>1167</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>1149</v>
+        <v>1166</v>
       </c>
       <c r="O40" s="5">
         <v>507</v>
@@ -34472,7 +34963,7 @@
         <v>51</v>
       </c>
       <c r="Y40" s="2" t="s">
-        <v>1188</v>
+        <v>1205</v>
       </c>
       <c r="Z40" s="2" t="s">
         <v>0</v>
@@ -34510,13 +35001,13 @@
     </row>
     <row r="41" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>1187</v>
+        <v>1204</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>1187</v>
+        <v>1204</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D41" s="7">
         <v>46057</v>
@@ -34534,22 +35025,22 @@
         <v>386</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>1155</v>
+        <v>1172</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>446</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>1159</v>
+        <v>1176</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>1158</v>
+        <v>1175</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>1124</v>
+        <v>1141</v>
       </c>
       <c r="O41" s="8">
         <v>2000</v>
@@ -34582,7 +35073,7 @@
         <v>51</v>
       </c>
       <c r="Y41" s="3" t="s">
-        <v>1154</v>
+        <v>1171</v>
       </c>
       <c r="Z41" s="3" t="s">
         <v>0</v>
@@ -34620,13 +35111,13 @@
     </row>
     <row r="42" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>1186</v>
+        <v>1203</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1186</v>
+        <v>1203</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D42" s="4">
         <v>46058</v>
@@ -34638,10 +35129,10 @@
         <v>61</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1152</v>
+        <v>1169</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>1151</v>
+        <v>1168</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>163</v>
@@ -34653,13 +35144,13 @@
         <v>632</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>1150</v>
+        <v>1167</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>1149</v>
+        <v>1166</v>
       </c>
       <c r="O42" s="5">
         <v>507</v>
@@ -34692,7 +35183,7 @@
         <v>51</v>
       </c>
       <c r="Y42" s="2" t="s">
-        <v>1185</v>
+        <v>1202</v>
       </c>
       <c r="Z42" s="2" t="s">
         <v>0</v>
@@ -34730,13 +35221,13 @@
     </row>
     <row r="43" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>1184</v>
+        <v>1201</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>1184</v>
+        <v>1201</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D43" s="7">
         <v>46058</v>
@@ -34748,10 +35239,10 @@
         <v>61</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>1121</v>
+        <v>1138</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>1120</v>
+        <v>1137</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>163</v>
@@ -34763,13 +35254,13 @@
         <v>417</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>1175</v>
+        <v>1192</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>1174</v>
+        <v>1191</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>1173</v>
+        <v>1190</v>
       </c>
       <c r="O43" s="8">
         <v>1800</v>
@@ -34802,7 +35293,7 @@
         <v>51</v>
       </c>
       <c r="Y43" s="3" t="s">
-        <v>1183</v>
+        <v>1200</v>
       </c>
       <c r="Z43" s="3" t="s">
         <v>0</v>
@@ -34840,13 +35331,13 @@
     </row>
     <row r="44" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>1182</v>
+        <v>1199</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>1182</v>
+        <v>1199</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D44" s="4">
         <v>46059</v>
@@ -34858,10 +35349,10 @@
         <v>40</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1181</v>
+        <v>1198</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>1180</v>
+        <v>1197</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>43</v>
@@ -34873,13 +35364,13 @@
         <v>784</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>1111</v>
+        <v>1079</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>1110</v>
+        <v>1078</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>1109</v>
+        <v>1077</v>
       </c>
       <c r="O44" s="5">
         <v>500</v>
@@ -34912,7 +35403,7 @@
         <v>51</v>
       </c>
       <c r="Y44" s="2" t="s">
-        <v>1179</v>
+        <v>1196</v>
       </c>
       <c r="Z44" s="2" t="s">
         <v>0</v>
@@ -34950,13 +35441,13 @@
     </row>
     <row r="45" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>1178</v>
+        <v>1195</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>1178</v>
+        <v>1195</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D45" s="7">
         <v>46059</v>
@@ -34968,10 +35459,10 @@
         <v>40</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>1177</v>
+        <v>1194</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>1176</v>
+        <v>1193</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>43</v>
@@ -34983,13 +35474,13 @@
         <v>417</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>1175</v>
+        <v>1192</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>1174</v>
+        <v>1191</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>1173</v>
+        <v>1190</v>
       </c>
       <c r="O45" s="8">
         <v>200</v>
@@ -35022,7 +35513,7 @@
         <v>51</v>
       </c>
       <c r="Y45" s="3" t="s">
-        <v>1172</v>
+        <v>1189</v>
       </c>
       <c r="Z45" s="3" t="s">
         <v>0</v>
@@ -35060,28 +35551,28 @@
     </row>
     <row r="46" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>1171</v>
+        <v>1188</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1171</v>
+        <v>1188</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D46" s="4">
         <v>46063</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1170</v>
+        <v>1187</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>267</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1169</v>
+        <v>1186</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>1168</v>
+        <v>1185</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>139</v>
@@ -35090,7 +35581,7 @@
         <v>140</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>1068</v>
+        <v>1094</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>0</v>
@@ -35132,7 +35623,7 @@
         <v>0</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>1167</v>
+        <v>1184</v>
       </c>
       <c r="Z46" s="2" t="s">
         <v>0</v>
@@ -35147,10 +35638,10 @@
         <v>74</v>
       </c>
       <c r="AD46" s="2" t="s">
-        <v>1066</v>
+        <v>1092</v>
       </c>
       <c r="AE46" s="2" t="s">
-        <v>1065</v>
+        <v>1091</v>
       </c>
       <c r="AF46" s="2" t="s">
         <v>0</v>
@@ -35170,13 +35661,13 @@
     </row>
     <row r="47" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>1166</v>
+        <v>1183</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>1166</v>
+        <v>1183</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D47" s="7">
         <v>46064</v>
@@ -35188,10 +35679,10 @@
         <v>61</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>1165</v>
+        <v>1182</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>1164</v>
+        <v>1181</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>139</v>
@@ -35203,13 +35694,13 @@
         <v>417</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>1163</v>
+        <v>1180</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>1162</v>
+        <v>1179</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="O47" s="8">
         <v>1000</v>
@@ -35242,7 +35733,7 @@
         <v>51</v>
       </c>
       <c r="Y47" s="3" t="s">
-        <v>1160</v>
+        <v>1177</v>
       </c>
       <c r="Z47" s="3" t="s">
         <v>0</v>
@@ -35280,13 +35771,13 @@
     </row>
     <row r="48" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D48" s="4">
         <v>46064</v>
@@ -35304,22 +35795,22 @@
         <v>386</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>1155</v>
+        <v>1172</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>446</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>1159</v>
+        <v>1176</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>1158</v>
+        <v>1175</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>1124</v>
+        <v>1141</v>
       </c>
       <c r="O48" s="5">
         <v>1000</v>
@@ -35352,7 +35843,7 @@
         <v>51</v>
       </c>
       <c r="Y48" s="2" t="s">
-        <v>1154</v>
+        <v>1171</v>
       </c>
       <c r="Z48" s="2" t="s">
         <v>0</v>
@@ -35390,13 +35881,13 @@
     </row>
     <row r="49" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D49" s="7">
         <v>46064</v>
@@ -35414,22 +35905,22 @@
         <v>386</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>1155</v>
+        <v>1172</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>446</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>1126</v>
+        <v>1143</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>1125</v>
+        <v>1142</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>1124</v>
+        <v>1141</v>
       </c>
       <c r="O49" s="8">
         <v>1000</v>
@@ -35462,7 +35953,7 @@
         <v>51</v>
       </c>
       <c r="Y49" s="3" t="s">
-        <v>1154</v>
+        <v>1171</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>0</v>
@@ -35500,13 +35991,13 @@
     </row>
     <row r="50" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>1153</v>
+        <v>1170</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>1153</v>
+        <v>1170</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D50" s="4">
         <v>46066</v>
@@ -35518,10 +36009,10 @@
         <v>61</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1152</v>
+        <v>1169</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>1151</v>
+        <v>1168</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>163</v>
@@ -35533,13 +36024,13 @@
         <v>632</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>1150</v>
+        <v>1167</v>
       </c>
       <c r="M50" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>1149</v>
+        <v>1166</v>
       </c>
       <c r="O50" s="5">
         <v>507</v>
@@ -35572,7 +36063,7 @@
         <v>51</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>1148</v>
+        <v>1165</v>
       </c>
       <c r="Z50" s="2" t="s">
         <v>0</v>
@@ -35610,13 +36101,13 @@
     </row>
     <row r="51" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>1147</v>
+        <v>1164</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>1147</v>
+        <v>1164</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D51" s="7">
         <v>46071</v>
@@ -35640,16 +36131,16 @@
         <v>164</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>1086</v>
+        <v>1111</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>1146</v>
+        <v>1163</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>1145</v>
+        <v>1162</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>1144</v>
+        <v>1161</v>
       </c>
       <c r="O51" s="8">
         <v>500</v>
@@ -35682,7 +36173,7 @@
         <v>51</v>
       </c>
       <c r="Y51" s="3" t="s">
-        <v>1143</v>
+        <v>1160</v>
       </c>
       <c r="Z51" s="3" t="s">
         <v>0</v>
@@ -35697,10 +36188,10 @@
         <v>111</v>
       </c>
       <c r="AD51" s="3" t="s">
-        <v>1081</v>
+        <v>1106</v>
       </c>
       <c r="AE51" s="3" t="s">
-        <v>1080</v>
+        <v>1105</v>
       </c>
       <c r="AF51" s="3" t="s">
         <v>77</v>
@@ -35720,13 +36211,13 @@
     </row>
     <row r="52" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>1142</v>
+        <v>1159</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1142</v>
+        <v>1159</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D52" s="4">
         <v>46071</v>
@@ -35738,10 +36229,10 @@
         <v>61</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1141</v>
+        <v>1158</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>1140</v>
+        <v>1157</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>139</v>
@@ -35753,13 +36244,13 @@
         <v>446</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>1126</v>
+        <v>1143</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>1125</v>
+        <v>1142</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>1124</v>
+        <v>1141</v>
       </c>
       <c r="O52" s="5">
         <v>200</v>
@@ -35792,7 +36283,7 @@
         <v>51</v>
       </c>
       <c r="Y52" s="2" t="s">
-        <v>1139</v>
+        <v>1156</v>
       </c>
       <c r="Z52" s="2" t="s">
         <v>0</v>
@@ -35830,13 +36321,13 @@
     </row>
     <row r="53" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>1138</v>
+        <v>1155</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>1138</v>
+        <v>1155</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D53" s="7">
         <v>46072</v>
@@ -35848,10 +36339,10 @@
         <v>40</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>1070</v>
+        <v>1096</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>1069</v>
+        <v>1095</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>43</v>
@@ -35863,13 +36354,13 @@
         <v>440</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>1137</v>
+        <v>1154</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>1136</v>
+        <v>1153</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>1135</v>
+        <v>1152</v>
       </c>
       <c r="O53" s="8">
         <v>50</v>
@@ -35893,16 +36384,16 @@
         <v>0</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>1134</v>
+        <v>1151</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>1133</v>
+        <v>1150</v>
       </c>
       <c r="X53" s="3" t="s">
         <v>51</v>
       </c>
       <c r="Y53" s="3" t="s">
-        <v>1132</v>
+        <v>1149</v>
       </c>
       <c r="Z53" s="3" t="s">
         <v>0</v>
@@ -35940,13 +36431,13 @@
     </row>
     <row r="54" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>1131</v>
+        <v>1148</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1131</v>
+        <v>1148</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D54" s="4">
         <v>46072</v>
@@ -35958,10 +36449,10 @@
         <v>61</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1121</v>
+        <v>1138</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>1120</v>
+        <v>1137</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>163</v>
@@ -35973,13 +36464,13 @@
         <v>417</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>1106</v>
+        <v>1128</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>1105</v>
+        <v>1127</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>1104</v>
+        <v>1087</v>
       </c>
       <c r="O54" s="5">
         <v>1600</v>
@@ -36012,7 +36503,7 @@
         <v>51</v>
       </c>
       <c r="Y54" s="2" t="s">
-        <v>1130</v>
+        <v>1147</v>
       </c>
       <c r="Z54" s="2" t="s">
         <v>0</v>
@@ -36050,13 +36541,13 @@
     </row>
     <row r="55" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>1129</v>
+        <v>1146</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>1129</v>
+        <v>1146</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D55" s="7">
         <v>46072</v>
@@ -36068,10 +36559,10 @@
         <v>40</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>1128</v>
+        <v>1145</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>1127</v>
+        <v>1144</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>43</v>
@@ -36083,13 +36574,13 @@
         <v>446</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>1126</v>
+        <v>1143</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>1125</v>
+        <v>1142</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>1124</v>
+        <v>1141</v>
       </c>
       <c r="O55" s="8">
         <v>500</v>
@@ -36122,7 +36613,7 @@
         <v>51</v>
       </c>
       <c r="Y55" s="3" t="s">
-        <v>1123</v>
+        <v>1140</v>
       </c>
       <c r="Z55" s="3" t="s">
         <v>0</v>
@@ -36160,13 +36651,13 @@
     </row>
     <row r="56" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>1122</v>
+        <v>1139</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1122</v>
+        <v>1139</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D56" s="4">
         <v>46076</v>
@@ -36178,10 +36669,10 @@
         <v>61</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1121</v>
+        <v>1138</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>1120</v>
+        <v>1137</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>163</v>
@@ -36193,13 +36684,13 @@
         <v>417</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>1106</v>
+        <v>1128</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>1105</v>
+        <v>1127</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>1104</v>
+        <v>1087</v>
       </c>
       <c r="O56" s="5">
         <v>1700</v>
@@ -36232,7 +36723,7 @@
         <v>51</v>
       </c>
       <c r="Y56" s="2" t="s">
-        <v>1119</v>
+        <v>1136</v>
       </c>
       <c r="Z56" s="2" t="s">
         <v>0</v>
@@ -36270,13 +36761,13 @@
     </row>
     <row r="57" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>1116</v>
+        <v>1133</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>1116</v>
+        <v>1133</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D57" s="7">
         <v>46077</v>
@@ -36300,16 +36791,16 @@
         <v>164</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>1091</v>
+        <v>1116</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>1118</v>
+        <v>1135</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>1117</v>
+        <v>1134</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>1088</v>
+        <v>1113</v>
       </c>
       <c r="O57" s="8">
         <v>500</v>
@@ -36342,7 +36833,7 @@
         <v>51</v>
       </c>
       <c r="Y57" s="3" t="s">
-        <v>1115</v>
+        <v>1132</v>
       </c>
       <c r="Z57" s="3" t="s">
         <v>0</v>
@@ -36380,13 +36871,13 @@
     </row>
     <row r="58" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>1116</v>
+        <v>1133</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1116</v>
+        <v>1133</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D58" s="4">
         <v>46077</v>
@@ -36410,16 +36901,16 @@
         <v>164</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>1086</v>
+        <v>1111</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>1085</v>
+        <v>1110</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>1084</v>
+        <v>1109</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>1083</v>
+        <v>1108</v>
       </c>
       <c r="O58" s="5">
         <v>500</v>
@@ -36452,7 +36943,7 @@
         <v>51</v>
       </c>
       <c r="Y58" s="2" t="s">
-        <v>1115</v>
+        <v>1132</v>
       </c>
       <c r="Z58" s="2" t="s">
         <v>0</v>
@@ -36467,10 +36958,10 @@
         <v>111</v>
       </c>
       <c r="AD58" s="2" t="s">
-        <v>1081</v>
+        <v>1106</v>
       </c>
       <c r="AE58" s="2" t="s">
-        <v>1080</v>
+        <v>1105</v>
       </c>
       <c r="AF58" s="2" t="s">
         <v>77</v>
@@ -36490,13 +36981,13 @@
     </row>
     <row r="59" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>1114</v>
+        <v>1131</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>1114</v>
+        <v>1131</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D59" s="7">
         <v>46078</v>
@@ -36508,10 +36999,10 @@
         <v>40</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>1113</v>
+        <v>1081</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>1112</v>
+        <v>1080</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>139</v>
@@ -36523,13 +37014,13 @@
         <v>784</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>1111</v>
+        <v>1079</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>1110</v>
+        <v>1078</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>1109</v>
+        <v>1077</v>
       </c>
       <c r="O59" s="8">
         <v>225</v>
@@ -36562,7 +37053,7 @@
         <v>51</v>
       </c>
       <c r="Y59" s="3" t="s">
-        <v>1108</v>
+        <v>1130</v>
       </c>
       <c r="Z59" s="3" t="s">
         <v>0</v>
@@ -36600,13 +37091,13 @@
     </row>
     <row r="60" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>1107</v>
+        <v>1129</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1107</v>
+        <v>1129</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D60" s="4">
         <v>46079</v>
@@ -36633,13 +37124,13 @@
         <v>417</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>1106</v>
+        <v>1128</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>1105</v>
+        <v>1127</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>1104</v>
+        <v>1087</v>
       </c>
       <c r="O60" s="5">
         <v>5000</v>
@@ -36663,16 +37154,16 @@
         <v>2354</v>
       </c>
       <c r="V60" s="2" t="s">
-        <v>1103</v>
+        <v>1086</v>
       </c>
       <c r="W60" s="2" t="s">
-        <v>1102</v>
+        <v>1085</v>
       </c>
       <c r="X60" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Y60" s="2" t="s">
-        <v>1101</v>
+        <v>1126</v>
       </c>
       <c r="Z60" s="2" t="s">
         <v>0</v>
@@ -36710,13 +37201,13 @@
     </row>
     <row r="61" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>1100</v>
+        <v>1125</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>1100</v>
+        <v>1125</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D61" s="7">
         <v>46079</v>
@@ -36743,13 +37234,13 @@
         <v>1060</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>1099</v>
+        <v>1124</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>1098</v>
+        <v>1123</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>1097</v>
+        <v>1122</v>
       </c>
       <c r="O61" s="8">
         <v>12000</v>
@@ -36782,7 +37273,7 @@
         <v>51</v>
       </c>
       <c r="Y61" s="3" t="s">
-        <v>1096</v>
+        <v>1121</v>
       </c>
       <c r="Z61" s="3" t="s">
         <v>0</v>
@@ -36820,13 +37311,13 @@
     </row>
     <row r="62" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>1095</v>
+        <v>1120</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1095</v>
+        <v>1120</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D62" s="4">
         <v>46085</v>
@@ -36853,13 +37344,13 @@
         <v>633</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>1094</v>
+        <v>1119</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>652</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>1093</v>
+        <v>1118</v>
       </c>
       <c r="O62" s="5">
         <v>5005</v>
@@ -36892,7 +37383,7 @@
         <v>51</v>
       </c>
       <c r="Y62" s="2" t="s">
-        <v>1092</v>
+        <v>1117</v>
       </c>
       <c r="Z62" s="2" t="s">
         <v>0</v>
@@ -36930,13 +37421,13 @@
     </row>
     <row r="63" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>1087</v>
+        <v>1112</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>1087</v>
+        <v>1112</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D63" s="7">
         <v>46085</v>
@@ -36960,16 +37451,16 @@
         <v>164</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>1091</v>
+        <v>1116</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>1090</v>
+        <v>1115</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>1089</v>
+        <v>1114</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>1088</v>
+        <v>1113</v>
       </c>
       <c r="O63" s="8">
         <v>500</v>
@@ -37002,7 +37493,7 @@
         <v>51</v>
       </c>
       <c r="Y63" s="3" t="s">
-        <v>1082</v>
+        <v>1107</v>
       </c>
       <c r="Z63" s="3" t="s">
         <v>0</v>
@@ -37040,13 +37531,13 @@
     </row>
     <row r="64" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>1087</v>
+        <v>1112</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1087</v>
+        <v>1112</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D64" s="4">
         <v>46085</v>
@@ -37070,16 +37561,16 @@
         <v>164</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>1086</v>
+        <v>1111</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>1085</v>
+        <v>1110</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>1084</v>
+        <v>1109</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>1083</v>
+        <v>1108</v>
       </c>
       <c r="O64" s="5">
         <v>500</v>
@@ -37112,7 +37603,7 @@
         <v>51</v>
       </c>
       <c r="Y64" s="2" t="s">
-        <v>1082</v>
+        <v>1107</v>
       </c>
       <c r="Z64" s="2" t="s">
         <v>0</v>
@@ -37127,10 +37618,10 @@
         <v>111</v>
       </c>
       <c r="AD64" s="2" t="s">
-        <v>1081</v>
+        <v>1106</v>
       </c>
       <c r="AE64" s="2" t="s">
-        <v>1080</v>
+        <v>1105</v>
       </c>
       <c r="AF64" s="2" t="s">
         <v>77</v>
@@ -37150,13 +37641,13 @@
     </row>
     <row r="65" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>1079</v>
+        <v>1104</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>1079</v>
+        <v>1104</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D65" s="7">
         <v>46085</v>
@@ -37168,10 +37659,10 @@
         <v>40</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>1078</v>
+        <v>1103</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>1077</v>
+        <v>1102</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>163</v>
@@ -37183,13 +37674,13 @@
         <v>154</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>1076</v>
+        <v>1101</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>1075</v>
+        <v>1100</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>1074</v>
+        <v>1099</v>
       </c>
       <c r="O65" s="8">
         <v>3700</v>
@@ -37222,7 +37713,7 @@
         <v>51</v>
       </c>
       <c r="Y65" s="3" t="s">
-        <v>1073</v>
+        <v>1098</v>
       </c>
       <c r="Z65" s="3" t="s">
         <v>0</v>
@@ -37260,13 +37751,13 @@
     </row>
     <row r="66" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>1072</v>
+        <v>1097</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1072</v>
+        <v>1097</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D66" s="4">
         <v>46085</v>
@@ -37278,10 +37769,10 @@
         <v>40</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1070</v>
+        <v>1096</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>1069</v>
+        <v>1095</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>139</v>
@@ -37290,7 +37781,7 @@
         <v>140</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>1068</v>
+        <v>1094</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>0</v>
@@ -37332,7 +37823,7 @@
         <v>0</v>
       </c>
       <c r="Y66" s="2" t="s">
-        <v>1067</v>
+        <v>1093</v>
       </c>
       <c r="Z66" s="2" t="s">
         <v>0</v>
@@ -37347,10 +37838,10 @@
         <v>298</v>
       </c>
       <c r="AD66" s="2" t="s">
-        <v>1066</v>
+        <v>1092</v>
       </c>
       <c r="AE66" s="2" t="s">
-        <v>1065</v>
+        <v>1091</v>
       </c>
       <c r="AF66" s="2" t="s">
         <v>0</v>
@@ -37366,6 +37857,226 @@
       </c>
       <c r="AJ66" s="5">
         <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="3" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D67" s="7">
+        <v>46091</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>1089</v>
+      </c>
+      <c r="M67" s="3" t="s">
+        <v>1088</v>
+      </c>
+      <c r="N67" s="3" t="s">
+        <v>1087</v>
+      </c>
+      <c r="O67" s="8">
+        <v>5000</v>
+      </c>
+      <c r="P67" s="8">
+        <v>11.77</v>
+      </c>
+      <c r="Q67" s="9">
+        <v>58850</v>
+      </c>
+      <c r="R67" s="9">
+        <v>1912.63</v>
+      </c>
+      <c r="S67" s="9">
+        <v>60762.63</v>
+      </c>
+      <c r="T67" s="9">
+        <v>58850</v>
+      </c>
+      <c r="U67" s="9">
+        <v>2354</v>
+      </c>
+      <c r="V67" s="3" t="s">
+        <v>1086</v>
+      </c>
+      <c r="W67" s="3" t="s">
+        <v>1085</v>
+      </c>
+      <c r="X67" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y67" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="Z67" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA67" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB67" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="AC67" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="AD67" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE67" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF67" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG67" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH67" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI67" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ67" s="8">
+        <v>48943.45</v>
+      </c>
+    </row>
+    <row r="68" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D68" s="4">
+        <v>46091</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="O68" s="5">
+        <v>225</v>
+      </c>
+      <c r="P68" s="5">
+        <v>12.25</v>
+      </c>
+      <c r="Q68" s="6">
+        <v>2756.25</v>
+      </c>
+      <c r="R68" s="6">
+        <v>89.58</v>
+      </c>
+      <c r="S68" s="6">
+        <v>2845.83</v>
+      </c>
+      <c r="T68" s="6">
+        <v>2756.25</v>
+      </c>
+      <c r="U68" s="6">
+        <v>110.25</v>
+      </c>
+      <c r="V68" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="W68" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="X68" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y68" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="Z68" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB68" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC68" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD68" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE68" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF68" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG68" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ68" s="5">
+        <v>2225.1802499999999</v>
       </c>
     </row>
   </sheetData>

--- a/BASE_KEMPARTS.xlsx
+++ b/BASE_KEMPARTS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dash_kp_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97583B37-DC83-4DD0-9F4C-6CDFE6B33DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4411F3B8-10E0-4D1D-BC04-9B36A6AE8EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{CB469FB5-CC63-49DF-8F0A-CC2C928DC074}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{54047E8A-2573-47AA-9902-914A4DC7D30A}"/>
   </bookViews>
   <sheets>
     <sheet name="FSP" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7547" uniqueCount="1305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7722" uniqueCount="1325">
   <si>
     <t/>
   </si>
@@ -3251,6 +3251,102 @@
     <t>153309</t>
   </si>
   <si>
+    <t>000015554</t>
+  </si>
+  <si>
+    <t>173734</t>
+  </si>
+  <si>
+    <t>000015555</t>
+  </si>
+  <si>
+    <t>T00166</t>
+  </si>
+  <si>
+    <t>IBERICO TRANSPORTES E LOGISTICA EIRELI</t>
+  </si>
+  <si>
+    <t>173852</t>
+  </si>
+  <si>
+    <t>000015556</t>
+  </si>
+  <si>
+    <t>C00481</t>
+  </si>
+  <si>
+    <t>FLEXCOR TINTAS EIRELLI</t>
+  </si>
+  <si>
+    <t>T00151</t>
+  </si>
+  <si>
+    <t>LUSEANNA TRANSP ARMAZ LTDA</t>
+  </si>
+  <si>
+    <t>173853</t>
+  </si>
+  <si>
+    <t>003309</t>
+  </si>
+  <si>
+    <t>TRANSPARE TRANSPORTES ARMAZENS GERAIS LT</t>
+  </si>
+  <si>
+    <t>T00258</t>
+  </si>
+  <si>
+    <t>2024.357.04.</t>
+  </si>
+  <si>
+    <t>240706</t>
+  </si>
+  <si>
+    <t>2024.357.04.240706</t>
+  </si>
+  <si>
+    <t>KEMPARTS COMERCIO INTERNACIONAL DE PRODU</t>
+  </si>
+  <si>
+    <t>C00001</t>
+  </si>
+  <si>
+    <t>TRANSFERENCIA DE MERC. ADQUIRIDA/RECEBIDA DE TERCEIROS</t>
+  </si>
+  <si>
+    <t>6152</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>000002511</t>
+  </si>
+  <si>
+    <t>2025.357.05.</t>
+  </si>
+  <si>
+    <t>20250903</t>
+  </si>
+  <si>
+    <t>2025.357.05.20250903</t>
+  </si>
+  <si>
+    <t>2025.004.01.</t>
+  </si>
+  <si>
+    <t>25021048</t>
+  </si>
+  <si>
+    <t>2025.004.01.25021048</t>
+  </si>
+  <si>
+    <t>2024.004.14.</t>
+  </si>
+  <si>
+    <t>2024.004.14.24121064</t>
+  </si>
+  <si>
     <t>003301</t>
   </si>
   <si>
@@ -3269,9 +3365,6 @@
     <t>C00341</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>000002510</t>
   </si>
   <si>
@@ -3284,15 +3377,6 @@
     <t>T00213</t>
   </si>
   <si>
-    <t>2025.004.01.</t>
-  </si>
-  <si>
-    <t>25021048</t>
-  </si>
-  <si>
-    <t>2025.004.01.25021048</t>
-  </si>
-  <si>
     <t>000002509</t>
   </si>
   <si>
@@ -3578,12 +3662,6 @@
     <t>003257</t>
   </si>
   <si>
-    <t>KEMPARTS COMERCIO INTERNACIONAL DE PRODU</t>
-  </si>
-  <si>
-    <t>C00001</t>
-  </si>
-  <si>
     <t>6101</t>
   </si>
   <si>
@@ -3593,9 +3671,6 @@
     <t>003253</t>
   </si>
   <si>
-    <t>2024.004.14.</t>
-  </si>
-  <si>
     <t>24121037</t>
   </si>
   <si>
@@ -3650,9 +3725,6 @@
     <t>CH 332</t>
   </si>
   <si>
-    <t>TRANSPARE TRANSPORTES ARMAZENS GERAIS LT</t>
-  </si>
-  <si>
     <t>F00813</t>
   </si>
   <si>
@@ -3749,9 +3821,6 @@
     <t>003219</t>
   </si>
   <si>
-    <t>T00258</t>
-  </si>
-  <si>
     <t>2025.435.</t>
   </si>
   <si>
@@ -3761,12 +3830,6 @@
     <t>2025.435.030001006106</t>
   </si>
   <si>
-    <t>TRANSFERENCIA DE MERC. ADQUIRIDA/RECEBIDA DE TERCEIROS</t>
-  </si>
-  <si>
-    <t>6152</t>
-  </si>
-  <si>
     <t>000002456</t>
   </si>
   <si>
@@ -3876,9 +3939,6 @@
   </si>
   <si>
     <t>003200</t>
-  </si>
-  <si>
-    <t>2025.357.05.</t>
   </si>
   <si>
     <t>250501</t>
@@ -4882,8 +4942,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B26A77ED-7CEE-4E89-8BE8-34DC8758E529}">
-  <dimension ref="A1:AJ233"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91811D7F-73CA-4BD0-A771-919B24F863E7}">
+  <dimension ref="A1:AJ236"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -30553,14 +30613,344 @@
         <v>9.8208099999999998</v>
       </c>
     </row>
+    <row r="234" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A234" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D234" s="4">
+        <v>46092</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F234" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G234" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="H234" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I234" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="J234" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="K234" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L234" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="M234" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="N234" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="O234" s="5">
+        <v>370</v>
+      </c>
+      <c r="P234" s="5">
+        <v>25.75</v>
+      </c>
+      <c r="Q234" s="6">
+        <v>9527.5</v>
+      </c>
+      <c r="R234" s="6">
+        <v>309.64</v>
+      </c>
+      <c r="S234" s="6">
+        <v>9837.14</v>
+      </c>
+      <c r="T234" s="6">
+        <v>9527.5</v>
+      </c>
+      <c r="U234" s="6">
+        <v>381.1</v>
+      </c>
+      <c r="V234" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="W234" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="X234" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y234" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="Z234" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA234" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB234" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC234" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="AD234" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE234" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF234" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG234" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH234" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI234" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ234" s="5">
+        <v>4912.8082000000004</v>
+      </c>
+    </row>
+    <row r="235" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A235" s="3" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D235" s="7">
+        <v>46092</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F235" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G235" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="H235" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I235" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J235" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="K235" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="L235" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="M235" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="N235" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="O235" s="8">
+        <v>14800</v>
+      </c>
+      <c r="P235" s="8">
+        <v>12.23531</v>
+      </c>
+      <c r="Q235" s="9">
+        <v>181082.59</v>
+      </c>
+      <c r="R235" s="9">
+        <v>0</v>
+      </c>
+      <c r="S235" s="9">
+        <v>181082.59</v>
+      </c>
+      <c r="T235" s="9">
+        <v>0</v>
+      </c>
+      <c r="U235" s="9">
+        <v>0</v>
+      </c>
+      <c r="V235" s="3" t="s">
+        <v>1079</v>
+      </c>
+      <c r="W235" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="X235" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y235" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="Z235" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA235" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB235" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC235" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD235" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE235" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF235" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG235" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH235" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI235" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ235" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A236" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D236" s="4">
+        <v>46092</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F236" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G236" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="H236" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="I236" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="J236" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="K236" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="L236" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="M236" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="N236" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="O236" s="5">
+        <v>1000</v>
+      </c>
+      <c r="P236" s="5">
+        <v>15.02</v>
+      </c>
+      <c r="Q236" s="6">
+        <v>15020</v>
+      </c>
+      <c r="R236" s="6">
+        <v>488.15</v>
+      </c>
+      <c r="S236" s="6">
+        <v>15508.15</v>
+      </c>
+      <c r="T236" s="6">
+        <v>15020</v>
+      </c>
+      <c r="U236" s="6">
+        <v>600.79999999999995</v>
+      </c>
+      <c r="V236" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="W236" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="X236" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y236" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="Z236" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA236" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB236" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC236" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AD236" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE236" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF236" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG236" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH236" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI236" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ236" s="5">
+        <v>10341.27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49746817-01A4-4A9C-9061-C45AA702B917}">
-  <dimension ref="A1:AJ68"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C7F5C9F-1B8B-4223-BCB6-9F8E23135EC6}">
+  <dimension ref="A1:AJ72"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -30711,13 +31101,13 @@
     </row>
     <row r="2" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>1304</v>
+        <v>1324</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1304</v>
+        <v>1324</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D2" s="4">
         <v>46024</v>
@@ -30729,10 +31119,10 @@
         <v>40</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1096</v>
+        <v>1124</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>1095</v>
+        <v>1123</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>43</v>
@@ -30744,13 +31134,13 @@
         <v>440</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>1154</v>
+        <v>1182</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>1153</v>
+        <v>1181</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>1152</v>
+        <v>1180</v>
       </c>
       <c r="O2" s="5">
         <v>50</v>
@@ -30774,16 +31164,16 @@
         <v>39.06</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>1151</v>
+        <v>1179</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>1150</v>
+        <v>1178</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>1303</v>
+        <v>1323</v>
       </c>
       <c r="Z2" s="2" t="s">
         <v>0</v>
@@ -30821,13 +31211,13 @@
     </row>
     <row r="3" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>1302</v>
+        <v>1322</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1302</v>
+        <v>1322</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D3" s="7">
         <v>46027</v>
@@ -30839,10 +31229,10 @@
         <v>61</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1169</v>
+        <v>1197</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1168</v>
+        <v>1196</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>163</v>
@@ -30854,13 +31244,13 @@
         <v>632</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1167</v>
+        <v>1195</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>648</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>1166</v>
+        <v>1194</v>
       </c>
       <c r="O3" s="8">
         <v>1001</v>
@@ -30893,7 +31283,7 @@
         <v>51</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>1301</v>
+        <v>1321</v>
       </c>
       <c r="Z3" s="3" t="s">
         <v>0</v>
@@ -30931,13 +31321,13 @@
     </row>
     <row r="4" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>1300</v>
+        <v>1320</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1300</v>
+        <v>1320</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D4" s="4">
         <v>46027</v>
@@ -30949,10 +31339,10 @@
         <v>61</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1299</v>
+        <v>1319</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1298</v>
+        <v>1318</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>152</v>
@@ -30964,13 +31354,13 @@
         <v>342</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1297</v>
+        <v>1317</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1296</v>
+        <v>1316</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1295</v>
+        <v>1315</v>
       </c>
       <c r="O4" s="5">
         <v>600</v>
@@ -30994,16 +31384,16 @@
         <v>355.68</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>1294</v>
+        <v>1314</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>1293</v>
+        <v>1313</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>1292</v>
+        <v>1312</v>
       </c>
       <c r="Z4" s="2" t="s">
         <v>0</v>
@@ -31041,13 +31431,13 @@
     </row>
     <row r="5" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>1291</v>
+        <v>1311</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1291</v>
+        <v>1311</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D5" s="7">
         <v>46029</v>
@@ -31059,10 +31449,10 @@
         <v>212</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>1210</v>
+        <v>1234</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1209</v>
+        <v>1089</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>139</v>
@@ -31071,7 +31461,7 @@
         <v>140</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>1290</v>
+        <v>1310</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>0</v>
@@ -31113,7 +31503,7 @@
         <v>87</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>1289</v>
+        <v>1309</v>
       </c>
       <c r="Z5" s="3" t="s">
         <v>0</v>
@@ -31151,13 +31541,13 @@
     </row>
     <row r="6" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>1291</v>
+        <v>1311</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1291</v>
+        <v>1311</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D6" s="4">
         <v>46029</v>
@@ -31169,10 +31559,10 @@
         <v>212</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1210</v>
+        <v>1234</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1209</v>
+        <v>1089</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>139</v>
@@ -31181,7 +31571,7 @@
         <v>140</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>1290</v>
+        <v>1310</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>0</v>
@@ -31223,7 +31613,7 @@
         <v>87</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>1289</v>
+        <v>1309</v>
       </c>
       <c r="Z6" s="2" t="s">
         <v>0</v>
@@ -31261,13 +31651,13 @@
     </row>
     <row r="7" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>1288</v>
+        <v>1308</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1288</v>
+        <v>1308</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D7" s="7">
         <v>46029</v>
@@ -31285,22 +31675,22 @@
         <v>386</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>1173</v>
+        <v>1201</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>1172</v>
+        <v>1200</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>1060</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>1287</v>
+        <v>1307</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>1286</v>
+        <v>1306</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>1285</v>
+        <v>1100</v>
       </c>
       <c r="O7" s="8">
         <v>1000</v>
@@ -31333,7 +31723,7 @@
         <v>51</v>
       </c>
       <c r="Y7" s="3" t="s">
-        <v>1284</v>
+        <v>1305</v>
       </c>
       <c r="Z7" s="3" t="s">
         <v>0</v>
@@ -31371,13 +31761,13 @@
     </row>
     <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>1283</v>
+        <v>1304</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1283</v>
+        <v>1304</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D8" s="4">
         <v>46036</v>
@@ -31389,10 +31779,10 @@
         <v>61</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1169</v>
+        <v>1197</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>1168</v>
+        <v>1196</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>163</v>
@@ -31404,13 +31794,13 @@
         <v>632</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>1167</v>
+        <v>1195</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1166</v>
+        <v>1194</v>
       </c>
       <c r="O8" s="5">
         <v>1001</v>
@@ -31443,7 +31833,7 @@
         <v>51</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>1282</v>
+        <v>1303</v>
       </c>
       <c r="Z8" s="2" t="s">
         <v>0</v>
@@ -31481,13 +31871,13 @@
     </row>
     <row r="9" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>1281</v>
+        <v>1302</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1281</v>
+        <v>1302</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D9" s="7">
         <v>46037</v>
@@ -31499,10 +31889,10 @@
         <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>1182</v>
+        <v>1210</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1181</v>
+        <v>1209</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>163</v>
@@ -31514,13 +31904,13 @@
         <v>417</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>1280</v>
+        <v>1301</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>1043</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>1178</v>
+        <v>1206</v>
       </c>
       <c r="O9" s="8">
         <v>1000</v>
@@ -31553,7 +31943,7 @@
         <v>51</v>
       </c>
       <c r="Y9" s="3" t="s">
-        <v>1279</v>
+        <v>1300</v>
       </c>
       <c r="Z9" s="3" t="s">
         <v>0</v>
@@ -31591,13 +31981,13 @@
     </row>
     <row r="10" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>1278</v>
+        <v>1299</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1278</v>
+        <v>1299</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D10" s="4">
         <v>46037</v>
@@ -31609,10 +31999,10 @@
         <v>40</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1081</v>
+        <v>1113</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1080</v>
+        <v>1112</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>139</v>
@@ -31624,13 +32014,13 @@
         <v>784</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>1079</v>
+        <v>1111</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1078</v>
+        <v>1110</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1077</v>
+        <v>1109</v>
       </c>
       <c r="O10" s="5">
         <v>300</v>
@@ -31663,7 +32053,7 @@
         <v>51</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>1277</v>
+        <v>1298</v>
       </c>
       <c r="Z10" s="2" t="s">
         <v>0</v>
@@ -31701,13 +32091,13 @@
     </row>
     <row r="11" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>1276</v>
+        <v>1297</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1276</v>
+        <v>1297</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D11" s="7">
         <v>46037</v>
@@ -31719,10 +32109,10 @@
         <v>40</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>1220</v>
+        <v>1244</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1219</v>
+        <v>1243</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>43</v>
@@ -31734,13 +32124,13 @@
         <v>300</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>1275</v>
+        <v>1296</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>1274</v>
+        <v>1295</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="O11" s="8">
         <v>25</v>
@@ -31773,7 +32163,7 @@
         <v>51</v>
       </c>
       <c r="Y11" s="3" t="s">
-        <v>1272</v>
+        <v>1293</v>
       </c>
       <c r="Z11" s="3" t="s">
         <v>0</v>
@@ -31811,13 +32201,13 @@
     </row>
     <row r="12" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>1271</v>
+        <v>1292</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1271</v>
+        <v>1292</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D12" s="4">
         <v>46041</v>
@@ -31829,10 +32219,10 @@
         <v>212</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1210</v>
+        <v>1234</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1209</v>
+        <v>1089</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>139</v>
@@ -31841,7 +32231,7 @@
         <v>140</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>1111</v>
+        <v>1139</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>0</v>
@@ -31883,7 +32273,7 @@
         <v>87</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>1270</v>
+        <v>1291</v>
       </c>
       <c r="Z12" s="2" t="s">
         <v>0</v>
@@ -31898,10 +32288,10 @@
         <v>55</v>
       </c>
       <c r="AD12" s="2" t="s">
-        <v>1106</v>
+        <v>1134</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>1105</v>
+        <v>1133</v>
       </c>
       <c r="AF12" s="2" t="s">
         <v>442</v>
@@ -31921,13 +32311,13 @@
     </row>
     <row r="13" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>1269</v>
+        <v>1290</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1269</v>
+        <v>1290</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D13" s="7">
         <v>46042</v>
@@ -31945,22 +32335,22 @@
         <v>386</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>1173</v>
+        <v>1201</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>1172</v>
+        <v>1200</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>446</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>1176</v>
+        <v>1204</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>1175</v>
+        <v>1203</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>1141</v>
+        <v>1169</v>
       </c>
       <c r="O13" s="8">
         <v>2000</v>
@@ -31993,7 +32383,7 @@
         <v>51</v>
       </c>
       <c r="Y13" s="3" t="s">
-        <v>1268</v>
+        <v>1289</v>
       </c>
       <c r="Z13" s="3" t="s">
         <v>0</v>
@@ -32031,13 +32421,13 @@
     </row>
     <row r="14" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>1267</v>
+        <v>1288</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1267</v>
+        <v>1288</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D14" s="4">
         <v>46042</v>
@@ -32061,16 +32451,16 @@
         <v>294</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>1111</v>
+        <v>1139</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>1235</v>
+        <v>1259</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1234</v>
+        <v>1258</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1108</v>
+        <v>1136</v>
       </c>
       <c r="O14" s="5">
         <v>6000</v>
@@ -32094,16 +32484,16 @@
         <v>12873.6</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>1266</v>
+        <v>1287</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>1265</v>
+        <v>1286</v>
       </c>
       <c r="X14" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>1264</v>
+        <v>1285</v>
       </c>
       <c r="Z14" s="2" t="s">
         <v>0</v>
@@ -32118,10 +32508,10 @@
         <v>298</v>
       </c>
       <c r="AD14" s="2" t="s">
-        <v>1106</v>
+        <v>1134</v>
       </c>
       <c r="AE14" s="2" t="s">
-        <v>1105</v>
+        <v>1133</v>
       </c>
       <c r="AF14" s="2" t="s">
         <v>77</v>
@@ -32141,13 +32531,13 @@
     </row>
     <row r="15" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>1263</v>
+        <v>1284</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1263</v>
+        <v>1284</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D15" s="7">
         <v>46042</v>
@@ -32159,10 +32549,10 @@
         <v>212</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>1210</v>
+        <v>1234</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>1209</v>
+        <v>1089</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>139</v>
@@ -32213,7 +32603,7 @@
         <v>87</v>
       </c>
       <c r="Y15" s="3" t="s">
-        <v>1262</v>
+        <v>1283</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>0</v>
@@ -32234,7 +32624,7 @@
         <v>518</v>
       </c>
       <c r="AF15" s="3" t="s">
-        <v>1230</v>
+        <v>1254</v>
       </c>
       <c r="AG15" s="9">
         <v>0</v>
@@ -32251,13 +32641,13 @@
     </row>
     <row r="16" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>1263</v>
+        <v>1284</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1263</v>
+        <v>1284</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D16" s="4">
         <v>46042</v>
@@ -32269,10 +32659,10 @@
         <v>212</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1210</v>
+        <v>1234</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1209</v>
+        <v>1089</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>139</v>
@@ -32323,7 +32713,7 @@
         <v>87</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>1262</v>
+        <v>1283</v>
       </c>
       <c r="Z16" s="2" t="s">
         <v>0</v>
@@ -32344,7 +32734,7 @@
         <v>518</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>1230</v>
+        <v>1254</v>
       </c>
       <c r="AG16" s="6">
         <v>0</v>
@@ -32361,13 +32751,13 @@
     </row>
     <row r="17" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>1261</v>
+        <v>1282</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1261</v>
+        <v>1282</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D17" s="7">
         <v>46043</v>
@@ -32394,13 +32784,13 @@
         <v>417</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>1180</v>
+        <v>1208</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>1179</v>
+        <v>1207</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>1178</v>
+        <v>1206</v>
       </c>
       <c r="O17" s="8">
         <v>1000</v>
@@ -32433,7 +32823,7 @@
         <v>51</v>
       </c>
       <c r="Y17" s="3" t="s">
-        <v>1260</v>
+        <v>1281</v>
       </c>
       <c r="Z17" s="3" t="s">
         <v>0</v>
@@ -32471,28 +32861,28 @@
     </row>
     <row r="18" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>1248</v>
+        <v>1269</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1248</v>
+        <v>1269</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D18" s="4">
         <v>46045</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1247</v>
+        <v>1097</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1246</v>
+        <v>1096</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1186</v>
+        <v>1095</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>1185</v>
+        <v>1094</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>139</v>
@@ -32504,13 +32894,13 @@
         <v>628</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>1259</v>
+        <v>1280</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1258</v>
+        <v>1279</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1257</v>
+        <v>1278</v>
       </c>
       <c r="O18" s="5">
         <v>2000</v>
@@ -32534,16 +32924,16 @@
         <v>0</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>1242</v>
+        <v>1090</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>1209</v>
+        <v>1089</v>
       </c>
       <c r="X18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>1241</v>
+        <v>1265</v>
       </c>
       <c r="Z18" s="2" t="s">
         <v>0</v>
@@ -32581,28 +32971,28 @@
     </row>
     <row r="19" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>1248</v>
+        <v>1269</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>1248</v>
+        <v>1269</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D19" s="7">
         <v>46045</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>1247</v>
+        <v>1097</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>1246</v>
+        <v>1096</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>1186</v>
+        <v>1095</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>1185</v>
+        <v>1094</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>139</v>
@@ -32614,13 +33004,13 @@
         <v>631</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>1256</v>
+        <v>1277</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>1255</v>
+        <v>1276</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>1243</v>
+        <v>1266</v>
       </c>
       <c r="O19" s="8">
         <v>11725</v>
@@ -32644,16 +33034,16 @@
         <v>0</v>
       </c>
       <c r="V19" s="3" t="s">
-        <v>1242</v>
+        <v>1090</v>
       </c>
       <c r="W19" s="3" t="s">
-        <v>1209</v>
+        <v>1089</v>
       </c>
       <c r="X19" s="3" t="s">
         <v>87</v>
       </c>
       <c r="Y19" s="3" t="s">
-        <v>1241</v>
+        <v>1265</v>
       </c>
       <c r="Z19" s="3" t="s">
         <v>0</v>
@@ -32691,28 +33081,28 @@
     </row>
     <row r="20" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>1248</v>
+        <v>1269</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1248</v>
+        <v>1269</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D20" s="4">
         <v>46045</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1247</v>
+        <v>1097</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1246</v>
+        <v>1096</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1186</v>
+        <v>1095</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1185</v>
+        <v>1094</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>139</v>
@@ -32724,13 +33114,13 @@
         <v>632</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>1167</v>
+        <v>1195</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1166</v>
+        <v>1194</v>
       </c>
       <c r="O20" s="5">
         <v>2925</v>
@@ -32754,16 +33144,16 @@
         <v>0</v>
       </c>
       <c r="V20" s="2" t="s">
-        <v>1242</v>
+        <v>1090</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>1209</v>
+        <v>1089</v>
       </c>
       <c r="X20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>1241</v>
+        <v>1265</v>
       </c>
       <c r="Z20" s="2" t="s">
         <v>0</v>
@@ -32801,28 +33191,28 @@
     </row>
     <row r="21" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>1248</v>
+        <v>1269</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>1248</v>
+        <v>1269</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D21" s="7">
         <v>46045</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>1247</v>
+        <v>1097</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>1246</v>
+        <v>1096</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>1186</v>
+        <v>1095</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>1185</v>
+        <v>1094</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>139</v>
@@ -32834,13 +33224,13 @@
         <v>633</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>1119</v>
+        <v>1147</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>652</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>1118</v>
+        <v>1146</v>
       </c>
       <c r="O21" s="8">
         <v>2925</v>
@@ -32864,16 +33254,16 @@
         <v>0</v>
       </c>
       <c r="V21" s="3" t="s">
-        <v>1242</v>
+        <v>1090</v>
       </c>
       <c r="W21" s="3" t="s">
-        <v>1209</v>
+        <v>1089</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>87</v>
       </c>
       <c r="Y21" s="3" t="s">
-        <v>1241</v>
+        <v>1265</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>0</v>
@@ -32911,28 +33301,28 @@
     </row>
     <row r="22" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>1248</v>
+        <v>1269</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1248</v>
+        <v>1269</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D22" s="4">
         <v>46045</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1247</v>
+        <v>1097</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1246</v>
+        <v>1096</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1186</v>
+        <v>1095</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1185</v>
+        <v>1094</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>139</v>
@@ -32944,13 +33334,13 @@
         <v>465</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1254</v>
+        <v>1275</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1253</v>
+        <v>1274</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="O22" s="5">
         <v>2400</v>
@@ -32974,16 +33364,16 @@
         <v>0</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>1242</v>
+        <v>1090</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>1209</v>
+        <v>1089</v>
       </c>
       <c r="X22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>1241</v>
+        <v>1265</v>
       </c>
       <c r="Z22" s="2" t="s">
         <v>0</v>
@@ -33021,28 +33411,28 @@
     </row>
     <row r="23" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>1248</v>
+        <v>1269</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>1248</v>
+        <v>1269</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D23" s="7">
         <v>46045</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>1247</v>
+        <v>1097</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>1246</v>
+        <v>1096</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>1186</v>
+        <v>1095</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>1185</v>
+        <v>1094</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>139</v>
@@ -33054,13 +33444,13 @@
         <v>465</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>1251</v>
+        <v>1272</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>1250</v>
+        <v>1271</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>1249</v>
+        <v>1270</v>
       </c>
       <c r="O23" s="8">
         <v>1800</v>
@@ -33084,16 +33474,16 @@
         <v>0</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>1242</v>
+        <v>1090</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>1209</v>
+        <v>1089</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>87</v>
       </c>
       <c r="Y23" s="3" t="s">
-        <v>1241</v>
+        <v>1265</v>
       </c>
       <c r="Z23" s="3" t="s">
         <v>0</v>
@@ -33131,28 +33521,28 @@
     </row>
     <row r="24" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>1248</v>
+        <v>1269</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1248</v>
+        <v>1269</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D24" s="4">
         <v>46045</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1247</v>
+        <v>1097</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1246</v>
+        <v>1096</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1186</v>
+        <v>1095</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1185</v>
+        <v>1094</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>139</v>
@@ -33164,13 +33554,13 @@
         <v>634</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>1245</v>
+        <v>1268</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1244</v>
+        <v>1267</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1243</v>
+        <v>1266</v>
       </c>
       <c r="O24" s="5">
         <v>1400</v>
@@ -33194,16 +33584,16 @@
         <v>0</v>
       </c>
       <c r="V24" s="2" t="s">
-        <v>1242</v>
+        <v>1090</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>1209</v>
+        <v>1089</v>
       </c>
       <c r="X24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>1241</v>
+        <v>1265</v>
       </c>
       <c r="Z24" s="2" t="s">
         <v>0</v>
@@ -33241,13 +33631,13 @@
     </row>
     <row r="25" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>1240</v>
+        <v>1264</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>1240</v>
+        <v>1264</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D25" s="7">
         <v>46048</v>
@@ -33274,13 +33664,13 @@
         <v>417</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>1192</v>
+        <v>1217</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>1191</v>
+        <v>1216</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>1190</v>
+        <v>1106</v>
       </c>
       <c r="O25" s="8">
         <v>5000</v>
@@ -33304,16 +33694,16 @@
         <v>2354</v>
       </c>
       <c r="V25" s="3" t="s">
-        <v>1086</v>
+        <v>1117</v>
       </c>
       <c r="W25" s="3" t="s">
-        <v>1085</v>
+        <v>1116</v>
       </c>
       <c r="X25" s="3" t="s">
         <v>51</v>
       </c>
       <c r="Y25" s="3" t="s">
-        <v>1239</v>
+        <v>1263</v>
       </c>
       <c r="Z25" s="3" t="s">
         <v>0</v>
@@ -33351,13 +33741,13 @@
     </row>
     <row r="26" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>1238</v>
+        <v>1262</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1238</v>
+        <v>1262</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D26" s="4">
         <v>46048</v>
@@ -33369,10 +33759,10 @@
         <v>40</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1081</v>
+        <v>1113</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1080</v>
+        <v>1112</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>139</v>
@@ -33384,13 +33774,13 @@
         <v>784</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>1079</v>
+        <v>1111</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1078</v>
+        <v>1110</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1077</v>
+        <v>1109</v>
       </c>
       <c r="O26" s="5">
         <v>300</v>
@@ -33423,7 +33813,7 @@
         <v>51</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>1237</v>
+        <v>1261</v>
       </c>
       <c r="Z26" s="2" t="s">
         <v>0</v>
@@ -33461,13 +33851,13 @@
     </row>
     <row r="27" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>1236</v>
+        <v>1260</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>1236</v>
+        <v>1260</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D27" s="7">
         <v>46048</v>
@@ -33479,10 +33869,10 @@
         <v>61</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>1169</v>
+        <v>1197</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>1168</v>
+        <v>1196</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>163</v>
@@ -33494,13 +33884,13 @@
         <v>632</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>1167</v>
+        <v>1195</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>648</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>1166</v>
+        <v>1194</v>
       </c>
       <c r="O27" s="8">
         <v>611</v>
@@ -33533,7 +33923,7 @@
         <v>51</v>
       </c>
       <c r="Y27" s="3" t="s">
-        <v>1233</v>
+        <v>1257</v>
       </c>
       <c r="Z27" s="3" t="s">
         <v>0</v>
@@ -33571,13 +33961,13 @@
     </row>
     <row r="28" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>1236</v>
+        <v>1260</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1236</v>
+        <v>1260</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D28" s="4">
         <v>46048</v>
@@ -33589,10 +33979,10 @@
         <v>61</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1169</v>
+        <v>1197</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1168</v>
+        <v>1196</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>163</v>
@@ -33601,16 +33991,16 @@
         <v>164</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>1111</v>
+        <v>1139</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>1235</v>
+        <v>1259</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1234</v>
+        <v>1258</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1108</v>
+        <v>1136</v>
       </c>
       <c r="O28" s="5">
         <v>700</v>
@@ -33643,7 +34033,7 @@
         <v>51</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>1233</v>
+        <v>1257</v>
       </c>
       <c r="Z28" s="2" t="s">
         <v>0</v>
@@ -33658,10 +34048,10 @@
         <v>55</v>
       </c>
       <c r="AD28" s="2" t="s">
-        <v>1106</v>
+        <v>1134</v>
       </c>
       <c r="AE28" s="2" t="s">
-        <v>1105</v>
+        <v>1133</v>
       </c>
       <c r="AF28" s="2" t="s">
         <v>77</v>
@@ -33681,13 +34071,13 @@
     </row>
     <row r="29" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>1232</v>
+        <v>1256</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>1232</v>
+        <v>1256</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D29" s="7">
         <v>46048</v>
@@ -33699,10 +34089,10 @@
         <v>212</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>1210</v>
+        <v>1234</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>1209</v>
+        <v>1089</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>139</v>
@@ -33753,7 +34143,7 @@
         <v>87</v>
       </c>
       <c r="Y29" s="3" t="s">
-        <v>1231</v>
+        <v>1255</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>0</v>
@@ -33774,7 +34164,7 @@
         <v>57</v>
       </c>
       <c r="AF29" s="3" t="s">
-        <v>1230</v>
+        <v>1254</v>
       </c>
       <c r="AG29" s="9">
         <v>0</v>
@@ -33791,13 +34181,13 @@
     </row>
     <row r="30" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>1229</v>
+        <v>1253</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1229</v>
+        <v>1253</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D30" s="4">
         <v>46049</v>
@@ -33809,10 +34199,10 @@
         <v>212</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1210</v>
+        <v>1234</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1209</v>
+        <v>1089</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>139</v>
@@ -33863,7 +34253,7 @@
         <v>87</v>
       </c>
       <c r="Y30" s="2" t="s">
-        <v>1228</v>
+        <v>1252</v>
       </c>
       <c r="Z30" s="2" t="s">
         <v>0</v>
@@ -33901,13 +34291,13 @@
     </row>
     <row r="31" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>1229</v>
+        <v>1253</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>1229</v>
+        <v>1253</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D31" s="7">
         <v>46049</v>
@@ -33919,10 +34309,10 @@
         <v>212</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>1210</v>
+        <v>1234</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>1209</v>
+        <v>1089</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>139</v>
@@ -33973,7 +34363,7 @@
         <v>87</v>
       </c>
       <c r="Y31" s="3" t="s">
-        <v>1228</v>
+        <v>1252</v>
       </c>
       <c r="Z31" s="3" t="s">
         <v>0</v>
@@ -34011,13 +34401,13 @@
     </row>
     <row r="32" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>1225</v>
+        <v>1249</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1225</v>
+        <v>1249</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D32" s="4">
         <v>46050</v>
@@ -34035,22 +34425,22 @@
         <v>386</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>1173</v>
+        <v>1201</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>1172</v>
+        <v>1200</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>446</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>1227</v>
+        <v>1251</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>448</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1226</v>
+        <v>1250</v>
       </c>
       <c r="O32" s="5">
         <v>1000</v>
@@ -34083,7 +34473,7 @@
         <v>51</v>
       </c>
       <c r="Y32" s="2" t="s">
-        <v>1224</v>
+        <v>1248</v>
       </c>
       <c r="Z32" s="2" t="s">
         <v>0</v>
@@ -34121,13 +34511,13 @@
     </row>
     <row r="33" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>1225</v>
+        <v>1249</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>1225</v>
+        <v>1249</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D33" s="7">
         <v>46050</v>
@@ -34145,22 +34535,22 @@
         <v>386</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>1173</v>
+        <v>1201</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>1172</v>
+        <v>1200</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>446</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>1176</v>
+        <v>1204</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>1175</v>
+        <v>1203</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>1141</v>
+        <v>1169</v>
       </c>
       <c r="O33" s="8">
         <v>1000</v>
@@ -34193,7 +34583,7 @@
         <v>51</v>
       </c>
       <c r="Y33" s="3" t="s">
-        <v>1224</v>
+        <v>1248</v>
       </c>
       <c r="Z33" s="3" t="s">
         <v>0</v>
@@ -34231,13 +34621,13 @@
     </row>
     <row r="34" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>1223</v>
+        <v>1247</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1223</v>
+        <v>1247</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D34" s="4">
         <v>46050</v>
@@ -34249,10 +34639,10 @@
         <v>212</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1210</v>
+        <v>1234</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>1209</v>
+        <v>1089</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>139</v>
@@ -34303,7 +34693,7 @@
         <v>87</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>1222</v>
+        <v>1246</v>
       </c>
       <c r="Z34" s="2" t="s">
         <v>0</v>
@@ -34341,13 +34731,13 @@
     </row>
     <row r="35" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>1221</v>
+        <v>1245</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>1221</v>
+        <v>1245</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D35" s="7">
         <v>46051</v>
@@ -34359,10 +34749,10 @@
         <v>40</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>1220</v>
+        <v>1244</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>1219</v>
+        <v>1243</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>43</v>
@@ -34374,13 +34764,13 @@
         <v>632</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>1167</v>
+        <v>1195</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>648</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>1166</v>
+        <v>1194</v>
       </c>
       <c r="O35" s="8">
         <v>26</v>
@@ -34413,7 +34803,7 @@
         <v>51</v>
       </c>
       <c r="Y35" s="3" t="s">
-        <v>1218</v>
+        <v>1242</v>
       </c>
       <c r="Z35" s="3" t="s">
         <v>0</v>
@@ -34451,13 +34841,13 @@
     </row>
     <row r="36" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>1217</v>
+        <v>1241</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>1217</v>
+        <v>1241</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D36" s="4">
         <v>46052</v>
@@ -34469,10 +34859,10 @@
         <v>61</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1169</v>
+        <v>1197</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>1168</v>
+        <v>1196</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>163</v>
@@ -34484,13 +34874,13 @@
         <v>632</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>1167</v>
+        <v>1195</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1166</v>
+        <v>1194</v>
       </c>
       <c r="O36" s="5">
         <v>507</v>
@@ -34523,7 +34913,7 @@
         <v>51</v>
       </c>
       <c r="Y36" s="2" t="s">
-        <v>1216</v>
+        <v>1240</v>
       </c>
       <c r="Z36" s="2" t="s">
         <v>0</v>
@@ -34561,13 +34951,13 @@
     </row>
     <row r="37" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>1215</v>
+        <v>1239</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>1215</v>
+        <v>1239</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D37" s="7">
         <v>46052</v>
@@ -34591,16 +34981,16 @@
         <v>164</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>1116</v>
+        <v>1144</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>1135</v>
+        <v>1163</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>1134</v>
+        <v>1162</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>1113</v>
+        <v>1141</v>
       </c>
       <c r="O37" s="8">
         <v>500</v>
@@ -34633,7 +35023,7 @@
         <v>51</v>
       </c>
       <c r="Y37" s="3" t="s">
-        <v>1214</v>
+        <v>1238</v>
       </c>
       <c r="Z37" s="3" t="s">
         <v>0</v>
@@ -34671,13 +35061,13 @@
     </row>
     <row r="38" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>1213</v>
+        <v>1237</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1213</v>
+        <v>1237</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D38" s="4">
         <v>46052</v>
@@ -34689,10 +35079,10 @@
         <v>40</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>1081</v>
+        <v>1113</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>1080</v>
+        <v>1112</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>139</v>
@@ -34704,13 +35094,13 @@
         <v>784</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>1079</v>
+        <v>1111</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>1078</v>
+        <v>1110</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>1077</v>
+        <v>1109</v>
       </c>
       <c r="O38" s="5">
         <v>300</v>
@@ -34743,7 +35133,7 @@
         <v>51</v>
       </c>
       <c r="Y38" s="2" t="s">
-        <v>1212</v>
+        <v>1236</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>0</v>
@@ -34781,13 +35171,13 @@
     </row>
     <row r="39" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>1211</v>
+        <v>1235</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>1211</v>
+        <v>1235</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D39" s="7">
         <v>46055</v>
@@ -34799,10 +35189,10 @@
         <v>212</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>1210</v>
+        <v>1234</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>1209</v>
+        <v>1089</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>139</v>
@@ -34811,7 +35201,7 @@
         <v>140</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>1208</v>
+        <v>1233</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>0</v>
@@ -34853,7 +35243,7 @@
         <v>87</v>
       </c>
       <c r="Y39" s="3" t="s">
-        <v>1207</v>
+        <v>1232</v>
       </c>
       <c r="Z39" s="3" t="s">
         <v>0</v>
@@ -34891,13 +35281,13 @@
     </row>
     <row r="40" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>1206</v>
+        <v>1231</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1206</v>
+        <v>1231</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D40" s="4">
         <v>46057</v>
@@ -34909,10 +35299,10 @@
         <v>61</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1169</v>
+        <v>1197</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>1168</v>
+        <v>1196</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>163</v>
@@ -34924,13 +35314,13 @@
         <v>632</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>1167</v>
+        <v>1195</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>1166</v>
+        <v>1194</v>
       </c>
       <c r="O40" s="5">
         <v>507</v>
@@ -34963,7 +35353,7 @@
         <v>51</v>
       </c>
       <c r="Y40" s="2" t="s">
-        <v>1205</v>
+        <v>1230</v>
       </c>
       <c r="Z40" s="2" t="s">
         <v>0</v>
@@ -35001,13 +35391,13 @@
     </row>
     <row r="41" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>1204</v>
+        <v>1229</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>1204</v>
+        <v>1229</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D41" s="7">
         <v>46057</v>
@@ -35025,22 +35415,22 @@
         <v>386</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>1173</v>
+        <v>1201</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>1172</v>
+        <v>1200</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>446</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>1176</v>
+        <v>1204</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>1175</v>
+        <v>1203</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>1141</v>
+        <v>1169</v>
       </c>
       <c r="O41" s="8">
         <v>2000</v>
@@ -35073,7 +35463,7 @@
         <v>51</v>
       </c>
       <c r="Y41" s="3" t="s">
-        <v>1171</v>
+        <v>1199</v>
       </c>
       <c r="Z41" s="3" t="s">
         <v>0</v>
@@ -35111,13 +35501,13 @@
     </row>
     <row r="42" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>1203</v>
+        <v>1228</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1203</v>
+        <v>1228</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D42" s="4">
         <v>46058</v>
@@ -35129,10 +35519,10 @@
         <v>61</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1169</v>
+        <v>1197</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>1168</v>
+        <v>1196</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>163</v>
@@ -35144,13 +35534,13 @@
         <v>632</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>1167</v>
+        <v>1195</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>1166</v>
+        <v>1194</v>
       </c>
       <c r="O42" s="5">
         <v>507</v>
@@ -35183,7 +35573,7 @@
         <v>51</v>
       </c>
       <c r="Y42" s="2" t="s">
-        <v>1202</v>
+        <v>1227</v>
       </c>
       <c r="Z42" s="2" t="s">
         <v>0</v>
@@ -35221,13 +35611,13 @@
     </row>
     <row r="43" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>1201</v>
+        <v>1226</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>1201</v>
+        <v>1226</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D43" s="7">
         <v>46058</v>
@@ -35239,10 +35629,10 @@
         <v>61</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>1138</v>
+        <v>1166</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>1137</v>
+        <v>1165</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>163</v>
@@ -35254,13 +35644,13 @@
         <v>417</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>1192</v>
+        <v>1217</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>1191</v>
+        <v>1216</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>1190</v>
+        <v>1106</v>
       </c>
       <c r="O43" s="8">
         <v>1800</v>
@@ -35293,7 +35683,7 @@
         <v>51</v>
       </c>
       <c r="Y43" s="3" t="s">
-        <v>1200</v>
+        <v>1225</v>
       </c>
       <c r="Z43" s="3" t="s">
         <v>0</v>
@@ -35331,13 +35721,13 @@
     </row>
     <row r="44" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>1199</v>
+        <v>1224</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>1199</v>
+        <v>1224</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D44" s="4">
         <v>46059</v>
@@ -35349,10 +35739,10 @@
         <v>40</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>1197</v>
+        <v>1222</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>43</v>
@@ -35364,13 +35754,13 @@
         <v>784</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>1079</v>
+        <v>1111</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>1078</v>
+        <v>1110</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>1077</v>
+        <v>1109</v>
       </c>
       <c r="O44" s="5">
         <v>500</v>
@@ -35403,7 +35793,7 @@
         <v>51</v>
       </c>
       <c r="Y44" s="2" t="s">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="Z44" s="2" t="s">
         <v>0</v>
@@ -35441,13 +35831,13 @@
     </row>
     <row r="45" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>1195</v>
+        <v>1220</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>1195</v>
+        <v>1220</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D45" s="7">
         <v>46059</v>
@@ -35459,10 +35849,10 @@
         <v>40</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>1194</v>
+        <v>1219</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>1193</v>
+        <v>1218</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>43</v>
@@ -35474,13 +35864,13 @@
         <v>417</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>1192</v>
+        <v>1217</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>1191</v>
+        <v>1216</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>1190</v>
+        <v>1106</v>
       </c>
       <c r="O45" s="8">
         <v>200</v>
@@ -35513,7 +35903,7 @@
         <v>51</v>
       </c>
       <c r="Y45" s="3" t="s">
-        <v>1189</v>
+        <v>1215</v>
       </c>
       <c r="Z45" s="3" t="s">
         <v>0</v>
@@ -35551,28 +35941,28 @@
     </row>
     <row r="46" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>1188</v>
+        <v>1214</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1188</v>
+        <v>1214</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D46" s="4">
         <v>46063</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1187</v>
+        <v>1213</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>267</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1186</v>
+        <v>1095</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>1185</v>
+        <v>1094</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>139</v>
@@ -35581,7 +35971,7 @@
         <v>140</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>1094</v>
+        <v>1122</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>0</v>
@@ -35623,7 +36013,7 @@
         <v>0</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>1184</v>
+        <v>1212</v>
       </c>
       <c r="Z46" s="2" t="s">
         <v>0</v>
@@ -35638,10 +36028,10 @@
         <v>74</v>
       </c>
       <c r="AD46" s="2" t="s">
-        <v>1092</v>
+        <v>1120</v>
       </c>
       <c r="AE46" s="2" t="s">
-        <v>1091</v>
+        <v>1119</v>
       </c>
       <c r="AF46" s="2" t="s">
         <v>0</v>
@@ -35661,13 +36051,13 @@
     </row>
     <row r="47" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>1183</v>
+        <v>1211</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>1183</v>
+        <v>1211</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D47" s="7">
         <v>46064</v>
@@ -35679,10 +36069,10 @@
         <v>61</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>1182</v>
+        <v>1210</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>1181</v>
+        <v>1209</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>139</v>
@@ -35694,13 +36084,13 @@
         <v>417</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>1180</v>
+        <v>1208</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>1179</v>
+        <v>1207</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>1178</v>
+        <v>1206</v>
       </c>
       <c r="O47" s="8">
         <v>1000</v>
@@ -35733,7 +36123,7 @@
         <v>51</v>
       </c>
       <c r="Y47" s="3" t="s">
-        <v>1177</v>
+        <v>1205</v>
       </c>
       <c r="Z47" s="3" t="s">
         <v>0</v>
@@ -35771,13 +36161,13 @@
     </row>
     <row r="48" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>1174</v>
+        <v>1202</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1174</v>
+        <v>1202</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D48" s="4">
         <v>46064</v>
@@ -35795,22 +36185,22 @@
         <v>386</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>1173</v>
+        <v>1201</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>1172</v>
+        <v>1200</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>446</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>1176</v>
+        <v>1204</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>1175</v>
+        <v>1203</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>1141</v>
+        <v>1169</v>
       </c>
       <c r="O48" s="5">
         <v>1000</v>
@@ -35843,7 +36233,7 @@
         <v>51</v>
       </c>
       <c r="Y48" s="2" t="s">
-        <v>1171</v>
+        <v>1199</v>
       </c>
       <c r="Z48" s="2" t="s">
         <v>0</v>
@@ -35881,13 +36271,13 @@
     </row>
     <row r="49" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>1174</v>
+        <v>1202</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>1174</v>
+        <v>1202</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D49" s="7">
         <v>46064</v>
@@ -35905,22 +36295,22 @@
         <v>386</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>1173</v>
+        <v>1201</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>1172</v>
+        <v>1200</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>446</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>1143</v>
+        <v>1171</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>1142</v>
+        <v>1170</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>1141</v>
+        <v>1169</v>
       </c>
       <c r="O49" s="8">
         <v>1000</v>
@@ -35953,7 +36343,7 @@
         <v>51</v>
       </c>
       <c r="Y49" s="3" t="s">
-        <v>1171</v>
+        <v>1199</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>0</v>
@@ -35991,13 +36381,13 @@
     </row>
     <row r="50" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>1170</v>
+        <v>1198</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>1170</v>
+        <v>1198</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D50" s="4">
         <v>46066</v>
@@ -36009,10 +36399,10 @@
         <v>61</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1169</v>
+        <v>1197</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>1168</v>
+        <v>1196</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>163</v>
@@ -36024,13 +36414,13 @@
         <v>632</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>1167</v>
+        <v>1195</v>
       </c>
       <c r="M50" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>1166</v>
+        <v>1194</v>
       </c>
       <c r="O50" s="5">
         <v>507</v>
@@ -36063,7 +36453,7 @@
         <v>51</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>1165</v>
+        <v>1193</v>
       </c>
       <c r="Z50" s="2" t="s">
         <v>0</v>
@@ -36101,13 +36491,13 @@
     </row>
     <row r="51" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>1164</v>
+        <v>1192</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>1164</v>
+        <v>1192</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D51" s="7">
         <v>46071</v>
@@ -36131,16 +36521,16 @@
         <v>164</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>1111</v>
+        <v>1139</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>1163</v>
+        <v>1191</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>1162</v>
+        <v>1190</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>1161</v>
+        <v>1189</v>
       </c>
       <c r="O51" s="8">
         <v>500</v>
@@ -36173,7 +36563,7 @@
         <v>51</v>
       </c>
       <c r="Y51" s="3" t="s">
-        <v>1160</v>
+        <v>1188</v>
       </c>
       <c r="Z51" s="3" t="s">
         <v>0</v>
@@ -36188,10 +36578,10 @@
         <v>111</v>
       </c>
       <c r="AD51" s="3" t="s">
-        <v>1106</v>
+        <v>1134</v>
       </c>
       <c r="AE51" s="3" t="s">
-        <v>1105</v>
+        <v>1133</v>
       </c>
       <c r="AF51" s="3" t="s">
         <v>77</v>
@@ -36211,13 +36601,13 @@
     </row>
     <row r="52" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>1159</v>
+        <v>1187</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1159</v>
+        <v>1187</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D52" s="4">
         <v>46071</v>
@@ -36229,10 +36619,10 @@
         <v>61</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1158</v>
+        <v>1186</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>1157</v>
+        <v>1185</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>139</v>
@@ -36244,13 +36634,13 @@
         <v>446</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>1143</v>
+        <v>1171</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>1142</v>
+        <v>1170</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>1141</v>
+        <v>1169</v>
       </c>
       <c r="O52" s="5">
         <v>200</v>
@@ -36283,7 +36673,7 @@
         <v>51</v>
       </c>
       <c r="Y52" s="2" t="s">
-        <v>1156</v>
+        <v>1184</v>
       </c>
       <c r="Z52" s="2" t="s">
         <v>0</v>
@@ -36321,13 +36711,13 @@
     </row>
     <row r="53" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>1155</v>
+        <v>1183</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>1155</v>
+        <v>1183</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D53" s="7">
         <v>46072</v>
@@ -36339,10 +36729,10 @@
         <v>40</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>1096</v>
+        <v>1124</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>1095</v>
+        <v>1123</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>43</v>
@@ -36354,13 +36744,13 @@
         <v>440</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>1154</v>
+        <v>1182</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>1153</v>
+        <v>1181</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>1152</v>
+        <v>1180</v>
       </c>
       <c r="O53" s="8">
         <v>50</v>
@@ -36384,16 +36774,16 @@
         <v>0</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>1151</v>
+        <v>1179</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>1150</v>
+        <v>1178</v>
       </c>
       <c r="X53" s="3" t="s">
         <v>51</v>
       </c>
       <c r="Y53" s="3" t="s">
-        <v>1149</v>
+        <v>1177</v>
       </c>
       <c r="Z53" s="3" t="s">
         <v>0</v>
@@ -36431,13 +36821,13 @@
     </row>
     <row r="54" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>1148</v>
+        <v>1176</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1148</v>
+        <v>1176</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D54" s="4">
         <v>46072</v>
@@ -36449,10 +36839,10 @@
         <v>61</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1138</v>
+        <v>1166</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>1137</v>
+        <v>1165</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>163</v>
@@ -36464,13 +36854,13 @@
         <v>417</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>1128</v>
+        <v>1156</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>1127</v>
+        <v>1155</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>1087</v>
+        <v>1103</v>
       </c>
       <c r="O54" s="5">
         <v>1600</v>
@@ -36503,7 +36893,7 @@
         <v>51</v>
       </c>
       <c r="Y54" s="2" t="s">
-        <v>1147</v>
+        <v>1175</v>
       </c>
       <c r="Z54" s="2" t="s">
         <v>0</v>
@@ -36541,13 +36931,13 @@
     </row>
     <row r="55" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>1146</v>
+        <v>1174</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>1146</v>
+        <v>1174</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D55" s="7">
         <v>46072</v>
@@ -36559,10 +36949,10 @@
         <v>40</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>1145</v>
+        <v>1173</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>1144</v>
+        <v>1172</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>43</v>
@@ -36574,13 +36964,13 @@
         <v>446</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>1143</v>
+        <v>1171</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>1142</v>
+        <v>1170</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>1141</v>
+        <v>1169</v>
       </c>
       <c r="O55" s="8">
         <v>500</v>
@@ -36613,7 +37003,7 @@
         <v>51</v>
       </c>
       <c r="Y55" s="3" t="s">
-        <v>1140</v>
+        <v>1168</v>
       </c>
       <c r="Z55" s="3" t="s">
         <v>0</v>
@@ -36651,13 +37041,13 @@
     </row>
     <row r="56" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>1139</v>
+        <v>1167</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1139</v>
+        <v>1167</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D56" s="4">
         <v>46076</v>
@@ -36669,10 +37059,10 @@
         <v>61</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1138</v>
+        <v>1166</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>1137</v>
+        <v>1165</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>163</v>
@@ -36684,13 +37074,13 @@
         <v>417</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>1128</v>
+        <v>1156</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>1127</v>
+        <v>1155</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>1087</v>
+        <v>1103</v>
       </c>
       <c r="O56" s="5">
         <v>1700</v>
@@ -36723,7 +37113,7 @@
         <v>51</v>
       </c>
       <c r="Y56" s="2" t="s">
-        <v>1136</v>
+        <v>1164</v>
       </c>
       <c r="Z56" s="2" t="s">
         <v>0</v>
@@ -36761,13 +37151,13 @@
     </row>
     <row r="57" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D57" s="7">
         <v>46077</v>
@@ -36791,16 +37181,16 @@
         <v>164</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>1116</v>
+        <v>1144</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>1135</v>
+        <v>1163</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>1134</v>
+        <v>1162</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>1113</v>
+        <v>1141</v>
       </c>
       <c r="O57" s="8">
         <v>500</v>
@@ -36833,7 +37223,7 @@
         <v>51</v>
       </c>
       <c r="Y57" s="3" t="s">
-        <v>1132</v>
+        <v>1160</v>
       </c>
       <c r="Z57" s="3" t="s">
         <v>0</v>
@@ -36871,13 +37261,13 @@
     </row>
     <row r="58" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D58" s="4">
         <v>46077</v>
@@ -36901,16 +37291,16 @@
         <v>164</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>1111</v>
+        <v>1139</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>1110</v>
+        <v>1138</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>1109</v>
+        <v>1137</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>1108</v>
+        <v>1136</v>
       </c>
       <c r="O58" s="5">
         <v>500</v>
@@ -36943,7 +37333,7 @@
         <v>51</v>
       </c>
       <c r="Y58" s="2" t="s">
-        <v>1132</v>
+        <v>1160</v>
       </c>
       <c r="Z58" s="2" t="s">
         <v>0</v>
@@ -36958,10 +37348,10 @@
         <v>111</v>
       </c>
       <c r="AD58" s="2" t="s">
-        <v>1106</v>
+        <v>1134</v>
       </c>
       <c r="AE58" s="2" t="s">
-        <v>1105</v>
+        <v>1133</v>
       </c>
       <c r="AF58" s="2" t="s">
         <v>77</v>
@@ -36981,13 +37371,13 @@
     </row>
     <row r="59" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>1131</v>
+        <v>1159</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>1131</v>
+        <v>1159</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D59" s="7">
         <v>46078</v>
@@ -36999,10 +37389,10 @@
         <v>40</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>1081</v>
+        <v>1113</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>1080</v>
+        <v>1112</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>139</v>
@@ -37014,13 +37404,13 @@
         <v>784</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>1079</v>
+        <v>1111</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>1078</v>
+        <v>1110</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>1077</v>
+        <v>1109</v>
       </c>
       <c r="O59" s="8">
         <v>225</v>
@@ -37053,7 +37443,7 @@
         <v>51</v>
       </c>
       <c r="Y59" s="3" t="s">
-        <v>1130</v>
+        <v>1158</v>
       </c>
       <c r="Z59" s="3" t="s">
         <v>0</v>
@@ -37091,13 +37481,13 @@
     </row>
     <row r="60" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>1129</v>
+        <v>1157</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1129</v>
+        <v>1157</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D60" s="4">
         <v>46079</v>
@@ -37124,13 +37514,13 @@
         <v>417</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>1128</v>
+        <v>1156</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>1127</v>
+        <v>1155</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>1087</v>
+        <v>1103</v>
       </c>
       <c r="O60" s="5">
         <v>5000</v>
@@ -37154,16 +37544,16 @@
         <v>2354</v>
       </c>
       <c r="V60" s="2" t="s">
-        <v>1086</v>
+        <v>1117</v>
       </c>
       <c r="W60" s="2" t="s">
-        <v>1085</v>
+        <v>1116</v>
       </c>
       <c r="X60" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Y60" s="2" t="s">
-        <v>1126</v>
+        <v>1154</v>
       </c>
       <c r="Z60" s="2" t="s">
         <v>0</v>
@@ -37201,13 +37591,13 @@
     </row>
     <row r="61" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>1125</v>
+        <v>1153</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>1125</v>
+        <v>1153</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D61" s="7">
         <v>46079</v>
@@ -37234,13 +37624,13 @@
         <v>1060</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>1124</v>
+        <v>1152</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>1123</v>
+        <v>1151</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>1122</v>
+        <v>1150</v>
       </c>
       <c r="O61" s="8">
         <v>12000</v>
@@ -37273,7 +37663,7 @@
         <v>51</v>
       </c>
       <c r="Y61" s="3" t="s">
-        <v>1121</v>
+        <v>1149</v>
       </c>
       <c r="Z61" s="3" t="s">
         <v>0</v>
@@ -37311,13 +37701,13 @@
     </row>
     <row r="62" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>1120</v>
+        <v>1148</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1120</v>
+        <v>1148</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D62" s="4">
         <v>46085</v>
@@ -37344,13 +37734,13 @@
         <v>633</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>1119</v>
+        <v>1147</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>652</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>1118</v>
+        <v>1146</v>
       </c>
       <c r="O62" s="5">
         <v>5005</v>
@@ -37383,7 +37773,7 @@
         <v>51</v>
       </c>
       <c r="Y62" s="2" t="s">
-        <v>1117</v>
+        <v>1145</v>
       </c>
       <c r="Z62" s="2" t="s">
         <v>0</v>
@@ -37421,13 +37811,13 @@
     </row>
     <row r="63" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>1112</v>
+        <v>1140</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>1112</v>
+        <v>1140</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D63" s="7">
         <v>46085</v>
@@ -37451,16 +37841,16 @@
         <v>164</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>1116</v>
+        <v>1144</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>1115</v>
+        <v>1143</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>1114</v>
+        <v>1142</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>1113</v>
+        <v>1141</v>
       </c>
       <c r="O63" s="8">
         <v>500</v>
@@ -37493,7 +37883,7 @@
         <v>51</v>
       </c>
       <c r="Y63" s="3" t="s">
-        <v>1107</v>
+        <v>1135</v>
       </c>
       <c r="Z63" s="3" t="s">
         <v>0</v>
@@ -37531,13 +37921,13 @@
     </row>
     <row r="64" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>1112</v>
+        <v>1140</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1112</v>
+        <v>1140</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D64" s="4">
         <v>46085</v>
@@ -37561,16 +37951,16 @@
         <v>164</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>1111</v>
+        <v>1139</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>1110</v>
+        <v>1138</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>1109</v>
+        <v>1137</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>1108</v>
+        <v>1136</v>
       </c>
       <c r="O64" s="5">
         <v>500</v>
@@ -37603,7 +37993,7 @@
         <v>51</v>
       </c>
       <c r="Y64" s="2" t="s">
-        <v>1107</v>
+        <v>1135</v>
       </c>
       <c r="Z64" s="2" t="s">
         <v>0</v>
@@ -37618,10 +38008,10 @@
         <v>111</v>
       </c>
       <c r="AD64" s="2" t="s">
-        <v>1106</v>
+        <v>1134</v>
       </c>
       <c r="AE64" s="2" t="s">
-        <v>1105</v>
+        <v>1133</v>
       </c>
       <c r="AF64" s="2" t="s">
         <v>77</v>
@@ -37641,13 +38031,13 @@
     </row>
     <row r="65" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>1104</v>
+        <v>1132</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>1104</v>
+        <v>1132</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D65" s="7">
         <v>46085</v>
@@ -37659,10 +38049,10 @@
         <v>40</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>1103</v>
+        <v>1131</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>1102</v>
+        <v>1130</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>163</v>
@@ -37674,13 +38064,13 @@
         <v>154</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>1101</v>
+        <v>1129</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>1100</v>
+        <v>1128</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>1099</v>
+        <v>1127</v>
       </c>
       <c r="O65" s="8">
         <v>3700</v>
@@ -37713,7 +38103,7 @@
         <v>51</v>
       </c>
       <c r="Y65" s="3" t="s">
-        <v>1098</v>
+        <v>1126</v>
       </c>
       <c r="Z65" s="3" t="s">
         <v>0</v>
@@ -37751,13 +38141,13 @@
     </row>
     <row r="66" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>1097</v>
+        <v>1125</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1097</v>
+        <v>1125</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D66" s="4">
         <v>46085</v>
@@ -37769,10 +38159,10 @@
         <v>40</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1096</v>
+        <v>1124</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>1095</v>
+        <v>1123</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>139</v>
@@ -37781,7 +38171,7 @@
         <v>140</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>1094</v>
+        <v>1122</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>0</v>
@@ -37823,7 +38213,7 @@
         <v>0</v>
       </c>
       <c r="Y66" s="2" t="s">
-        <v>1093</v>
+        <v>1121</v>
       </c>
       <c r="Z66" s="2" t="s">
         <v>0</v>
@@ -37838,10 +38228,10 @@
         <v>298</v>
       </c>
       <c r="AD66" s="2" t="s">
-        <v>1092</v>
+        <v>1120</v>
       </c>
       <c r="AE66" s="2" t="s">
-        <v>1091</v>
+        <v>1119</v>
       </c>
       <c r="AF66" s="2" t="s">
         <v>0</v>
@@ -37861,13 +38251,13 @@
     </row>
     <row r="67" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>1090</v>
+        <v>1118</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>1090</v>
+        <v>1118</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D67" s="7">
         <v>46091</v>
@@ -37894,13 +38284,13 @@
         <v>417</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>1089</v>
+        <v>1105</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>1088</v>
+        <v>1104</v>
       </c>
       <c r="N67" s="3" t="s">
-        <v>1087</v>
+        <v>1103</v>
       </c>
       <c r="O67" s="8">
         <v>5000</v>
@@ -37924,16 +38314,16 @@
         <v>2354</v>
       </c>
       <c r="V67" s="3" t="s">
-        <v>1086</v>
+        <v>1117</v>
       </c>
       <c r="W67" s="3" t="s">
-        <v>1085</v>
+        <v>1116</v>
       </c>
       <c r="X67" s="3" t="s">
         <v>51</v>
       </c>
       <c r="Y67" s="3" t="s">
-        <v>1084</v>
+        <v>1115</v>
       </c>
       <c r="Z67" s="3" t="s">
         <v>0</v>
@@ -37971,13 +38361,13 @@
     </row>
     <row r="68" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>1083</v>
+        <v>1114</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1083</v>
+        <v>1114</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="D68" s="4">
         <v>46091</v>
@@ -37989,10 +38379,10 @@
         <v>40</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>1081</v>
+        <v>1113</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>1080</v>
+        <v>1112</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>139</v>
@@ -38004,13 +38394,13 @@
         <v>784</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>1079</v>
+        <v>1111</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>1078</v>
+        <v>1110</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>1077</v>
+        <v>1109</v>
       </c>
       <c r="O68" s="5">
         <v>225</v>
@@ -38043,7 +38433,7 @@
         <v>51</v>
       </c>
       <c r="Y68" s="2" t="s">
-        <v>1076</v>
+        <v>1108</v>
       </c>
       <c r="Z68" s="2" t="s">
         <v>0</v>
@@ -38077,6 +38467,446 @@
       </c>
       <c r="AJ68" s="5">
         <v>2225.1802499999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D69" s="7">
+        <v>46092</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="L69" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="M69" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="N69" s="3" t="s">
+        <v>1106</v>
+      </c>
+      <c r="O69" s="8">
+        <v>10000</v>
+      </c>
+      <c r="P69" s="8">
+        <v>8.2807300000000001</v>
+      </c>
+      <c r="Q69" s="9">
+        <v>82807.3</v>
+      </c>
+      <c r="R69" s="9">
+        <v>2691.23</v>
+      </c>
+      <c r="S69" s="9">
+        <v>85498.53</v>
+      </c>
+      <c r="T69" s="9">
+        <v>205676.76</v>
+      </c>
+      <c r="U69" s="9">
+        <v>3312.29</v>
+      </c>
+      <c r="V69" s="3" t="s">
+        <v>1090</v>
+      </c>
+      <c r="W69" s="3" t="s">
+        <v>1089</v>
+      </c>
+      <c r="X69" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y69" s="3" t="s">
+        <v>1088</v>
+      </c>
+      <c r="Z69" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB69" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC69" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD69" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE69" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF69" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG69" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ69" s="8">
+        <v>101325.9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D70" s="4">
+        <v>46092</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>1094</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>1105</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="O70" s="5">
+        <v>5000</v>
+      </c>
+      <c r="P70" s="5">
+        <v>7.7957700000000001</v>
+      </c>
+      <c r="Q70" s="6">
+        <v>38978.85</v>
+      </c>
+      <c r="R70" s="6">
+        <v>1266.81</v>
+      </c>
+      <c r="S70" s="6">
+        <v>40245.660000000003</v>
+      </c>
+      <c r="T70" s="6">
+        <v>205676.76</v>
+      </c>
+      <c r="U70" s="6">
+        <v>1559.15</v>
+      </c>
+      <c r="V70" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="W70" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="X70" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y70" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="Z70" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB70" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC70" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD70" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE70" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF70" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ70" s="5">
+        <v>48943.45</v>
+      </c>
+    </row>
+    <row r="71" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D71" s="7">
+        <v>46092</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="L71" s="3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="M71" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="N71" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="O71" s="8">
+        <v>8400</v>
+      </c>
+      <c r="P71" s="8">
+        <v>7.6801399999999997</v>
+      </c>
+      <c r="Q71" s="9">
+        <v>64513.18</v>
+      </c>
+      <c r="R71" s="9">
+        <v>2096.6799999999998</v>
+      </c>
+      <c r="S71" s="9">
+        <v>66609.86</v>
+      </c>
+      <c r="T71" s="9">
+        <v>205676.76</v>
+      </c>
+      <c r="U71" s="9">
+        <v>2580.5300000000002</v>
+      </c>
+      <c r="V71" s="3" t="s">
+        <v>1090</v>
+      </c>
+      <c r="W71" s="3" t="s">
+        <v>1089</v>
+      </c>
+      <c r="X71" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y71" s="3" t="s">
+        <v>1088</v>
+      </c>
+      <c r="Z71" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB71" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC71" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD71" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="AE71" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="AF71" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ71" s="8">
+        <v>70249.703999999998</v>
+      </c>
+    </row>
+    <row r="72" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D72" s="4">
+        <v>46092</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>1094</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>1092</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="O72" s="5">
+        <v>2400</v>
+      </c>
+      <c r="P72" s="5">
+        <v>8.0739300000000007</v>
+      </c>
+      <c r="Q72" s="6">
+        <v>19377.43</v>
+      </c>
+      <c r="R72" s="6">
+        <v>629.77</v>
+      </c>
+      <c r="S72" s="6">
+        <v>20007.2</v>
+      </c>
+      <c r="T72" s="6">
+        <v>205676.76</v>
+      </c>
+      <c r="U72" s="6">
+        <v>775.1</v>
+      </c>
+      <c r="V72" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="W72" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="X72" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y72" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="Z72" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA72" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB72" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC72" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD72" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE72" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF72" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH72" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI72" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ72" s="5">
+        <v>23735.256000000001</v>
       </c>
     </row>
   </sheetData>

--- a/BASE_KEMPARTS.xlsx
+++ b/BASE_KEMPARTS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dash_kp_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3665815-13D9-4495-BE2A-87C9BDF3712C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5645B91-F09B-49FB-B37D-BD81249B5F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{AA580DC9-C95C-4DA9-B895-704AEDCE78B9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{78875E9F-F8B2-45C9-B510-7C6062415979}"/>
   </bookViews>
   <sheets>
     <sheet name="FSP" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7772" uniqueCount="1339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7797" uniqueCount="1342">
   <si>
     <t/>
   </si>
@@ -3321,6 +3321,15 @@
   </si>
   <si>
     <t>173873</t>
+  </si>
+  <si>
+    <t>000015566</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>173878</t>
   </si>
   <si>
     <t>003310</t>
@@ -4984,8 +4993,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{721A248D-7949-4F08-ACA9-1D45E33E30C7}">
-  <dimension ref="A1:AJ237"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1C22518-2E03-4AF8-94AF-81F32468EBBC}">
+  <dimension ref="A1:AJ238"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -31095,13 +31104,123 @@
         <v>0</v>
       </c>
     </row>
+    <row r="238" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A238" s="2" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D238" s="4">
+        <v>46094</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F238" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G238" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="H238" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="I238" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="J238" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="K238" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L238" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="M238" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="N238" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O238" s="5">
+        <v>0</v>
+      </c>
+      <c r="P238" s="5">
+        <v>2103.25</v>
+      </c>
+      <c r="Q238" s="6">
+        <v>2103.25</v>
+      </c>
+      <c r="R238" s="6">
+        <v>68.36</v>
+      </c>
+      <c r="S238" s="6">
+        <v>2171.61</v>
+      </c>
+      <c r="T238" s="6">
+        <v>2103.25</v>
+      </c>
+      <c r="U238" s="6">
+        <v>378.59</v>
+      </c>
+      <c r="V238" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="W238" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="X238" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="Y238" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="Z238" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA238" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB238" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC238" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD238" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE238" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF238" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG238" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH238" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI238" s="6">
+        <v>18</v>
+      </c>
+      <c r="AJ238" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66E8590A-227B-4AA7-93BD-7C8719288B78}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26A9CA2A-55CB-4E16-8C38-D221AD8EA67E}">
   <dimension ref="A1:AJ73"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -31253,13 +31372,13 @@
     </row>
     <row r="2" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D2" s="4">
         <v>46024</v>
@@ -31271,10 +31390,10 @@
         <v>40</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>43</v>
@@ -31286,13 +31405,13 @@
         <v>440</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="O2" s="5">
         <v>50</v>
@@ -31316,16 +31435,16 @@
         <v>39.06</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="Z2" s="2" t="s">
         <v>0</v>
@@ -31363,13 +31482,13 @@
     </row>
     <row r="3" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D3" s="7">
         <v>46027</v>
@@ -31381,10 +31500,10 @@
         <v>61</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>163</v>
@@ -31396,13 +31515,13 @@
         <v>632</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>648</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="O3" s="8">
         <v>1001</v>
@@ -31435,7 +31554,7 @@
         <v>51</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="Z3" s="3" t="s">
         <v>0</v>
@@ -31473,13 +31592,13 @@
     </row>
     <row r="4" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D4" s="4">
         <v>46027</v>
@@ -31491,10 +31610,10 @@
         <v>61</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>152</v>
@@ -31506,13 +31625,13 @@
         <v>342</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1329</v>
+        <v>1332</v>
       </c>
       <c r="O4" s="5">
         <v>600</v>
@@ -31536,16 +31655,16 @@
         <v>355.68</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>1327</v>
+        <v>1330</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>1326</v>
+        <v>1329</v>
       </c>
       <c r="Z4" s="2" t="s">
         <v>0</v>
@@ -31583,13 +31702,13 @@
     </row>
     <row r="5" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D5" s="7">
         <v>46029</v>
@@ -31601,10 +31720,10 @@
         <v>212</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>139</v>
@@ -31613,7 +31732,7 @@
         <v>140</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>0</v>
@@ -31655,7 +31774,7 @@
         <v>87</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="Z5" s="3" t="s">
         <v>0</v>
@@ -31693,13 +31812,13 @@
     </row>
     <row r="6" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D6" s="4">
         <v>46029</v>
@@ -31711,10 +31830,10 @@
         <v>212</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>139</v>
@@ -31723,7 +31842,7 @@
         <v>140</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>0</v>
@@ -31765,7 +31884,7 @@
         <v>87</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="Z6" s="2" t="s">
         <v>0</v>
@@ -31803,13 +31922,13 @@
     </row>
     <row r="7" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D7" s="7">
         <v>46029</v>
@@ -31827,22 +31946,22 @@
         <v>386</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>1058</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="O7" s="8">
         <v>1000</v>
@@ -31875,7 +31994,7 @@
         <v>51</v>
       </c>
       <c r="Y7" s="3" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="Z7" s="3" t="s">
         <v>0</v>
@@ -31913,13 +32032,13 @@
     </row>
     <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D8" s="4">
         <v>46036</v>
@@ -31931,10 +32050,10 @@
         <v>61</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>163</v>
@@ -31946,13 +32065,13 @@
         <v>632</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="O8" s="5">
         <v>1001</v>
@@ -31985,7 +32104,7 @@
         <v>51</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="Z8" s="2" t="s">
         <v>0</v>
@@ -32023,13 +32142,13 @@
     </row>
     <row r="9" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D9" s="7">
         <v>46037</v>
@@ -32041,10 +32160,10 @@
         <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>163</v>
@@ -32056,13 +32175,13 @@
         <v>417</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>1041</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="O9" s="8">
         <v>1000</v>
@@ -32095,7 +32214,7 @@
         <v>51</v>
       </c>
       <c r="Y9" s="3" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
       <c r="Z9" s="3" t="s">
         <v>0</v>
@@ -32133,13 +32252,13 @@
     </row>
     <row r="10" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D10" s="4">
         <v>46037</v>
@@ -32151,10 +32270,10 @@
         <v>40</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>139</v>
@@ -32166,13 +32285,13 @@
         <v>782</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="O10" s="5">
         <v>300</v>
@@ -32205,7 +32324,7 @@
         <v>51</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
       <c r="Z10" s="2" t="s">
         <v>0</v>
@@ -32243,13 +32362,13 @@
     </row>
     <row r="11" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D11" s="7">
         <v>46037</v>
@@ -32261,10 +32380,10 @@
         <v>40</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>43</v>
@@ -32276,13 +32395,13 @@
         <v>300</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="O11" s="8">
         <v>25</v>
@@ -32315,7 +32434,7 @@
         <v>51</v>
       </c>
       <c r="Y11" s="3" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="Z11" s="3" t="s">
         <v>0</v>
@@ -32353,13 +32472,13 @@
     </row>
     <row r="12" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D12" s="4">
         <v>46041</v>
@@ -32371,10 +32490,10 @@
         <v>212</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>139</v>
@@ -32383,7 +32502,7 @@
         <v>140</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>0</v>
@@ -32425,7 +32544,7 @@
         <v>87</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="Z12" s="2" t="s">
         <v>0</v>
@@ -32440,10 +32559,10 @@
         <v>55</v>
       </c>
       <c r="AD12" s="2" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="AF12" s="2" t="s">
         <v>442</v>
@@ -32463,13 +32582,13 @@
     </row>
     <row r="13" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D13" s="7">
         <v>46042</v>
@@ -32487,22 +32606,22 @@
         <v>386</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>446</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="O13" s="8">
         <v>2000</v>
@@ -32535,7 +32654,7 @@
         <v>51</v>
       </c>
       <c r="Y13" s="3" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="Z13" s="3" t="s">
         <v>0</v>
@@ -32573,13 +32692,13 @@
     </row>
     <row r="14" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D14" s="4">
         <v>46042</v>
@@ -32603,16 +32722,16 @@
         <v>294</v>
       </c>
       <c r="K14" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>1276</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="N14" s="2" t="s">
         <v>1157</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>1273</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>1272</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>1154</v>
       </c>
       <c r="O14" s="5">
         <v>6000</v>
@@ -32636,16 +32755,16 @@
         <v>12873.6</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="X14" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="Z14" s="2" t="s">
         <v>0</v>
@@ -32660,10 +32779,10 @@
         <v>298</v>
       </c>
       <c r="AD14" s="2" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="AE14" s="2" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="AF14" s="2" t="s">
         <v>77</v>
@@ -32683,13 +32802,13 @@
     </row>
     <row r="15" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D15" s="7">
         <v>46042</v>
@@ -32701,10 +32820,10 @@
         <v>212</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>139</v>
@@ -32755,7 +32874,7 @@
         <v>87</v>
       </c>
       <c r="Y15" s="3" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>0</v>
@@ -32776,7 +32895,7 @@
         <v>518</v>
       </c>
       <c r="AF15" s="3" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="AG15" s="9">
         <v>0</v>
@@ -32793,13 +32912,13 @@
     </row>
     <row r="16" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D16" s="4">
         <v>46042</v>
@@ -32811,10 +32930,10 @@
         <v>212</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>139</v>
@@ -32865,7 +32984,7 @@
         <v>87</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="Z16" s="2" t="s">
         <v>0</v>
@@ -32886,7 +33005,7 @@
         <v>518</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="AG16" s="6">
         <v>0</v>
@@ -32903,13 +33022,13 @@
     </row>
     <row r="17" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D17" s="7">
         <v>46043</v>
@@ -32936,13 +33055,13 @@
         <v>417</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="O17" s="8">
         <v>1000</v>
@@ -32975,7 +33094,7 @@
         <v>51</v>
       </c>
       <c r="Y17" s="3" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="Z17" s="3" t="s">
         <v>0</v>
@@ -33013,28 +33132,28 @@
     </row>
     <row r="18" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D18" s="4">
         <v>46045</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>1116</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>1115</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>1114</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>1113</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>139</v>
@@ -33046,13 +33165,13 @@
         <v>628</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="O18" s="5">
         <v>2000</v>
@@ -33076,16 +33195,16 @@
         <v>0</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="X18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="Z18" s="2" t="s">
         <v>0</v>
@@ -33123,28 +33242,28 @@
     </row>
     <row r="19" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D19" s="7">
         <v>46045</v>
       </c>
       <c r="E19" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>1116</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>1115</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>1114</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>1113</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>139</v>
@@ -33156,13 +33275,13 @@
         <v>631</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="O19" s="8">
         <v>11725</v>
@@ -33186,16 +33305,16 @@
         <v>0</v>
       </c>
       <c r="V19" s="3" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="W19" s="3" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="X19" s="3" t="s">
         <v>87</v>
       </c>
       <c r="Y19" s="3" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="Z19" s="3" t="s">
         <v>0</v>
@@ -33233,28 +33352,28 @@
     </row>
     <row r="20" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D20" s="4">
         <v>46045</v>
       </c>
       <c r="E20" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>1116</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>1115</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>1114</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>1113</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>139</v>
@@ -33266,13 +33385,13 @@
         <v>632</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="O20" s="5">
         <v>2925</v>
@@ -33296,16 +33415,16 @@
         <v>0</v>
       </c>
       <c r="V20" s="2" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="X20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="Z20" s="2" t="s">
         <v>0</v>
@@ -33343,28 +33462,28 @@
     </row>
     <row r="21" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D21" s="7">
         <v>46045</v>
       </c>
       <c r="E21" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>1116</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>1115</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>1114</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>1113</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>139</v>
@@ -33376,13 +33495,13 @@
         <v>633</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>652</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="O21" s="8">
         <v>2925</v>
@@ -33406,16 +33525,16 @@
         <v>0</v>
       </c>
       <c r="V21" s="3" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="W21" s="3" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>87</v>
       </c>
       <c r="Y21" s="3" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>0</v>
@@ -33453,28 +33572,28 @@
     </row>
     <row r="22" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D22" s="4">
         <v>46045</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>1116</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>1115</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>1114</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>1113</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>139</v>
@@ -33486,13 +33605,13 @@
         <v>465</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="O22" s="5">
         <v>2400</v>
@@ -33516,16 +33635,16 @@
         <v>0</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="X22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="Z22" s="2" t="s">
         <v>0</v>
@@ -33563,28 +33682,28 @@
     </row>
     <row r="23" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D23" s="7">
         <v>46045</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>1116</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>1115</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>1114</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>1113</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>139</v>
@@ -33596,13 +33715,13 @@
         <v>465</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="O23" s="8">
         <v>1800</v>
@@ -33626,16 +33745,16 @@
         <v>0</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>87</v>
       </c>
       <c r="Y23" s="3" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="Z23" s="3" t="s">
         <v>0</v>
@@ -33673,28 +33792,28 @@
     </row>
     <row r="24" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D24" s="4">
         <v>46045</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>1116</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>1115</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>1114</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>1113</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>139</v>
@@ -33706,13 +33825,13 @@
         <v>634</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="O24" s="5">
         <v>1400</v>
@@ -33736,16 +33855,16 @@
         <v>0</v>
       </c>
       <c r="V24" s="2" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="X24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="Z24" s="2" t="s">
         <v>0</v>
@@ -33783,13 +33902,13 @@
     </row>
     <row r="25" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D25" s="7">
         <v>46048</v>
@@ -33816,13 +33935,13 @@
         <v>417</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="O25" s="8">
         <v>5000</v>
@@ -33846,16 +33965,16 @@
         <v>2354</v>
       </c>
       <c r="V25" s="3" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="W25" s="3" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="X25" s="3" t="s">
         <v>51</v>
       </c>
       <c r="Y25" s="3" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="Z25" s="3" t="s">
         <v>0</v>
@@ -33893,13 +34012,13 @@
     </row>
     <row r="26" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D26" s="4">
         <v>46048</v>
@@ -33911,10 +34030,10 @@
         <v>40</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>139</v>
@@ -33926,13 +34045,13 @@
         <v>782</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="O26" s="5">
         <v>300</v>
@@ -33965,7 +34084,7 @@
         <v>51</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="Z26" s="2" t="s">
         <v>0</v>
@@ -34003,13 +34122,13 @@
     </row>
     <row r="27" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D27" s="7">
         <v>46048</v>
@@ -34021,10 +34140,10 @@
         <v>61</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>163</v>
@@ -34036,13 +34155,13 @@
         <v>632</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>648</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="O27" s="8">
         <v>611</v>
@@ -34075,7 +34194,7 @@
         <v>51</v>
       </c>
       <c r="Y27" s="3" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="Z27" s="3" t="s">
         <v>0</v>
@@ -34113,13 +34232,13 @@
     </row>
     <row r="28" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D28" s="4">
         <v>46048</v>
@@ -34131,10 +34250,10 @@
         <v>61</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>163</v>
@@ -34143,16 +34262,16 @@
         <v>164</v>
       </c>
       <c r="K28" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>1276</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="N28" s="2" t="s">
         <v>1157</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>1273</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>1272</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>1154</v>
       </c>
       <c r="O28" s="5">
         <v>700</v>
@@ -34185,7 +34304,7 @@
         <v>51</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="Z28" s="2" t="s">
         <v>0</v>
@@ -34200,10 +34319,10 @@
         <v>55</v>
       </c>
       <c r="AD28" s="2" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="AE28" s="2" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="AF28" s="2" t="s">
         <v>77</v>
@@ -34223,13 +34342,13 @@
     </row>
     <row r="29" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D29" s="7">
         <v>46048</v>
@@ -34241,10 +34360,10 @@
         <v>212</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>139</v>
@@ -34295,7 +34414,7 @@
         <v>87</v>
       </c>
       <c r="Y29" s="3" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>0</v>
@@ -34316,7 +34435,7 @@
         <v>57</v>
       </c>
       <c r="AF29" s="3" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="AG29" s="9">
         <v>0</v>
@@ -34333,13 +34452,13 @@
     </row>
     <row r="30" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D30" s="4">
         <v>46049</v>
@@ -34351,10 +34470,10 @@
         <v>212</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>139</v>
@@ -34405,7 +34524,7 @@
         <v>87</v>
       </c>
       <c r="Y30" s="2" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="Z30" s="2" t="s">
         <v>0</v>
@@ -34443,13 +34562,13 @@
     </row>
     <row r="31" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D31" s="7">
         <v>46049</v>
@@ -34461,10 +34580,10 @@
         <v>212</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>139</v>
@@ -34515,7 +34634,7 @@
         <v>87</v>
       </c>
       <c r="Y31" s="3" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="Z31" s="3" t="s">
         <v>0</v>
@@ -34553,13 +34672,13 @@
     </row>
     <row r="32" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D32" s="4">
         <v>46050</v>
@@ -34577,22 +34696,22 @@
         <v>386</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>446</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>448</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="O32" s="5">
         <v>1000</v>
@@ -34625,7 +34744,7 @@
         <v>51</v>
       </c>
       <c r="Y32" s="2" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="Z32" s="2" t="s">
         <v>0</v>
@@ -34663,13 +34782,13 @@
     </row>
     <row r="33" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D33" s="7">
         <v>46050</v>
@@ -34687,22 +34806,22 @@
         <v>386</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>446</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="O33" s="8">
         <v>1000</v>
@@ -34735,7 +34854,7 @@
         <v>51</v>
       </c>
       <c r="Y33" s="3" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="Z33" s="3" t="s">
         <v>0</v>
@@ -34773,13 +34892,13 @@
     </row>
     <row r="34" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D34" s="4">
         <v>46050</v>
@@ -34791,10 +34910,10 @@
         <v>212</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>139</v>
@@ -34845,7 +34964,7 @@
         <v>87</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="Z34" s="2" t="s">
         <v>0</v>
@@ -34883,13 +35002,13 @@
     </row>
     <row r="35" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D35" s="7">
         <v>46051</v>
@@ -34901,10 +35020,10 @@
         <v>40</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>43</v>
@@ -34916,13 +35035,13 @@
         <v>632</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>648</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="O35" s="8">
         <v>26</v>
@@ -34955,7 +35074,7 @@
         <v>51</v>
       </c>
       <c r="Y35" s="3" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="Z35" s="3" t="s">
         <v>0</v>
@@ -34993,13 +35112,13 @@
     </row>
     <row r="36" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D36" s="4">
         <v>46052</v>
@@ -35011,10 +35130,10 @@
         <v>61</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>163</v>
@@ -35026,13 +35145,13 @@
         <v>632</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="O36" s="5">
         <v>507</v>
@@ -35065,7 +35184,7 @@
         <v>51</v>
       </c>
       <c r="Y36" s="2" t="s">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="Z36" s="2" t="s">
         <v>0</v>
@@ -35103,13 +35222,13 @@
     </row>
     <row r="37" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D37" s="7">
         <v>46052</v>
@@ -35133,16 +35252,16 @@
         <v>164</v>
       </c>
       <c r="K37" s="3" t="s">
+        <v>1165</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>1182</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>1181</v>
+      </c>
+      <c r="N37" s="3" t="s">
         <v>1162</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>1179</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>1178</v>
-      </c>
-      <c r="N37" s="3" t="s">
-        <v>1159</v>
       </c>
       <c r="O37" s="8">
         <v>500</v>
@@ -35175,7 +35294,7 @@
         <v>51</v>
       </c>
       <c r="Y37" s="3" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="Z37" s="3" t="s">
         <v>0</v>
@@ -35213,13 +35332,13 @@
     </row>
     <row r="38" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D38" s="4">
         <v>46052</v>
@@ -35231,10 +35350,10 @@
         <v>40</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>139</v>
@@ -35246,13 +35365,13 @@
         <v>782</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="O38" s="5">
         <v>300</v>
@@ -35285,7 +35404,7 @@
         <v>51</v>
       </c>
       <c r="Y38" s="2" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>0</v>
@@ -35323,13 +35442,13 @@
     </row>
     <row r="39" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D39" s="7">
         <v>46055</v>
@@ -35341,10 +35460,10 @@
         <v>212</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>139</v>
@@ -35353,7 +35472,7 @@
         <v>140</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>0</v>
@@ -35395,7 +35514,7 @@
         <v>87</v>
       </c>
       <c r="Y39" s="3" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="Z39" s="3" t="s">
         <v>0</v>
@@ -35433,13 +35552,13 @@
     </row>
     <row r="40" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D40" s="4">
         <v>46057</v>
@@ -35451,10 +35570,10 @@
         <v>61</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>163</v>
@@ -35466,13 +35585,13 @@
         <v>632</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="O40" s="5">
         <v>507</v>
@@ -35505,7 +35624,7 @@
         <v>51</v>
       </c>
       <c r="Y40" s="2" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="Z40" s="2" t="s">
         <v>0</v>
@@ -35543,13 +35662,13 @@
     </row>
     <row r="41" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D41" s="7">
         <v>46057</v>
@@ -35567,22 +35686,22 @@
         <v>386</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>446</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="O41" s="8">
         <v>2000</v>
@@ -35615,7 +35734,7 @@
         <v>51</v>
       </c>
       <c r="Y41" s="3" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="Z41" s="3" t="s">
         <v>0</v>
@@ -35653,13 +35772,13 @@
     </row>
     <row r="42" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D42" s="4">
         <v>46058</v>
@@ -35671,10 +35790,10 @@
         <v>61</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>163</v>
@@ -35686,13 +35805,13 @@
         <v>632</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="O42" s="5">
         <v>507</v>
@@ -35725,7 +35844,7 @@
         <v>51</v>
       </c>
       <c r="Y42" s="2" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="Z42" s="2" t="s">
         <v>0</v>
@@ -35763,13 +35882,13 @@
     </row>
     <row r="43" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D43" s="7">
         <v>46058</v>
@@ -35781,10 +35900,10 @@
         <v>61</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>163</v>
@@ -35796,13 +35915,13 @@
         <v>417</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="O43" s="8">
         <v>1800</v>
@@ -35835,7 +35954,7 @@
         <v>51</v>
       </c>
       <c r="Y43" s="3" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="Z43" s="3" t="s">
         <v>0</v>
@@ -35873,13 +35992,13 @@
     </row>
     <row r="44" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>1238</v>
+        <v>1241</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>1238</v>
+        <v>1241</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D44" s="4">
         <v>46059</v>
@@ -35891,10 +36010,10 @@
         <v>40</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>43</v>
@@ -35906,13 +36025,13 @@
         <v>782</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="O44" s="5">
         <v>500</v>
@@ -35945,7 +36064,7 @@
         <v>51</v>
       </c>
       <c r="Y44" s="2" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
       <c r="Z44" s="2" t="s">
         <v>0</v>
@@ -35983,13 +36102,13 @@
     </row>
     <row r="45" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D45" s="7">
         <v>46059</v>
@@ -36001,10 +36120,10 @@
         <v>40</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>43</v>
@@ -36016,13 +36135,13 @@
         <v>417</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="O45" s="8">
         <v>200</v>
@@ -36055,7 +36174,7 @@
         <v>51</v>
       </c>
       <c r="Y45" s="3" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
       <c r="Z45" s="3" t="s">
         <v>0</v>
@@ -36093,28 +36212,28 @@
     </row>
     <row r="46" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D46" s="4">
         <v>46063</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>267</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>139</v>
@@ -36123,7 +36242,7 @@
         <v>140</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>0</v>
@@ -36165,7 +36284,7 @@
         <v>0</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="Z46" s="2" t="s">
         <v>0</v>
@@ -36180,10 +36299,10 @@
         <v>74</v>
       </c>
       <c r="AD46" s="2" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="AE46" s="2" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="AF46" s="2" t="s">
         <v>0</v>
@@ -36203,13 +36322,13 @@
     </row>
     <row r="47" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D47" s="7">
         <v>46064</v>
@@ -36221,10 +36340,10 @@
         <v>61</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>139</v>
@@ -36236,13 +36355,13 @@
         <v>417</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="O47" s="8">
         <v>1000</v>
@@ -36275,7 +36394,7 @@
         <v>51</v>
       </c>
       <c r="Y47" s="3" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="Z47" s="3" t="s">
         <v>0</v>
@@ -36313,13 +36432,13 @@
     </row>
     <row r="48" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D48" s="4">
         <v>46064</v>
@@ -36337,22 +36456,22 @@
         <v>386</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>446</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="O48" s="5">
         <v>1000</v>
@@ -36385,7 +36504,7 @@
         <v>51</v>
       </c>
       <c r="Y48" s="2" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="Z48" s="2" t="s">
         <v>0</v>
@@ -36423,13 +36542,13 @@
     </row>
     <row r="49" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D49" s="7">
         <v>46064</v>
@@ -36447,22 +36566,22 @@
         <v>386</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>446</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="O49" s="8">
         <v>1000</v>
@@ -36495,7 +36614,7 @@
         <v>51</v>
       </c>
       <c r="Y49" s="3" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>0</v>
@@ -36533,13 +36652,13 @@
     </row>
     <row r="50" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D50" s="4">
         <v>46066</v>
@@ -36551,10 +36670,10 @@
         <v>61</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>163</v>
@@ -36566,13 +36685,13 @@
         <v>632</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="M50" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="O50" s="5">
         <v>507</v>
@@ -36605,7 +36724,7 @@
         <v>51</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="Z50" s="2" t="s">
         <v>0</v>
@@ -36643,13 +36762,13 @@
     </row>
     <row r="51" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D51" s="7">
         <v>46071</v>
@@ -36673,16 +36792,16 @@
         <v>164</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="O51" s="8">
         <v>500</v>
@@ -36715,7 +36834,7 @@
         <v>51</v>
       </c>
       <c r="Y51" s="3" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="Z51" s="3" t="s">
         <v>0</v>
@@ -36730,10 +36849,10 @@
         <v>111</v>
       </c>
       <c r="AD51" s="3" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="AE51" s="3" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="AF51" s="3" t="s">
         <v>77</v>
@@ -36753,13 +36872,13 @@
     </row>
     <row r="52" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D52" s="4">
         <v>46071</v>
@@ -36771,10 +36890,10 @@
         <v>61</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>139</v>
@@ -36786,13 +36905,13 @@
         <v>446</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="O52" s="5">
         <v>200</v>
@@ -36825,7 +36944,7 @@
         <v>51</v>
       </c>
       <c r="Y52" s="2" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="Z52" s="2" t="s">
         <v>0</v>
@@ -36863,13 +36982,13 @@
     </row>
     <row r="53" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D53" s="7">
         <v>46072</v>
@@ -36881,10 +37000,10 @@
         <v>40</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>43</v>
@@ -36896,13 +37015,13 @@
         <v>440</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="O53" s="8">
         <v>50</v>
@@ -36926,16 +37045,16 @@
         <v>0</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="X53" s="3" t="s">
         <v>51</v>
       </c>
       <c r="Y53" s="3" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
       <c r="Z53" s="3" t="s">
         <v>0</v>
@@ -36973,13 +37092,13 @@
     </row>
     <row r="54" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D54" s="4">
         <v>46072</v>
@@ -36991,10 +37110,10 @@
         <v>61</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>163</v>
@@ -37006,13 +37125,13 @@
         <v>417</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="O54" s="5">
         <v>1600</v>
@@ -37045,7 +37164,7 @@
         <v>51</v>
       </c>
       <c r="Y54" s="2" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="Z54" s="2" t="s">
         <v>0</v>
@@ -37083,13 +37202,13 @@
     </row>
     <row r="55" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D55" s="7">
         <v>46072</v>
@@ -37101,10 +37220,10 @@
         <v>40</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>43</v>
@@ -37116,13 +37235,13 @@
         <v>446</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="O55" s="8">
         <v>500</v>
@@ -37155,7 +37274,7 @@
         <v>51</v>
       </c>
       <c r="Y55" s="3" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="Z55" s="3" t="s">
         <v>0</v>
@@ -37193,13 +37312,13 @@
     </row>
     <row r="56" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D56" s="4">
         <v>46076</v>
@@ -37211,10 +37330,10 @@
         <v>61</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>163</v>
@@ -37226,13 +37345,13 @@
         <v>417</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="O56" s="5">
         <v>1700</v>
@@ -37265,7 +37384,7 @@
         <v>51</v>
       </c>
       <c r="Y56" s="2" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="Z56" s="2" t="s">
         <v>0</v>
@@ -37303,13 +37422,13 @@
     </row>
     <row r="57" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D57" s="7">
         <v>46077</v>
@@ -37333,16 +37452,16 @@
         <v>164</v>
       </c>
       <c r="K57" s="3" t="s">
+        <v>1165</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>1182</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>1181</v>
+      </c>
+      <c r="N57" s="3" t="s">
         <v>1162</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>1179</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>1178</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>1159</v>
       </c>
       <c r="O57" s="8">
         <v>500</v>
@@ -37375,7 +37494,7 @@
         <v>51</v>
       </c>
       <c r="Y57" s="3" t="s">
-        <v>1176</v>
+        <v>1179</v>
       </c>
       <c r="Z57" s="3" t="s">
         <v>0</v>
@@ -37413,13 +37532,13 @@
     </row>
     <row r="58" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D58" s="4">
         <v>46077</v>
@@ -37443,16 +37562,16 @@
         <v>164</v>
       </c>
       <c r="K58" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="N58" s="2" t="s">
         <v>1157</v>
-      </c>
-      <c r="L58" s="2" t="s">
-        <v>1156</v>
-      </c>
-      <c r="M58" s="2" t="s">
-        <v>1155</v>
-      </c>
-      <c r="N58" s="2" t="s">
-        <v>1154</v>
       </c>
       <c r="O58" s="5">
         <v>500</v>
@@ -37485,7 +37604,7 @@
         <v>51</v>
       </c>
       <c r="Y58" s="2" t="s">
-        <v>1176</v>
+        <v>1179</v>
       </c>
       <c r="Z58" s="2" t="s">
         <v>0</v>
@@ -37500,10 +37619,10 @@
         <v>111</v>
       </c>
       <c r="AD58" s="2" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="AE58" s="2" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="AF58" s="2" t="s">
         <v>77</v>
@@ -37523,13 +37642,13 @@
     </row>
     <row r="59" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D59" s="7">
         <v>46078</v>
@@ -37541,10 +37660,10 @@
         <v>40</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>139</v>
@@ -37556,13 +37675,13 @@
         <v>782</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="O59" s="8">
         <v>225</v>
@@ -37595,7 +37714,7 @@
         <v>51</v>
       </c>
       <c r="Y59" s="3" t="s">
-        <v>1174</v>
+        <v>1177</v>
       </c>
       <c r="Z59" s="3" t="s">
         <v>0</v>
@@ -37633,13 +37752,13 @@
     </row>
     <row r="60" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D60" s="4">
         <v>46079</v>
@@ -37666,13 +37785,13 @@
         <v>417</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="O60" s="5">
         <v>5000</v>
@@ -37696,16 +37815,16 @@
         <v>2354</v>
       </c>
       <c r="V60" s="2" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="W60" s="2" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="X60" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Y60" s="2" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="Z60" s="2" t="s">
         <v>0</v>
@@ -37743,13 +37862,13 @@
     </row>
     <row r="61" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D61" s="7">
         <v>46079</v>
@@ -37776,13 +37895,13 @@
         <v>1058</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="O61" s="8">
         <v>12000</v>
@@ -37815,7 +37934,7 @@
         <v>51</v>
       </c>
       <c r="Y61" s="3" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="Z61" s="3" t="s">
         <v>0</v>
@@ -37853,13 +37972,13 @@
     </row>
     <row r="62" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D62" s="4">
         <v>46085</v>
@@ -37886,13 +38005,13 @@
         <v>633</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>652</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="O62" s="5">
         <v>5005</v>
@@ -37925,7 +38044,7 @@
         <v>51</v>
       </c>
       <c r="Y62" s="2" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="Z62" s="2" t="s">
         <v>0</v>
@@ -37963,13 +38082,13 @@
     </row>
     <row r="63" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D63" s="7">
         <v>46085</v>
@@ -37993,16 +38112,16 @@
         <v>164</v>
       </c>
       <c r="K63" s="3" t="s">
+        <v>1165</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>1164</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>1163</v>
+      </c>
+      <c r="N63" s="3" t="s">
         <v>1162</v>
-      </c>
-      <c r="L63" s="3" t="s">
-        <v>1161</v>
-      </c>
-      <c r="M63" s="3" t="s">
-        <v>1160</v>
-      </c>
-      <c r="N63" s="3" t="s">
-        <v>1159</v>
       </c>
       <c r="O63" s="8">
         <v>500</v>
@@ -38035,7 +38154,7 @@
         <v>51</v>
       </c>
       <c r="Y63" s="3" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="Z63" s="3" t="s">
         <v>0</v>
@@ -38073,13 +38192,13 @@
     </row>
     <row r="64" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D64" s="4">
         <v>46085</v>
@@ -38103,16 +38222,16 @@
         <v>164</v>
       </c>
       <c r="K64" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="N64" s="2" t="s">
         <v>1157</v>
-      </c>
-      <c r="L64" s="2" t="s">
-        <v>1156</v>
-      </c>
-      <c r="M64" s="2" t="s">
-        <v>1155</v>
-      </c>
-      <c r="N64" s="2" t="s">
-        <v>1154</v>
       </c>
       <c r="O64" s="5">
         <v>500</v>
@@ -38145,7 +38264,7 @@
         <v>51</v>
       </c>
       <c r="Y64" s="2" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="Z64" s="2" t="s">
         <v>0</v>
@@ -38160,10 +38279,10 @@
         <v>111</v>
       </c>
       <c r="AD64" s="2" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="AE64" s="2" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="AF64" s="2" t="s">
         <v>77</v>
@@ -38183,13 +38302,13 @@
     </row>
     <row r="65" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D65" s="7">
         <v>46085</v>
@@ -38201,10 +38320,10 @@
         <v>40</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>163</v>
@@ -38216,13 +38335,13 @@
         <v>154</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
       <c r="O65" s="8">
         <v>3700</v>
@@ -38255,7 +38374,7 @@
         <v>51</v>
       </c>
       <c r="Y65" s="3" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="Z65" s="3" t="s">
         <v>0</v>
@@ -38293,13 +38412,13 @@
     </row>
     <row r="66" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D66" s="4">
         <v>46085</v>
@@ -38311,10 +38430,10 @@
         <v>40</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>139</v>
@@ -38323,7 +38442,7 @@
         <v>140</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>0</v>
@@ -38365,7 +38484,7 @@
         <v>0</v>
       </c>
       <c r="Y66" s="2" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="Z66" s="2" t="s">
         <v>0</v>
@@ -38380,10 +38499,10 @@
         <v>298</v>
       </c>
       <c r="AD66" s="2" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="AE66" s="2" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="AF66" s="2" t="s">
         <v>0</v>
@@ -38403,13 +38522,13 @@
     </row>
     <row r="67" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D67" s="7">
         <v>46091</v>
@@ -38436,13 +38555,13 @@
         <v>417</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="N67" s="3" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="O67" s="8">
         <v>5000</v>
@@ -38466,16 +38585,16 @@
         <v>2354</v>
       </c>
       <c r="V67" s="3" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="W67" s="3" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="X67" s="3" t="s">
         <v>51</v>
       </c>
       <c r="Y67" s="3" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="Z67" s="3" t="s">
         <v>0</v>
@@ -38513,13 +38632,13 @@
     </row>
     <row r="68" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D68" s="4">
         <v>46091</v>
@@ -38531,10 +38650,10 @@
         <v>40</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>139</v>
@@ -38546,13 +38665,13 @@
         <v>782</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="O68" s="5">
         <v>225</v>
@@ -38585,7 +38704,7 @@
         <v>51</v>
       </c>
       <c r="Y68" s="2" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="Z68" s="2" t="s">
         <v>0</v>
@@ -38623,28 +38742,28 @@
     </row>
     <row r="69" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D69" s="7">
         <v>46092</v>
       </c>
       <c r="E69" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H69" s="3" t="s">
         <v>1116</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>1115</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>1114</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>1113</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>139</v>
@@ -38656,13 +38775,13 @@
         <v>272</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="M69" s="3" t="s">
         <v>274</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="O69" s="8">
         <v>10000</v>
@@ -38686,16 +38805,16 @@
         <v>3312.29</v>
       </c>
       <c r="V69" s="3" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="W69" s="3" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="X69" s="3" t="s">
         <v>87</v>
       </c>
       <c r="Y69" s="3" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="Z69" s="3" t="s">
         <v>0</v>
@@ -38733,28 +38852,28 @@
     </row>
     <row r="70" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D70" s="4">
         <v>46092</v>
       </c>
       <c r="E70" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H70" s="2" t="s">
         <v>1116</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>1115</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>1114</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>1113</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>139</v>
@@ -38766,13 +38885,13 @@
         <v>417</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="O70" s="5">
         <v>5000</v>
@@ -38796,16 +38915,16 @@
         <v>1559.15</v>
       </c>
       <c r="V70" s="2" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="W70" s="2" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="X70" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y70" s="2" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="Z70" s="2" t="s">
         <v>0</v>
@@ -38843,28 +38962,28 @@
     </row>
     <row r="71" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D71" s="7">
         <v>46092</v>
       </c>
       <c r="E71" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H71" s="3" t="s">
         <v>1116</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>1115</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>1114</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>1113</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>139</v>
@@ -38876,13 +38995,13 @@
         <v>342</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="N71" s="3" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="O71" s="8">
         <v>8400</v>
@@ -38906,16 +39025,16 @@
         <v>2580.5300000000002</v>
       </c>
       <c r="V71" s="3" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="W71" s="3" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="X71" s="3" t="s">
         <v>87</v>
       </c>
       <c r="Y71" s="3" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="Z71" s="3" t="s">
         <v>0</v>
@@ -38953,28 +39072,28 @@
     </row>
     <row r="72" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D72" s="4">
         <v>46092</v>
       </c>
       <c r="E72" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H72" s="2" t="s">
         <v>1116</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>1115</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>1114</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>1113</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>139</v>
@@ -38986,13 +39105,13 @@
         <v>782</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="O72" s="5">
         <v>2400</v>
@@ -39016,16 +39135,16 @@
         <v>775.1</v>
       </c>
       <c r="V72" s="2" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="W72" s="2" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="X72" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y72" s="2" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="Z72" s="2" t="s">
         <v>0</v>
@@ -39063,13 +39182,13 @@
     </row>
     <row r="73" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D73" s="7">
         <v>46093</v>
@@ -39081,10 +39200,10 @@
         <v>61</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>163</v>
@@ -39096,13 +39215,13 @@
         <v>633</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="M73" s="3" t="s">
         <v>652</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="O73" s="8">
         <v>507</v>
@@ -39135,7 +39254,7 @@
         <v>51</v>
       </c>
       <c r="Y73" s="3" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="Z73" s="3" t="s">
         <v>0</v>

--- a/BASE_KEMPARTS.xlsx
+++ b/BASE_KEMPARTS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dash_kp_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA8A3F2C-866D-42B3-8A3C-2D6D932EF647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{37747EB9-AC77-457C-916A-EFE6DAB95DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{923D3E5D-1ACF-4B7D-A9DE-3134991C402F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{EF136881-73C8-429C-8DA8-74B3A074961C}"/>
   </bookViews>
   <sheets>
     <sheet name="FSP" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5497" uniqueCount="1076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5597" uniqueCount="1084">
   <si>
     <t>Numero</t>
   </si>
@@ -2649,6 +2649,18 @@
     <t>2025.103.08.</t>
   </si>
   <si>
+    <t>000015572</t>
+  </si>
+  <si>
+    <t>C00084</t>
+  </si>
+  <si>
+    <t>COLORART INDUSTRIA E COMERCIO DE TINTAS</t>
+  </si>
+  <si>
+    <t>173896</t>
+  </si>
+  <si>
     <t>000002433</t>
   </si>
   <si>
@@ -3265,6 +3277,18 @@
   </si>
   <si>
     <t>003281</t>
+  </si>
+  <si>
+    <t>000002514</t>
+  </si>
+  <si>
+    <t>003303</t>
+  </si>
+  <si>
+    <t>000002515</t>
+  </si>
+  <si>
+    <t>003320</t>
   </si>
 </sst>
 </file>
@@ -3723,7 +3747,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2E0A97F-906F-4148-9006-57F27B41FC68}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6464A559-2DDB-4F7B-AC86-4AB84A7663F7}">
   <dimension ref="A1:AJ175"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -22023,8 +22047,226 @@
         <v>46573.902600000001</v>
       </c>
     </row>
-    <row r="167" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D167" s="3">
+        <v>46098</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="H167" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="I167" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="J167" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="K167" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="L167" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="M167" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="N167" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="O167" s="4">
+        <v>200</v>
+      </c>
+      <c r="P167" s="4">
+        <v>13.99</v>
+      </c>
+      <c r="Q167" s="5">
+        <v>2798</v>
+      </c>
+      <c r="R167" s="5">
+        <v>90.94</v>
+      </c>
+      <c r="S167" s="5">
+        <v>2888.94</v>
+      </c>
+      <c r="T167" s="5">
+        <v>13990</v>
+      </c>
+      <c r="U167" s="5">
+        <v>503.64</v>
+      </c>
+      <c r="V167" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="W167" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="X167" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y167" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="Z167" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA167" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB167" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC167" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD167" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE167" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF167" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG167" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH167" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI167" s="5">
+        <v>18</v>
+      </c>
+      <c r="AJ167" s="4">
+        <v>1966.3</v>
+      </c>
+    </row>
+    <row r="168" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D168" s="7">
+        <v>46098</v>
+      </c>
+      <c r="E168" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F168" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G168" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="H168" s="6" t="s">
+        <v>872</v>
+      </c>
+      <c r="I168" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="J168" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K168" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="L168" s="6" t="s">
+        <v>815</v>
+      </c>
+      <c r="M168" s="6" t="s">
+        <v>816</v>
+      </c>
+      <c r="N168" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="O168" s="8">
+        <v>800</v>
+      </c>
+      <c r="P168" s="8">
+        <v>13.99</v>
+      </c>
+      <c r="Q168" s="9">
+        <v>11192</v>
+      </c>
+      <c r="R168" s="9">
+        <v>363.74</v>
+      </c>
+      <c r="S168" s="9">
+        <v>11555.74</v>
+      </c>
+      <c r="T168" s="9">
+        <v>13990</v>
+      </c>
+      <c r="U168" s="9">
+        <v>2014.56</v>
+      </c>
+      <c r="V168" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="W168" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="X168" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y168" s="6" t="s">
+        <v>873</v>
+      </c>
+      <c r="Z168" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA168" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB168" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC168" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD168" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE168" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF168" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG168" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH168" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI168" s="9">
+        <v>18</v>
+      </c>
+      <c r="AJ168" s="8">
+        <v>7865.2</v>
+      </c>
+    </row>
     <row r="169" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="170" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="171" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -22038,7 +22280,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA6E2153-9182-4875-A12C-C48238189A2F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91012DBE-85F6-4275-8A99-FD2D47C0B73C}">
   <dimension ref="A1:AJ63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -22189,13 +22431,13 @@
     </row>
     <row r="2" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D2" s="3">
         <v>46024</v>
@@ -22207,10 +22449,10 @@
         <v>39</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>42</v>
@@ -22219,16 +22461,16 @@
         <v>43</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="O2" s="4">
         <v>50</v>
@@ -22252,16 +22494,16 @@
         <v>39.06</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>50</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="Z2" s="2" t="s">
         <v>52</v>
@@ -22299,13 +22541,13 @@
     </row>
     <row r="3" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D3" s="7">
         <v>46027</v>
@@ -22317,10 +22559,10 @@
         <v>61</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>148</v>
@@ -22329,16 +22571,16 @@
         <v>149</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="O3" s="8">
         <v>1001</v>
@@ -22371,7 +22613,7 @@
         <v>50</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="Z3" s="6" t="s">
         <v>52</v>
@@ -22409,13 +22651,13 @@
     </row>
     <row r="4" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D4" s="3">
         <v>46027</v>
@@ -22427,10 +22669,10 @@
         <v>61</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>137</v>
@@ -22442,13 +22684,13 @@
         <v>441</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="O4" s="4">
         <v>600</v>
@@ -22472,16 +22714,16 @@
         <v>355.68</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>50</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="Z4" s="2" t="s">
         <v>52</v>
@@ -22519,13 +22761,13 @@
     </row>
     <row r="5" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D5" s="7">
         <v>46029</v>
@@ -22543,22 +22785,22 @@
         <v>330</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="K5" s="6" t="s">
         <v>852</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="O5" s="8">
         <v>1000</v>
@@ -22591,7 +22833,7 @@
         <v>50</v>
       </c>
       <c r="Y5" s="6" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="Z5" s="6" t="s">
         <v>52</v>
@@ -22629,13 +22871,13 @@
     </row>
     <row r="6" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D6" s="3">
         <v>46036</v>
@@ -22647,10 +22889,10 @@
         <v>61</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>148</v>
@@ -22659,16 +22901,16 @@
         <v>149</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="O6" s="4">
         <v>1001</v>
@@ -22701,7 +22943,7 @@
         <v>50</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="Z6" s="2" t="s">
         <v>52</v>
@@ -22739,13 +22981,13 @@
     </row>
     <row r="7" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D7" s="7">
         <v>46037</v>
@@ -22757,10 +22999,10 @@
         <v>61</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>148</v>
@@ -22772,13 +23014,13 @@
         <v>361</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="M7" s="6" t="s">
         <v>816</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="O7" s="8">
         <v>1000</v>
@@ -22811,7 +23053,7 @@
         <v>50</v>
       </c>
       <c r="Y7" s="6" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="Z7" s="6" t="s">
         <v>52</v>
@@ -22849,13 +23091,13 @@
     </row>
     <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D8" s="3">
         <v>46037</v>
@@ -22867,10 +23109,10 @@
         <v>39</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>174</v>
@@ -22879,16 +23121,16 @@
         <v>175</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="O8" s="4">
         <v>300</v>
@@ -22921,7 +23163,7 @@
         <v>50</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="Z8" s="2" t="s">
         <v>52</v>
@@ -22959,13 +23201,13 @@
     </row>
     <row r="9" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D9" s="7">
         <v>46037</v>
@@ -22977,10 +23219,10 @@
         <v>39</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>42</v>
@@ -22992,13 +23234,13 @@
         <v>494</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="O9" s="8">
         <v>25</v>
@@ -23031,7 +23273,7 @@
         <v>50</v>
       </c>
       <c r="Y9" s="6" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="Z9" s="6" t="s">
         <v>52</v>
@@ -23069,13 +23311,13 @@
     </row>
     <row r="10" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D10" s="7">
         <v>46042</v>
@@ -23093,22 +23335,22 @@
         <v>330</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>382</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="O10" s="8">
         <v>2000</v>
@@ -23141,7 +23383,7 @@
         <v>50</v>
       </c>
       <c r="Y10" s="6" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="Z10" s="6" t="s">
         <v>52</v>
@@ -23179,13 +23421,13 @@
     </row>
     <row r="11" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D11" s="3">
         <v>46042</v>
@@ -23209,16 +23451,16 @@
         <v>276</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="O11" s="4">
         <v>6000</v>
@@ -23242,16 +23484,16 @@
         <v>12873.6</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="X11" s="2" t="s">
         <v>50</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="Z11" s="2" t="s">
         <v>52</v>
@@ -23266,10 +23508,10 @@
         <v>280</v>
       </c>
       <c r="AD11" s="2" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="AE11" s="2" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="AF11" s="2" t="s">
         <v>77</v>
@@ -23289,13 +23531,13 @@
     </row>
     <row r="12" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D12" s="7">
         <v>46043</v>
@@ -23307,10 +23549,10 @@
         <v>61</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>42</v>
@@ -23322,13 +23564,13 @@
         <v>361</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="O12" s="8">
         <v>1000</v>
@@ -23361,7 +23603,7 @@
         <v>50</v>
       </c>
       <c r="Y12" s="6" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="Z12" s="6" t="s">
         <v>52</v>
@@ -23399,13 +23641,13 @@
     </row>
     <row r="13" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D13" s="7">
         <v>46048</v>
@@ -23417,10 +23659,10 @@
         <v>39</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>137</v>
@@ -23432,13 +23674,13 @@
         <v>361</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="O13" s="8">
         <v>5000</v>
@@ -23462,16 +23704,16 @@
         <v>2354</v>
       </c>
       <c r="V13" s="6" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="W13" s="6" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="X13" s="6" t="s">
         <v>50</v>
       </c>
       <c r="Y13" s="6" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="Z13" s="6" t="s">
         <v>52</v>
@@ -23509,13 +23751,13 @@
     </row>
     <row r="14" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D14" s="3">
         <v>46048</v>
@@ -23527,10 +23769,10 @@
         <v>39</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>174</v>
@@ -23539,16 +23781,16 @@
         <v>175</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="O14" s="4">
         <v>300</v>
@@ -23581,7 +23823,7 @@
         <v>50</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="Z14" s="2" t="s">
         <v>52</v>
@@ -23619,13 +23861,13 @@
     </row>
     <row r="15" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D15" s="7">
         <v>46048</v>
@@ -23637,10 +23879,10 @@
         <v>61</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>148</v>
@@ -23649,16 +23891,16 @@
         <v>149</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="O15" s="8">
         <v>611</v>
@@ -23691,7 +23933,7 @@
         <v>50</v>
       </c>
       <c r="Y15" s="6" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="Z15" s="6" t="s">
         <v>52</v>
@@ -23729,13 +23971,13 @@
     </row>
     <row r="16" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D16" s="3">
         <v>46048</v>
@@ -23747,10 +23989,10 @@
         <v>61</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>148</v>
@@ -23759,16 +24001,16 @@
         <v>149</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="O16" s="4">
         <v>700</v>
@@ -23801,7 +24043,7 @@
         <v>50</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="Z16" s="2" t="s">
         <v>52</v>
@@ -23816,10 +24058,10 @@
         <v>55</v>
       </c>
       <c r="AD16" s="2" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="AE16" s="2" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="AF16" s="2" t="s">
         <v>77</v>
@@ -23839,13 +24081,13 @@
     </row>
     <row r="17" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D17" s="3">
         <v>46050</v>
@@ -23863,22 +24105,22 @@
         <v>330</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>382</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>384</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="O17" s="4">
         <v>1000</v>
@@ -23911,7 +24153,7 @@
         <v>50</v>
       </c>
       <c r="Y17" s="2" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="Z17" s="2" t="s">
         <v>52</v>
@@ -23949,13 +24191,13 @@
     </row>
     <row r="18" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D18" s="7">
         <v>46050</v>
@@ -23973,22 +24215,22 @@
         <v>330</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>382</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="O18" s="8">
         <v>1000</v>
@@ -24021,7 +24263,7 @@
         <v>50</v>
       </c>
       <c r="Y18" s="6" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="Z18" s="6" t="s">
         <v>52</v>
@@ -24059,13 +24301,13 @@
     </row>
     <row r="19" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D19" s="7">
         <v>46051</v>
@@ -24077,10 +24319,10 @@
         <v>39</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>42</v>
@@ -24089,16 +24331,16 @@
         <v>43</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="O19" s="8">
         <v>26</v>
@@ -24131,7 +24373,7 @@
         <v>50</v>
       </c>
       <c r="Y19" s="6" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="Z19" s="6" t="s">
         <v>52</v>
@@ -24169,13 +24411,13 @@
     </row>
     <row r="20" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D20" s="3">
         <v>46052</v>
@@ -24187,10 +24429,10 @@
         <v>61</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>148</v>
@@ -24199,16 +24441,16 @@
         <v>149</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="O20" s="4">
         <v>507</v>
@@ -24241,7 +24483,7 @@
         <v>50</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="Z20" s="2" t="s">
         <v>52</v>
@@ -24279,13 +24521,13 @@
     </row>
     <row r="21" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D21" s="7">
         <v>46052</v>
@@ -24309,16 +24551,16 @@
         <v>149</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="O21" s="8">
         <v>500</v>
@@ -24351,7 +24593,7 @@
         <v>50</v>
       </c>
       <c r="Y21" s="6" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="Z21" s="6" t="s">
         <v>52</v>
@@ -24389,13 +24631,13 @@
     </row>
     <row r="22" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D22" s="3">
         <v>46052</v>
@@ -24407,10 +24649,10 @@
         <v>39</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>174</v>
@@ -24419,16 +24661,16 @@
         <v>175</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="O22" s="4">
         <v>300</v>
@@ -24461,7 +24703,7 @@
         <v>50</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="Z22" s="2" t="s">
         <v>52</v>
@@ -24499,13 +24741,13 @@
     </row>
     <row r="23" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D23" s="3">
         <v>46057</v>
@@ -24517,10 +24759,10 @@
         <v>61</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>148</v>
@@ -24529,16 +24771,16 @@
         <v>149</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="O23" s="4">
         <v>507</v>
@@ -24571,7 +24813,7 @@
         <v>50</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="Z23" s="2" t="s">
         <v>52</v>
@@ -24609,13 +24851,13 @@
     </row>
     <row r="24" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D24" s="7">
         <v>46057</v>
@@ -24633,22 +24875,22 @@
         <v>330</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>382</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="O24" s="8">
         <v>2000</v>
@@ -24681,7 +24923,7 @@
         <v>50</v>
       </c>
       <c r="Y24" s="6" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="Z24" s="6" t="s">
         <v>52</v>
@@ -24719,13 +24961,13 @@
     </row>
     <row r="25" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D25" s="3">
         <v>46058</v>
@@ -24737,10 +24979,10 @@
         <v>61</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>148</v>
@@ -24749,16 +24991,16 @@
         <v>149</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="O25" s="4">
         <v>507</v>
@@ -24791,7 +25033,7 @@
         <v>50</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="Z25" s="2" t="s">
         <v>52</v>
@@ -24829,13 +25071,13 @@
     </row>
     <row r="26" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D26" s="7">
         <v>46058</v>
@@ -24847,10 +25089,10 @@
         <v>61</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>148</v>
@@ -24862,13 +25104,13 @@
         <v>361</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="O26" s="8">
         <v>1800</v>
@@ -24901,7 +25143,7 @@
         <v>50</v>
       </c>
       <c r="Y26" s="6" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="Z26" s="6" t="s">
         <v>52</v>
@@ -24939,13 +25181,13 @@
     </row>
     <row r="27" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D27" s="3">
         <v>46059</v>
@@ -24957,10 +25199,10 @@
         <v>39</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>42</v>
@@ -24969,16 +25211,16 @@
         <v>43</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="O27" s="4">
         <v>500</v>
@@ -25011,7 +25253,7 @@
         <v>50</v>
       </c>
       <c r="Y27" s="2" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="Z27" s="2" t="s">
         <v>52</v>
@@ -25049,13 +25291,13 @@
     </row>
     <row r="28" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D28" s="7">
         <v>46059</v>
@@ -25067,10 +25309,10 @@
         <v>39</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>42</v>
@@ -25082,13 +25324,13 @@
         <v>361</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="O28" s="8">
         <v>200</v>
@@ -25121,7 +25363,7 @@
         <v>50</v>
       </c>
       <c r="Y28" s="6" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="Z28" s="6" t="s">
         <v>52</v>
@@ -25159,28 +25401,28 @@
     </row>
     <row r="29" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D29" s="3">
         <v>46063</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>249</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>174</v>
@@ -25189,7 +25431,7 @@
         <v>175</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>52</v>
@@ -25231,7 +25473,7 @@
         <v>52</v>
       </c>
       <c r="Y29" s="2" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="Z29" s="2" t="s">
         <v>52</v>
@@ -25240,16 +25482,16 @@
         <v>53</v>
       </c>
       <c r="AB29" s="2" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="AC29" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AD29" s="2" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="AE29" s="2" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="AF29" s="2" t="s">
         <v>52</v>
@@ -25269,13 +25511,13 @@
     </row>
     <row r="30" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D30" s="7">
         <v>46064</v>
@@ -25287,10 +25529,10 @@
         <v>61</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="I30" s="6" t="s">
         <v>174</v>
@@ -25302,13 +25544,13 @@
         <v>361</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="O30" s="8">
         <v>1000</v>
@@ -25341,7 +25583,7 @@
         <v>50</v>
       </c>
       <c r="Y30" s="6" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="Z30" s="6" t="s">
         <v>52</v>
@@ -25379,13 +25621,13 @@
     </row>
     <row r="31" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D31" s="3">
         <v>46064</v>
@@ -25403,22 +25645,22 @@
         <v>330</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>382</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="O31" s="4">
         <v>1000</v>
@@ -25451,7 +25693,7 @@
         <v>50</v>
       </c>
       <c r="Y31" s="2" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="Z31" s="2" t="s">
         <v>52</v>
@@ -25489,13 +25731,13 @@
     </row>
     <row r="32" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D32" s="7">
         <v>46064</v>
@@ -25513,22 +25755,22 @@
         <v>330</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>382</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="O32" s="8">
         <v>1000</v>
@@ -25561,7 +25803,7 @@
         <v>50</v>
       </c>
       <c r="Y32" s="6" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="Z32" s="6" t="s">
         <v>52</v>
@@ -25599,13 +25841,13 @@
     </row>
     <row r="33" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D33" s="3">
         <v>46066</v>
@@ -25617,10 +25859,10 @@
         <v>61</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>148</v>
@@ -25629,16 +25871,16 @@
         <v>149</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="O33" s="4">
         <v>507</v>
@@ -25671,7 +25913,7 @@
         <v>50</v>
       </c>
       <c r="Y33" s="2" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="Z33" s="2" t="s">
         <v>52</v>
@@ -25709,13 +25951,13 @@
     </row>
     <row r="34" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D34" s="7">
         <v>46071</v>
@@ -25739,16 +25981,16 @@
         <v>149</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="O34" s="8">
         <v>500</v>
@@ -25781,7 +26023,7 @@
         <v>50</v>
       </c>
       <c r="Y34" s="6" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="Z34" s="6" t="s">
         <v>52</v>
@@ -25796,10 +26038,10 @@
         <v>111</v>
       </c>
       <c r="AD34" s="6" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="AE34" s="6" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="AF34" s="6" t="s">
         <v>77</v>
@@ -25819,13 +26061,13 @@
     </row>
     <row r="35" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D35" s="3">
         <v>46071</v>
@@ -25837,10 +26079,10 @@
         <v>61</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>174</v>
@@ -25852,13 +26094,13 @@
         <v>382</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="O35" s="4">
         <v>200</v>
@@ -25891,7 +26133,7 @@
         <v>50</v>
       </c>
       <c r="Y35" s="2" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="Z35" s="2" t="s">
         <v>52</v>
@@ -25929,13 +26171,13 @@
     </row>
     <row r="36" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D36" s="7">
         <v>46072</v>
@@ -25947,10 +26189,10 @@
         <v>39</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="I36" s="6" t="s">
         <v>42</v>
@@ -25959,16 +26201,16 @@
         <v>43</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="O36" s="8">
         <v>50</v>
@@ -25992,16 +26234,16 @@
         <v>0</v>
       </c>
       <c r="V36" s="6" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="W36" s="6" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="X36" s="6" t="s">
         <v>50</v>
       </c>
       <c r="Y36" s="6" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="Z36" s="6" t="s">
         <v>52</v>
@@ -26039,13 +26281,13 @@
     </row>
     <row r="37" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D37" s="3">
         <v>46072</v>
@@ -26057,10 +26299,10 @@
         <v>61</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>148</v>
@@ -26072,13 +26314,13 @@
         <v>361</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="O37" s="4">
         <v>1600</v>
@@ -26111,7 +26353,7 @@
         <v>50</v>
       </c>
       <c r="Y37" s="2" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="Z37" s="2" t="s">
         <v>52</v>
@@ -26149,13 +26391,13 @@
     </row>
     <row r="38" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D38" s="7">
         <v>46072</v>
@@ -26167,10 +26409,10 @@
         <v>39</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="I38" s="6" t="s">
         <v>42</v>
@@ -26182,13 +26424,13 @@
         <v>382</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="O38" s="8">
         <v>500</v>
@@ -26221,7 +26463,7 @@
         <v>50</v>
       </c>
       <c r="Y38" s="6" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="Z38" s="6" t="s">
         <v>52</v>
@@ -26259,13 +26501,13 @@
     </row>
     <row r="39" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D39" s="3">
         <v>46076</v>
@@ -26277,10 +26519,10 @@
         <v>61</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>148</v>
@@ -26292,13 +26534,13 @@
         <v>361</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="O39" s="4">
         <v>1700</v>
@@ -26331,7 +26573,7 @@
         <v>50</v>
       </c>
       <c r="Y39" s="2" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="Z39" s="2" t="s">
         <v>52</v>
@@ -26369,13 +26611,13 @@
     </row>
     <row r="40" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D40" s="7">
         <v>46077</v>
@@ -26399,16 +26641,16 @@
         <v>149</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="O40" s="8">
         <v>500</v>
@@ -26441,7 +26683,7 @@
         <v>50</v>
       </c>
       <c r="Y40" s="6" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="Z40" s="6" t="s">
         <v>52</v>
@@ -26479,13 +26721,13 @@
     </row>
     <row r="41" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D41" s="3">
         <v>46077</v>
@@ -26509,16 +26751,16 @@
         <v>149</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="O41" s="4">
         <v>500</v>
@@ -26551,7 +26793,7 @@
         <v>50</v>
       </c>
       <c r="Y41" s="2" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="Z41" s="2" t="s">
         <v>52</v>
@@ -26566,10 +26808,10 @@
         <v>111</v>
       </c>
       <c r="AD41" s="2" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="AE41" s="2" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="AF41" s="2" t="s">
         <v>77</v>
@@ -26589,13 +26831,13 @@
     </row>
     <row r="42" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D42" s="7">
         <v>46078</v>
@@ -26607,10 +26849,10 @@
         <v>39</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="I42" s="6" t="s">
         <v>174</v>
@@ -26619,16 +26861,16 @@
         <v>175</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="O42" s="8">
         <v>225</v>
@@ -26661,7 +26903,7 @@
         <v>50</v>
       </c>
       <c r="Y42" s="6" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="Z42" s="6" t="s">
         <v>52</v>
@@ -26699,13 +26941,13 @@
     </row>
     <row r="43" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D43" s="3">
         <v>46079</v>
@@ -26717,10 +26959,10 @@
         <v>39</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>137</v>
@@ -26732,13 +26974,13 @@
         <v>361</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="O43" s="4">
         <v>5000</v>
@@ -26762,16 +27004,16 @@
         <v>2354</v>
       </c>
       <c r="V43" s="2" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="W43" s="2" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="X43" s="2" t="s">
         <v>50</v>
       </c>
       <c r="Y43" s="2" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="Z43" s="2" t="s">
         <v>52</v>
@@ -26809,13 +27051,13 @@
     </row>
     <row r="44" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D44" s="7">
         <v>46079</v>
@@ -26842,13 +27084,13 @@
         <v>852</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="O44" s="8">
         <v>12000</v>
@@ -26881,7 +27123,7 @@
         <v>50</v>
       </c>
       <c r="Y44" s="6" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="Z44" s="6" t="s">
         <v>52</v>
@@ -26919,13 +27161,13 @@
     </row>
     <row r="45" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D45" s="3">
         <v>46085</v>
@@ -26949,16 +27191,16 @@
         <v>149</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="O45" s="4">
         <v>5005</v>
@@ -26991,7 +27233,7 @@
         <v>50</v>
       </c>
       <c r="Y45" s="2" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="Z45" s="2" t="s">
         <v>52</v>
@@ -27029,13 +27271,13 @@
     </row>
     <row r="46" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D46" s="7">
         <v>46085</v>
@@ -27059,16 +27301,16 @@
         <v>149</v>
       </c>
       <c r="K46" s="6" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="O46" s="8">
         <v>500</v>
@@ -27101,7 +27343,7 @@
         <v>50</v>
       </c>
       <c r="Y46" s="6" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="Z46" s="6" t="s">
         <v>52</v>
@@ -27139,13 +27381,13 @@
     </row>
     <row r="47" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D47" s="3">
         <v>46085</v>
@@ -27169,16 +27411,16 @@
         <v>149</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="O47" s="4">
         <v>500</v>
@@ -27211,7 +27453,7 @@
         <v>50</v>
       </c>
       <c r="Y47" s="2" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="Z47" s="2" t="s">
         <v>52</v>
@@ -27226,10 +27468,10 @@
         <v>111</v>
       </c>
       <c r="AD47" s="2" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="AE47" s="2" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="AF47" s="2" t="s">
         <v>77</v>
@@ -27249,13 +27491,13 @@
     </row>
     <row r="48" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D48" s="7">
         <v>46085</v>
@@ -27267,10 +27509,10 @@
         <v>39</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="I48" s="6" t="s">
         <v>148</v>
@@ -27282,13 +27524,13 @@
         <v>139</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="O48" s="8">
         <v>3700</v>
@@ -27321,7 +27563,7 @@
         <v>50</v>
       </c>
       <c r="Y48" s="6" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="Z48" s="6" t="s">
         <v>52</v>
@@ -27359,13 +27601,13 @@
     </row>
     <row r="49" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D49" s="3">
         <v>46085</v>
@@ -27377,10 +27619,10 @@
         <v>39</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>174</v>
@@ -27389,7 +27631,7 @@
         <v>175</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>52</v>
@@ -27431,7 +27673,7 @@
         <v>52</v>
       </c>
       <c r="Y49" s="2" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="Z49" s="2" t="s">
         <v>52</v>
@@ -27446,10 +27688,10 @@
         <v>280</v>
       </c>
       <c r="AD49" s="2" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="AE49" s="2" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="AF49" s="2" t="s">
         <v>52</v>
@@ -27469,13 +27711,13 @@
     </row>
     <row r="50" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D50" s="7">
         <v>46091</v>
@@ -27487,10 +27729,10 @@
         <v>39</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="I50" s="6" t="s">
         <v>137</v>
@@ -27502,13 +27744,13 @@
         <v>361</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="O50" s="8">
         <v>5000</v>
@@ -27532,16 +27774,16 @@
         <v>2354</v>
       </c>
       <c r="V50" s="6" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="W50" s="6" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="X50" s="6" t="s">
         <v>50</v>
       </c>
       <c r="Y50" s="6" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="Z50" s="6" t="s">
         <v>52</v>
@@ -27579,13 +27821,13 @@
     </row>
     <row r="51" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D51" s="3">
         <v>46091</v>
@@ -27597,10 +27839,10 @@
         <v>39</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>174</v>
@@ -27609,16 +27851,16 @@
         <v>175</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="O51" s="4">
         <v>225</v>
@@ -27651,7 +27893,7 @@
         <v>50</v>
       </c>
       <c r="Y51" s="2" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="Z51" s="2" t="s">
         <v>52</v>
@@ -27689,13 +27931,13 @@
     </row>
     <row r="52" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D52" s="7">
         <v>46093</v>
@@ -27707,10 +27949,10 @@
         <v>61</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="I52" s="6" t="s">
         <v>148</v>
@@ -27719,16 +27961,16 @@
         <v>149</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="O52" s="8">
         <v>507</v>
@@ -27761,7 +28003,7 @@
         <v>50</v>
       </c>
       <c r="Y52" s="6" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="Z52" s="6" t="s">
         <v>52</v>
@@ -27799,13 +28041,13 @@
     </row>
     <row r="53" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D53" s="3">
         <v>46097</v>
@@ -27823,22 +28065,22 @@
         <v>330</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>382</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="O53" s="4">
         <v>3000</v>
@@ -27871,7 +28113,7 @@
         <v>50</v>
       </c>
       <c r="Y53" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="Z53" s="2" t="s">
         <v>52</v>
@@ -27907,8 +28149,226 @@
         <v>31170.42</v>
       </c>
     </row>
-    <row r="54" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="6" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>875</v>
+      </c>
+      <c r="D54" s="7">
+        <v>46098</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="J54" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="K54" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>928</v>
+      </c>
+      <c r="M54" s="6" t="s">
+        <v>929</v>
+      </c>
+      <c r="N54" s="6" t="s">
+        <v>930</v>
+      </c>
+      <c r="O54" s="8">
+        <v>10000</v>
+      </c>
+      <c r="P54" s="8">
+        <v>12.27</v>
+      </c>
+      <c r="Q54" s="9">
+        <v>122700</v>
+      </c>
+      <c r="R54" s="9">
+        <v>3987.75</v>
+      </c>
+      <c r="S54" s="9">
+        <v>126687.75</v>
+      </c>
+      <c r="T54" s="9">
+        <v>122700</v>
+      </c>
+      <c r="U54" s="9">
+        <v>14724</v>
+      </c>
+      <c r="V54" s="6" t="s">
+        <v>942</v>
+      </c>
+      <c r="W54" s="6" t="s">
+        <v>943</v>
+      </c>
+      <c r="X54" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y54" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="Z54" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA54" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB54" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC54" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="AD54" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="AE54" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="AF54" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG54" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH54" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI54" s="9">
+        <v>12</v>
+      </c>
+      <c r="AJ54" s="8">
+        <v>75850.3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="D55" s="3">
+        <v>46098</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="O55" s="4">
+        <v>507</v>
+      </c>
+      <c r="P55" s="4">
+        <v>21.96</v>
+      </c>
+      <c r="Q55" s="5">
+        <v>11133.72</v>
+      </c>
+      <c r="R55" s="5">
+        <v>361.85</v>
+      </c>
+      <c r="S55" s="5">
+        <v>11495.57</v>
+      </c>
+      <c r="T55" s="5">
+        <v>11133.72</v>
+      </c>
+      <c r="U55" s="5">
+        <v>445.35</v>
+      </c>
+      <c r="V55" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="W55" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="X55" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y55" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="Z55" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA55" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB55" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC55" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD55" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="AE55" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="AF55" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG55" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI55" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ55" s="4">
+        <v>5539.1575199999997</v>
+      </c>
+    </row>
     <row r="56" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="57" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="58" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/BASE_KEMPARTS.xlsx
+++ b/BASE_KEMPARTS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dash_kp_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC390F54-92EB-4098-ACF3-305FE1A8CFEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E915C991-35C9-4E4F-9481-863CFC39587D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{DF8863EB-EDB6-492C-9A1E-3E830035440B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{499751FD-66CF-41BC-81F4-D02557A09316}"/>
   </bookViews>
   <sheets>
     <sheet name="FSP" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8272" uniqueCount="1382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8497" uniqueCount="1407">
   <si>
     <t/>
   </si>
@@ -3437,6 +3437,90 @@
     <t>173938</t>
   </si>
   <si>
+    <t>000015583</t>
+  </si>
+  <si>
+    <t>173879</t>
+  </si>
+  <si>
+    <t>000015584</t>
+  </si>
+  <si>
+    <t>T00217</t>
+  </si>
+  <si>
+    <t>AUDREY ALMEIDA AVON TRANSPORTES</t>
+  </si>
+  <si>
+    <t>173883</t>
+  </si>
+  <si>
+    <t>000015586</t>
+  </si>
+  <si>
+    <t>173936</t>
+  </si>
+  <si>
+    <t>000015587</t>
+  </si>
+  <si>
+    <t>C00320</t>
+  </si>
+  <si>
+    <t>DESTILARIA BAURU LTDA</t>
+  </si>
+  <si>
+    <t>T00237</t>
+  </si>
+  <si>
+    <t>RODOTITANIO TRANSPORTES RODIVIARIO</t>
+  </si>
+  <si>
+    <t>173941</t>
+  </si>
+  <si>
+    <t>000015588</t>
+  </si>
+  <si>
+    <t>C00161</t>
+  </si>
+  <si>
+    <t>ARTEFATOS DE BORRACHA PCR LTDA</t>
+  </si>
+  <si>
+    <t>153703</t>
+  </si>
+  <si>
+    <t>000015589</t>
+  </si>
+  <si>
+    <t>173930</t>
+  </si>
+  <si>
+    <t>003307</t>
+  </si>
+  <si>
+    <t>TRANSPORTADORA NIMEC LT</t>
+  </si>
+  <si>
+    <t>T00213</t>
+  </si>
+  <si>
+    <t>2024.357.09.</t>
+  </si>
+  <si>
+    <t>250106</t>
+  </si>
+  <si>
+    <t>2024.357.09.250106</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>000002516</t>
+  </si>
+  <si>
     <t>003320</t>
   </si>
   <si>
@@ -3452,9 +3536,6 @@
     <t>C00385</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>000002515</t>
   </si>
   <si>
@@ -3591,12 +3672,6 @@
   </si>
   <si>
     <t>003293</t>
-  </si>
-  <si>
-    <t>TRANSPORTADORA NIMEC LT</t>
-  </si>
-  <si>
-    <t>T00213</t>
   </si>
   <si>
     <t>000002509</t>
@@ -5113,8 +5188,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3E0C65F-D9F5-4B69-AA21-5AE0E8CB4BF5}">
-  <dimension ref="A1:AJ254"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB2A3478-9B6D-4ED4-9F43-DF7B8E819B1F}">
+  <dimension ref="A1:AJ262"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -33094,14 +33169,894 @@
         <v>4.9579800000000001</v>
       </c>
     </row>
+    <row r="255" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A255" s="3" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D255" s="7">
+        <v>46100</v>
+      </c>
+      <c r="E255" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F255" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G255" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="H255" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="I255" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J255" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K255" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="L255" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="M255" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="N255" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="O255" s="8">
+        <v>850</v>
+      </c>
+      <c r="P255" s="8">
+        <v>24.59</v>
+      </c>
+      <c r="Q255" s="9">
+        <v>20901.5</v>
+      </c>
+      <c r="R255" s="9">
+        <v>679.3</v>
+      </c>
+      <c r="S255" s="9">
+        <v>21580.799999999999</v>
+      </c>
+      <c r="T255" s="9">
+        <v>20901.5</v>
+      </c>
+      <c r="U255" s="9">
+        <v>3762.27</v>
+      </c>
+      <c r="V255" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="W255" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="X255" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y255" s="3" t="s">
+        <v>1139</v>
+      </c>
+      <c r="Z255" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA255" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB255" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC255" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD255" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE255" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF255" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG255" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH255" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI255" s="9">
+        <v>18</v>
+      </c>
+      <c r="AJ255" s="8">
+        <v>9462.8544999999995</v>
+      </c>
+    </row>
+    <row r="256" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A256" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D256" s="4">
+        <v>46100</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F256" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G256" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="H256" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="I256" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="J256" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="K256" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="L256" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="M256" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="N256" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="O256" s="5">
+        <v>2450</v>
+      </c>
+      <c r="P256" s="5">
+        <v>21.31</v>
+      </c>
+      <c r="Q256" s="6">
+        <v>52209.5</v>
+      </c>
+      <c r="R256" s="6">
+        <v>1696.81</v>
+      </c>
+      <c r="S256" s="6">
+        <v>53906.31</v>
+      </c>
+      <c r="T256" s="6">
+        <v>52209.5</v>
+      </c>
+      <c r="U256" s="6">
+        <v>2088.38</v>
+      </c>
+      <c r="V256" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="W256" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="X256" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y256" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="Z256" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA256" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB256" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC256" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD256" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="AE256" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="AF256" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG256" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH256" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI256" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ256" s="5">
+        <v>62462.946000000004</v>
+      </c>
+    </row>
+    <row r="257" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A257" s="3" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B257" s="3" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C257" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D257" s="7">
+        <v>46100</v>
+      </c>
+      <c r="E257" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G257" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H257" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="I257" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="J257" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="K257" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="L257" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="M257" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="N257" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="O257" s="8">
+        <v>2720</v>
+      </c>
+      <c r="P257" s="8">
+        <v>27.69</v>
+      </c>
+      <c r="Q257" s="9">
+        <v>75316.800000000003</v>
+      </c>
+      <c r="R257" s="9">
+        <v>2447.8000000000002</v>
+      </c>
+      <c r="S257" s="9">
+        <v>77764.600000000006</v>
+      </c>
+      <c r="T257" s="9">
+        <v>94146</v>
+      </c>
+      <c r="U257" s="9">
+        <v>13557.02</v>
+      </c>
+      <c r="V257" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="W257" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="X257" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y257" s="3" t="s">
+        <v>1145</v>
+      </c>
+      <c r="Z257" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA257" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB257" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC257" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD257" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE257" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF257" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG257" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH257" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI257" s="9">
+        <v>18</v>
+      </c>
+      <c r="AJ257" s="8">
+        <v>30281.134399999999</v>
+      </c>
+    </row>
+    <row r="258" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A258" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D258" s="4">
+        <v>46100</v>
+      </c>
+      <c r="E258" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F258" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G258" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="H258" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I258" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="J258" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="K258" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="L258" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="M258" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="N258" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="O258" s="5">
+        <v>680</v>
+      </c>
+      <c r="P258" s="5">
+        <v>27.69</v>
+      </c>
+      <c r="Q258" s="6">
+        <v>18829.2</v>
+      </c>
+      <c r="R258" s="6">
+        <v>611.95000000000005</v>
+      </c>
+      <c r="S258" s="6">
+        <v>19441.150000000001</v>
+      </c>
+      <c r="T258" s="6">
+        <v>94146</v>
+      </c>
+      <c r="U258" s="6">
+        <v>3389.26</v>
+      </c>
+      <c r="V258" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="W258" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="X258" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y258" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="Z258" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA258" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB258" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC258" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD258" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE258" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF258" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG258" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH258" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI258" s="6">
+        <v>18</v>
+      </c>
+      <c r="AJ258" s="5">
+        <v>7570.2835999999998</v>
+      </c>
+    </row>
+    <row r="259" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A259" s="3" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B259" s="3" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C259" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D259" s="7">
+        <v>46100</v>
+      </c>
+      <c r="E259" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F259" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G259" s="3" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H259" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I259" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J259" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K259" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="L259" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="M259" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="N259" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="O259" s="8">
+        <v>175</v>
+      </c>
+      <c r="P259" s="8">
+        <v>31.044029999999999</v>
+      </c>
+      <c r="Q259" s="9">
+        <v>5432.71</v>
+      </c>
+      <c r="R259" s="9">
+        <v>176.56</v>
+      </c>
+      <c r="S259" s="9">
+        <v>5609.27</v>
+      </c>
+      <c r="T259" s="9">
+        <v>5432.71</v>
+      </c>
+      <c r="U259" s="9">
+        <v>977.89</v>
+      </c>
+      <c r="V259" s="3" t="s">
+        <v>1149</v>
+      </c>
+      <c r="W259" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="X259" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y259" s="3" t="s">
+        <v>1151</v>
+      </c>
+      <c r="Z259" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA259" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB259" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC259" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD259" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="AE259" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="AF259" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG259" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH259" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI259" s="9">
+        <v>18</v>
+      </c>
+      <c r="AJ259" s="8">
+        <v>4461.6390000000001</v>
+      </c>
+    </row>
+    <row r="260" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A260" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D260" s="4">
+        <v>46100</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F260" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G260" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="H260" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="I260" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J260" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K260" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="L260" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="M260" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="N260" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="O260" s="5">
+        <v>1</v>
+      </c>
+      <c r="P260" s="5">
+        <v>10</v>
+      </c>
+      <c r="Q260" s="6">
+        <v>10</v>
+      </c>
+      <c r="R260" s="6">
+        <v>0</v>
+      </c>
+      <c r="S260" s="6">
+        <v>10</v>
+      </c>
+      <c r="T260" s="6">
+        <v>0</v>
+      </c>
+      <c r="U260" s="6">
+        <v>0</v>
+      </c>
+      <c r="V260" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="W260" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="X260" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y260" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="Z260" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA260" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB260" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AC260" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="AD260" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="AE260" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="AF260" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="AG260" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH260" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI260" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ260" s="5">
+        <v>30.725000000000001</v>
+      </c>
+    </row>
+    <row r="261" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A261" s="3" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B261" s="3" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D261" s="7">
+        <v>46100</v>
+      </c>
+      <c r="E261" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F261" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G261" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="H261" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="I261" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J261" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K261" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="L261" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="M261" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="N261" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="O261" s="8">
+        <v>220</v>
+      </c>
+      <c r="P261" s="8">
+        <v>26.150649999999999</v>
+      </c>
+      <c r="Q261" s="9">
+        <v>5753.14</v>
+      </c>
+      <c r="R261" s="9">
+        <v>186.98</v>
+      </c>
+      <c r="S261" s="9">
+        <v>5940.12</v>
+      </c>
+      <c r="T261" s="9">
+        <v>18867.93</v>
+      </c>
+      <c r="U261" s="9">
+        <v>1035.57</v>
+      </c>
+      <c r="V261" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="W261" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="X261" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y261" s="3" t="s">
+        <v>1157</v>
+      </c>
+      <c r="Z261" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA261" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB261" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC261" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD261" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="AE261" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="AF261" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG261" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH261" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI261" s="9">
+        <v>18</v>
+      </c>
+      <c r="AJ261" s="8">
+        <v>4063.6442000000002</v>
+      </c>
+    </row>
+    <row r="262" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A262" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D262" s="4">
+        <v>46100</v>
+      </c>
+      <c r="E262" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F262" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G262" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="H262" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="I262" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="J262" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K262" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="L262" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="M262" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="N262" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="O262" s="5">
+        <v>50</v>
+      </c>
+      <c r="P262" s="5">
+        <v>262.29575</v>
+      </c>
+      <c r="Q262" s="6">
+        <v>13114.79</v>
+      </c>
+      <c r="R262" s="6">
+        <v>426.23</v>
+      </c>
+      <c r="S262" s="6">
+        <v>13541.02</v>
+      </c>
+      <c r="T262" s="6">
+        <v>18867.93</v>
+      </c>
+      <c r="U262" s="6">
+        <v>2360.66</v>
+      </c>
+      <c r="V262" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="W262" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="X262" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y262" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="Z262" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA262" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB262" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC262" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD262" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="AE262" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="AF262" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG262" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH262" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI262" s="6">
+        <v>18</v>
+      </c>
+      <c r="AJ262" s="5">
+        <v>6261.2264999999998</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{793BD3A3-14EA-4F5C-9942-2D3D526137BF}">
-  <dimension ref="A1:AJ76"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C195BCC-B02B-4690-8307-EB489A5ABA90}">
+  <dimension ref="A1:AJ77"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -33252,13 +34207,13 @@
     </row>
     <row r="2" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>1381</v>
+        <v>1406</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1381</v>
+        <v>1406</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D2" s="4">
         <v>46024</v>
@@ -33270,10 +34225,10 @@
         <v>40</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>1197</v>
+        <v>1222</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>43</v>
@@ -33285,13 +34240,13 @@
         <v>440</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>1251</v>
+        <v>1276</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>1249</v>
+        <v>1274</v>
       </c>
       <c r="O2" s="5">
         <v>50</v>
@@ -33315,16 +34270,16 @@
         <v>39.06</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>1248</v>
+        <v>1273</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>1247</v>
+        <v>1272</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>1380</v>
+        <v>1405</v>
       </c>
       <c r="Z2" s="2" t="s">
         <v>0</v>
@@ -33362,13 +34317,13 @@
     </row>
     <row r="3" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>1379</v>
+        <v>1404</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1379</v>
+        <v>1404</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D3" s="7">
         <v>46027</v>
@@ -33380,10 +34335,10 @@
         <v>61</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1142</v>
+        <v>1170</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1141</v>
+        <v>1169</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>163</v>
@@ -33395,13 +34350,13 @@
         <v>632</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1140</v>
+        <v>1168</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>648</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>1139</v>
+        <v>1167</v>
       </c>
       <c r="O3" s="8">
         <v>1001</v>
@@ -33434,7 +34389,7 @@
         <v>51</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>1378</v>
+        <v>1403</v>
       </c>
       <c r="Z3" s="3" t="s">
         <v>0</v>
@@ -33472,13 +34427,13 @@
     </row>
     <row r="4" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>1377</v>
+        <v>1402</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1377</v>
+        <v>1402</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D4" s="4">
         <v>46027</v>
@@ -33490,10 +34445,10 @@
         <v>61</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1376</v>
+        <v>1401</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1375</v>
+        <v>1400</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>152</v>
@@ -33505,13 +34460,13 @@
         <v>342</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1374</v>
+        <v>1399</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1373</v>
+        <v>1398</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1372</v>
+        <v>1397</v>
       </c>
       <c r="O4" s="5">
         <v>600</v>
@@ -33535,16 +34490,16 @@
         <v>355.68</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>1371</v>
+        <v>1396</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>1370</v>
+        <v>1395</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>1369</v>
+        <v>1394</v>
       </c>
       <c r="Z4" s="2" t="s">
         <v>0</v>
@@ -33582,13 +34537,13 @@
     </row>
     <row r="5" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>1368</v>
+        <v>1393</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1368</v>
+        <v>1393</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D5" s="7">
         <v>46029</v>
@@ -33600,10 +34555,10 @@
         <v>212</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>1297</v>
+        <v>1322</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1164</v>
+        <v>1191</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>139</v>
@@ -33612,7 +34567,7 @@
         <v>140</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>1367</v>
+        <v>1392</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>0</v>
@@ -33654,7 +34609,7 @@
         <v>87</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>1366</v>
+        <v>1391</v>
       </c>
       <c r="Z5" s="3" t="s">
         <v>0</v>
@@ -33692,13 +34647,13 @@
     </row>
     <row r="6" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>1368</v>
+        <v>1393</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1368</v>
+        <v>1393</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D6" s="4">
         <v>46029</v>
@@ -33710,10 +34665,10 @@
         <v>212</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1297</v>
+        <v>1322</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1164</v>
+        <v>1191</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>139</v>
@@ -33722,7 +34677,7 @@
         <v>140</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>1367</v>
+        <v>1392</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>0</v>
@@ -33764,7 +34719,7 @@
         <v>87</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>1366</v>
+        <v>1391</v>
       </c>
       <c r="Z6" s="2" t="s">
         <v>0</v>
@@ -33802,13 +34757,13 @@
     </row>
     <row r="7" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>1365</v>
+        <v>1390</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1365</v>
+        <v>1390</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D7" s="7">
         <v>46029</v>
@@ -33826,22 +34781,22 @@
         <v>386</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>1157</v>
+        <v>1184</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>1156</v>
+        <v>1183</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>1058</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>1364</v>
+        <v>1389</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>1363</v>
+        <v>1388</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>1174</v>
+        <v>1201</v>
       </c>
       <c r="O7" s="8">
         <v>1000</v>
@@ -33874,7 +34829,7 @@
         <v>51</v>
       </c>
       <c r="Y7" s="3" t="s">
-        <v>1362</v>
+        <v>1387</v>
       </c>
       <c r="Z7" s="3" t="s">
         <v>0</v>
@@ -33912,13 +34867,13 @@
     </row>
     <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>1361</v>
+        <v>1386</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1361</v>
+        <v>1386</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D8" s="4">
         <v>46036</v>
@@ -33930,10 +34885,10 @@
         <v>61</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1142</v>
+        <v>1170</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>1141</v>
+        <v>1169</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>163</v>
@@ -33945,13 +34900,13 @@
         <v>632</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>1140</v>
+        <v>1168</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1139</v>
+        <v>1167</v>
       </c>
       <c r="O8" s="5">
         <v>1001</v>
@@ -33984,7 +34939,7 @@
         <v>51</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>1360</v>
+        <v>1385</v>
       </c>
       <c r="Z8" s="2" t="s">
         <v>0</v>
@@ -34022,13 +34977,13 @@
     </row>
     <row r="9" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>1359</v>
+        <v>1384</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1359</v>
+        <v>1384</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D9" s="7">
         <v>46037</v>
@@ -34040,10 +34995,10 @@
         <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>1273</v>
+        <v>1298</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1272</v>
+        <v>1297</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>163</v>
@@ -34055,13 +35010,13 @@
         <v>417</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>1358</v>
+        <v>1383</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>1041</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>1269</v>
+        <v>1294</v>
       </c>
       <c r="O9" s="8">
         <v>1000</v>
@@ -34094,7 +35049,7 @@
         <v>51</v>
       </c>
       <c r="Y9" s="3" t="s">
-        <v>1357</v>
+        <v>1382</v>
       </c>
       <c r="Z9" s="3" t="s">
         <v>0</v>
@@ -34132,13 +35087,13 @@
     </row>
     <row r="10" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>1356</v>
+        <v>1381</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1356</v>
+        <v>1381</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D10" s="4">
         <v>46037</v>
@@ -34150,10 +35105,10 @@
         <v>40</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1187</v>
+        <v>1214</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1186</v>
+        <v>1213</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>139</v>
@@ -34165,13 +35120,13 @@
         <v>782</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>1185</v>
+        <v>1212</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1184</v>
+        <v>1211</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1183</v>
+        <v>1210</v>
       </c>
       <c r="O10" s="5">
         <v>300</v>
@@ -34204,7 +35159,7 @@
         <v>51</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>1355</v>
+        <v>1380</v>
       </c>
       <c r="Z10" s="2" t="s">
         <v>0</v>
@@ -34242,13 +35197,13 @@
     </row>
     <row r="11" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>1354</v>
+        <v>1379</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1354</v>
+        <v>1379</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D11" s="7">
         <v>46037</v>
@@ -34260,10 +35215,10 @@
         <v>40</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>1307</v>
+        <v>1332</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1306</v>
+        <v>1331</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>43</v>
@@ -34275,13 +35230,13 @@
         <v>300</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>1150</v>
+        <v>1177</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>1149</v>
+        <v>1176</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>1148</v>
+        <v>1175</v>
       </c>
       <c r="O11" s="8">
         <v>25</v>
@@ -34314,7 +35269,7 @@
         <v>51</v>
       </c>
       <c r="Y11" s="3" t="s">
-        <v>1353</v>
+        <v>1378</v>
       </c>
       <c r="Z11" s="3" t="s">
         <v>0</v>
@@ -34352,13 +35307,13 @@
     </row>
     <row r="12" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>1352</v>
+        <v>1377</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1352</v>
+        <v>1377</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D12" s="4">
         <v>46041</v>
@@ -34370,10 +35325,10 @@
         <v>212</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1297</v>
+        <v>1322</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1164</v>
+        <v>1191</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>139</v>
@@ -34382,7 +35337,7 @@
         <v>140</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>1213</v>
+        <v>1238</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>0</v>
@@ -34424,7 +35379,7 @@
         <v>87</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>1351</v>
+        <v>1376</v>
       </c>
       <c r="Z12" s="2" t="s">
         <v>0</v>
@@ -34439,10 +35394,10 @@
         <v>55</v>
       </c>
       <c r="AD12" s="2" t="s">
-        <v>1208</v>
+        <v>1233</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>1207</v>
+        <v>1232</v>
       </c>
       <c r="AF12" s="2" t="s">
         <v>442</v>
@@ -34462,13 +35417,13 @@
     </row>
     <row r="13" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>1350</v>
+        <v>1375</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1350</v>
+        <v>1375</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D13" s="7">
         <v>46042</v>
@@ -34486,22 +35441,22 @@
         <v>386</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>1157</v>
+        <v>1184</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>1156</v>
+        <v>1183</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>446</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>1267</v>
+        <v>1292</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>1266</v>
+        <v>1291</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>1153</v>
+        <v>1180</v>
       </c>
       <c r="O13" s="8">
         <v>2000</v>
@@ -34534,7 +35489,7 @@
         <v>51</v>
       </c>
       <c r="Y13" s="3" t="s">
-        <v>1349</v>
+        <v>1374</v>
       </c>
       <c r="Z13" s="3" t="s">
         <v>0</v>
@@ -34572,13 +35527,13 @@
     </row>
     <row r="14" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>1348</v>
+        <v>1373</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1348</v>
+        <v>1373</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D14" s="4">
         <v>46042</v>
@@ -34602,16 +35557,16 @@
         <v>294</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>1213</v>
+        <v>1238</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>1322</v>
+        <v>1347</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1321</v>
+        <v>1346</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1210</v>
+        <v>1235</v>
       </c>
       <c r="O14" s="5">
         <v>6000</v>
@@ -34635,16 +35590,16 @@
         <v>12873.6</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>1147</v>
+        <v>1174</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>1146</v>
+        <v>1173</v>
       </c>
       <c r="X14" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>1347</v>
+        <v>1372</v>
       </c>
       <c r="Z14" s="2" t="s">
         <v>0</v>
@@ -34659,10 +35614,10 @@
         <v>298</v>
       </c>
       <c r="AD14" s="2" t="s">
-        <v>1208</v>
+        <v>1233</v>
       </c>
       <c r="AE14" s="2" t="s">
-        <v>1207</v>
+        <v>1232</v>
       </c>
       <c r="AF14" s="2" t="s">
         <v>77</v>
@@ -34682,13 +35637,13 @@
     </row>
     <row r="15" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>1346</v>
+        <v>1371</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1346</v>
+        <v>1371</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D15" s="7">
         <v>46042</v>
@@ -34700,10 +35655,10 @@
         <v>212</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>1297</v>
+        <v>1322</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>1164</v>
+        <v>1191</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>139</v>
@@ -34754,7 +35709,7 @@
         <v>87</v>
       </c>
       <c r="Y15" s="3" t="s">
-        <v>1345</v>
+        <v>1370</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>0</v>
@@ -34775,7 +35730,7 @@
         <v>518</v>
       </c>
       <c r="AF15" s="3" t="s">
-        <v>1317</v>
+        <v>1342</v>
       </c>
       <c r="AG15" s="9">
         <v>0</v>
@@ -34792,13 +35747,13 @@
     </row>
     <row r="16" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>1346</v>
+        <v>1371</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1346</v>
+        <v>1371</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D16" s="4">
         <v>46042</v>
@@ -34810,10 +35765,10 @@
         <v>212</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1297</v>
+        <v>1322</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1164</v>
+        <v>1191</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>139</v>
@@ -34864,7 +35819,7 @@
         <v>87</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>1345</v>
+        <v>1370</v>
       </c>
       <c r="Z16" s="2" t="s">
         <v>0</v>
@@ -34885,7 +35840,7 @@
         <v>518</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>1317</v>
+        <v>1342</v>
       </c>
       <c r="AG16" s="6">
         <v>0</v>
@@ -34902,13 +35857,13 @@
     </row>
     <row r="17" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>1344</v>
+        <v>1369</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1344</v>
+        <v>1369</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D17" s="7">
         <v>46043</v>
@@ -34935,13 +35890,13 @@
         <v>417</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>1271</v>
+        <v>1296</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>1270</v>
+        <v>1295</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>1269</v>
+        <v>1294</v>
       </c>
       <c r="O17" s="8">
         <v>1000</v>
@@ -34974,7 +35929,7 @@
         <v>51</v>
       </c>
       <c r="Y17" s="3" t="s">
-        <v>1343</v>
+        <v>1368</v>
       </c>
       <c r="Z17" s="3" t="s">
         <v>0</v>
@@ -35012,28 +35967,28 @@
     </row>
     <row r="18" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>1332</v>
+        <v>1357</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1332</v>
+        <v>1357</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D18" s="4">
         <v>46045</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1172</v>
+        <v>1199</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1171</v>
+        <v>1198</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1170</v>
+        <v>1197</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>1169</v>
+        <v>1196</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>139</v>
@@ -35045,13 +36000,13 @@
         <v>628</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>1342</v>
+        <v>1367</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1341</v>
+        <v>1366</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1340</v>
+        <v>1365</v>
       </c>
       <c r="O18" s="5">
         <v>2000</v>
@@ -35075,16 +36030,16 @@
         <v>0</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>1165</v>
+        <v>1192</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>1164</v>
+        <v>1191</v>
       </c>
       <c r="X18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>1328</v>
+        <v>1353</v>
       </c>
       <c r="Z18" s="2" t="s">
         <v>0</v>
@@ -35122,28 +36077,28 @@
     </row>
     <row r="19" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>1332</v>
+        <v>1357</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>1332</v>
+        <v>1357</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D19" s="7">
         <v>46045</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>1172</v>
+        <v>1199</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>1171</v>
+        <v>1198</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>1170</v>
+        <v>1197</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>1169</v>
+        <v>1196</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>139</v>
@@ -35155,13 +36110,13 @@
         <v>631</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>1339</v>
+        <v>1364</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>1338</v>
+        <v>1363</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>1329</v>
+        <v>1354</v>
       </c>
       <c r="O19" s="8">
         <v>11725</v>
@@ -35185,16 +36140,16 @@
         <v>0</v>
       </c>
       <c r="V19" s="3" t="s">
-        <v>1165</v>
+        <v>1192</v>
       </c>
       <c r="W19" s="3" t="s">
-        <v>1164</v>
+        <v>1191</v>
       </c>
       <c r="X19" s="3" t="s">
         <v>87</v>
       </c>
       <c r="Y19" s="3" t="s">
-        <v>1328</v>
+        <v>1353</v>
       </c>
       <c r="Z19" s="3" t="s">
         <v>0</v>
@@ -35232,28 +36187,28 @@
     </row>
     <row r="20" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>1332</v>
+        <v>1357</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1332</v>
+        <v>1357</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D20" s="4">
         <v>46045</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1172</v>
+        <v>1199</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1171</v>
+        <v>1198</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1170</v>
+        <v>1197</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1169</v>
+        <v>1196</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>139</v>
@@ -35265,13 +36220,13 @@
         <v>632</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>1140</v>
+        <v>1168</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1139</v>
+        <v>1167</v>
       </c>
       <c r="O20" s="5">
         <v>2925</v>
@@ -35295,16 +36250,16 @@
         <v>0</v>
       </c>
       <c r="V20" s="2" t="s">
-        <v>1165</v>
+        <v>1192</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>1164</v>
+        <v>1191</v>
       </c>
       <c r="X20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>1328</v>
+        <v>1353</v>
       </c>
       <c r="Z20" s="2" t="s">
         <v>0</v>
@@ -35342,28 +36297,28 @@
     </row>
     <row r="21" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>1332</v>
+        <v>1357</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>1332</v>
+        <v>1357</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D21" s="7">
         <v>46045</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>1172</v>
+        <v>1199</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>1171</v>
+        <v>1198</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>1170</v>
+        <v>1197</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>1169</v>
+        <v>1196</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>139</v>
@@ -35375,13 +36330,13 @@
         <v>633</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>1161</v>
+        <v>1188</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>652</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>1160</v>
+        <v>1187</v>
       </c>
       <c r="O21" s="8">
         <v>2925</v>
@@ -35405,16 +36360,16 @@
         <v>0</v>
       </c>
       <c r="V21" s="3" t="s">
-        <v>1165</v>
+        <v>1192</v>
       </c>
       <c r="W21" s="3" t="s">
-        <v>1164</v>
+        <v>1191</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>87</v>
       </c>
       <c r="Y21" s="3" t="s">
-        <v>1328</v>
+        <v>1353</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>0</v>
@@ -35452,28 +36407,28 @@
     </row>
     <row r="22" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>1332</v>
+        <v>1357</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1332</v>
+        <v>1357</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D22" s="4">
         <v>46045</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1172</v>
+        <v>1199</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1171</v>
+        <v>1198</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1170</v>
+        <v>1197</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1169</v>
+        <v>1196</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>139</v>
@@ -35485,13 +36440,13 @@
         <v>465</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1337</v>
+        <v>1362</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>1109</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1336</v>
+        <v>1361</v>
       </c>
       <c r="O22" s="5">
         <v>2400</v>
@@ -35515,16 +36470,16 @@
         <v>0</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>1165</v>
+        <v>1192</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>1164</v>
+        <v>1191</v>
       </c>
       <c r="X22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>1328</v>
+        <v>1353</v>
       </c>
       <c r="Z22" s="2" t="s">
         <v>0</v>
@@ -35562,28 +36517,28 @@
     </row>
     <row r="23" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>1332</v>
+        <v>1357</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>1332</v>
+        <v>1357</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D23" s="7">
         <v>46045</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>1172</v>
+        <v>1199</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>1171</v>
+        <v>1198</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>1170</v>
+        <v>1197</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>1169</v>
+        <v>1196</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>139</v>
@@ -35595,13 +36550,13 @@
         <v>465</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>1335</v>
+        <v>1360</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>1334</v>
+        <v>1359</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>1333</v>
+        <v>1358</v>
       </c>
       <c r="O23" s="8">
         <v>1800</v>
@@ -35625,16 +36580,16 @@
         <v>0</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>1165</v>
+        <v>1192</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>1164</v>
+        <v>1191</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>87</v>
       </c>
       <c r="Y23" s="3" t="s">
-        <v>1328</v>
+        <v>1353</v>
       </c>
       <c r="Z23" s="3" t="s">
         <v>0</v>
@@ -35672,28 +36627,28 @@
     </row>
     <row r="24" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>1332</v>
+        <v>1357</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1332</v>
+        <v>1357</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D24" s="4">
         <v>46045</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1172</v>
+        <v>1199</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1171</v>
+        <v>1198</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1170</v>
+        <v>1197</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1169</v>
+        <v>1196</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>139</v>
@@ -35705,13 +36660,13 @@
         <v>634</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>1331</v>
+        <v>1356</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1330</v>
+        <v>1355</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1329</v>
+        <v>1354</v>
       </c>
       <c r="O24" s="5">
         <v>1400</v>
@@ -35735,16 +36690,16 @@
         <v>0</v>
       </c>
       <c r="V24" s="2" t="s">
-        <v>1165</v>
+        <v>1192</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>1164</v>
+        <v>1191</v>
       </c>
       <c r="X24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>1328</v>
+        <v>1353</v>
       </c>
       <c r="Z24" s="2" t="s">
         <v>0</v>
@@ -35782,13 +36737,13 @@
     </row>
     <row r="25" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>1327</v>
+        <v>1352</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>1327</v>
+        <v>1352</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D25" s="7">
         <v>46048</v>
@@ -35815,13 +36770,13 @@
         <v>417</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>1280</v>
+        <v>1305</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>1279</v>
+        <v>1304</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>1180</v>
+        <v>1207</v>
       </c>
       <c r="O25" s="8">
         <v>5000</v>
@@ -35845,16 +36800,16 @@
         <v>2354</v>
       </c>
       <c r="V25" s="3" t="s">
-        <v>1191</v>
+        <v>1160</v>
       </c>
       <c r="W25" s="3" t="s">
-        <v>1190</v>
+        <v>1159</v>
       </c>
       <c r="X25" s="3" t="s">
         <v>51</v>
       </c>
       <c r="Y25" s="3" t="s">
-        <v>1326</v>
+        <v>1351</v>
       </c>
       <c r="Z25" s="3" t="s">
         <v>0</v>
@@ -35892,13 +36847,13 @@
     </row>
     <row r="26" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>1325</v>
+        <v>1350</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1325</v>
+        <v>1350</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D26" s="4">
         <v>46048</v>
@@ -35910,10 +36865,10 @@
         <v>40</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1187</v>
+        <v>1214</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1186</v>
+        <v>1213</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>139</v>
@@ -35925,13 +36880,13 @@
         <v>782</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>1185</v>
+        <v>1212</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1184</v>
+        <v>1211</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1183</v>
+        <v>1210</v>
       </c>
       <c r="O26" s="5">
         <v>300</v>
@@ -35964,7 +36919,7 @@
         <v>51</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>1324</v>
+        <v>1349</v>
       </c>
       <c r="Z26" s="2" t="s">
         <v>0</v>
@@ -36002,13 +36957,13 @@
     </row>
     <row r="27" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>1323</v>
+        <v>1348</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>1323</v>
+        <v>1348</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D27" s="7">
         <v>46048</v>
@@ -36020,10 +36975,10 @@
         <v>61</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>1142</v>
+        <v>1170</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>1141</v>
+        <v>1169</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>163</v>
@@ -36035,13 +36990,13 @@
         <v>632</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>1140</v>
+        <v>1168</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>648</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>1139</v>
+        <v>1167</v>
       </c>
       <c r="O27" s="8">
         <v>611</v>
@@ -36074,7 +37029,7 @@
         <v>51</v>
       </c>
       <c r="Y27" s="3" t="s">
-        <v>1320</v>
+        <v>1345</v>
       </c>
       <c r="Z27" s="3" t="s">
         <v>0</v>
@@ -36112,13 +37067,13 @@
     </row>
     <row r="28" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>1323</v>
+        <v>1348</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1323</v>
+        <v>1348</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D28" s="4">
         <v>46048</v>
@@ -36130,10 +37085,10 @@
         <v>61</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1142</v>
+        <v>1170</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1141</v>
+        <v>1169</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>163</v>
@@ -36142,16 +37097,16 @@
         <v>164</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>1213</v>
+        <v>1238</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>1322</v>
+        <v>1347</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1321</v>
+        <v>1346</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1210</v>
+        <v>1235</v>
       </c>
       <c r="O28" s="5">
         <v>700</v>
@@ -36184,7 +37139,7 @@
         <v>51</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>1320</v>
+        <v>1345</v>
       </c>
       <c r="Z28" s="2" t="s">
         <v>0</v>
@@ -36199,10 +37154,10 @@
         <v>55</v>
       </c>
       <c r="AD28" s="2" t="s">
-        <v>1208</v>
+        <v>1233</v>
       </c>
       <c r="AE28" s="2" t="s">
-        <v>1207</v>
+        <v>1232</v>
       </c>
       <c r="AF28" s="2" t="s">
         <v>77</v>
@@ -36222,13 +37177,13 @@
     </row>
     <row r="29" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>1319</v>
+        <v>1344</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>1319</v>
+        <v>1344</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D29" s="7">
         <v>46048</v>
@@ -36240,10 +37195,10 @@
         <v>212</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>1297</v>
+        <v>1322</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>1164</v>
+        <v>1191</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>139</v>
@@ -36294,7 +37249,7 @@
         <v>87</v>
       </c>
       <c r="Y29" s="3" t="s">
-        <v>1318</v>
+        <v>1343</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>0</v>
@@ -36315,7 +37270,7 @@
         <v>57</v>
       </c>
       <c r="AF29" s="3" t="s">
-        <v>1317</v>
+        <v>1342</v>
       </c>
       <c r="AG29" s="9">
         <v>0</v>
@@ -36332,13 +37287,13 @@
     </row>
     <row r="30" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>1316</v>
+        <v>1341</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1316</v>
+        <v>1341</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D30" s="4">
         <v>46049</v>
@@ -36350,10 +37305,10 @@
         <v>212</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1297</v>
+        <v>1322</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1164</v>
+        <v>1191</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>139</v>
@@ -36404,7 +37359,7 @@
         <v>87</v>
       </c>
       <c r="Y30" s="2" t="s">
-        <v>1315</v>
+        <v>1340</v>
       </c>
       <c r="Z30" s="2" t="s">
         <v>0</v>
@@ -36442,13 +37397,13 @@
     </row>
     <row r="31" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>1316</v>
+        <v>1341</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>1316</v>
+        <v>1341</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D31" s="7">
         <v>46049</v>
@@ -36460,10 +37415,10 @@
         <v>212</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>1297</v>
+        <v>1322</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>1164</v>
+        <v>1191</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>139</v>
@@ -36514,7 +37469,7 @@
         <v>87</v>
       </c>
       <c r="Y31" s="3" t="s">
-        <v>1315</v>
+        <v>1340</v>
       </c>
       <c r="Z31" s="3" t="s">
         <v>0</v>
@@ -36552,13 +37507,13 @@
     </row>
     <row r="32" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>1312</v>
+        <v>1337</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1312</v>
+        <v>1337</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D32" s="4">
         <v>46050</v>
@@ -36576,22 +37531,22 @@
         <v>386</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>1157</v>
+        <v>1184</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>1156</v>
+        <v>1183</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>446</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>1314</v>
+        <v>1339</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>448</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1313</v>
+        <v>1338</v>
       </c>
       <c r="O32" s="5">
         <v>1000</v>
@@ -36624,7 +37579,7 @@
         <v>51</v>
       </c>
       <c r="Y32" s="2" t="s">
-        <v>1311</v>
+        <v>1336</v>
       </c>
       <c r="Z32" s="2" t="s">
         <v>0</v>
@@ -36662,13 +37617,13 @@
     </row>
     <row r="33" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>1312</v>
+        <v>1337</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>1312</v>
+        <v>1337</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D33" s="7">
         <v>46050</v>
@@ -36686,22 +37641,22 @@
         <v>386</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>1157</v>
+        <v>1184</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>1156</v>
+        <v>1183</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>446</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>1267</v>
+        <v>1292</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>1266</v>
+        <v>1291</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>1153</v>
+        <v>1180</v>
       </c>
       <c r="O33" s="8">
         <v>1000</v>
@@ -36734,7 +37689,7 @@
         <v>51</v>
       </c>
       <c r="Y33" s="3" t="s">
-        <v>1311</v>
+        <v>1336</v>
       </c>
       <c r="Z33" s="3" t="s">
         <v>0</v>
@@ -36772,13 +37727,13 @@
     </row>
     <row r="34" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>1310</v>
+        <v>1335</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1310</v>
+        <v>1335</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D34" s="4">
         <v>46050</v>
@@ -36790,10 +37745,10 @@
         <v>212</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1297</v>
+        <v>1322</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>1164</v>
+        <v>1191</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>139</v>
@@ -36844,7 +37799,7 @@
         <v>87</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>1309</v>
+        <v>1334</v>
       </c>
       <c r="Z34" s="2" t="s">
         <v>0</v>
@@ -36882,13 +37837,13 @@
     </row>
     <row r="35" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>1308</v>
+        <v>1333</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>1308</v>
+        <v>1333</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D35" s="7">
         <v>46051</v>
@@ -36900,10 +37855,10 @@
         <v>40</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>1307</v>
+        <v>1332</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>1306</v>
+        <v>1331</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>43</v>
@@ -36915,13 +37870,13 @@
         <v>632</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>1140</v>
+        <v>1168</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>648</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>1139</v>
+        <v>1167</v>
       </c>
       <c r="O35" s="8">
         <v>26</v>
@@ -36954,7 +37909,7 @@
         <v>51</v>
       </c>
       <c r="Y35" s="3" t="s">
-        <v>1305</v>
+        <v>1330</v>
       </c>
       <c r="Z35" s="3" t="s">
         <v>0</v>
@@ -36992,13 +37947,13 @@
     </row>
     <row r="36" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>1304</v>
+        <v>1329</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>1304</v>
+        <v>1329</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D36" s="4">
         <v>46052</v>
@@ -37010,10 +37965,10 @@
         <v>61</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1142</v>
+        <v>1170</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>1141</v>
+        <v>1169</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>163</v>
@@ -37025,13 +37980,13 @@
         <v>632</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>1140</v>
+        <v>1168</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1139</v>
+        <v>1167</v>
       </c>
       <c r="O36" s="5">
         <v>507</v>
@@ -37064,7 +38019,7 @@
         <v>51</v>
       </c>
       <c r="Y36" s="2" t="s">
-        <v>1303</v>
+        <v>1328</v>
       </c>
       <c r="Z36" s="2" t="s">
         <v>0</v>
@@ -37102,13 +38057,13 @@
     </row>
     <row r="37" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>1302</v>
+        <v>1327</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>1302</v>
+        <v>1327</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D37" s="7">
         <v>46052</v>
@@ -37132,16 +38087,16 @@
         <v>164</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>1218</v>
+        <v>1243</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>1235</v>
+        <v>1260</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>1234</v>
+        <v>1259</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>1215</v>
+        <v>1240</v>
       </c>
       <c r="O37" s="8">
         <v>500</v>
@@ -37174,7 +38129,7 @@
         <v>51</v>
       </c>
       <c r="Y37" s="3" t="s">
-        <v>1301</v>
+        <v>1326</v>
       </c>
       <c r="Z37" s="3" t="s">
         <v>0</v>
@@ -37212,13 +38167,13 @@
     </row>
     <row r="38" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>1300</v>
+        <v>1325</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1300</v>
+        <v>1325</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D38" s="4">
         <v>46052</v>
@@ -37230,10 +38185,10 @@
         <v>40</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>1187</v>
+        <v>1214</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>1186</v>
+        <v>1213</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>139</v>
@@ -37245,13 +38200,13 @@
         <v>782</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>1185</v>
+        <v>1212</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>1184</v>
+        <v>1211</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>1183</v>
+        <v>1210</v>
       </c>
       <c r="O38" s="5">
         <v>300</v>
@@ -37284,7 +38239,7 @@
         <v>51</v>
       </c>
       <c r="Y38" s="2" t="s">
-        <v>1299</v>
+        <v>1324</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>0</v>
@@ -37322,13 +38277,13 @@
     </row>
     <row r="39" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>1298</v>
+        <v>1323</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>1298</v>
+        <v>1323</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D39" s="7">
         <v>46055</v>
@@ -37340,10 +38295,10 @@
         <v>212</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>1297</v>
+        <v>1322</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>1164</v>
+        <v>1191</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>139</v>
@@ -37352,7 +38307,7 @@
         <v>140</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>1296</v>
+        <v>1321</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>0</v>
@@ -37394,7 +38349,7 @@
         <v>87</v>
       </c>
       <c r="Y39" s="3" t="s">
-        <v>1295</v>
+        <v>1320</v>
       </c>
       <c r="Z39" s="3" t="s">
         <v>0</v>
@@ -37432,13 +38387,13 @@
     </row>
     <row r="40" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>1294</v>
+        <v>1319</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1294</v>
+        <v>1319</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D40" s="4">
         <v>46057</v>
@@ -37450,10 +38405,10 @@
         <v>61</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1142</v>
+        <v>1170</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>1141</v>
+        <v>1169</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>163</v>
@@ -37465,13 +38420,13 @@
         <v>632</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>1140</v>
+        <v>1168</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>1139</v>
+        <v>1167</v>
       </c>
       <c r="O40" s="5">
         <v>507</v>
@@ -37504,7 +38459,7 @@
         <v>51</v>
       </c>
       <c r="Y40" s="2" t="s">
-        <v>1293</v>
+        <v>1318</v>
       </c>
       <c r="Z40" s="2" t="s">
         <v>0</v>
@@ -37542,13 +38497,13 @@
     </row>
     <row r="41" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>1292</v>
+        <v>1317</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>1292</v>
+        <v>1317</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D41" s="7">
         <v>46057</v>
@@ -37566,22 +38521,22 @@
         <v>386</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>1157</v>
+        <v>1184</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>1156</v>
+        <v>1183</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>446</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>1267</v>
+        <v>1292</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>1266</v>
+        <v>1291</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>1153</v>
+        <v>1180</v>
       </c>
       <c r="O41" s="8">
         <v>2000</v>
@@ -37614,7 +38569,7 @@
         <v>51</v>
       </c>
       <c r="Y41" s="3" t="s">
-        <v>1264</v>
+        <v>1289</v>
       </c>
       <c r="Z41" s="3" t="s">
         <v>0</v>
@@ -37652,13 +38607,13 @@
     </row>
     <row r="42" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>1291</v>
+        <v>1316</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1291</v>
+        <v>1316</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D42" s="4">
         <v>46058</v>
@@ -37670,10 +38625,10 @@
         <v>61</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1142</v>
+        <v>1170</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>1141</v>
+        <v>1169</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>163</v>
@@ -37685,13 +38640,13 @@
         <v>632</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>1140</v>
+        <v>1168</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>1139</v>
+        <v>1167</v>
       </c>
       <c r="O42" s="5">
         <v>507</v>
@@ -37724,7 +38679,7 @@
         <v>51</v>
       </c>
       <c r="Y42" s="2" t="s">
-        <v>1290</v>
+        <v>1315</v>
       </c>
       <c r="Z42" s="2" t="s">
         <v>0</v>
@@ -37762,13 +38717,13 @@
     </row>
     <row r="43" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>1289</v>
+        <v>1314</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>1289</v>
+        <v>1314</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D43" s="7">
         <v>46058</v>
@@ -37780,10 +38735,10 @@
         <v>61</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>1238</v>
+        <v>1263</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>1237</v>
+        <v>1262</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>163</v>
@@ -37795,13 +38750,13 @@
         <v>417</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>1280</v>
+        <v>1305</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>1279</v>
+        <v>1304</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>1180</v>
+        <v>1207</v>
       </c>
       <c r="O43" s="8">
         <v>1800</v>
@@ -37834,7 +38789,7 @@
         <v>51</v>
       </c>
       <c r="Y43" s="3" t="s">
-        <v>1288</v>
+        <v>1313</v>
       </c>
       <c r="Z43" s="3" t="s">
         <v>0</v>
@@ -37872,13 +38827,13 @@
     </row>
     <row r="44" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>1287</v>
+        <v>1312</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>1287</v>
+        <v>1312</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D44" s="4">
         <v>46059</v>
@@ -37890,10 +38845,10 @@
         <v>40</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1286</v>
+        <v>1311</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>1285</v>
+        <v>1310</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>43</v>
@@ -37905,13 +38860,13 @@
         <v>782</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>1185</v>
+        <v>1212</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>1184</v>
+        <v>1211</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>1183</v>
+        <v>1210</v>
       </c>
       <c r="O44" s="5">
         <v>500</v>
@@ -37944,7 +38899,7 @@
         <v>51</v>
       </c>
       <c r="Y44" s="2" t="s">
-        <v>1284</v>
+        <v>1309</v>
       </c>
       <c r="Z44" s="2" t="s">
         <v>0</v>
@@ -37982,13 +38937,13 @@
     </row>
     <row r="45" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>1283</v>
+        <v>1308</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>1283</v>
+        <v>1308</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D45" s="7">
         <v>46059</v>
@@ -38000,10 +38955,10 @@
         <v>40</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>1282</v>
+        <v>1307</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>1281</v>
+        <v>1306</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>43</v>
@@ -38015,13 +38970,13 @@
         <v>417</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>1280</v>
+        <v>1305</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>1279</v>
+        <v>1304</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>1180</v>
+        <v>1207</v>
       </c>
       <c r="O45" s="8">
         <v>200</v>
@@ -38054,7 +39009,7 @@
         <v>51</v>
       </c>
       <c r="Y45" s="3" t="s">
-        <v>1278</v>
+        <v>1303</v>
       </c>
       <c r="Z45" s="3" t="s">
         <v>0</v>
@@ -38092,28 +39047,28 @@
     </row>
     <row r="46" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>1277</v>
+        <v>1302</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1277</v>
+        <v>1302</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D46" s="4">
         <v>46063</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1276</v>
+        <v>1301</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>267</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1170</v>
+        <v>1197</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>1169</v>
+        <v>1196</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>139</v>
@@ -38122,7 +39077,7 @@
         <v>140</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>0</v>
@@ -38164,7 +39119,7 @@
         <v>0</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>1275</v>
+        <v>1300</v>
       </c>
       <c r="Z46" s="2" t="s">
         <v>0</v>
@@ -38179,10 +39134,10 @@
         <v>74</v>
       </c>
       <c r="AD46" s="2" t="s">
-        <v>1194</v>
+        <v>1219</v>
       </c>
       <c r="AE46" s="2" t="s">
-        <v>1193</v>
+        <v>1218</v>
       </c>
       <c r="AF46" s="2" t="s">
         <v>0</v>
@@ -38202,13 +39157,13 @@
     </row>
     <row r="47" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>1274</v>
+        <v>1299</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>1274</v>
+        <v>1299</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D47" s="7">
         <v>46064</v>
@@ -38220,10 +39175,10 @@
         <v>61</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>1273</v>
+        <v>1298</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>1272</v>
+        <v>1297</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>139</v>
@@ -38235,13 +39190,13 @@
         <v>417</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>1271</v>
+        <v>1296</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>1270</v>
+        <v>1295</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>1269</v>
+        <v>1294</v>
       </c>
       <c r="O47" s="8">
         <v>1000</v>
@@ -38274,7 +39229,7 @@
         <v>51</v>
       </c>
       <c r="Y47" s="3" t="s">
-        <v>1268</v>
+        <v>1293</v>
       </c>
       <c r="Z47" s="3" t="s">
         <v>0</v>
@@ -38312,13 +39267,13 @@
     </row>
     <row r="48" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>1265</v>
+        <v>1290</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1265</v>
+        <v>1290</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D48" s="4">
         <v>46064</v>
@@ -38336,22 +39291,22 @@
         <v>386</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>1157</v>
+        <v>1184</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>1156</v>
+        <v>1183</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>446</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>1267</v>
+        <v>1292</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>1266</v>
+        <v>1291</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>1153</v>
+        <v>1180</v>
       </c>
       <c r="O48" s="5">
         <v>1000</v>
@@ -38384,7 +39339,7 @@
         <v>51</v>
       </c>
       <c r="Y48" s="2" t="s">
-        <v>1264</v>
+        <v>1289</v>
       </c>
       <c r="Z48" s="2" t="s">
         <v>0</v>
@@ -38422,13 +39377,13 @@
     </row>
     <row r="49" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>1265</v>
+        <v>1290</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>1265</v>
+        <v>1290</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D49" s="7">
         <v>46064</v>
@@ -38446,22 +39401,22 @@
         <v>386</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>1157</v>
+        <v>1184</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>1156</v>
+        <v>1183</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>446</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>1155</v>
+        <v>1182</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>1154</v>
+        <v>1181</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>1153</v>
+        <v>1180</v>
       </c>
       <c r="O49" s="8">
         <v>1000</v>
@@ -38494,7 +39449,7 @@
         <v>51</v>
       </c>
       <c r="Y49" s="3" t="s">
-        <v>1264</v>
+        <v>1289</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>0</v>
@@ -38532,13 +39487,13 @@
     </row>
     <row r="50" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>1263</v>
+        <v>1288</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>1263</v>
+        <v>1288</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D50" s="4">
         <v>46066</v>
@@ -38550,10 +39505,10 @@
         <v>61</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1142</v>
+        <v>1170</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>1141</v>
+        <v>1169</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>163</v>
@@ -38565,13 +39520,13 @@
         <v>632</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>1140</v>
+        <v>1168</v>
       </c>
       <c r="M50" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>1139</v>
+        <v>1167</v>
       </c>
       <c r="O50" s="5">
         <v>507</v>
@@ -38604,7 +39559,7 @@
         <v>51</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>1262</v>
+        <v>1287</v>
       </c>
       <c r="Z50" s="2" t="s">
         <v>0</v>
@@ -38642,13 +39597,13 @@
     </row>
     <row r="51" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>1261</v>
+        <v>1286</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>1261</v>
+        <v>1286</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D51" s="7">
         <v>46071</v>
@@ -38672,16 +39627,16 @@
         <v>164</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>1213</v>
+        <v>1238</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>1260</v>
+        <v>1285</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>1259</v>
+        <v>1284</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>1258</v>
+        <v>1283</v>
       </c>
       <c r="O51" s="8">
         <v>500</v>
@@ -38714,7 +39669,7 @@
         <v>51</v>
       </c>
       <c r="Y51" s="3" t="s">
-        <v>1257</v>
+        <v>1282</v>
       </c>
       <c r="Z51" s="3" t="s">
         <v>0</v>
@@ -38729,10 +39684,10 @@
         <v>111</v>
       </c>
       <c r="AD51" s="3" t="s">
-        <v>1208</v>
+        <v>1233</v>
       </c>
       <c r="AE51" s="3" t="s">
-        <v>1207</v>
+        <v>1232</v>
       </c>
       <c r="AF51" s="3" t="s">
         <v>77</v>
@@ -38752,13 +39707,13 @@
     </row>
     <row r="52" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>1256</v>
+        <v>1281</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1256</v>
+        <v>1281</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D52" s="4">
         <v>46071</v>
@@ -38770,10 +39725,10 @@
         <v>61</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1255</v>
+        <v>1280</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>1254</v>
+        <v>1279</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>139</v>
@@ -38785,13 +39740,13 @@
         <v>446</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>1155</v>
+        <v>1182</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>1154</v>
+        <v>1181</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>1153</v>
+        <v>1180</v>
       </c>
       <c r="O52" s="5">
         <v>200</v>
@@ -38824,7 +39779,7 @@
         <v>51</v>
       </c>
       <c r="Y52" s="2" t="s">
-        <v>1253</v>
+        <v>1278</v>
       </c>
       <c r="Z52" s="2" t="s">
         <v>0</v>
@@ -38862,13 +39817,13 @@
     </row>
     <row r="53" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>1252</v>
+        <v>1277</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>1252</v>
+        <v>1277</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D53" s="7">
         <v>46072</v>
@@ -38880,10 +39835,10 @@
         <v>40</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>1197</v>
+        <v>1222</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>43</v>
@@ -38895,13 +39850,13 @@
         <v>440</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>1251</v>
+        <v>1276</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>1249</v>
+        <v>1274</v>
       </c>
       <c r="O53" s="8">
         <v>50</v>
@@ -38925,16 +39880,16 @@
         <v>0</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>1248</v>
+        <v>1273</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>1247</v>
+        <v>1272</v>
       </c>
       <c r="X53" s="3" t="s">
         <v>51</v>
       </c>
       <c r="Y53" s="3" t="s">
-        <v>1246</v>
+        <v>1271</v>
       </c>
       <c r="Z53" s="3" t="s">
         <v>0</v>
@@ -38972,13 +39927,13 @@
     </row>
     <row r="54" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>1245</v>
+        <v>1270</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1245</v>
+        <v>1270</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D54" s="4">
         <v>46072</v>
@@ -38990,10 +39945,10 @@
         <v>61</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1238</v>
+        <v>1263</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>1237</v>
+        <v>1262</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>163</v>
@@ -39005,13 +39960,13 @@
         <v>417</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>1228</v>
+        <v>1253</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>1227</v>
+        <v>1252</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>1177</v>
+        <v>1204</v>
       </c>
       <c r="O54" s="5">
         <v>1600</v>
@@ -39044,7 +39999,7 @@
         <v>51</v>
       </c>
       <c r="Y54" s="2" t="s">
-        <v>1244</v>
+        <v>1269</v>
       </c>
       <c r="Z54" s="2" t="s">
         <v>0</v>
@@ -39082,13 +40037,13 @@
     </row>
     <row r="55" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>1243</v>
+        <v>1268</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>1243</v>
+        <v>1268</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D55" s="7">
         <v>46072</v>
@@ -39100,10 +40055,10 @@
         <v>40</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>1242</v>
+        <v>1267</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>1241</v>
+        <v>1266</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>43</v>
@@ -39115,13 +40070,13 @@
         <v>446</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>1155</v>
+        <v>1182</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>1154</v>
+        <v>1181</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>1153</v>
+        <v>1180</v>
       </c>
       <c r="O55" s="8">
         <v>500</v>
@@ -39154,7 +40109,7 @@
         <v>51</v>
       </c>
       <c r="Y55" s="3" t="s">
-        <v>1240</v>
+        <v>1265</v>
       </c>
       <c r="Z55" s="3" t="s">
         <v>0</v>
@@ -39192,13 +40147,13 @@
     </row>
     <row r="56" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>1239</v>
+        <v>1264</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1239</v>
+        <v>1264</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D56" s="4">
         <v>46076</v>
@@ -39210,10 +40165,10 @@
         <v>61</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1238</v>
+        <v>1263</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>1237</v>
+        <v>1262</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>163</v>
@@ -39225,13 +40180,13 @@
         <v>417</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>1228</v>
+        <v>1253</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>1227</v>
+        <v>1252</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>1177</v>
+        <v>1204</v>
       </c>
       <c r="O56" s="5">
         <v>1700</v>
@@ -39264,7 +40219,7 @@
         <v>51</v>
       </c>
       <c r="Y56" s="2" t="s">
-        <v>1236</v>
+        <v>1261</v>
       </c>
       <c r="Z56" s="2" t="s">
         <v>0</v>
@@ -39302,13 +40257,13 @@
     </row>
     <row r="57" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>1233</v>
+        <v>1258</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>1233</v>
+        <v>1258</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D57" s="7">
         <v>46077</v>
@@ -39332,16 +40287,16 @@
         <v>164</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>1218</v>
+        <v>1243</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>1235</v>
+        <v>1260</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>1234</v>
+        <v>1259</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>1215</v>
+        <v>1240</v>
       </c>
       <c r="O57" s="8">
         <v>500</v>
@@ -39374,7 +40329,7 @@
         <v>51</v>
       </c>
       <c r="Y57" s="3" t="s">
-        <v>1232</v>
+        <v>1257</v>
       </c>
       <c r="Z57" s="3" t="s">
         <v>0</v>
@@ -39412,13 +40367,13 @@
     </row>
     <row r="58" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>1233</v>
+        <v>1258</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1233</v>
+        <v>1258</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D58" s="4">
         <v>46077</v>
@@ -39442,16 +40397,16 @@
         <v>164</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>1213</v>
+        <v>1238</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>1212</v>
+        <v>1237</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>1211</v>
+        <v>1236</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>1210</v>
+        <v>1235</v>
       </c>
       <c r="O58" s="5">
         <v>500</v>
@@ -39484,7 +40439,7 @@
         <v>51</v>
       </c>
       <c r="Y58" s="2" t="s">
-        <v>1232</v>
+        <v>1257</v>
       </c>
       <c r="Z58" s="2" t="s">
         <v>0</v>
@@ -39499,10 +40454,10 @@
         <v>111</v>
       </c>
       <c r="AD58" s="2" t="s">
-        <v>1208</v>
+        <v>1233</v>
       </c>
       <c r="AE58" s="2" t="s">
-        <v>1207</v>
+        <v>1232</v>
       </c>
       <c r="AF58" s="2" t="s">
         <v>77</v>
@@ -39522,13 +40477,13 @@
     </row>
     <row r="59" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>1231</v>
+        <v>1256</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>1231</v>
+        <v>1256</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D59" s="7">
         <v>46078</v>
@@ -39540,10 +40495,10 @@
         <v>40</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>1187</v>
+        <v>1214</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>1186</v>
+        <v>1213</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>139</v>
@@ -39555,13 +40510,13 @@
         <v>782</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>1185</v>
+        <v>1212</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>1184</v>
+        <v>1211</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>1183</v>
+        <v>1210</v>
       </c>
       <c r="O59" s="8">
         <v>225</v>
@@ -39594,7 +40549,7 @@
         <v>51</v>
       </c>
       <c r="Y59" s="3" t="s">
-        <v>1230</v>
+        <v>1255</v>
       </c>
       <c r="Z59" s="3" t="s">
         <v>0</v>
@@ -39632,13 +40587,13 @@
     </row>
     <row r="60" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>1229</v>
+        <v>1254</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1229</v>
+        <v>1254</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D60" s="4">
         <v>46079</v>
@@ -39665,13 +40620,13 @@
         <v>417</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>1228</v>
+        <v>1253</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>1227</v>
+        <v>1252</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>1177</v>
+        <v>1204</v>
       </c>
       <c r="O60" s="5">
         <v>5000</v>
@@ -39695,16 +40650,16 @@
         <v>2354</v>
       </c>
       <c r="V60" s="2" t="s">
-        <v>1191</v>
+        <v>1160</v>
       </c>
       <c r="W60" s="2" t="s">
-        <v>1190</v>
+        <v>1159</v>
       </c>
       <c r="X60" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Y60" s="2" t="s">
-        <v>1226</v>
+        <v>1251</v>
       </c>
       <c r="Z60" s="2" t="s">
         <v>0</v>
@@ -39742,13 +40697,13 @@
     </row>
     <row r="61" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>1225</v>
+        <v>1250</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>1225</v>
+        <v>1250</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D61" s="7">
         <v>46079</v>
@@ -39775,13 +40730,13 @@
         <v>1058</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>1224</v>
+        <v>1249</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>1223</v>
+        <v>1248</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>1222</v>
+        <v>1247</v>
       </c>
       <c r="O61" s="8">
         <v>12000</v>
@@ -39814,7 +40769,7 @@
         <v>51</v>
       </c>
       <c r="Y61" s="3" t="s">
-        <v>1221</v>
+        <v>1246</v>
       </c>
       <c r="Z61" s="3" t="s">
         <v>0</v>
@@ -39852,13 +40807,13 @@
     </row>
     <row r="62" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>1220</v>
+        <v>1245</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1220</v>
+        <v>1245</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D62" s="4">
         <v>46085</v>
@@ -39885,13 +40840,13 @@
         <v>633</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>1161</v>
+        <v>1188</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>652</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>1160</v>
+        <v>1187</v>
       </c>
       <c r="O62" s="5">
         <v>5005</v>
@@ -39924,7 +40879,7 @@
         <v>51</v>
       </c>
       <c r="Y62" s="2" t="s">
-        <v>1219</v>
+        <v>1244</v>
       </c>
       <c r="Z62" s="2" t="s">
         <v>0</v>
@@ -39962,13 +40917,13 @@
     </row>
     <row r="63" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>1214</v>
+        <v>1239</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>1214</v>
+        <v>1239</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D63" s="7">
         <v>46085</v>
@@ -39992,16 +40947,16 @@
         <v>164</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>1218</v>
+        <v>1243</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>1217</v>
+        <v>1242</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>1216</v>
+        <v>1241</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>1215</v>
+        <v>1240</v>
       </c>
       <c r="O63" s="8">
         <v>500</v>
@@ -40034,7 +40989,7 @@
         <v>51</v>
       </c>
       <c r="Y63" s="3" t="s">
-        <v>1209</v>
+        <v>1234</v>
       </c>
       <c r="Z63" s="3" t="s">
         <v>0</v>
@@ -40072,13 +41027,13 @@
     </row>
     <row r="64" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>1214</v>
+        <v>1239</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1214</v>
+        <v>1239</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D64" s="4">
         <v>46085</v>
@@ -40102,16 +41057,16 @@
         <v>164</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>1213</v>
+        <v>1238</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>1212</v>
+        <v>1237</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>1211</v>
+        <v>1236</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>1210</v>
+        <v>1235</v>
       </c>
       <c r="O64" s="5">
         <v>500</v>
@@ -40144,7 +41099,7 @@
         <v>51</v>
       </c>
       <c r="Y64" s="2" t="s">
-        <v>1209</v>
+        <v>1234</v>
       </c>
       <c r="Z64" s="2" t="s">
         <v>0</v>
@@ -40159,10 +41114,10 @@
         <v>111</v>
       </c>
       <c r="AD64" s="2" t="s">
-        <v>1208</v>
+        <v>1233</v>
       </c>
       <c r="AE64" s="2" t="s">
-        <v>1207</v>
+        <v>1232</v>
       </c>
       <c r="AF64" s="2" t="s">
         <v>77</v>
@@ -40182,13 +41137,13 @@
     </row>
     <row r="65" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>1206</v>
+        <v>1231</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>1206</v>
+        <v>1231</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D65" s="7">
         <v>46085</v>
@@ -40200,10 +41155,10 @@
         <v>40</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>1205</v>
+        <v>1230</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>1204</v>
+        <v>1229</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>163</v>
@@ -40215,13 +41170,13 @@
         <v>154</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>1203</v>
+        <v>1228</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>1202</v>
+        <v>1227</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>1201</v>
+        <v>1226</v>
       </c>
       <c r="O65" s="8">
         <v>3700</v>
@@ -40254,7 +41209,7 @@
         <v>51</v>
       </c>
       <c r="Y65" s="3" t="s">
-        <v>1200</v>
+        <v>1225</v>
       </c>
       <c r="Z65" s="3" t="s">
         <v>0</v>
@@ -40292,13 +41247,13 @@
     </row>
     <row r="66" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>1199</v>
+        <v>1224</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1199</v>
+        <v>1224</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D66" s="4">
         <v>46085</v>
@@ -40310,10 +41265,10 @@
         <v>40</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1198</v>
+        <v>1223</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>1197</v>
+        <v>1222</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>139</v>
@@ -40322,7 +41277,7 @@
         <v>140</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>1196</v>
+        <v>1221</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>0</v>
@@ -40364,7 +41319,7 @@
         <v>0</v>
       </c>
       <c r="Y66" s="2" t="s">
-        <v>1195</v>
+        <v>1220</v>
       </c>
       <c r="Z66" s="2" t="s">
         <v>0</v>
@@ -40379,10 +41334,10 @@
         <v>298</v>
       </c>
       <c r="AD66" s="2" t="s">
-        <v>1194</v>
+        <v>1219</v>
       </c>
       <c r="AE66" s="2" t="s">
-        <v>1193</v>
+        <v>1218</v>
       </c>
       <c r="AF66" s="2" t="s">
         <v>0</v>
@@ -40402,13 +41357,13 @@
     </row>
     <row r="67" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>1192</v>
+        <v>1217</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>1192</v>
+        <v>1217</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D67" s="7">
         <v>46091</v>
@@ -40435,13 +41390,13 @@
         <v>417</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>1179</v>
+        <v>1206</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>1178</v>
+        <v>1205</v>
       </c>
       <c r="N67" s="3" t="s">
-        <v>1177</v>
+        <v>1204</v>
       </c>
       <c r="O67" s="8">
         <v>5000</v>
@@ -40465,16 +41420,16 @@
         <v>2354</v>
       </c>
       <c r="V67" s="3" t="s">
-        <v>1191</v>
+        <v>1160</v>
       </c>
       <c r="W67" s="3" t="s">
-        <v>1190</v>
+        <v>1159</v>
       </c>
       <c r="X67" s="3" t="s">
         <v>51</v>
       </c>
       <c r="Y67" s="3" t="s">
-        <v>1189</v>
+        <v>1216</v>
       </c>
       <c r="Z67" s="3" t="s">
         <v>0</v>
@@ -40512,13 +41467,13 @@
     </row>
     <row r="68" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>1188</v>
+        <v>1215</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1188</v>
+        <v>1215</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D68" s="4">
         <v>46091</v>
@@ -40530,10 +41485,10 @@
         <v>40</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>1187</v>
+        <v>1214</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>1186</v>
+        <v>1213</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>139</v>
@@ -40545,13 +41500,13 @@
         <v>782</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>1185</v>
+        <v>1212</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>1184</v>
+        <v>1211</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>1183</v>
+        <v>1210</v>
       </c>
       <c r="O68" s="5">
         <v>225</v>
@@ -40584,7 +41539,7 @@
         <v>51</v>
       </c>
       <c r="Y68" s="2" t="s">
-        <v>1182</v>
+        <v>1209</v>
       </c>
       <c r="Z68" s="2" t="s">
         <v>0</v>
@@ -40622,28 +41577,28 @@
     </row>
     <row r="69" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>1173</v>
+        <v>1200</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>1173</v>
+        <v>1200</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D69" s="7">
         <v>46092</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>1172</v>
+        <v>1199</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>1171</v>
+        <v>1198</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>1170</v>
+        <v>1197</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>1169</v>
+        <v>1196</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>139</v>
@@ -40655,13 +41610,13 @@
         <v>272</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>1181</v>
+        <v>1208</v>
       </c>
       <c r="M69" s="3" t="s">
         <v>274</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>1180</v>
+        <v>1207</v>
       </c>
       <c r="O69" s="8">
         <v>10000</v>
@@ -40685,16 +41640,16 @@
         <v>3312.29</v>
       </c>
       <c r="V69" s="3" t="s">
-        <v>1165</v>
+        <v>1192</v>
       </c>
       <c r="W69" s="3" t="s">
-        <v>1164</v>
+        <v>1191</v>
       </c>
       <c r="X69" s="3" t="s">
         <v>87</v>
       </c>
       <c r="Y69" s="3" t="s">
-        <v>1163</v>
+        <v>1190</v>
       </c>
       <c r="Z69" s="3" t="s">
         <v>0</v>
@@ -40732,28 +41687,28 @@
     </row>
     <row r="70" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>1173</v>
+        <v>1200</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1173</v>
+        <v>1200</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D70" s="4">
         <v>46092</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>1172</v>
+        <v>1199</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>1171</v>
+        <v>1198</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>1170</v>
+        <v>1197</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>1169</v>
+        <v>1196</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>139</v>
@@ -40765,13 +41720,13 @@
         <v>417</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>1179</v>
+        <v>1206</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>1178</v>
+        <v>1205</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>1177</v>
+        <v>1204</v>
       </c>
       <c r="O70" s="5">
         <v>5000</v>
@@ -40795,16 +41750,16 @@
         <v>1559.15</v>
       </c>
       <c r="V70" s="2" t="s">
-        <v>1165</v>
+        <v>1192</v>
       </c>
       <c r="W70" s="2" t="s">
-        <v>1164</v>
+        <v>1191</v>
       </c>
       <c r="X70" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y70" s="2" t="s">
-        <v>1163</v>
+        <v>1190</v>
       </c>
       <c r="Z70" s="2" t="s">
         <v>0</v>
@@ -40842,28 +41797,28 @@
     </row>
     <row r="71" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>1173</v>
+        <v>1200</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>1173</v>
+        <v>1200</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D71" s="7">
         <v>46092</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>1172</v>
+        <v>1199</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>1171</v>
+        <v>1198</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>1170</v>
+        <v>1197</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>1169</v>
+        <v>1196</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>139</v>
@@ -40875,13 +41830,13 @@
         <v>342</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>1176</v>
+        <v>1203</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>1175</v>
+        <v>1202</v>
       </c>
       <c r="N71" s="3" t="s">
-        <v>1174</v>
+        <v>1201</v>
       </c>
       <c r="O71" s="8">
         <v>8400</v>
@@ -40905,16 +41860,16 @@
         <v>2580.5300000000002</v>
       </c>
       <c r="V71" s="3" t="s">
-        <v>1165</v>
+        <v>1192</v>
       </c>
       <c r="W71" s="3" t="s">
-        <v>1164</v>
+        <v>1191</v>
       </c>
       <c r="X71" s="3" t="s">
         <v>87</v>
       </c>
       <c r="Y71" s="3" t="s">
-        <v>1163</v>
+        <v>1190</v>
       </c>
       <c r="Z71" s="3" t="s">
         <v>0</v>
@@ -40952,28 +41907,28 @@
     </row>
     <row r="72" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>1173</v>
+        <v>1200</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1173</v>
+        <v>1200</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D72" s="4">
         <v>46092</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>1172</v>
+        <v>1199</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>1171</v>
+        <v>1198</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>1170</v>
+        <v>1197</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>1169</v>
+        <v>1196</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>139</v>
@@ -40985,13 +41940,13 @@
         <v>782</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>1168</v>
+        <v>1195</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>1167</v>
+        <v>1194</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>1166</v>
+        <v>1193</v>
       </c>
       <c r="O72" s="5">
         <v>2400</v>
@@ -41015,16 +41970,16 @@
         <v>775.1</v>
       </c>
       <c r="V72" s="2" t="s">
-        <v>1165</v>
+        <v>1192</v>
       </c>
       <c r="W72" s="2" t="s">
-        <v>1164</v>
+        <v>1191</v>
       </c>
       <c r="X72" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y72" s="2" t="s">
-        <v>1163</v>
+        <v>1190</v>
       </c>
       <c r="Z72" s="2" t="s">
         <v>0</v>
@@ -41062,13 +42017,13 @@
     </row>
     <row r="73" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>1162</v>
+        <v>1189</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>1162</v>
+        <v>1189</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D73" s="7">
         <v>46093</v>
@@ -41080,10 +42035,10 @@
         <v>61</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>1142</v>
+        <v>1170</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>1141</v>
+        <v>1169</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>163</v>
@@ -41095,13 +42050,13 @@
         <v>633</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>1161</v>
+        <v>1188</v>
       </c>
       <c r="M73" s="3" t="s">
         <v>652</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>1160</v>
+        <v>1187</v>
       </c>
       <c r="O73" s="8">
         <v>507</v>
@@ -41134,7 +42089,7 @@
         <v>51</v>
       </c>
       <c r="Y73" s="3" t="s">
-        <v>1159</v>
+        <v>1186</v>
       </c>
       <c r="Z73" s="3" t="s">
         <v>0</v>
@@ -41172,13 +42127,13 @@
     </row>
     <row r="74" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>1158</v>
+        <v>1185</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1158</v>
+        <v>1185</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D74" s="4">
         <v>46097</v>
@@ -41196,22 +42151,22 @@
         <v>386</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>1157</v>
+        <v>1184</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>1156</v>
+        <v>1183</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>446</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>1155</v>
+        <v>1182</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>1154</v>
+        <v>1181</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>1153</v>
+        <v>1180</v>
       </c>
       <c r="O74" s="5">
         <v>3000</v>
@@ -41244,7 +42199,7 @@
         <v>51</v>
       </c>
       <c r="Y74" s="2" t="s">
-        <v>1152</v>
+        <v>1179</v>
       </c>
       <c r="Z74" s="2" t="s">
         <v>0</v>
@@ -41282,13 +42237,13 @@
     </row>
     <row r="75" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>1151</v>
+        <v>1178</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>1151</v>
+        <v>1178</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D75" s="7">
         <v>46098</v>
@@ -41315,13 +42270,13 @@
         <v>300</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>1150</v>
+        <v>1177</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>1149</v>
+        <v>1176</v>
       </c>
       <c r="N75" s="3" t="s">
-        <v>1148</v>
+        <v>1175</v>
       </c>
       <c r="O75" s="8">
         <v>10000</v>
@@ -41345,16 +42300,16 @@
         <v>14724</v>
       </c>
       <c r="V75" s="3" t="s">
-        <v>1147</v>
+        <v>1174</v>
       </c>
       <c r="W75" s="3" t="s">
-        <v>1146</v>
+        <v>1173</v>
       </c>
       <c r="X75" s="3" t="s">
         <v>51</v>
       </c>
       <c r="Y75" s="3" t="s">
-        <v>1145</v>
+        <v>1172</v>
       </c>
       <c r="Z75" s="3" t="s">
         <v>0</v>
@@ -41392,13 +42347,13 @@
     </row>
     <row r="76" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>1144</v>
+        <v>1171</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1144</v>
+        <v>1171</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="D76" s="4">
         <v>46098</v>
@@ -41410,10 +42365,10 @@
         <v>61</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>1142</v>
+        <v>1170</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>1141</v>
+        <v>1169</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>163</v>
@@ -41425,13 +42380,13 @@
         <v>632</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>1140</v>
+        <v>1168</v>
       </c>
       <c r="M76" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>1139</v>
+        <v>1167</v>
       </c>
       <c r="O76" s="5">
         <v>507</v>
@@ -41464,7 +42419,7 @@
         <v>51</v>
       </c>
       <c r="Y76" s="2" t="s">
-        <v>1138</v>
+        <v>1166</v>
       </c>
       <c r="Z76" s="2" t="s">
         <v>0</v>
@@ -41498,6 +42453,116 @@
       </c>
       <c r="AJ76" s="5">
         <v>5539.1575199999997</v>
+      </c>
+    </row>
+    <row r="77" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="3" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D77" s="7">
+        <v>46100</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="L77" s="3" t="s">
+        <v>1163</v>
+      </c>
+      <c r="M77" s="3" t="s">
+        <v>1162</v>
+      </c>
+      <c r="N77" s="3" t="s">
+        <v>1161</v>
+      </c>
+      <c r="O77" s="8">
+        <v>10000</v>
+      </c>
+      <c r="P77" s="8">
+        <v>8.9</v>
+      </c>
+      <c r="Q77" s="9">
+        <v>89000</v>
+      </c>
+      <c r="R77" s="9">
+        <v>2892.5</v>
+      </c>
+      <c r="S77" s="9">
+        <v>91892.5</v>
+      </c>
+      <c r="T77" s="9">
+        <v>89000</v>
+      </c>
+      <c r="U77" s="9">
+        <v>3560</v>
+      </c>
+      <c r="V77" s="3" t="s">
+        <v>1160</v>
+      </c>
+      <c r="W77" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="X77" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y77" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="Z77" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB77" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="AC77" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="AD77" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE77" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF77" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG77" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ77" s="8">
+        <v>98896.9</v>
       </c>
     </row>
   </sheetData>

--- a/BASE_KEMPARTS.xlsx
+++ b/BASE_KEMPARTS.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dash_kp_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE8612BF-9B3D-4A9E-8556-57259B85E732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F27AB54-042C-4F7F-B743-E9F15D232D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{2980BE97-CF4C-415F-B4D1-6FE288E199F1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{2980BE97-CF4C-415F-B4D1-6FE288E199F1}"/>
   </bookViews>
   <sheets>
     <sheet name="FSP" sheetId="2" r:id="rId1"/>
-    <sheet name="FSC" sheetId="1" r:id="rId2"/>
+    <sheet name="FSC" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7797" uniqueCount="1339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9297" uniqueCount="1498">
   <si>
     <t>Numero</t>
   </si>
@@ -4054,6 +4054,483 @@
   </si>
   <si>
     <t>000015314</t>
+  </si>
+  <si>
+    <t>003268</t>
+  </si>
+  <si>
+    <t>2025.357.07.</t>
+  </si>
+  <si>
+    <t>251014</t>
+  </si>
+  <si>
+    <t>2025.357.07.251014</t>
+  </si>
+  <si>
+    <t>000002500</t>
+  </si>
+  <si>
+    <t>003169</t>
+  </si>
+  <si>
+    <t>25021046</t>
+  </si>
+  <si>
+    <t>2025.004.01.25021046</t>
+  </si>
+  <si>
+    <t>000002499</t>
+  </si>
+  <si>
+    <t>003283</t>
+  </si>
+  <si>
+    <t>000002498</t>
+  </si>
+  <si>
+    <t>003279</t>
+  </si>
+  <si>
+    <t>000002494</t>
+  </si>
+  <si>
+    <t>24091029</t>
+  </si>
+  <si>
+    <t>2025.004.03.24091029</t>
+  </si>
+  <si>
+    <t>003277</t>
+  </si>
+  <si>
+    <t>RESICOLOR INDUSTRIA DE PRODUTOS QUIMICOS</t>
+  </si>
+  <si>
+    <t>C00101</t>
+  </si>
+  <si>
+    <t>000002490</t>
+  </si>
+  <si>
+    <t>003270</t>
+  </si>
+  <si>
+    <t>MEKAL INDUSTRIA DE TINTAS LTDA</t>
+  </si>
+  <si>
+    <t>C00365</t>
+  </si>
+  <si>
+    <t>000002488</t>
+  </si>
+  <si>
+    <t>003272</t>
+  </si>
+  <si>
+    <t>000002487</t>
+  </si>
+  <si>
+    <t>003274</t>
+  </si>
+  <si>
+    <t>EXPRESSO BATISTENSE TRANSPORTES LTDA</t>
+  </si>
+  <si>
+    <t>T00223</t>
+  </si>
+  <si>
+    <t>2024.675.04.</t>
+  </si>
+  <si>
+    <t>2024.675.04.202407</t>
+  </si>
+  <si>
+    <t>000002486</t>
+  </si>
+  <si>
+    <t>003266</t>
+  </si>
+  <si>
+    <t>BRAVUS INDUSTRIA E COMERCIO DE TINTAS LTDA</t>
+  </si>
+  <si>
+    <t>C01196</t>
+  </si>
+  <si>
+    <t>000002485</t>
+  </si>
+  <si>
+    <t>003264</t>
+  </si>
+  <si>
+    <t>2025.357.</t>
+  </si>
+  <si>
+    <t>08250329-01</t>
+  </si>
+  <si>
+    <t>2025.357.08250329-01</t>
+  </si>
+  <si>
+    <t>000002483</t>
+  </si>
+  <si>
+    <t>003258</t>
+  </si>
+  <si>
+    <t>000002482</t>
+  </si>
+  <si>
+    <t>003227</t>
+  </si>
+  <si>
+    <t>000002481</t>
+  </si>
+  <si>
+    <t>25031037</t>
+  </si>
+  <si>
+    <t>2025.004.04.25031037</t>
+  </si>
+  <si>
+    <t>003240</t>
+  </si>
+  <si>
+    <t>2024.004.13.</t>
+  </si>
+  <si>
+    <t>24121018</t>
+  </si>
+  <si>
+    <t>2024.004.13.24121018</t>
+  </si>
+  <si>
+    <t>FARBEN SA INDUSTRIA QUIMICA</t>
+  </si>
+  <si>
+    <t>C01097</t>
+  </si>
+  <si>
+    <t>000002480</t>
+  </si>
+  <si>
+    <t>003257</t>
+  </si>
+  <si>
+    <t>6101</t>
+  </si>
+  <si>
+    <t>000002479</t>
+  </si>
+  <si>
+    <t>003253</t>
+  </si>
+  <si>
+    <t>24121037</t>
+  </si>
+  <si>
+    <t>2024.004.14.24121037</t>
+  </si>
+  <si>
+    <t>TINTAS ALESSI LTDA</t>
+  </si>
+  <si>
+    <t>C00361</t>
+  </si>
+  <si>
+    <t>000002478</t>
+  </si>
+  <si>
+    <t>003251</t>
+  </si>
+  <si>
+    <t>DACAR QUIMICA DO BRASIL S/A</t>
+  </si>
+  <si>
+    <t>C00347</t>
+  </si>
+  <si>
+    <t>000002477</t>
+  </si>
+  <si>
+    <t>003248</t>
+  </si>
+  <si>
+    <t>000002476</t>
+  </si>
+  <si>
+    <t>003246</t>
+  </si>
+  <si>
+    <t>000002475</t>
+  </si>
+  <si>
+    <t>000002474</t>
+  </si>
+  <si>
+    <t>003243</t>
+  </si>
+  <si>
+    <t>000002473</t>
+  </si>
+  <si>
+    <t>003242</t>
+  </si>
+  <si>
+    <t>CH 332</t>
+  </si>
+  <si>
+    <t>F00813</t>
+  </si>
+  <si>
+    <t>000002472</t>
+  </si>
+  <si>
+    <t>003238</t>
+  </si>
+  <si>
+    <t>000002471</t>
+  </si>
+  <si>
+    <t>003236</t>
+  </si>
+  <si>
+    <t>000002470</t>
+  </si>
+  <si>
+    <t>003234</t>
+  </si>
+  <si>
+    <t>000002469</t>
+  </si>
+  <si>
+    <t>003231</t>
+  </si>
+  <si>
+    <t>GAMACOR TINTAS E SOLVENTES LTDA</t>
+  </si>
+  <si>
+    <t>C00648</t>
+  </si>
+  <si>
+    <t>000002467</t>
+  </si>
+  <si>
+    <t>003233</t>
+  </si>
+  <si>
+    <t>000002466</t>
+  </si>
+  <si>
+    <t>003229</t>
+  </si>
+  <si>
+    <t>000002465</t>
+  </si>
+  <si>
+    <t>2025.004.02.</t>
+  </si>
+  <si>
+    <t>2025.004.02.25011197</t>
+  </si>
+  <si>
+    <t>003226</t>
+  </si>
+  <si>
+    <t>000002464</t>
+  </si>
+  <si>
+    <t>TAMBORES D</t>
+  </si>
+  <si>
+    <t>003224</t>
+  </si>
+  <si>
+    <t>000002463</t>
+  </si>
+  <si>
+    <t>003222</t>
+  </si>
+  <si>
+    <t>250206-01</t>
+  </si>
+  <si>
+    <t>2025.357.03.250206-01</t>
+  </si>
+  <si>
+    <t>000002462</t>
+  </si>
+  <si>
+    <t>003220</t>
+  </si>
+  <si>
+    <t>000002461</t>
+  </si>
+  <si>
+    <t>003167</t>
+  </si>
+  <si>
+    <t>000002460</t>
+  </si>
+  <si>
+    <t>003219</t>
+  </si>
+  <si>
+    <t>2025.435.</t>
+  </si>
+  <si>
+    <t>030001006106</t>
+  </si>
+  <si>
+    <t>2025.435.030001006106</t>
+  </si>
+  <si>
+    <t>000002456</t>
+  </si>
+  <si>
+    <t>2023.103.07.</t>
+  </si>
+  <si>
+    <t>2023.103.07.T230726</t>
+  </si>
+  <si>
+    <t>2025.103.01.</t>
+  </si>
+  <si>
+    <t>2025.103.01.250122</t>
+  </si>
+  <si>
+    <t>030001006352</t>
+  </si>
+  <si>
+    <t>2025.435.030001006352</t>
+  </si>
+  <si>
+    <t>2025.004.05.</t>
+  </si>
+  <si>
+    <t>25021104</t>
+  </si>
+  <si>
+    <t>2025.004.05.25021104</t>
+  </si>
+  <si>
+    <t>003217</t>
+  </si>
+  <si>
+    <t>000002454</t>
+  </si>
+  <si>
+    <t>003216</t>
+  </si>
+  <si>
+    <t>000002453</t>
+  </si>
+  <si>
+    <t>003094</t>
+  </si>
+  <si>
+    <t>000002452</t>
+  </si>
+  <si>
+    <t>003202</t>
+  </si>
+  <si>
+    <t>000002451</t>
+  </si>
+  <si>
+    <t>003215</t>
+  </si>
+  <si>
+    <t>000002450</t>
+  </si>
+  <si>
+    <t>003213</t>
+  </si>
+  <si>
+    <t>000002441</t>
+  </si>
+  <si>
+    <t>003211</t>
+  </si>
+  <si>
+    <t>000002440</t>
+  </si>
+  <si>
+    <t>003209</t>
+  </si>
+  <si>
+    <t>2024.004.13.24121017</t>
+  </si>
+  <si>
+    <t>000002439</t>
+  </si>
+  <si>
+    <t>003207</t>
+  </si>
+  <si>
+    <t>000002438</t>
+  </si>
+  <si>
+    <t>003200</t>
+  </si>
+  <si>
+    <t>250501</t>
+  </si>
+  <si>
+    <t>2025.357.05.250501</t>
+  </si>
+  <si>
+    <t>000002437</t>
+  </si>
+  <si>
+    <t>003206</t>
+  </si>
+  <si>
+    <t>GA 100</t>
+  </si>
+  <si>
+    <t>000002436</t>
+  </si>
+  <si>
+    <t>003191</t>
+  </si>
+  <si>
+    <t>TRANSPORTES OURO NEGRO LTDA</t>
+  </si>
+  <si>
+    <t>T00113</t>
+  </si>
+  <si>
+    <t>2025.357.01.</t>
+  </si>
+  <si>
+    <t>20250301</t>
+  </si>
+  <si>
+    <t>2025.357.01.20250301</t>
+  </si>
+  <si>
+    <t>PARIS INL DO BRAS TINTAS E VERNIZES LTDA</t>
+  </si>
+  <si>
+    <t>C00627</t>
+  </si>
+  <si>
+    <t>000002435</t>
+  </si>
+  <si>
+    <t>003189</t>
+  </si>
+  <si>
+    <t>000002434</t>
+  </si>
+  <si>
+    <t>003183</t>
+  </si>
+  <si>
+    <t>000002433</t>
   </si>
 </sst>
 </file>
@@ -36348,8 +36825,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD33B125-63FE-4BA9-B3BF-966D2FF5272D}">
-  <dimension ref="A1:AJ22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24A7CC20-A86F-46BC-A3E2-700C425FEDA4}">
+  <dimension ref="A1:AJ82"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -36359,19 +36836,18 @@
     <col min="5" max="5" width="4.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="64.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="48" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="50.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="25.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="22.85546875" bestFit="1" customWidth="1"/>
     <col min="19" max="20" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.140625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="48" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14.42578125" bestFit="1" customWidth="1"/>
@@ -36382,7 +36858,7 @@
     <col min="29" max="29" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="6" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="12.140625" bestFit="1" customWidth="1"/>
@@ -36501,16 +36977,16 @@
     </row>
     <row r="2" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>36</v>
+        <v>1497</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>36</v>
+        <v>1497</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D2" s="3">
-        <v>46085</v>
+        <v>46024</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>38</v>
@@ -36519,61 +36995,61 @@
         <v>39</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>42</v>
+        <v>201</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>43</v>
+        <v>202</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>44</v>
+        <v>300</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>45</v>
+        <v>1368</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>46</v>
+        <v>303</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>47</v>
+        <v>1367</v>
       </c>
       <c r="O2" s="4">
-        <v>5005</v>
+        <v>50</v>
       </c>
       <c r="P2" s="4">
-        <v>21.21</v>
+        <v>19.53</v>
       </c>
       <c r="Q2" s="5">
-        <v>106156.05</v>
+        <v>976.5</v>
       </c>
       <c r="R2" s="5">
-        <v>3450.07</v>
+        <v>0</v>
       </c>
       <c r="S2" s="5">
-        <v>109606.12</v>
+        <v>976.5</v>
       </c>
       <c r="T2" s="5">
-        <v>106156.05</v>
+        <v>976.5</v>
       </c>
       <c r="U2" s="5">
-        <v>4246.24</v>
+        <v>39.06</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>48</v>
+        <v>1366</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>49</v>
+        <v>1365</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>50</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>51</v>
+        <v>1496</v>
       </c>
       <c r="Z2" s="2" t="s">
         <v>52</v>
@@ -36582,16 +37058,16 @@
         <v>53</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>56</v>
+        <v>295</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>57</v>
+        <v>294</v>
       </c>
       <c r="AF2" s="2" t="s">
         <v>58</v>
@@ -36606,33 +37082,33 @@
         <v>4</v>
       </c>
       <c r="AJ2" s="4">
-        <v>71699.37775</v>
+        <v>559.65099999999995</v>
       </c>
     </row>
     <row r="3" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>59</v>
+        <v>1495</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>59</v>
+        <v>1495</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D3" s="7">
-        <v>46085</v>
+        <v>46027</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>38</v>
+        <v>144</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>42</v>
@@ -36641,49 +37117,49 @@
         <v>43</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>60</v>
+        <v>177</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>61</v>
+        <v>178</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>62</v>
+        <v>179</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>63</v>
+        <v>180</v>
       </c>
       <c r="O3" s="8">
-        <v>500</v>
+        <v>1001</v>
       </c>
       <c r="P3" s="8">
-        <v>13.56</v>
+        <v>22.18</v>
       </c>
       <c r="Q3" s="9">
-        <v>6780</v>
+        <v>22202.18</v>
       </c>
       <c r="R3" s="9">
-        <v>220.35</v>
+        <v>721.57</v>
       </c>
       <c r="S3" s="9">
-        <v>7000.35</v>
+        <v>22923.75</v>
       </c>
       <c r="T3" s="9">
-        <v>16635</v>
+        <v>22202.18</v>
       </c>
       <c r="U3" s="9">
-        <v>271.2</v>
+        <v>888.09</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="X3" s="6" t="s">
         <v>50</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>64</v>
+        <v>1494</v>
       </c>
       <c r="Z3" s="6" t="s">
         <v>52</v>
@@ -36695,13 +37171,13 @@
         <v>54</v>
       </c>
       <c r="AC3" s="6" t="s">
-        <v>55</v>
+        <v>149</v>
       </c>
       <c r="AD3" s="6" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="AE3" s="6" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="AF3" s="6" t="s">
         <v>58</v>
@@ -36716,84 +37192,84 @@
         <v>4</v>
       </c>
       <c r="AJ3" s="8">
-        <v>4405.1099999999997</v>
+        <v>10936.27535</v>
       </c>
     </row>
     <row r="4" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>59</v>
+        <v>1493</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>59</v>
+        <v>1493</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D4" s="3">
-        <v>46085</v>
+        <v>46027</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>38</v>
+        <v>144</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>40</v>
+        <v>1492</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>41</v>
+        <v>1491</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>68</v>
+        <v>1490</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>69</v>
+        <v>1489</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>70</v>
+        <v>1488</v>
       </c>
       <c r="O4" s="4">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="P4" s="4">
-        <v>19.71</v>
+        <v>14.82</v>
       </c>
       <c r="Q4" s="5">
-        <v>9855</v>
+        <v>8892</v>
       </c>
       <c r="R4" s="5">
-        <v>320.29000000000002</v>
+        <v>288.99</v>
       </c>
       <c r="S4" s="5">
-        <v>10175.290000000001</v>
+        <v>9180.99</v>
       </c>
       <c r="T4" s="5">
-        <v>16635</v>
+        <v>8892</v>
       </c>
       <c r="U4" s="5">
-        <v>1182.5999999999999</v>
+        <v>355.68</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>48</v>
+        <v>1487</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>49</v>
+        <v>1486</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>50</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>64</v>
+        <v>1485</v>
       </c>
       <c r="Z4" s="2" t="s">
         <v>52</v>
@@ -36805,13 +37281,13 @@
         <v>54</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>55</v>
+        <v>149</v>
       </c>
       <c r="AD4" s="2" t="s">
-        <v>71</v>
+        <v>138</v>
       </c>
       <c r="AE4" s="2" t="s">
-        <v>72</v>
+        <v>139</v>
       </c>
       <c r="AF4" s="2" t="s">
         <v>58</v>
@@ -36823,87 +37299,87 @@
         <v>52</v>
       </c>
       <c r="AI4" s="5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AJ4" s="4">
-        <v>4836.3900000000003</v>
+        <v>5599.0079999999998</v>
       </c>
     </row>
     <row r="5" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>73</v>
+        <v>1484</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>73</v>
+        <v>1484</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D5" s="7">
-        <v>46085</v>
+        <v>46029</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>38</v>
+        <v>512</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>39</v>
+        <v>511</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>74</v>
+        <v>1414</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>76</v>
+        <v>1483</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="O5" s="8">
-        <v>3700</v>
+        <v>15000</v>
       </c>
       <c r="P5" s="8">
-        <v>19.260000000000002</v>
+        <v>7.52067</v>
       </c>
       <c r="Q5" s="9">
-        <v>71262</v>
+        <v>112810.05</v>
       </c>
       <c r="R5" s="9">
-        <v>2316.02</v>
+        <v>0</v>
       </c>
       <c r="S5" s="9">
-        <v>73578.02</v>
+        <v>112810.05</v>
       </c>
       <c r="T5" s="9">
-        <v>71262</v>
+        <v>0</v>
       </c>
       <c r="U5" s="9">
-        <v>2850.48</v>
+        <v>0</v>
       </c>
       <c r="V5" s="6" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="W5" s="6" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="X5" s="6" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="Y5" s="6" t="s">
-        <v>82</v>
+        <v>1482</v>
       </c>
       <c r="Z5" s="6" t="s">
         <v>52</v>
@@ -36912,19 +37388,19 @@
         <v>53</v>
       </c>
       <c r="AB5" s="6" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="AC5" s="6" t="s">
-        <v>55</v>
+        <v>149</v>
       </c>
       <c r="AD5" s="6" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="AE5" s="6" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="AF5" s="6" t="s">
-        <v>85</v>
+        <v>992</v>
       </c>
       <c r="AG5" s="9">
         <v>0</v>
@@ -36933,36 +37409,36 @@
         <v>52</v>
       </c>
       <c r="AI5" s="9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="8">
-        <v>51373.093999999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>86</v>
+        <v>1484</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>86</v>
+        <v>1484</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D6" s="3">
-        <v>46085</v>
+        <v>46029</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>38</v>
+        <v>512</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>39</v>
+        <v>511</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>87</v>
+        <v>1414</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>89</v>
@@ -36971,7 +37447,7 @@
         <v>90</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>91</v>
+        <v>1483</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>52</v>
@@ -36983,25 +37459,25 @@
         <v>52</v>
       </c>
       <c r="O6" s="4">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P6" s="4">
-        <v>32.32</v>
+        <v>7.52067</v>
       </c>
       <c r="Q6" s="5">
-        <v>32.32</v>
+        <v>75206.7</v>
       </c>
       <c r="R6" s="5">
         <v>0</v>
       </c>
       <c r="S6" s="5">
-        <v>32.32</v>
+        <v>75206.7</v>
       </c>
       <c r="T6" s="5">
         <v>0</v>
       </c>
       <c r="U6" s="5">
-        <v>32.32</v>
+        <v>0</v>
       </c>
       <c r="V6" s="2" t="s">
         <v>52</v>
@@ -37010,10 +37486,10 @@
         <v>52</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>92</v>
+        <v>1482</v>
       </c>
       <c r="Z6" s="2" t="s">
         <v>52</v>
@@ -37022,19 +37498,19 @@
         <v>53</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>94</v>
+        <v>149</v>
       </c>
       <c r="AD6" s="2" t="s">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AE6" s="2" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>52</v>
+        <v>992</v>
       </c>
       <c r="AG6" s="5">
         <v>0</v>
@@ -37043,7 +37519,7 @@
         <v>52</v>
       </c>
       <c r="AI6" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ6" s="4">
         <v>0</v>
@@ -37051,79 +37527,79 @@
     </row>
     <row r="7" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>97</v>
+        <v>1481</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>97</v>
+        <v>1481</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D7" s="7">
-        <v>46091</v>
+        <v>46029</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>38</v>
+        <v>144</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>98</v>
+        <v>151</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>99</v>
+        <v>152</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>100</v>
+        <v>153</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>101</v>
+        <v>154</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>102</v>
+        <v>532</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>103</v>
+        <v>1480</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>104</v>
+        <v>1479</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="O7" s="8">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="P7" s="8">
-        <v>11.77</v>
+        <v>13.57</v>
       </c>
       <c r="Q7" s="9">
-        <v>58850</v>
+        <v>13570</v>
       </c>
       <c r="R7" s="9">
-        <v>1912.63</v>
+        <v>441.03</v>
       </c>
       <c r="S7" s="9">
-        <v>60762.63</v>
+        <v>14011.03</v>
       </c>
       <c r="T7" s="9">
-        <v>58850</v>
+        <v>13570</v>
       </c>
       <c r="U7" s="9">
-        <v>2354</v>
+        <v>542.79999999999995</v>
       </c>
       <c r="V7" s="6" t="s">
-        <v>106</v>
+        <v>159</v>
       </c>
       <c r="W7" s="6" t="s">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="X7" s="6" t="s">
         <v>50</v>
       </c>
       <c r="Y7" s="6" t="s">
-        <v>108</v>
+        <v>1478</v>
       </c>
       <c r="Z7" s="6" t="s">
         <v>52</v>
@@ -37132,10 +37608,10 @@
         <v>53</v>
       </c>
       <c r="AB7" s="6" t="s">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="AC7" s="6" t="s">
-        <v>94</v>
+        <v>149</v>
       </c>
       <c r="AD7" s="6" t="s">
         <v>65</v>
@@ -37156,72 +37632,72 @@
         <v>4</v>
       </c>
       <c r="AJ7" s="8">
-        <v>48943.45</v>
+        <v>7047.1</v>
       </c>
     </row>
     <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>109</v>
+        <v>1477</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>109</v>
+        <v>1477</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D8" s="3">
-        <v>46091</v>
+        <v>46036</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>38</v>
+        <v>144</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>112</v>
+        <v>177</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>113</v>
+        <v>178</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>114</v>
+        <v>179</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>115</v>
+        <v>180</v>
       </c>
       <c r="O8" s="4">
-        <v>225</v>
+        <v>1001</v>
       </c>
       <c r="P8" s="4">
-        <v>12.25</v>
+        <v>22.18</v>
       </c>
       <c r="Q8" s="5">
-        <v>2756.25</v>
+        <v>22202.18</v>
       </c>
       <c r="R8" s="5">
-        <v>89.58</v>
+        <v>721.57</v>
       </c>
       <c r="S8" s="5">
-        <v>2845.83</v>
+        <v>22923.75</v>
       </c>
       <c r="T8" s="5">
-        <v>2756.25</v>
+        <v>22202.18</v>
       </c>
       <c r="U8" s="5">
-        <v>110.25</v>
+        <v>888.09</v>
       </c>
       <c r="V8" s="2" t="s">
         <v>116</v>
@@ -37233,7 +37709,7 @@
         <v>50</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>118</v>
+        <v>1476</v>
       </c>
       <c r="Z8" s="2" t="s">
         <v>52</v>
@@ -37245,13 +37721,13 @@
         <v>54</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>55</v>
+        <v>149</v>
       </c>
       <c r="AD8" s="2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="AF8" s="2" t="s">
         <v>58</v>
@@ -37266,84 +37742,84 @@
         <v>4</v>
       </c>
       <c r="AJ8" s="4">
-        <v>2225.1802499999999</v>
+        <v>10936.27535</v>
       </c>
     </row>
     <row r="9" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>119</v>
+        <v>1475</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>119</v>
+        <v>1475</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D9" s="7">
-        <v>46092</v>
+        <v>46037</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>122</v>
+        <v>1390</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>123</v>
+        <v>1389</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>125</v>
+        <v>1474</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>126</v>
+        <v>454</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>127</v>
+        <v>1386</v>
       </c>
       <c r="O9" s="8">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="P9" s="8">
-        <v>8.2807300000000001</v>
+        <v>12.75</v>
       </c>
       <c r="Q9" s="9">
-        <v>82807.3</v>
+        <v>12750</v>
       </c>
       <c r="R9" s="9">
-        <v>2691.23</v>
+        <v>414.38</v>
       </c>
       <c r="S9" s="9">
-        <v>85498.53</v>
+        <v>13164.38</v>
       </c>
       <c r="T9" s="9">
-        <v>205676.76</v>
+        <v>12750</v>
       </c>
       <c r="U9" s="9">
-        <v>3312.29</v>
+        <v>2167.5</v>
       </c>
       <c r="V9" s="6" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="W9" s="6" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="X9" s="6" t="s">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="Y9" s="6" t="s">
-        <v>131</v>
+        <v>1473</v>
       </c>
       <c r="Z9" s="6" t="s">
         <v>52</v>
@@ -37352,10 +37828,10 @@
         <v>53</v>
       </c>
       <c r="AB9" s="6" t="s">
-        <v>132</v>
+        <v>54</v>
       </c>
       <c r="AC9" s="6" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="AD9" s="6" t="s">
         <v>65</v>
@@ -37373,36 +37849,36 @@
         <v>52</v>
       </c>
       <c r="AI9" s="9">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="AJ9" s="8">
-        <v>101325.9</v>
+        <v>9879.4500000000007</v>
       </c>
     </row>
     <row r="10" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>119</v>
+        <v>1472</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>119</v>
+        <v>1472</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D10" s="3">
-        <v>46092</v>
+        <v>46037</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>89</v>
@@ -37411,49 +37887,49 @@
         <v>90</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="O10" s="4">
-        <v>5000</v>
+        <v>300</v>
       </c>
       <c r="P10" s="4">
-        <v>7.7957700000000001</v>
+        <v>12.25</v>
       </c>
       <c r="Q10" s="5">
-        <v>38978.85</v>
+        <v>3675</v>
       </c>
       <c r="R10" s="5">
-        <v>1266.81</v>
+        <v>119.44</v>
       </c>
       <c r="S10" s="5">
-        <v>40245.660000000003</v>
+        <v>3794.44</v>
       </c>
       <c r="T10" s="5">
-        <v>205676.76</v>
+        <v>3675</v>
       </c>
       <c r="U10" s="5">
-        <v>1559.15</v>
+        <v>147</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>131</v>
+        <v>1471</v>
       </c>
       <c r="Z10" s="2" t="s">
         <v>52</v>
@@ -37462,10 +37938,10 @@
         <v>53</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>132</v>
+        <v>54</v>
       </c>
       <c r="AC10" s="2" t="s">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="AD10" s="2" t="s">
         <v>65</v>
@@ -37486,84 +37962,84 @@
         <v>4</v>
       </c>
       <c r="AJ10" s="4">
-        <v>48943.45</v>
+        <v>2966.9070000000002</v>
       </c>
     </row>
     <row r="11" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>119</v>
+        <v>1470</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>119</v>
+        <v>1470</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D11" s="7">
-        <v>46092</v>
+        <v>46037</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>122</v>
+        <v>1424</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>123</v>
+        <v>1423</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>89</v>
+        <v>201</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>90</v>
+        <v>202</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>137</v>
+        <v>170</v>
       </c>
       <c r="O11" s="8">
-        <v>8400</v>
+        <v>25</v>
       </c>
       <c r="P11" s="8">
-        <v>7.6801399999999997</v>
+        <v>16.3</v>
       </c>
       <c r="Q11" s="9">
-        <v>64513.18</v>
+        <v>407.5</v>
       </c>
       <c r="R11" s="9">
-        <v>2096.6799999999998</v>
+        <v>13.24</v>
       </c>
       <c r="S11" s="9">
-        <v>66609.86</v>
+        <v>420.74</v>
       </c>
       <c r="T11" s="9">
-        <v>205676.76</v>
+        <v>407.5</v>
       </c>
       <c r="U11" s="9">
-        <v>2580.5300000000002</v>
+        <v>48.9</v>
       </c>
       <c r="V11" s="6" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="W11" s="6" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="X11" s="6" t="s">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="Y11" s="6" t="s">
-        <v>131</v>
+        <v>1469</v>
       </c>
       <c r="Z11" s="6" t="s">
         <v>52</v>
@@ -37572,19 +38048,19 @@
         <v>53</v>
       </c>
       <c r="AB11" s="6" t="s">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="AC11" s="6" t="s">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="AD11" s="6" t="s">
-        <v>138</v>
+        <v>174</v>
       </c>
       <c r="AE11" s="6" t="s">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="AF11" s="6" t="s">
-        <v>58</v>
+        <v>1096</v>
       </c>
       <c r="AG11" s="9">
         <v>0</v>
@@ -37593,36 +38069,36 @@
         <v>52</v>
       </c>
       <c r="AI11" s="9">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AJ11" s="8">
-        <v>70249.703999999998</v>
+        <v>189.62575000000001</v>
       </c>
     </row>
     <row r="12" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>119</v>
+        <v>1468</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>1468</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D12" s="3">
-        <v>46092</v>
+        <v>46041</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>120</v>
+        <v>512</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>121</v>
+        <v>511</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>122</v>
+        <v>1414</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>89</v>
@@ -37631,49 +38107,49 @@
         <v>90</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>141</v>
+        <v>52</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>142</v>
+        <v>52</v>
       </c>
       <c r="O12" s="4">
-        <v>2400</v>
+        <v>24000</v>
       </c>
       <c r="P12" s="4">
-        <v>8.0739300000000007</v>
+        <v>8.3525399999999994</v>
       </c>
       <c r="Q12" s="5">
-        <v>19377.43</v>
+        <v>200460.96</v>
       </c>
       <c r="R12" s="5">
-        <v>629.77</v>
+        <v>0</v>
       </c>
       <c r="S12" s="5">
-        <v>20007.2</v>
+        <v>200460.96</v>
       </c>
       <c r="T12" s="5">
-        <v>205676.76</v>
+        <v>0</v>
       </c>
       <c r="U12" s="5">
-        <v>775.1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>129</v>
+        <v>52</v>
       </c>
       <c r="X12" s="2" t="s">
         <v>130</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>131</v>
+        <v>1467</v>
       </c>
       <c r="Z12" s="2" t="s">
         <v>52</v>
@@ -37685,16 +38161,16 @@
         <v>132</v>
       </c>
       <c r="AC12" s="2" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="AD12" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="AF12" s="2" t="s">
-        <v>58</v>
+        <v>992</v>
       </c>
       <c r="AG12" s="5">
         <v>0</v>
@@ -37703,24 +38179,24 @@
         <v>52</v>
       </c>
       <c r="AI12" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ12" s="4">
-        <v>23735.256000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>143</v>
+        <v>1466</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>143</v>
+        <v>1466</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D13" s="7">
-        <v>46093</v>
+        <v>46042</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>144</v>
@@ -37729,61 +38205,61 @@
         <v>145</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>42</v>
+        <v>153</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>43</v>
+        <v>154</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>45</v>
+        <v>1384</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>46</v>
+        <v>1383</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="O13" s="8">
-        <v>507</v>
+        <v>2000</v>
       </c>
       <c r="P13" s="8">
-        <v>21.96</v>
+        <v>12.22</v>
       </c>
       <c r="Q13" s="9">
-        <v>11133.72</v>
+        <v>24440</v>
       </c>
       <c r="R13" s="9">
-        <v>361.85</v>
+        <v>794.3</v>
       </c>
       <c r="S13" s="9">
-        <v>11495.57</v>
+        <v>25234.3</v>
       </c>
       <c r="T13" s="9">
-        <v>11133.72</v>
+        <v>24440</v>
       </c>
       <c r="U13" s="9">
-        <v>445.35</v>
+        <v>977.6</v>
       </c>
       <c r="V13" s="6" t="s">
-        <v>116</v>
+        <v>159</v>
       </c>
       <c r="W13" s="6" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="X13" s="6" t="s">
         <v>50</v>
       </c>
       <c r="Y13" s="6" t="s">
-        <v>148</v>
+        <v>1465</v>
       </c>
       <c r="Z13" s="6" t="s">
         <v>52</v>
@@ -37798,10 +38274,10 @@
         <v>149</v>
       </c>
       <c r="AD13" s="6" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="AE13" s="6" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="AF13" s="6" t="s">
         <v>58</v>
@@ -37816,84 +38292,84 @@
         <v>4</v>
       </c>
       <c r="AJ13" s="8">
-        <v>7263.0538500000002</v>
+        <v>20682.54</v>
       </c>
     </row>
     <row r="14" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>150</v>
+        <v>1464</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>150</v>
+        <v>1464</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D14" s="3">
-        <v>46097</v>
+        <v>46042</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>144</v>
+        <v>38</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>155</v>
+        <v>67</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>156</v>
+        <v>1439</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>157</v>
+        <v>1438</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="O14" s="4">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="P14" s="4">
-        <v>12.22</v>
+        <v>17.88</v>
       </c>
       <c r="Q14" s="5">
-        <v>36660</v>
+        <v>107280</v>
       </c>
       <c r="R14" s="5">
-        <v>1191.45</v>
+        <v>3486.6</v>
       </c>
       <c r="S14" s="5">
-        <v>37851.449999999997</v>
+        <v>110766.6</v>
       </c>
       <c r="T14" s="5">
-        <v>36660</v>
+        <v>107280</v>
       </c>
       <c r="U14" s="5">
-        <v>1466.4</v>
+        <v>12873.6</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="X14" s="2" t="s">
         <v>50</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>161</v>
+        <v>1463</v>
       </c>
       <c r="Z14" s="2" t="s">
         <v>52</v>
@@ -37905,13 +38381,13 @@
         <v>54</v>
       </c>
       <c r="AC14" s="2" t="s">
-        <v>149</v>
+        <v>94</v>
       </c>
       <c r="AD14" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="AE14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="AF14" s="2" t="s">
         <v>58</v>
@@ -37923,87 +38399,87 @@
         <v>52</v>
       </c>
       <c r="AI14" s="5">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AJ14" s="4">
-        <v>31170.42</v>
+        <v>67831.62</v>
       </c>
     </row>
     <row r="15" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>162</v>
+        <v>1462</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>162</v>
+        <v>1462</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D15" s="7">
-        <v>46098</v>
+        <v>46042</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>38</v>
+        <v>512</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>39</v>
+        <v>511</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>163</v>
+        <v>1414</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>165</v>
+        <v>89</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>166</v>
+        <v>90</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>167</v>
+        <v>406</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>168</v>
+        <v>52</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>169</v>
+        <v>52</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>170</v>
+        <v>52</v>
       </c>
       <c r="O15" s="8">
-        <v>10000</v>
+        <v>23100</v>
       </c>
       <c r="P15" s="8">
-        <v>12.27</v>
+        <v>24.923310000000001</v>
       </c>
       <c r="Q15" s="9">
-        <v>122700</v>
+        <v>575728.46</v>
       </c>
       <c r="R15" s="9">
-        <v>3987.75</v>
+        <v>0</v>
       </c>
       <c r="S15" s="9">
-        <v>126687.75</v>
+        <v>575728.46</v>
       </c>
       <c r="T15" s="9">
-        <v>122700</v>
+        <v>0</v>
       </c>
       <c r="U15" s="9">
-        <v>14724</v>
+        <v>0</v>
       </c>
       <c r="V15" s="6" t="s">
-        <v>171</v>
+        <v>52</v>
       </c>
       <c r="W15" s="6" t="s">
-        <v>172</v>
+        <v>52</v>
       </c>
       <c r="X15" s="6" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="Y15" s="6" t="s">
-        <v>173</v>
+        <v>1461</v>
       </c>
       <c r="Z15" s="6" t="s">
         <v>52</v>
@@ -38012,19 +38488,19 @@
         <v>53</v>
       </c>
       <c r="AB15" s="6" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="AC15" s="6" t="s">
-        <v>94</v>
+        <v>149</v>
       </c>
       <c r="AD15" s="6" t="s">
-        <v>174</v>
+        <v>281</v>
       </c>
       <c r="AE15" s="6" t="s">
-        <v>175</v>
+        <v>280</v>
       </c>
       <c r="AF15" s="6" t="s">
-        <v>58</v>
+        <v>1434</v>
       </c>
       <c r="AG15" s="9">
         <v>0</v>
@@ -38033,87 +38509,87 @@
         <v>52</v>
       </c>
       <c r="AI15" s="9">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ15" s="8">
-        <v>75850.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>176</v>
+        <v>1462</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>176</v>
+        <v>1462</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D16" s="3">
-        <v>46098</v>
+        <v>46042</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>144</v>
+        <v>512</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>145</v>
+        <v>511</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>146</v>
+        <v>1414</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>177</v>
+        <v>636</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>178</v>
+        <v>52</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>179</v>
+        <v>52</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>180</v>
+        <v>52</v>
       </c>
       <c r="O16" s="4">
-        <v>507</v>
+        <v>1400</v>
       </c>
       <c r="P16" s="4">
-        <v>21.96</v>
+        <v>14.135249999999999</v>
       </c>
       <c r="Q16" s="5">
-        <v>11133.72</v>
+        <v>19789.349999999999</v>
       </c>
       <c r="R16" s="5">
-        <v>361.85</v>
+        <v>0</v>
       </c>
       <c r="S16" s="5">
-        <v>11495.57</v>
+        <v>19789.349999999999</v>
       </c>
       <c r="T16" s="5">
-        <v>11133.72</v>
+        <v>0</v>
       </c>
       <c r="U16" s="5">
-        <v>445.35</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>116</v>
+        <v>52</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>117</v>
+        <v>52</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>181</v>
+        <v>1461</v>
       </c>
       <c r="Z16" s="2" t="s">
         <v>52</v>
@@ -38122,19 +38598,19 @@
         <v>53</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="AC16" s="2" t="s">
         <v>149</v>
       </c>
       <c r="AD16" s="2" t="s">
-        <v>56</v>
+        <v>281</v>
       </c>
       <c r="AE16" s="2" t="s">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>58</v>
+        <v>1434</v>
       </c>
       <c r="AG16" s="5">
         <v>0</v>
@@ -38143,87 +38619,87 @@
         <v>52</v>
       </c>
       <c r="AI16" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ16" s="4">
-        <v>5539.1575199999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>182</v>
+        <v>1460</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>182</v>
+        <v>1460</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D17" s="7">
-        <v>46100</v>
+        <v>46043</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>38</v>
+        <v>144</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>98</v>
+        <v>691</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>99</v>
+        <v>690</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>100</v>
+        <v>201</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>101</v>
+        <v>202</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>183</v>
+        <v>1388</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>184</v>
+        <v>1387</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>185</v>
+        <v>1386</v>
       </c>
       <c r="O17" s="8">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="P17" s="8">
-        <v>8.9</v>
+        <v>14.48</v>
       </c>
       <c r="Q17" s="9">
-        <v>89000</v>
+        <v>14480</v>
       </c>
       <c r="R17" s="9">
-        <v>2892.5</v>
+        <v>470.6</v>
       </c>
       <c r="S17" s="9">
-        <v>91892.5</v>
+        <v>14950.6</v>
       </c>
       <c r="T17" s="9">
-        <v>89000</v>
+        <v>14480</v>
       </c>
       <c r="U17" s="9">
-        <v>3560</v>
+        <v>579.20000000000005</v>
       </c>
       <c r="V17" s="6" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="W17" s="6" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="X17" s="6" t="s">
         <v>50</v>
       </c>
       <c r="Y17" s="6" t="s">
-        <v>186</v>
+        <v>1459</v>
       </c>
       <c r="Z17" s="6" t="s">
         <v>52</v>
@@ -38232,10 +38708,10 @@
         <v>53</v>
       </c>
       <c r="AB17" s="6" t="s">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="AC17" s="6" t="s">
-        <v>94</v>
+        <v>149</v>
       </c>
       <c r="AD17" s="6" t="s">
         <v>65</v>
@@ -38256,84 +38732,84 @@
         <v>4</v>
       </c>
       <c r="AJ17" s="8">
-        <v>98896.9</v>
+        <v>9879.4500000000007</v>
       </c>
     </row>
     <row r="18" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>187</v>
+        <v>1449</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>187</v>
+        <v>1449</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D18" s="3">
-        <v>46104</v>
+        <v>46045</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>44</v>
+        <v>1032</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>45</v>
+        <v>1458</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>46</v>
+        <v>1457</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>47</v>
+        <v>1456</v>
       </c>
       <c r="O18" s="4">
-        <v>1170</v>
+        <v>2000</v>
       </c>
       <c r="P18" s="4">
-        <v>21.21</v>
+        <v>8.66648</v>
       </c>
       <c r="Q18" s="5">
-        <v>24815.7</v>
+        <v>17332.96</v>
       </c>
       <c r="R18" s="5">
-        <v>806.51</v>
+        <v>563.32000000000005</v>
       </c>
       <c r="S18" s="5">
-        <v>25622.21</v>
+        <v>17896.28</v>
       </c>
       <c r="T18" s="5">
-        <v>84924.84</v>
+        <v>456610.21</v>
       </c>
       <c r="U18" s="5">
-        <v>992.63</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>188</v>
+        <v>128</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>189</v>
+        <v>129</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>190</v>
+        <v>1445</v>
       </c>
       <c r="Z18" s="2" t="s">
         <v>52</v>
@@ -38342,19 +38818,19 @@
         <v>53</v>
       </c>
       <c r="AB18" s="2" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="AC18" s="2" t="s">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="AD18" s="2" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="AE18" s="2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="AF18" s="2" t="s">
-        <v>58</v>
+        <v>1029</v>
       </c>
       <c r="AG18" s="5">
         <v>0</v>
@@ -38363,87 +38839,87 @@
         <v>52</v>
       </c>
       <c r="AI18" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ18" s="4">
-        <v>16760.893499999998</v>
+        <v>20543.54</v>
       </c>
     </row>
     <row r="19" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>187</v>
+        <v>1449</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>187</v>
+        <v>1449</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D19" s="7">
-        <v>46104</v>
+        <v>46045</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>44</v>
+        <v>406</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>191</v>
+        <v>1455</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>192</v>
+        <v>1454</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>193</v>
+        <v>1446</v>
       </c>
       <c r="O19" s="8">
-        <v>2834</v>
+        <v>11725</v>
       </c>
       <c r="P19" s="8">
-        <v>21.21</v>
+        <v>24.923310000000001</v>
       </c>
       <c r="Q19" s="9">
-        <v>60109.14</v>
+        <v>292225.81</v>
       </c>
       <c r="R19" s="9">
-        <v>1953.55</v>
+        <v>0</v>
       </c>
       <c r="S19" s="9">
-        <v>62062.69</v>
+        <v>292225.81</v>
       </c>
       <c r="T19" s="9">
-        <v>84924.84</v>
+        <v>456610.21</v>
       </c>
       <c r="U19" s="9">
-        <v>2404.36</v>
+        <v>0</v>
       </c>
       <c r="V19" s="6" t="s">
-        <v>188</v>
+        <v>128</v>
       </c>
       <c r="W19" s="6" t="s">
-        <v>189</v>
+        <v>129</v>
       </c>
       <c r="X19" s="6" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="Y19" s="6" t="s">
-        <v>190</v>
+        <v>1445</v>
       </c>
       <c r="Z19" s="6" t="s">
         <v>52</v>
@@ -38452,19 +38928,19 @@
         <v>53</v>
       </c>
       <c r="AB19" s="6" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="AC19" s="6" t="s">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="AD19" s="6" t="s">
-        <v>56</v>
+        <v>281</v>
       </c>
       <c r="AE19" s="6" t="s">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="AF19" s="6" t="s">
-        <v>58</v>
+        <v>1029</v>
       </c>
       <c r="AG19" s="9">
         <v>0</v>
@@ -38473,87 +38949,87 @@
         <v>52</v>
       </c>
       <c r="AI19" s="9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ19" s="8">
-        <v>40598.637040000001</v>
+        <v>298929.93024999998</v>
       </c>
     </row>
     <row r="20" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>194</v>
+        <v>1449</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>194</v>
+        <v>1449</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D20" s="3">
-        <v>46104</v>
+        <v>46045</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>60</v>
+        <v>177</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>61</v>
+        <v>178</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>62</v>
+        <v>179</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>63</v>
+        <v>180</v>
       </c>
       <c r="O20" s="4">
-        <v>1750</v>
+        <v>2925</v>
       </c>
       <c r="P20" s="4">
-        <v>13.48</v>
+        <v>10.91342</v>
       </c>
       <c r="Q20" s="5">
-        <v>23590</v>
+        <v>31921.75</v>
       </c>
       <c r="R20" s="5">
-        <v>766.68</v>
+        <v>1037.46</v>
       </c>
       <c r="S20" s="5">
-        <v>24356.68</v>
+        <v>32959.21</v>
       </c>
       <c r="T20" s="5">
-        <v>23590</v>
+        <v>456610.21</v>
       </c>
       <c r="U20" s="5">
-        <v>943.6</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="s">
-        <v>188</v>
+        <v>128</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>189</v>
+        <v>129</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>195</v>
+        <v>1445</v>
       </c>
       <c r="Z20" s="2" t="s">
         <v>52</v>
@@ -38562,19 +39038,19 @@
         <v>53</v>
       </c>
       <c r="AB20" s="2" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="AC20" s="2" t="s">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="AD20" s="2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="AE20" s="2" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="AF20" s="2" t="s">
-        <v>58</v>
+        <v>1029</v>
       </c>
       <c r="AG20" s="5">
         <v>0</v>
@@ -38583,87 +39059,87 @@
         <v>52</v>
       </c>
       <c r="AI20" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ20" s="4">
-        <v>15417.885</v>
+        <v>31956.64875</v>
       </c>
     </row>
     <row r="21" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>196</v>
+        <v>1449</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>196</v>
+        <v>1449</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D21" s="7">
-        <v>46104</v>
+        <v>46045</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="O21" s="8">
-        <v>2000</v>
+        <v>2925</v>
       </c>
       <c r="P21" s="8">
-        <v>18.53</v>
+        <v>15.992699999999999</v>
       </c>
       <c r="Q21" s="9">
-        <v>37060</v>
+        <v>46778.65</v>
       </c>
       <c r="R21" s="9">
-        <v>1204.45</v>
+        <v>1520.3</v>
       </c>
       <c r="S21" s="9">
-        <v>38264.449999999997</v>
+        <v>48298.95</v>
       </c>
       <c r="T21" s="9">
-        <v>37060</v>
+        <v>456610.21</v>
       </c>
       <c r="U21" s="9">
-        <v>4447.2</v>
+        <v>0</v>
       </c>
       <c r="V21" s="6" t="s">
-        <v>188</v>
+        <v>128</v>
       </c>
       <c r="W21" s="6" t="s">
-        <v>189</v>
+        <v>129</v>
       </c>
       <c r="X21" s="6" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="Y21" s="6" t="s">
-        <v>197</v>
+        <v>1445</v>
       </c>
       <c r="Z21" s="6" t="s">
         <v>52</v>
@@ -38672,19 +39148,19 @@
         <v>53</v>
       </c>
       <c r="AB21" s="6" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="AC21" s="6" t="s">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="AD21" s="6" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="AE21" s="6" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="AF21" s="6" t="s">
-        <v>58</v>
+        <v>1029</v>
       </c>
       <c r="AG21" s="9">
         <v>0</v>
@@ -38693,87 +39169,87 @@
         <v>52</v>
       </c>
       <c r="AI21" s="9">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ21" s="8">
-        <v>19345.560000000001</v>
+        <v>41812.787250000001</v>
       </c>
     </row>
     <row r="22" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>198</v>
+        <v>1449</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>198</v>
+        <v>1449</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D22" s="3">
-        <v>46105</v>
+        <v>46045</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>199</v>
+        <v>122</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>200</v>
+        <v>123</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>201</v>
+        <v>89</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>202</v>
+        <v>90</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>167</v>
+        <v>352</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>168</v>
+        <v>1453</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>169</v>
+        <v>505</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>170</v>
+        <v>1452</v>
       </c>
       <c r="O22" s="4">
-        <v>500</v>
+        <v>2400</v>
       </c>
       <c r="P22" s="4">
-        <v>12.94</v>
+        <v>12.46616</v>
       </c>
       <c r="Q22" s="5">
-        <v>6470</v>
+        <v>29918.78</v>
       </c>
       <c r="R22" s="5">
-        <v>210.28</v>
+        <v>972.36</v>
       </c>
       <c r="S22" s="5">
-        <v>6680.28</v>
+        <v>30891.14</v>
       </c>
       <c r="T22" s="5">
-        <v>6470</v>
+        <v>456610.21</v>
       </c>
       <c r="U22" s="5">
-        <v>776.4</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>203</v>
+        <v>128</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>204</v>
+        <v>129</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>205</v>
+        <v>1445</v>
       </c>
       <c r="Z22" s="2" t="s">
         <v>52</v>
@@ -38782,30 +39258,6630 @@
         <v>53</v>
       </c>
       <c r="AB22" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC22" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF22" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AG22" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI22" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="4">
+        <v>33755.375999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="6" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="7">
+        <v>46045</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>1451</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="N23" s="6" t="s">
+        <v>1450</v>
+      </c>
+      <c r="O23" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P23" s="8">
+        <v>10.35717</v>
+      </c>
+      <c r="Q23" s="9">
+        <v>18642.91</v>
+      </c>
+      <c r="R23" s="9">
+        <v>605.9</v>
+      </c>
+      <c r="S23" s="9">
+        <v>19248.810000000001</v>
+      </c>
+      <c r="T23" s="9">
+        <v>456610.21</v>
+      </c>
+      <c r="U23" s="9">
+        <v>0</v>
+      </c>
+      <c r="V23" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="W23" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="X23" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y23" s="6" t="s">
+        <v>1445</v>
+      </c>
+      <c r="Z23" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA23" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB23" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC23" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD23" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE23" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF23" s="6" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AG23" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI23" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="8">
+        <v>25316.531999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="3">
+        <v>46045</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>1448</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="O24" s="4">
+        <v>1400</v>
+      </c>
+      <c r="P24" s="4">
+        <v>14.135249999999999</v>
+      </c>
+      <c r="Q24" s="5">
+        <v>19789.349999999999</v>
+      </c>
+      <c r="R24" s="5">
+        <v>0</v>
+      </c>
+      <c r="S24" s="5">
+        <v>19789.349999999999</v>
+      </c>
+      <c r="T24" s="5">
+        <v>456610.21</v>
+      </c>
+      <c r="U24" s="5">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="X24" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y24" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="Z24" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA24" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB24" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC24" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD24" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="AE24" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AF24" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AG24" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI24" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="4">
+        <v>19885.75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="6" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="7">
+        <v>46048</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>1397</v>
+      </c>
+      <c r="M25" s="6" t="s">
+        <v>1396</v>
+      </c>
+      <c r="N25" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="O25" s="8">
+        <v>5000</v>
+      </c>
+      <c r="P25" s="8">
+        <v>11.77</v>
+      </c>
+      <c r="Q25" s="9">
+        <v>58850</v>
+      </c>
+      <c r="R25" s="9">
+        <v>1912.63</v>
+      </c>
+      <c r="S25" s="9">
+        <v>60762.63</v>
+      </c>
+      <c r="T25" s="9">
+        <v>58850</v>
+      </c>
+      <c r="U25" s="9">
+        <v>2354</v>
+      </c>
+      <c r="V25" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="W25" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="X25" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y25" s="6" t="s">
+        <v>1443</v>
+      </c>
+      <c r="Z25" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA25" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB25" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC25" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD25" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE25" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF25" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG25" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI25" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ25" s="8">
+        <v>49397.25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="3">
+        <v>46048</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="O26" s="4">
+        <v>300</v>
+      </c>
+      <c r="P26" s="4">
+        <v>12.25</v>
+      </c>
+      <c r="Q26" s="5">
+        <v>3675</v>
+      </c>
+      <c r="R26" s="5">
+        <v>119.44</v>
+      </c>
+      <c r="S26" s="5">
+        <v>3794.44</v>
+      </c>
+      <c r="T26" s="5">
+        <v>3675</v>
+      </c>
+      <c r="U26" s="5">
+        <v>147</v>
+      </c>
+      <c r="V26" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="W26" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="X26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y26" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="Z26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB26" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AC22" s="2" t="s">
+      <c r="AC26" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD26" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE26" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF26" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG26" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI26" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ26" s="4">
+        <v>2966.9070000000002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="7">
+        <v>46048</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="M27" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="N27" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="O27" s="8">
+        <v>611</v>
+      </c>
+      <c r="P27" s="8">
+        <v>21.96</v>
+      </c>
+      <c r="Q27" s="9">
+        <v>13417.56</v>
+      </c>
+      <c r="R27" s="9">
+        <v>436.07</v>
+      </c>
+      <c r="S27" s="9">
+        <v>13853.63</v>
+      </c>
+      <c r="T27" s="9">
+        <v>28642.560000000001</v>
+      </c>
+      <c r="U27" s="9">
+        <v>536.70000000000005</v>
+      </c>
+      <c r="V27" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="W27" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="X27" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y27" s="6" t="s">
+        <v>1437</v>
+      </c>
+      <c r="Z27" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA27" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB27" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC27" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD27" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE27" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF27" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG27" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI27" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ27" s="8">
+        <v>6675.3888500000003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="3">
+        <v>46048</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>1439</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>1438</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="O28" s="4">
+        <v>700</v>
+      </c>
+      <c r="P28" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="Q28" s="5">
+        <v>15225</v>
+      </c>
+      <c r="R28" s="5">
+        <v>494.81</v>
+      </c>
+      <c r="S28" s="5">
+        <v>15719.81</v>
+      </c>
+      <c r="T28" s="5">
+        <v>28642.560000000001</v>
+      </c>
+      <c r="U28" s="5">
+        <v>2740.5</v>
+      </c>
+      <c r="V28" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="W28" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="X28" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y28" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="Z28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA28" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB28" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC28" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD28" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE28" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF28" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG28" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI28" s="5">
+        <v>18</v>
+      </c>
+      <c r="AJ28" s="4">
+        <v>6276.0389999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="6" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="7">
+        <v>46048</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>1414</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="M29" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="N29" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="O29" s="8">
+        <v>14800</v>
+      </c>
+      <c r="P29" s="8">
+        <v>12.62388</v>
+      </c>
+      <c r="Q29" s="9">
+        <v>186833.42</v>
+      </c>
+      <c r="R29" s="9">
+        <v>0</v>
+      </c>
+      <c r="S29" s="9">
+        <v>186833.42</v>
+      </c>
+      <c r="T29" s="9">
+        <v>0</v>
+      </c>
+      <c r="U29" s="9">
+        <v>0</v>
+      </c>
+      <c r="V29" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W29" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="X29" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y29" s="6" t="s">
+        <v>1435</v>
+      </c>
+      <c r="Z29" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA29" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB29" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC29" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD29" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE29" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF29" s="6" t="s">
+        <v>1434</v>
+      </c>
+      <c r="AG29" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI29" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" s="3">
+        <v>46049</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O30" s="4">
+        <v>16000</v>
+      </c>
+      <c r="P30" s="4">
+        <v>8.7436900000000009</v>
+      </c>
+      <c r="Q30" s="5">
+        <v>139899.04</v>
+      </c>
+      <c r="R30" s="5">
+        <v>0</v>
+      </c>
+      <c r="S30" s="5">
+        <v>139899.04</v>
+      </c>
+      <c r="T30" s="5">
+        <v>0</v>
+      </c>
+      <c r="U30" s="5">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="W30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="X30" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y30" s="2" t="s">
+        <v>1432</v>
+      </c>
+      <c r="Z30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA30" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB30" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC30" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD30" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE30" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF30" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="AG30" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI30" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="6" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="7">
+        <v>46049</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>1414</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="M31" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="N31" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="O31" s="8">
+        <v>9000</v>
+      </c>
+      <c r="P31" s="8">
+        <v>9.5912500000000005</v>
+      </c>
+      <c r="Q31" s="9">
+        <v>86321.25</v>
+      </c>
+      <c r="R31" s="9">
+        <v>0</v>
+      </c>
+      <c r="S31" s="9">
+        <v>86321.25</v>
+      </c>
+      <c r="T31" s="9">
+        <v>0</v>
+      </c>
+      <c r="U31" s="9">
+        <v>0</v>
+      </c>
+      <c r="V31" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W31" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="X31" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y31" s="6" t="s">
+        <v>1432</v>
+      </c>
+      <c r="Z31" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA31" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB31" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC31" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD31" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE31" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF31" s="6" t="s">
+        <v>992</v>
+      </c>
+      <c r="AG31" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI31" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="3">
+        <v>46050</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>1430</v>
+      </c>
+      <c r="O32" s="4">
+        <v>1000</v>
+      </c>
+      <c r="P32" s="4">
+        <v>12.22</v>
+      </c>
+      <c r="Q32" s="5">
+        <v>12220</v>
+      </c>
+      <c r="R32" s="5">
+        <v>397.15</v>
+      </c>
+      <c r="S32" s="5">
+        <v>12617.15</v>
+      </c>
+      <c r="T32" s="5">
+        <v>24440</v>
+      </c>
+      <c r="U32" s="5">
+        <v>488.8</v>
+      </c>
+      <c r="V32" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="W32" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="X32" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y32" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="Z32" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA32" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB32" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC32" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD32" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE32" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF32" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG32" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI32" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ32" s="4">
+        <v>10341.27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="6" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" s="7">
+        <v>46050</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>1384</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>1383</v>
+      </c>
+      <c r="N33" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="O33" s="8">
+        <v>1000</v>
+      </c>
+      <c r="P33" s="8">
+        <v>12.22</v>
+      </c>
+      <c r="Q33" s="9">
+        <v>12220</v>
+      </c>
+      <c r="R33" s="9">
+        <v>397.15</v>
+      </c>
+      <c r="S33" s="9">
+        <v>12617.15</v>
+      </c>
+      <c r="T33" s="9">
+        <v>24440</v>
+      </c>
+      <c r="U33" s="9">
+        <v>488.8</v>
+      </c>
+      <c r="V33" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W33" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="X33" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y33" s="6" t="s">
+        <v>1428</v>
+      </c>
+      <c r="Z33" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA33" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB33" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC33" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD33" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE33" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF33" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG33" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI33" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ33" s="8">
+        <v>10341.27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" s="3">
+        <v>46050</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O34" s="4">
+        <v>24000</v>
+      </c>
+      <c r="P34" s="4">
+        <v>7.5930600000000004</v>
+      </c>
+      <c r="Q34" s="5">
+        <v>182233.44</v>
+      </c>
+      <c r="R34" s="5">
+        <v>0</v>
+      </c>
+      <c r="S34" s="5">
+        <v>182233.44</v>
+      </c>
+      <c r="T34" s="5">
+        <v>0</v>
+      </c>
+      <c r="U34" s="5">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="W34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="X34" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y34" s="2" t="s">
+        <v>1426</v>
+      </c>
+      <c r="Z34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA34" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB34" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC34" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD34" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AE34" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AF34" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="AG34" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI34" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="6" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D35" s="7">
+        <v>46051</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>1424</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>1423</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="N35" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="O35" s="8">
+        <v>26</v>
+      </c>
+      <c r="P35" s="8">
+        <v>25.58</v>
+      </c>
+      <c r="Q35" s="9">
+        <v>665.08</v>
+      </c>
+      <c r="R35" s="9">
+        <v>21.62</v>
+      </c>
+      <c r="S35" s="9">
+        <v>686.7</v>
+      </c>
+      <c r="T35" s="9">
+        <v>665.08</v>
+      </c>
+      <c r="U35" s="9">
+        <v>26.6</v>
+      </c>
+      <c r="V35" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="W35" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="X35" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y35" s="6" t="s">
+        <v>1422</v>
+      </c>
+      <c r="Z35" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA35" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB35" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC35" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="AD22" s="2" t="s">
+      <c r="AD35" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE35" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF35" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG35" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI35" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ35" s="8">
+        <v>284.0591</v>
+      </c>
+    </row>
+    <row r="36" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="3">
+        <v>46052</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="O36" s="4">
+        <v>507</v>
+      </c>
+      <c r="P36" s="4">
+        <v>21.96</v>
+      </c>
+      <c r="Q36" s="5">
+        <v>11133.72</v>
+      </c>
+      <c r="R36" s="5">
+        <v>361.85</v>
+      </c>
+      <c r="S36" s="5">
+        <v>11495.57</v>
+      </c>
+      <c r="T36" s="5">
+        <v>11133.72</v>
+      </c>
+      <c r="U36" s="5">
+        <v>445.35</v>
+      </c>
+      <c r="V36" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="W36" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="X36" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y36" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="Z36" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA36" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB36" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC36" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD36" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE36" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF36" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI36" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ36" s="4">
+        <v>5539.1524499999996</v>
+      </c>
+    </row>
+    <row r="37" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D37" s="7">
+        <v>46052</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>1353</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>1352</v>
+      </c>
+      <c r="N37" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="O37" s="8">
+        <v>500</v>
+      </c>
+      <c r="P37" s="8">
+        <v>13.56</v>
+      </c>
+      <c r="Q37" s="9">
+        <v>6780</v>
+      </c>
+      <c r="R37" s="9">
+        <v>220.35</v>
+      </c>
+      <c r="S37" s="9">
+        <v>7000.35</v>
+      </c>
+      <c r="T37" s="9">
+        <v>6780</v>
+      </c>
+      <c r="U37" s="9">
+        <v>271.2</v>
+      </c>
+      <c r="V37" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="W37" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="X37" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y37" s="6" t="s">
+        <v>1418</v>
+      </c>
+      <c r="Z37" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA37" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB37" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC37" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD37" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE37" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF37" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG37" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI37" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ37" s="8">
+        <v>4405.1099999999997</v>
+      </c>
+    </row>
+    <row r="38" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="3">
+        <v>46052</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="O38" s="4">
+        <v>300</v>
+      </c>
+      <c r="P38" s="4">
+        <v>12.25</v>
+      </c>
+      <c r="Q38" s="5">
+        <v>3675</v>
+      </c>
+      <c r="R38" s="5">
+        <v>119.44</v>
+      </c>
+      <c r="S38" s="5">
+        <v>3794.44</v>
+      </c>
+      <c r="T38" s="5">
+        <v>3675</v>
+      </c>
+      <c r="U38" s="5">
+        <v>147</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="W38" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="X38" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y38" s="2" t="s">
+        <v>1416</v>
+      </c>
+      <c r="Z38" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA38" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB38" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC38" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD38" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE38" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF38" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG38" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH38" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI38" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ38" s="4">
+        <v>2966.9070000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="6" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D39" s="7">
+        <v>46055</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>1414</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>1413</v>
+      </c>
+      <c r="L39" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="M39" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="N39" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="O39" s="8">
+        <v>17920</v>
+      </c>
+      <c r="P39" s="8">
+        <v>9.2093600000000002</v>
+      </c>
+      <c r="Q39" s="9">
+        <v>165031.73000000001</v>
+      </c>
+      <c r="R39" s="9">
+        <v>0</v>
+      </c>
+      <c r="S39" s="9">
+        <v>165031.73000000001</v>
+      </c>
+      <c r="T39" s="9">
+        <v>0</v>
+      </c>
+      <c r="U39" s="9">
+        <v>0</v>
+      </c>
+      <c r="V39" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W39" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="X39" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y39" s="6" t="s">
+        <v>1412</v>
+      </c>
+      <c r="Z39" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA39" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB39" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC39" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD39" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE39" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF39" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ39" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D40" s="3">
+        <v>46057</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="O40" s="4">
+        <v>507</v>
+      </c>
+      <c r="P40" s="4">
+        <v>21.96</v>
+      </c>
+      <c r="Q40" s="5">
+        <v>11133.72</v>
+      </c>
+      <c r="R40" s="5">
+        <v>361.85</v>
+      </c>
+      <c r="S40" s="5">
+        <v>11495.57</v>
+      </c>
+      <c r="T40" s="5">
+        <v>11133.72</v>
+      </c>
+      <c r="U40" s="5">
+        <v>445.35</v>
+      </c>
+      <c r="V40" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="W40" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="X40" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y40" s="2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="Z40" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA40" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB40" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC40" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE40" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF40" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AG40" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH40" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI40" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ40" s="4">
+        <v>5539.1524499999996</v>
+      </c>
+    </row>
+    <row r="41" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="6" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D41" s="7">
+        <v>46057</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="L41" s="6" t="s">
+        <v>1384</v>
+      </c>
+      <c r="M41" s="6" t="s">
+        <v>1383</v>
+      </c>
+      <c r="N41" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="O41" s="8">
+        <v>2000</v>
+      </c>
+      <c r="P41" s="8">
+        <v>12.22</v>
+      </c>
+      <c r="Q41" s="9">
+        <v>24440</v>
+      </c>
+      <c r="R41" s="9">
+        <v>794.3</v>
+      </c>
+      <c r="S41" s="9">
+        <v>25234.3</v>
+      </c>
+      <c r="T41" s="9">
+        <v>24440</v>
+      </c>
+      <c r="U41" s="9">
+        <v>977.6</v>
+      </c>
+      <c r="V41" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W41" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="X41" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y41" s="6" t="s">
+        <v>1381</v>
+      </c>
+      <c r="Z41" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA41" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB41" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC41" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD41" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE41" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF41" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG41" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI41" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ41" s="8">
+        <v>20780.28</v>
+      </c>
+    </row>
+    <row r="42" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D42" s="3">
+        <v>46058</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="O42" s="4">
+        <v>507</v>
+      </c>
+      <c r="P42" s="4">
+        <v>21.96</v>
+      </c>
+      <c r="Q42" s="5">
+        <v>11133.72</v>
+      </c>
+      <c r="R42" s="5">
+        <v>361.85</v>
+      </c>
+      <c r="S42" s="5">
+        <v>11495.57</v>
+      </c>
+      <c r="T42" s="5">
+        <v>11133.72</v>
+      </c>
+      <c r="U42" s="5">
+        <v>445.35</v>
+      </c>
+      <c r="V42" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="W42" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="X42" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y42" s="2" t="s">
+        <v>1407</v>
+      </c>
+      <c r="Z42" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA42" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB42" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC42" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE42" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF42" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI42" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ42" s="4">
+        <v>5539.1524499999996</v>
+      </c>
+    </row>
+    <row r="43" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="6" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43" s="7">
+        <v>46058</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>1356</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>1355</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J43" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="L43" s="6" t="s">
+        <v>1397</v>
+      </c>
+      <c r="M43" s="6" t="s">
+        <v>1396</v>
+      </c>
+      <c r="N43" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="O43" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P43" s="8">
+        <v>15.18</v>
+      </c>
+      <c r="Q43" s="9">
+        <v>27324</v>
+      </c>
+      <c r="R43" s="9">
+        <v>888.03</v>
+      </c>
+      <c r="S43" s="9">
+        <v>28212.03</v>
+      </c>
+      <c r="T43" s="9">
+        <v>27324</v>
+      </c>
+      <c r="U43" s="9">
+        <v>1092.96</v>
+      </c>
+      <c r="V43" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="W43" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="X43" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y43" s="6" t="s">
+        <v>1405</v>
+      </c>
+      <c r="Z43" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA43" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB43" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC43" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD43" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE43" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF43" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG43" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI43" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ43" s="8">
+        <v>17614.835999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D44" s="3">
+        <v>46059</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>1403</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>1402</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="O44" s="4">
+        <v>500</v>
+      </c>
+      <c r="P44" s="4">
+        <v>13.18</v>
+      </c>
+      <c r="Q44" s="5">
+        <v>6590</v>
+      </c>
+      <c r="R44" s="5">
+        <v>214.18</v>
+      </c>
+      <c r="S44" s="5">
+        <v>6804.18</v>
+      </c>
+      <c r="T44" s="5">
+        <v>6590</v>
+      </c>
+      <c r="U44" s="5">
+        <v>263.60000000000002</v>
+      </c>
+      <c r="V44" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="W44" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="X44" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y44" s="2" t="s">
+        <v>1401</v>
+      </c>
+      <c r="Z44" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA44" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB44" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC44" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD44" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE44" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF44" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG44" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI44" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ44" s="4">
+        <v>4944.8450000000003</v>
+      </c>
+    </row>
+    <row r="45" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="6" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D45" s="7">
+        <v>46059</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>1398</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="K45" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="L45" s="6" t="s">
+        <v>1397</v>
+      </c>
+      <c r="M45" s="6" t="s">
+        <v>1396</v>
+      </c>
+      <c r="N45" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="O45" s="8">
+        <v>200</v>
+      </c>
+      <c r="P45" s="8">
+        <v>14.78</v>
+      </c>
+      <c r="Q45" s="9">
+        <v>2956</v>
+      </c>
+      <c r="R45" s="9">
+        <v>96.07</v>
+      </c>
+      <c r="S45" s="9">
+        <v>3052.07</v>
+      </c>
+      <c r="T45" s="9">
+        <v>2956</v>
+      </c>
+      <c r="U45" s="9">
+        <v>118.24</v>
+      </c>
+      <c r="V45" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="W45" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="X45" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y45" s="6" t="s">
+        <v>1395</v>
+      </c>
+      <c r="Z45" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA45" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB45" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC45" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD45" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE45" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF45" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG45" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI45" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ45" s="8">
+        <v>1957.0440000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D46" s="3">
+        <v>46063</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O46" s="4">
+        <v>0</v>
+      </c>
+      <c r="P46" s="4">
+        <v>18264.400000000001</v>
+      </c>
+      <c r="Q46" s="5">
+        <v>18264.400000000001</v>
+      </c>
+      <c r="R46" s="5">
+        <v>0</v>
+      </c>
+      <c r="S46" s="5">
+        <v>18264.400000000001</v>
+      </c>
+      <c r="T46" s="5">
+        <v>0</v>
+      </c>
+      <c r="U46" s="5">
+        <v>18264.400000000001</v>
+      </c>
+      <c r="V46" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="W46" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="X46" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y46" s="2" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Z46" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA46" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB46" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC46" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD46" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AE46" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AF46" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG46" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI46" s="5">
+        <v>12</v>
+      </c>
+      <c r="AJ46" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="6" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D47" s="7">
+        <v>46064</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>1390</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>1389</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="L47" s="6" t="s">
+        <v>1388</v>
+      </c>
+      <c r="M47" s="6" t="s">
+        <v>1387</v>
+      </c>
+      <c r="N47" s="6" t="s">
+        <v>1386</v>
+      </c>
+      <c r="O47" s="8">
+        <v>1000</v>
+      </c>
+      <c r="P47" s="8">
+        <v>12.75</v>
+      </c>
+      <c r="Q47" s="9">
+        <v>12750</v>
+      </c>
+      <c r="R47" s="9">
+        <v>414.38</v>
+      </c>
+      <c r="S47" s="9">
+        <v>13164.38</v>
+      </c>
+      <c r="T47" s="9">
+        <v>12750</v>
+      </c>
+      <c r="U47" s="9">
+        <v>510</v>
+      </c>
+      <c r="V47" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="W47" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="X47" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y47" s="6" t="s">
+        <v>1385</v>
+      </c>
+      <c r="Z47" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA47" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB47" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC47" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD47" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE47" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF47" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG47" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI47" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ47" s="8">
+        <v>9788.69</v>
+      </c>
+    </row>
+    <row r="48" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D48" s="3">
+        <v>46064</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>1384</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="O48" s="4">
+        <v>1000</v>
+      </c>
+      <c r="P48" s="4">
+        <v>12.22</v>
+      </c>
+      <c r="Q48" s="5">
+        <v>12220</v>
+      </c>
+      <c r="R48" s="5">
+        <v>397.15</v>
+      </c>
+      <c r="S48" s="5">
+        <v>12617.15</v>
+      </c>
+      <c r="T48" s="5">
+        <v>24440</v>
+      </c>
+      <c r="U48" s="5">
+        <v>488.8</v>
+      </c>
+      <c r="V48" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="W48" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="X48" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y48" s="2" t="s">
+        <v>1381</v>
+      </c>
+      <c r="Z48" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA48" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB48" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC48" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD48" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE48" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF48" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG48" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI48" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ48" s="4">
+        <v>10390.14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="6" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D49" s="7">
+        <v>46064</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="J49" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="K49" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="L49" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="M49" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="N49" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="O49" s="8">
+        <v>1000</v>
+      </c>
+      <c r="P49" s="8">
+        <v>12.22</v>
+      </c>
+      <c r="Q49" s="9">
+        <v>12220</v>
+      </c>
+      <c r="R49" s="9">
+        <v>397.15</v>
+      </c>
+      <c r="S49" s="9">
+        <v>12617.15</v>
+      </c>
+      <c r="T49" s="9">
+        <v>24440</v>
+      </c>
+      <c r="U49" s="9">
+        <v>488.8</v>
+      </c>
+      <c r="V49" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W49" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="X49" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y49" s="6" t="s">
+        <v>1381</v>
+      </c>
+      <c r="Z49" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA49" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB49" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC49" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD49" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE49" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF49" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG49" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI49" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ49" s="8">
+        <v>10390.14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D50" s="3">
+        <v>46066</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="O50" s="4">
+        <v>507</v>
+      </c>
+      <c r="P50" s="4">
+        <v>21.96</v>
+      </c>
+      <c r="Q50" s="5">
+        <v>11133.72</v>
+      </c>
+      <c r="R50" s="5">
+        <v>361.85</v>
+      </c>
+      <c r="S50" s="5">
+        <v>11495.57</v>
+      </c>
+      <c r="T50" s="5">
+        <v>11133.72</v>
+      </c>
+      <c r="U50" s="5">
+        <v>445.35</v>
+      </c>
+      <c r="V50" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="W50" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="X50" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y50" s="2" t="s">
+        <v>1379</v>
+      </c>
+      <c r="Z50" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA50" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB50" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC50" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD50" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE50" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF50" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG50" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI50" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ50" s="4">
+        <v>5539.1575199999997</v>
+      </c>
+    </row>
+    <row r="51" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="6" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D51" s="7">
+        <v>46071</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K51" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="L51" s="6" t="s">
+        <v>1377</v>
+      </c>
+      <c r="M51" s="6" t="s">
+        <v>1376</v>
+      </c>
+      <c r="N51" s="6" t="s">
+        <v>1375</v>
+      </c>
+      <c r="O51" s="8">
+        <v>500</v>
+      </c>
+      <c r="P51" s="8">
+        <v>19.420000000000002</v>
+      </c>
+      <c r="Q51" s="9">
+        <v>9710</v>
+      </c>
+      <c r="R51" s="9">
+        <v>315.58</v>
+      </c>
+      <c r="S51" s="9">
+        <v>10025.58</v>
+      </c>
+      <c r="T51" s="9">
+        <v>9710</v>
+      </c>
+      <c r="U51" s="9">
+        <v>1165.2</v>
+      </c>
+      <c r="V51" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="W51" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="X51" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y51" s="6" t="s">
+        <v>1374</v>
+      </c>
+      <c r="Z51" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA51" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB51" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC51" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD51" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE51" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF51" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI51" s="9">
+        <v>12</v>
+      </c>
+      <c r="AJ51" s="8">
+        <v>4836.3900000000003</v>
+      </c>
+    </row>
+    <row r="52" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D52" s="3">
+        <v>46071</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="O52" s="4">
+        <v>200</v>
+      </c>
+      <c r="P52" s="4">
+        <v>13.72</v>
+      </c>
+      <c r="Q52" s="5">
+        <v>2744</v>
+      </c>
+      <c r="R52" s="5">
+        <v>89.18</v>
+      </c>
+      <c r="S52" s="5">
+        <v>2833.18</v>
+      </c>
+      <c r="T52" s="5">
+        <v>2744</v>
+      </c>
+      <c r="U52" s="5">
+        <v>466.48</v>
+      </c>
+      <c r="V52" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="W52" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="X52" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y52" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="Z52" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA52" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB52" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC52" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD52" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE52" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF52" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG52" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI52" s="5">
+        <v>17</v>
+      </c>
+      <c r="AJ52" s="4">
+        <v>2078.0279999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="6" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D53" s="7">
+        <v>46072</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="J53" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="K53" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="L53" s="6" t="s">
+        <v>1368</v>
+      </c>
+      <c r="M53" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="N53" s="6" t="s">
+        <v>1367</v>
+      </c>
+      <c r="O53" s="8">
+        <v>50</v>
+      </c>
+      <c r="P53" s="8">
+        <v>16.16</v>
+      </c>
+      <c r="Q53" s="9">
+        <v>808</v>
+      </c>
+      <c r="R53" s="9">
+        <v>0</v>
+      </c>
+      <c r="S53" s="9">
+        <v>808</v>
+      </c>
+      <c r="T53" s="9">
+        <v>808</v>
+      </c>
+      <c r="U53" s="9">
+        <v>0</v>
+      </c>
+      <c r="V53" s="6" t="s">
+        <v>1366</v>
+      </c>
+      <c r="W53" s="6" t="s">
+        <v>1365</v>
+      </c>
+      <c r="X53" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y53" s="6" t="s">
+        <v>1364</v>
+      </c>
+      <c r="Z53" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA53" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB53" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC53" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD53" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="AE53" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="AF53" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="8">
+        <v>579.30799999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="2" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D54" s="3">
+        <v>46072</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="O54" s="4">
+        <v>1600</v>
+      </c>
+      <c r="P54" s="4">
+        <v>15.18</v>
+      </c>
+      <c r="Q54" s="5">
+        <v>24288</v>
+      </c>
+      <c r="R54" s="5">
+        <v>789.36</v>
+      </c>
+      <c r="S54" s="5">
+        <v>25077.360000000001</v>
+      </c>
+      <c r="T54" s="5">
+        <v>24288</v>
+      </c>
+      <c r="U54" s="5">
+        <v>971.52</v>
+      </c>
+      <c r="V54" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="W54" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="X54" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y54" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="Z54" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA54" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB54" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC54" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD54" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE54" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF54" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH54" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI54" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ54" s="4">
+        <v>15661.904</v>
+      </c>
+    </row>
+    <row r="55" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="6" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D55" s="7">
+        <v>46072</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>1360</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>1359</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="J55" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="K55" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="L55" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="M55" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="N55" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="O55" s="8">
+        <v>500</v>
+      </c>
+      <c r="P55" s="8">
+        <v>12.5</v>
+      </c>
+      <c r="Q55" s="9">
+        <v>6250</v>
+      </c>
+      <c r="R55" s="9">
+        <v>203.13</v>
+      </c>
+      <c r="S55" s="9">
+        <v>6453.13</v>
+      </c>
+      <c r="T55" s="9">
+        <v>6250</v>
+      </c>
+      <c r="U55" s="9">
+        <v>250</v>
+      </c>
+      <c r="V55" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="W55" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="X55" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y55" s="6" t="s">
+        <v>1358</v>
+      </c>
+      <c r="Z55" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA55" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB55" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC55" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD55" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE55" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF55" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI55" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ55" s="8">
+        <v>5195.07</v>
+      </c>
+    </row>
+    <row r="56" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="2" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D56" s="3">
+        <v>46076</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="O56" s="4">
+        <v>1700</v>
+      </c>
+      <c r="P56" s="4">
+        <v>15.18</v>
+      </c>
+      <c r="Q56" s="5">
+        <v>25806</v>
+      </c>
+      <c r="R56" s="5">
+        <v>838.7</v>
+      </c>
+      <c r="S56" s="5">
+        <v>26644.7</v>
+      </c>
+      <c r="T56" s="5">
+        <v>25806</v>
+      </c>
+      <c r="U56" s="5">
+        <v>1032.24</v>
+      </c>
+      <c r="V56" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="W56" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="X56" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y56" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="Z56" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA56" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB56" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC56" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD56" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE56" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF56" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH56" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI56" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ56" s="4">
+        <v>16640.773000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="6" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D57" s="7">
+        <v>46077</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J57" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K57" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="L57" s="6" t="s">
+        <v>1353</v>
+      </c>
+      <c r="M57" s="6" t="s">
+        <v>1352</v>
+      </c>
+      <c r="N57" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="O57" s="8">
+        <v>500</v>
+      </c>
+      <c r="P57" s="8">
+        <v>13.56</v>
+      </c>
+      <c r="Q57" s="9">
+        <v>6780</v>
+      </c>
+      <c r="R57" s="9">
+        <v>220.35</v>
+      </c>
+      <c r="S57" s="9">
+        <v>7000.35</v>
+      </c>
+      <c r="T57" s="9">
+        <v>16635</v>
+      </c>
+      <c r="U57" s="9">
+        <v>271.2</v>
+      </c>
+      <c r="V57" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="W57" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="X57" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y57" s="6" t="s">
+        <v>1350</v>
+      </c>
+      <c r="Z57" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA57" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB57" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC57" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD57" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE57" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF57" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG57" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI57" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ57" s="8">
+        <v>4405.1099999999997</v>
+      </c>
+    </row>
+    <row r="58" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D58" s="3">
+        <v>46077</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="O58" s="4">
+        <v>500</v>
+      </c>
+      <c r="P58" s="4">
+        <v>19.71</v>
+      </c>
+      <c r="Q58" s="5">
+        <v>9855</v>
+      </c>
+      <c r="R58" s="5">
+        <v>320.29000000000002</v>
+      </c>
+      <c r="S58" s="5">
+        <v>10175.290000000001</v>
+      </c>
+      <c r="T58" s="5">
+        <v>16635</v>
+      </c>
+      <c r="U58" s="5">
+        <v>1182.5999999999999</v>
+      </c>
+      <c r="V58" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W58" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X58" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y58" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="Z58" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA58" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB58" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC58" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD58" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE58" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF58" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI58" s="5">
+        <v>12</v>
+      </c>
+      <c r="AJ58" s="4">
+        <v>4836.3900000000003</v>
+      </c>
+    </row>
+    <row r="59" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="6" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D59" s="7">
+        <v>46078</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J59" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="K59" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="L59" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="M59" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="N59" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="O59" s="8">
+        <v>225</v>
+      </c>
+      <c r="P59" s="8">
+        <v>12.25</v>
+      </c>
+      <c r="Q59" s="9">
+        <v>2756.25</v>
+      </c>
+      <c r="R59" s="9">
+        <v>89.58</v>
+      </c>
+      <c r="S59" s="9">
+        <v>2845.83</v>
+      </c>
+      <c r="T59" s="9">
+        <v>2756.25</v>
+      </c>
+      <c r="U59" s="9">
+        <v>110.25</v>
+      </c>
+      <c r="V59" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="W59" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="X59" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y59" s="6" t="s">
+        <v>1348</v>
+      </c>
+      <c r="Z59" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA59" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB59" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC59" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD59" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE59" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF59" s="6" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AG59" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH59" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI59" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ59" s="8">
+        <v>2225.1802499999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D60" s="3">
+        <v>46079</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="N60" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="O60" s="4">
+        <v>5000</v>
+      </c>
+      <c r="P60" s="4">
+        <v>11.77</v>
+      </c>
+      <c r="Q60" s="5">
+        <v>58850</v>
+      </c>
+      <c r="R60" s="5">
+        <v>1912.63</v>
+      </c>
+      <c r="S60" s="5">
+        <v>60762.63</v>
+      </c>
+      <c r="T60" s="5">
+        <v>58850</v>
+      </c>
+      <c r="U60" s="5">
+        <v>2354</v>
+      </c>
+      <c r="V60" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="W60" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="X60" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y60" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="Z60" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA60" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB60" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC60" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD60" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE60" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF60" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH60" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI60" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ60" s="4">
+        <v>48943.45</v>
+      </c>
+    </row>
+    <row r="61" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="6" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D61" s="7">
+        <v>46079</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="J61" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="K61" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="L61" s="6" t="s">
+        <v>1342</v>
+      </c>
+      <c r="M61" s="6" t="s">
+        <v>1341</v>
+      </c>
+      <c r="N61" s="6" t="s">
+        <v>1340</v>
+      </c>
+      <c r="O61" s="8">
+        <v>12000</v>
+      </c>
+      <c r="P61" s="8">
+        <v>11.16</v>
+      </c>
+      <c r="Q61" s="9">
+        <v>133920</v>
+      </c>
+      <c r="R61" s="9">
+        <v>4352.3999999999996</v>
+      </c>
+      <c r="S61" s="9">
+        <v>138272.4</v>
+      </c>
+      <c r="T61" s="9">
+        <v>133920</v>
+      </c>
+      <c r="U61" s="9">
+        <v>5356.8</v>
+      </c>
+      <c r="V61" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="W61" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="X61" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y61" s="6" t="s">
+        <v>1339</v>
+      </c>
+      <c r="Z61" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA61" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB61" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC61" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD61" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE61" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF61" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG61" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI61" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ61" s="8">
+        <v>84565.56</v>
+      </c>
+    </row>
+    <row r="62" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D62" s="3">
+        <v>46085</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="O62" s="4">
+        <v>5005</v>
+      </c>
+      <c r="P62" s="4">
+        <v>21.21</v>
+      </c>
+      <c r="Q62" s="5">
+        <v>106156.05</v>
+      </c>
+      <c r="R62" s="5">
+        <v>3450.07</v>
+      </c>
+      <c r="S62" s="5">
+        <v>109606.12</v>
+      </c>
+      <c r="T62" s="5">
+        <v>106156.05</v>
+      </c>
+      <c r="U62" s="5">
+        <v>4246.24</v>
+      </c>
+      <c r="V62" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W62" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X62" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y62" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z62" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA62" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB62" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC62" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD62" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE62" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF62" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI62" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ62" s="4">
+        <v>71699.37775</v>
+      </c>
+    </row>
+    <row r="63" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D63" s="7">
+        <v>46085</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J63" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K63" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="L63" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="M63" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N63" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="O63" s="8">
+        <v>500</v>
+      </c>
+      <c r="P63" s="8">
+        <v>13.56</v>
+      </c>
+      <c r="Q63" s="9">
+        <v>6780</v>
+      </c>
+      <c r="R63" s="9">
+        <v>220.35</v>
+      </c>
+      <c r="S63" s="9">
+        <v>7000.35</v>
+      </c>
+      <c r="T63" s="9">
+        <v>16635</v>
+      </c>
+      <c r="U63" s="9">
+        <v>271.2</v>
+      </c>
+      <c r="V63" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="W63" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="X63" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y63" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z63" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA63" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB63" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC63" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD63" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE63" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF63" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG63" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI63" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ63" s="8">
+        <v>4405.1099999999997</v>
+      </c>
+    </row>
+    <row r="64" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D64" s="3">
+        <v>46085</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="O64" s="4">
+        <v>500</v>
+      </c>
+      <c r="P64" s="4">
+        <v>19.71</v>
+      </c>
+      <c r="Q64" s="5">
+        <v>9855</v>
+      </c>
+      <c r="R64" s="5">
+        <v>320.29000000000002</v>
+      </c>
+      <c r="S64" s="5">
+        <v>10175.290000000001</v>
+      </c>
+      <c r="T64" s="5">
+        <v>16635</v>
+      </c>
+      <c r="U64" s="5">
+        <v>1182.5999999999999</v>
+      </c>
+      <c r="V64" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W64" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X64" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y64" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z64" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA64" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB64" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC64" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD64" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE64" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF64" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI64" s="5">
+        <v>12</v>
+      </c>
+      <c r="AJ64" s="4">
+        <v>4836.3900000000003</v>
+      </c>
+    </row>
+    <row r="65" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D65" s="7">
+        <v>46085</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J65" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K65" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="L65" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="M65" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="N65" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O65" s="8">
+        <v>3700</v>
+      </c>
+      <c r="P65" s="8">
+        <v>19.260000000000002</v>
+      </c>
+      <c r="Q65" s="9">
+        <v>71262</v>
+      </c>
+      <c r="R65" s="9">
+        <v>2316.02</v>
+      </c>
+      <c r="S65" s="9">
+        <v>73578.02</v>
+      </c>
+      <c r="T65" s="9">
+        <v>71262</v>
+      </c>
+      <c r="U65" s="9">
+        <v>2850.48</v>
+      </c>
+      <c r="V65" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="W65" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="X65" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y65" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z65" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA65" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB65" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC65" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD65" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE65" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF65" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="AG65" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI65" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ65" s="8">
+        <v>51373.093999999997</v>
+      </c>
+    </row>
+    <row r="66" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D66" s="3">
+        <v>46085</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O66" s="4">
+        <v>0</v>
+      </c>
+      <c r="P66" s="4">
+        <v>32.32</v>
+      </c>
+      <c r="Q66" s="5">
+        <v>32.32</v>
+      </c>
+      <c r="R66" s="5">
+        <v>0</v>
+      </c>
+      <c r="S66" s="5">
+        <v>32.32</v>
+      </c>
+      <c r="T66" s="5">
+        <v>0</v>
+      </c>
+      <c r="U66" s="5">
+        <v>32.32</v>
+      </c>
+      <c r="V66" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="W66" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="X66" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y66" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z66" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA66" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB66" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC66" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD66" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AE66" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AF66" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH66" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI66" s="5">
+        <v>12</v>
+      </c>
+      <c r="AJ66" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D67" s="7">
+        <v>46091</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="J67" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="K67" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="L67" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="M67" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="N67" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O67" s="8">
+        <v>5000</v>
+      </c>
+      <c r="P67" s="8">
+        <v>11.77</v>
+      </c>
+      <c r="Q67" s="9">
+        <v>58850</v>
+      </c>
+      <c r="R67" s="9">
+        <v>1912.63</v>
+      </c>
+      <c r="S67" s="9">
+        <v>60762.63</v>
+      </c>
+      <c r="T67" s="9">
+        <v>58850</v>
+      </c>
+      <c r="U67" s="9">
+        <v>2354</v>
+      </c>
+      <c r="V67" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="W67" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="X67" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y67" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z67" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA67" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB67" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC67" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD67" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE67" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF67" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG67" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH67" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI67" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ67" s="8">
+        <v>48943.45</v>
+      </c>
+    </row>
+    <row r="68" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D68" s="3">
+        <v>46091</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="O68" s="4">
+        <v>225</v>
+      </c>
+      <c r="P68" s="4">
+        <v>12.25</v>
+      </c>
+      <c r="Q68" s="5">
+        <v>2756.25</v>
+      </c>
+      <c r="R68" s="5">
+        <v>89.58</v>
+      </c>
+      <c r="S68" s="5">
+        <v>2845.83</v>
+      </c>
+      <c r="T68" s="5">
+        <v>2756.25</v>
+      </c>
+      <c r="U68" s="5">
+        <v>110.25</v>
+      </c>
+      <c r="V68" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="W68" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="X68" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y68" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z68" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA68" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB68" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC68" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD68" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE68" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF68" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI68" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ68" s="4">
+        <v>2225.1802499999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D69" s="7">
+        <v>46092</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J69" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="K69" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="L69" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="M69" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="N69" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="O69" s="8">
+        <v>10000</v>
+      </c>
+      <c r="P69" s="8">
+        <v>8.2807300000000001</v>
+      </c>
+      <c r="Q69" s="9">
+        <v>82807.3</v>
+      </c>
+      <c r="R69" s="9">
+        <v>2691.23</v>
+      </c>
+      <c r="S69" s="9">
+        <v>85498.53</v>
+      </c>
+      <c r="T69" s="9">
+        <v>205676.76</v>
+      </c>
+      <c r="U69" s="9">
+        <v>3312.29</v>
+      </c>
+      <c r="V69" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="W69" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="X69" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y69" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="Z69" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA69" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB69" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC69" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD69" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE69" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF69" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG69" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI69" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ69" s="8">
+        <v>101325.9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D70" s="3">
+        <v>46092</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="O70" s="4">
+        <v>5000</v>
+      </c>
+      <c r="P70" s="4">
+        <v>7.7957700000000001</v>
+      </c>
+      <c r="Q70" s="5">
+        <v>38978.85</v>
+      </c>
+      <c r="R70" s="5">
+        <v>1266.81</v>
+      </c>
+      <c r="S70" s="5">
+        <v>40245.660000000003</v>
+      </c>
+      <c r="T70" s="5">
+        <v>205676.76</v>
+      </c>
+      <c r="U70" s="5">
+        <v>1559.15</v>
+      </c>
+      <c r="V70" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="W70" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="X70" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y70" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="Z70" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA70" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB70" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC70" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD70" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE70" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF70" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI70" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ70" s="4">
+        <v>48943.45</v>
+      </c>
+    </row>
+    <row r="71" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D71" s="7">
+        <v>46092</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J71" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="K71" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="L71" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="M71" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="N71" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="O71" s="8">
+        <v>8400</v>
+      </c>
+      <c r="P71" s="8">
+        <v>7.6801399999999997</v>
+      </c>
+      <c r="Q71" s="9">
+        <v>64513.18</v>
+      </c>
+      <c r="R71" s="9">
+        <v>2096.6799999999998</v>
+      </c>
+      <c r="S71" s="9">
+        <v>66609.86</v>
+      </c>
+      <c r="T71" s="9">
+        <v>205676.76</v>
+      </c>
+      <c r="U71" s="9">
+        <v>2580.5300000000002</v>
+      </c>
+      <c r="V71" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="W71" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="X71" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y71" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="Z71" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA71" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB71" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC71" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD71" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="AE71" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="AF71" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI71" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ71" s="8">
+        <v>70249.703999999998</v>
+      </c>
+    </row>
+    <row r="72" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D72" s="3">
+        <v>46092</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="O72" s="4">
+        <v>2400</v>
+      </c>
+      <c r="P72" s="4">
+        <v>8.0739300000000007</v>
+      </c>
+      <c r="Q72" s="5">
+        <v>19377.43</v>
+      </c>
+      <c r="R72" s="5">
+        <v>629.77</v>
+      </c>
+      <c r="S72" s="5">
+        <v>20007.2</v>
+      </c>
+      <c r="T72" s="5">
+        <v>205676.76</v>
+      </c>
+      <c r="U72" s="5">
+        <v>775.1</v>
+      </c>
+      <c r="V72" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="W72" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="X72" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y72" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="Z72" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA72" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB72" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC72" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD72" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE72" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF72" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG72" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH72" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI72" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ72" s="4">
+        <v>23735.256000000001</v>
+      </c>
+    </row>
+    <row r="73" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D73" s="7">
+        <v>46093</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J73" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K73" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L73" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M73" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="N73" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="O73" s="8">
+        <v>507</v>
+      </c>
+      <c r="P73" s="8">
+        <v>21.96</v>
+      </c>
+      <c r="Q73" s="9">
+        <v>11133.72</v>
+      </c>
+      <c r="R73" s="9">
+        <v>361.85</v>
+      </c>
+      <c r="S73" s="9">
+        <v>11495.57</v>
+      </c>
+      <c r="T73" s="9">
+        <v>11133.72</v>
+      </c>
+      <c r="U73" s="9">
+        <v>445.35</v>
+      </c>
+      <c r="V73" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="W73" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="X73" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y73" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="Z73" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA73" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB73" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC73" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD73" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE73" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF73" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG73" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI73" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ73" s="8">
+        <v>7263.0538500000002</v>
+      </c>
+    </row>
+    <row r="74" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D74" s="3">
+        <v>46097</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="M74" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="N74" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="O74" s="4">
+        <v>3000</v>
+      </c>
+      <c r="P74" s="4">
+        <v>12.22</v>
+      </c>
+      <c r="Q74" s="5">
+        <v>36660</v>
+      </c>
+      <c r="R74" s="5">
+        <v>1191.45</v>
+      </c>
+      <c r="S74" s="5">
+        <v>37851.449999999997</v>
+      </c>
+      <c r="T74" s="5">
+        <v>36660</v>
+      </c>
+      <c r="U74" s="5">
+        <v>1466.4</v>
+      </c>
+      <c r="V74" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="W74" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="X74" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y74" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="Z74" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA74" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB74" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC74" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD74" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE74" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF74" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG74" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI74" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ74" s="4">
+        <v>31170.42</v>
+      </c>
+    </row>
+    <row r="75" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D75" s="7">
+        <v>46098</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="J75" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="K75" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="L75" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="M75" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="N75" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="O75" s="8">
+        <v>10000</v>
+      </c>
+      <c r="P75" s="8">
+        <v>12.27</v>
+      </c>
+      <c r="Q75" s="9">
+        <v>122700</v>
+      </c>
+      <c r="R75" s="9">
+        <v>3987.75</v>
+      </c>
+      <c r="S75" s="9">
+        <v>126687.75</v>
+      </c>
+      <c r="T75" s="9">
+        <v>122700</v>
+      </c>
+      <c r="U75" s="9">
+        <v>14724</v>
+      </c>
+      <c r="V75" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="W75" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="X75" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y75" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z75" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA75" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB75" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC75" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD75" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="AE22" s="2" t="s">
+      <c r="AE75" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="AF22" s="2" t="s">
+      <c r="AF75" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="AG22" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI22" s="5">
+      <c r="AG75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI75" s="9">
         <v>12</v>
       </c>
-      <c r="AJ22" s="4">
+      <c r="AJ75" s="8">
+        <v>75850.3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D76" s="3">
+        <v>46098</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="N76" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="O76" s="4">
+        <v>507</v>
+      </c>
+      <c r="P76" s="4">
+        <v>21.96</v>
+      </c>
+      <c r="Q76" s="5">
+        <v>11133.72</v>
+      </c>
+      <c r="R76" s="5">
+        <v>361.85</v>
+      </c>
+      <c r="S76" s="5">
+        <v>11495.57</v>
+      </c>
+      <c r="T76" s="5">
+        <v>11133.72</v>
+      </c>
+      <c r="U76" s="5">
+        <v>445.35</v>
+      </c>
+      <c r="V76" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="W76" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="X76" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y76" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z76" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA76" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB76" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC76" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD76" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE76" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF76" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG76" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI76" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ76" s="4">
+        <v>5539.1575199999997</v>
+      </c>
+    </row>
+    <row r="77" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D77" s="7">
+        <v>46100</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G77" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="J77" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="K77" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="L77" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="M77" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="N77" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="O77" s="8">
+        <v>10000</v>
+      </c>
+      <c r="P77" s="8">
+        <v>8.9</v>
+      </c>
+      <c r="Q77" s="9">
+        <v>89000</v>
+      </c>
+      <c r="R77" s="9">
+        <v>2892.5</v>
+      </c>
+      <c r="S77" s="9">
+        <v>91892.5</v>
+      </c>
+      <c r="T77" s="9">
+        <v>89000</v>
+      </c>
+      <c r="U77" s="9">
+        <v>3560</v>
+      </c>
+      <c r="V77" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="W77" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="X77" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y77" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="Z77" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA77" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB77" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC77" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD77" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE77" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF77" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG77" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI77" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ77" s="8">
+        <v>98896.9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D78" s="3">
+        <v>46104</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M78" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N78" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="O78" s="4">
+        <v>1170</v>
+      </c>
+      <c r="P78" s="4">
+        <v>21.21</v>
+      </c>
+      <c r="Q78" s="5">
+        <v>24815.7</v>
+      </c>
+      <c r="R78" s="5">
+        <v>806.51</v>
+      </c>
+      <c r="S78" s="5">
+        <v>25622.21</v>
+      </c>
+      <c r="T78" s="5">
+        <v>84924.84</v>
+      </c>
+      <c r="U78" s="5">
+        <v>992.63</v>
+      </c>
+      <c r="V78" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="W78" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="X78" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y78" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="Z78" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA78" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB78" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC78" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD78" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE78" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF78" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG78" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH78" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI78" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ78" s="4">
+        <v>16760.893499999998</v>
+      </c>
+    </row>
+    <row r="79" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D79" s="7">
+        <v>46104</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J79" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K79" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L79" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="M79" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="N79" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="O79" s="8">
+        <v>2834</v>
+      </c>
+      <c r="P79" s="8">
+        <v>21.21</v>
+      </c>
+      <c r="Q79" s="9">
+        <v>60109.14</v>
+      </c>
+      <c r="R79" s="9">
+        <v>1953.55</v>
+      </c>
+      <c r="S79" s="9">
+        <v>62062.69</v>
+      </c>
+      <c r="T79" s="9">
+        <v>84924.84</v>
+      </c>
+      <c r="U79" s="9">
+        <v>2404.36</v>
+      </c>
+      <c r="V79" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="W79" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="X79" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y79" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="Z79" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA79" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB79" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC79" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD79" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE79" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF79" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG79" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH79" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI79" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ79" s="8">
+        <v>40598.637040000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D80" s="3">
+        <v>46104</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="O80" s="4">
+        <v>1750</v>
+      </c>
+      <c r="P80" s="4">
+        <v>13.48</v>
+      </c>
+      <c r="Q80" s="5">
+        <v>23590</v>
+      </c>
+      <c r="R80" s="5">
+        <v>766.68</v>
+      </c>
+      <c r="S80" s="5">
+        <v>24356.68</v>
+      </c>
+      <c r="T80" s="5">
+        <v>23590</v>
+      </c>
+      <c r="U80" s="5">
+        <v>943.6</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="W80" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="X80" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y80" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="Z80" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA80" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB80" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC80" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD80" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE80" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF80" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG80" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH80" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI80" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ80" s="4">
+        <v>15417.885</v>
+      </c>
+    </row>
+    <row r="81" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D81" s="7">
+        <v>46104</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F81" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I81" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J81" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K81" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="L81" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="M81" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="N81" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O81" s="8">
+        <v>2000</v>
+      </c>
+      <c r="P81" s="8">
+        <v>18.53</v>
+      </c>
+      <c r="Q81" s="9">
+        <v>37060</v>
+      </c>
+      <c r="R81" s="9">
+        <v>1204.45</v>
+      </c>
+      <c r="S81" s="9">
+        <v>38264.449999999997</v>
+      </c>
+      <c r="T81" s="9">
+        <v>37060</v>
+      </c>
+      <c r="U81" s="9">
+        <v>4447.2</v>
+      </c>
+      <c r="V81" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="W81" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="X81" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y81" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="Z81" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA81" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB81" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC81" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD81" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE81" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF81" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG81" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI81" s="9">
+        <v>12</v>
+      </c>
+      <c r="AJ81" s="8">
+        <v>19345.560000000001</v>
+      </c>
+    </row>
+    <row r="82" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D82" s="3">
+        <v>46105</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="M82" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="N82" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="O82" s="4">
+        <v>500</v>
+      </c>
+      <c r="P82" s="4">
+        <v>12.94</v>
+      </c>
+      <c r="Q82" s="5">
+        <v>6470</v>
+      </c>
+      <c r="R82" s="5">
+        <v>210.28</v>
+      </c>
+      <c r="S82" s="5">
+        <v>6680.28</v>
+      </c>
+      <c r="T82" s="5">
+        <v>6470</v>
+      </c>
+      <c r="U82" s="5">
+        <v>776.4</v>
+      </c>
+      <c r="V82" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="W82" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="X82" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y82" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="Z82" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA82" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB82" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC82" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD82" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="AE82" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="AF82" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG82" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH82" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI82" s="5">
+        <v>12</v>
+      </c>
+      <c r="AJ82" s="4">
         <v>3792.5149999999999</v>
       </c>
     </row>

--- a/BASE_KEMPARTS.xlsx
+++ b/BASE_KEMPARTS.xlsx
@@ -8,14 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dash_kp_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9824456D-FA5C-4E15-8549-F6B100066576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35A3A0E2-7993-4B57-A82C-613EBB63CB82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{0368ECA6-E340-40A0-90C6-24B3F78F139B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{0368ECA6-E340-40A0-90C6-24B3F78F139B}"/>
   </bookViews>
   <sheets>
     <sheet name="FSP" sheetId="1" r:id="rId1"/>
     <sheet name="FSC" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">FSC!$A$1:$AJ$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FSP!$A$1:$AJ$298</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9597" uniqueCount="1527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9572" uniqueCount="1525">
   <si>
     <t>Numero</t>
   </si>
@@ -3723,13 +3727,7 @@
     <t>PALETE (NÚ</t>
   </si>
   <si>
-    <t>000015607</t>
-  </si>
-  <si>
     <t>COMPLEMENTO DE ICMS</t>
-  </si>
-  <si>
-    <t>173929</t>
   </si>
   <si>
     <t>GGS</t>
@@ -5076,7 +5074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B3DA891-CC25-4139-B353-C23D51C96611}">
-  <dimension ref="A1:AJ299"/>
+  <dimension ref="A1:AJ298"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -36137,1876 +36135,1767 @@
       </c>
     </row>
     <row r="283" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A283" s="6" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B283" s="6" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C283" s="6" t="s">
+      <c r="A283" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C283" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D283" s="7">
+      <c r="D283" s="3">
         <v>46105</v>
       </c>
-      <c r="E283" s="6" t="s">
+      <c r="E283" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F283" s="6" t="s">
+      <c r="F283" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G283" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H283" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="I283" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="J283" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="K283" s="6" t="s">
-        <v>1229</v>
-      </c>
-      <c r="L283" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="M283" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="N283" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="O283" s="8">
-        <v>0</v>
-      </c>
-      <c r="P283" s="8">
-        <v>12216.15</v>
-      </c>
-      <c r="Q283" s="9">
-        <v>12216.15</v>
-      </c>
-      <c r="R283" s="9">
-        <v>0</v>
-      </c>
-      <c r="S283" s="9">
-        <v>12216.15</v>
-      </c>
-      <c r="T283" s="9">
-        <v>0</v>
-      </c>
-      <c r="U283" s="9">
-        <v>12216.15</v>
-      </c>
-      <c r="V283" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="W283" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="X283" s="6" t="s">
+      <c r="G283" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H283" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I283" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="J283" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="K283" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="L283" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="M283" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="N283" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="O283" s="4">
+        <v>340</v>
+      </c>
+      <c r="P283" s="4">
+        <v>23.9</v>
+      </c>
+      <c r="Q283" s="5">
+        <v>8126</v>
+      </c>
+      <c r="R283" s="5">
+        <v>264.10000000000002</v>
+      </c>
+      <c r="S283" s="5">
+        <v>8390.1</v>
+      </c>
+      <c r="T283" s="5">
+        <v>8126</v>
+      </c>
+      <c r="U283" s="5">
+        <v>1462.68</v>
+      </c>
+      <c r="V283" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="W283" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="X283" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="Y283" s="6" t="s">
-        <v>1230</v>
-      </c>
-      <c r="Z283" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA283" s="6" t="s">
+      <c r="Y283" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="Z283" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA283" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AB283" s="6" t="s">
+      <c r="AB283" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="AC283" s="6" t="s">
+      <c r="AC283" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD283" s="6" t="s">
-        <v>1231</v>
-      </c>
-      <c r="AE283" s="6" t="s">
-        <v>1232</v>
-      </c>
-      <c r="AF283" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AG283" s="9">
-        <v>0</v>
-      </c>
-      <c r="AH283" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI283" s="9">
+      <c r="AD283" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE283" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF283" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG283" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH283" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI283" s="5">
         <v>18</v>
       </c>
-      <c r="AJ283" s="8">
-        <v>0</v>
+      <c r="AJ283" s="4">
+        <v>3785.1417999999999</v>
       </c>
     </row>
     <row r="284" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A284" s="2" t="s">
-        <v>1233</v>
-      </c>
-      <c r="B284" s="2" t="s">
-        <v>1233</v>
-      </c>
-      <c r="C284" s="2" t="s">
+      <c r="A284" s="6" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B284" s="6" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C284" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D284" s="3">
+      <c r="D284" s="7">
         <v>46105</v>
       </c>
-      <c r="E284" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F284" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G284" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="H284" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="I284" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="J284" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="K284" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="L284" s="2" t="s">
-        <v>1234</v>
-      </c>
-      <c r="M284" s="2" t="s">
-        <v>1235</v>
-      </c>
-      <c r="N284" s="2" t="s">
-        <v>1013</v>
-      </c>
-      <c r="O284" s="4">
-        <v>340</v>
-      </c>
-      <c r="P284" s="4">
-        <v>23.9</v>
-      </c>
-      <c r="Q284" s="5">
-        <v>8126</v>
-      </c>
-      <c r="R284" s="5">
-        <v>264.10000000000002</v>
-      </c>
-      <c r="S284" s="5">
-        <v>8390.1</v>
-      </c>
-      <c r="T284" s="5">
-        <v>8126</v>
-      </c>
-      <c r="U284" s="5">
-        <v>1462.68</v>
-      </c>
-      <c r="V284" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="W284" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="X284" s="2" t="s">
+      <c r="E284" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F284" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G284" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H284" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="I284" s="6" t="s">
+        <v>1236</v>
+      </c>
+      <c r="J284" s="6" t="s">
+        <v>1237</v>
+      </c>
+      <c r="K284" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L284" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="M284" s="6" t="s">
+        <v>926</v>
+      </c>
+      <c r="N284" s="6" t="s">
+        <v>927</v>
+      </c>
+      <c r="O284" s="8">
+        <v>2220</v>
+      </c>
+      <c r="P284" s="8">
+        <v>19.98</v>
+      </c>
+      <c r="Q284" s="9">
+        <v>44355.6</v>
+      </c>
+      <c r="R284" s="9">
+        <v>1441.56</v>
+      </c>
+      <c r="S284" s="9">
+        <v>45797.16</v>
+      </c>
+      <c r="T284" s="9">
+        <v>88711.2</v>
+      </c>
+      <c r="U284" s="9">
+        <v>1774.22</v>
+      </c>
+      <c r="V284" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="W284" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="X284" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="Y284" s="2" t="s">
-        <v>1236</v>
-      </c>
-      <c r="Z284" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA284" s="2" t="s">
+      <c r="Y284" s="6" t="s">
+        <v>1238</v>
+      </c>
+      <c r="Z284" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA284" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AB284" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC284" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD284" s="2" t="s">
+      <c r="AB284" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC284" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="AD284" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="AE284" s="2" t="s">
+      <c r="AE284" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="AF284" s="2" t="s">
+      <c r="AF284" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="AG284" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH284" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI284" s="5">
-        <v>18</v>
-      </c>
-      <c r="AJ284" s="4">
-        <v>3785.1417999999999</v>
+      <c r="AG284" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH284" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI284" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ284" s="8">
+        <v>29293.166399999998</v>
       </c>
     </row>
     <row r="285" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A285" s="6" t="s">
+      <c r="A285" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C285" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D285" s="3">
+        <v>46105</v>
+      </c>
+      <c r="E285" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F285" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G285" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H285" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I285" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="J285" s="2" t="s">
         <v>1237</v>
       </c>
-      <c r="B285" s="6" t="s">
-        <v>1237</v>
-      </c>
-      <c r="C285" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D285" s="7">
-        <v>46105</v>
-      </c>
-      <c r="E285" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F285" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G285" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="H285" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="I285" s="6" t="s">
+      <c r="K285" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="L285" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="M285" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="N285" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O285" s="4">
+        <v>1295</v>
+      </c>
+      <c r="P285" s="4">
+        <v>19.98</v>
+      </c>
+      <c r="Q285" s="5">
+        <v>25874.1</v>
+      </c>
+      <c r="R285" s="5">
+        <v>840.91</v>
+      </c>
+      <c r="S285" s="5">
+        <v>26715.01</v>
+      </c>
+      <c r="T285" s="5">
+        <v>88711.2</v>
+      </c>
+      <c r="U285" s="5">
+        <v>1034.97</v>
+      </c>
+      <c r="V285" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="W285" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="X285" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y285" s="2" t="s">
         <v>1238</v>
       </c>
-      <c r="J285" s="6" t="s">
-        <v>1239</v>
-      </c>
-      <c r="K285" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="L285" s="6" t="s">
-        <v>925</v>
-      </c>
-      <c r="M285" s="6" t="s">
-        <v>926</v>
-      </c>
-      <c r="N285" s="6" t="s">
-        <v>927</v>
-      </c>
-      <c r="O285" s="8">
-        <v>2220</v>
-      </c>
-      <c r="P285" s="8">
-        <v>19.98</v>
-      </c>
-      <c r="Q285" s="9">
-        <v>44355.6</v>
-      </c>
-      <c r="R285" s="9">
-        <v>1441.56</v>
-      </c>
-      <c r="S285" s="9">
-        <v>45797.16</v>
-      </c>
-      <c r="T285" s="9">
-        <v>88711.2</v>
-      </c>
-      <c r="U285" s="9">
-        <v>1774.22</v>
-      </c>
-      <c r="V285" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="W285" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="X285" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y285" s="6" t="s">
-        <v>1240</v>
-      </c>
-      <c r="Z285" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA285" s="6" t="s">
+      <c r="Z285" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA285" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AB285" s="6" t="s">
+      <c r="AB285" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="AC285" s="6" t="s">
+      <c r="AC285" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AD285" s="6" t="s">
+      <c r="AD285" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="AE285" s="6" t="s">
+      <c r="AE285" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AF285" s="6" t="s">
+      <c r="AF285" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="AG285" s="9">
-        <v>0</v>
-      </c>
-      <c r="AH285" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI285" s="9">
+      <c r="AG285" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH285" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI285" s="5">
         <v>4</v>
       </c>
-      <c r="AJ285" s="8">
-        <v>29293.166399999998</v>
+      <c r="AJ285" s="4">
+        <v>16676.453150000001</v>
       </c>
     </row>
     <row r="286" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A286" s="2" t="s">
+      <c r="A286" s="6" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B286" s="6" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C286" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D286" s="7">
+        <v>46105</v>
+      </c>
+      <c r="E286" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F286" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G286" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H286" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="I286" s="6" t="s">
+        <v>1236</v>
+      </c>
+      <c r="J286" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="B286" s="2" t="s">
-        <v>1237</v>
-      </c>
-      <c r="C286" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D286" s="3">
-        <v>46105</v>
-      </c>
-      <c r="E286" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F286" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G286" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H286" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I286" s="2" t="s">
+      <c r="K286" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="L286" s="6" t="s">
+        <v>891</v>
+      </c>
+      <c r="M286" s="6" t="s">
+        <v>892</v>
+      </c>
+      <c r="N286" s="6" t="s">
+        <v>893</v>
+      </c>
+      <c r="O286" s="8">
+        <v>925</v>
+      </c>
+      <c r="P286" s="8">
+        <v>19.98</v>
+      </c>
+      <c r="Q286" s="9">
+        <v>18481.5</v>
+      </c>
+      <c r="R286" s="9">
+        <v>600.64</v>
+      </c>
+      <c r="S286" s="9">
+        <v>19082.14</v>
+      </c>
+      <c r="T286" s="9">
+        <v>88711.2</v>
+      </c>
+      <c r="U286" s="9">
+        <v>739.26</v>
+      </c>
+      <c r="V286" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="W286" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="X286" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y286" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="J286" s="2" t="s">
-        <v>1239</v>
-      </c>
-      <c r="K286" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="L286" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="M286" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="N286" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="O286" s="4">
-        <v>1295</v>
-      </c>
-      <c r="P286" s="4">
-        <v>19.98</v>
-      </c>
-      <c r="Q286" s="5">
-        <v>25874.1</v>
-      </c>
-      <c r="R286" s="5">
-        <v>840.91</v>
-      </c>
-      <c r="S286" s="5">
-        <v>26715.01</v>
-      </c>
-      <c r="T286" s="5">
-        <v>88711.2</v>
-      </c>
-      <c r="U286" s="5">
-        <v>1034.97</v>
-      </c>
-      <c r="V286" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="W286" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="X286" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y286" s="2" t="s">
-        <v>1240</v>
-      </c>
-      <c r="Z286" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA286" s="2" t="s">
+      <c r="Z286" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA286" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AB286" s="2" t="s">
+      <c r="AB286" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="AC286" s="2" t="s">
+      <c r="AC286" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="AD286" s="2" t="s">
+      <c r="AD286" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="AE286" s="2" t="s">
+      <c r="AE286" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="AF286" s="2" t="s">
+      <c r="AF286" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="AG286" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH286" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI286" s="5">
+      <c r="AG286" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH286" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI286" s="9">
         <v>4</v>
       </c>
-      <c r="AJ286" s="4">
-        <v>16676.453150000001</v>
+      <c r="AJ286" s="8">
+        <v>11911.75225</v>
       </c>
     </row>
     <row r="287" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A287" s="6" t="s">
+      <c r="A287" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B287" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C287" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D287" s="3">
+        <v>46105</v>
+      </c>
+      <c r="E287" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F287" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G287" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H287" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I287" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="J287" s="2" t="s">
         <v>1237</v>
       </c>
-      <c r="B287" s="6" t="s">
-        <v>1237</v>
-      </c>
-      <c r="C287" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D287" s="7">
-        <v>46105</v>
-      </c>
-      <c r="E287" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F287" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G287" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="H287" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="I287" s="6" t="s">
-        <v>1238</v>
-      </c>
-      <c r="J287" s="6" t="s">
-        <v>1239</v>
-      </c>
-      <c r="K287" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="L287" s="6" t="s">
-        <v>891</v>
-      </c>
-      <c r="M287" s="6" t="s">
-        <v>892</v>
-      </c>
-      <c r="N287" s="6" t="s">
-        <v>893</v>
-      </c>
-      <c r="O287" s="8">
-        <v>925</v>
-      </c>
-      <c r="P287" s="8">
-        <v>19.98</v>
-      </c>
-      <c r="Q287" s="9">
-        <v>18481.5</v>
-      </c>
-      <c r="R287" s="9">
-        <v>600.64</v>
-      </c>
-      <c r="S287" s="9">
-        <v>19082.14</v>
-      </c>
-      <c r="T287" s="9">
-        <v>88711.2</v>
-      </c>
-      <c r="U287" s="9">
-        <v>739.26</v>
-      </c>
-      <c r="V287" s="6" t="s">
+      <c r="K287" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L287" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="M287" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="N287" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="O287" s="4">
+        <v>3500</v>
+      </c>
+      <c r="P287" s="4">
+        <v>12.98</v>
+      </c>
+      <c r="Q287" s="5">
+        <v>45430</v>
+      </c>
+      <c r="R287" s="5">
+        <v>1476.48</v>
+      </c>
+      <c r="S287" s="5">
+        <v>46906.48</v>
+      </c>
+      <c r="T287" s="5">
+        <v>52150</v>
+      </c>
+      <c r="U287" s="5">
+        <v>1817.2</v>
+      </c>
+      <c r="V287" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="W287" s="6" t="s">
+      <c r="W287" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="X287" s="6" t="s">
+      <c r="X287" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="Y287" s="6" t="s">
+      <c r="Y287" s="2" t="s">
         <v>1240</v>
       </c>
-      <c r="Z287" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA287" s="6" t="s">
+      <c r="Z287" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA287" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AB287" s="6" t="s">
+      <c r="AB287" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="AC287" s="6" t="s">
+      <c r="AC287" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AD287" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="AE287" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF287" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="AG287" s="9">
-        <v>0</v>
-      </c>
-      <c r="AH287" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI287" s="9">
+      <c r="AD287" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="AE287" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="AF287" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG287" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH287" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI287" s="5">
         <v>4</v>
       </c>
-      <c r="AJ287" s="8">
-        <v>11911.75225</v>
+      <c r="AJ287" s="4">
+        <v>30421.825000000001</v>
       </c>
     </row>
     <row r="288" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A288" s="2" t="s">
-        <v>1241</v>
-      </c>
-      <c r="B288" s="2" t="s">
-        <v>1241</v>
-      </c>
-      <c r="C288" s="2" t="s">
+      <c r="A288" s="6" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B288" s="6" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C288" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D288" s="3">
+      <c r="D288" s="7">
         <v>46105</v>
       </c>
-      <c r="E288" s="2" t="s">
+      <c r="E288" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F288" s="2" t="s">
+      <c r="F288" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G288" s="2" t="s">
+      <c r="G288" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="H288" s="2" t="s">
+      <c r="H288" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="I288" s="2" t="s">
-        <v>1238</v>
-      </c>
-      <c r="J288" s="2" t="s">
-        <v>1239</v>
-      </c>
-      <c r="K288" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="L288" s="2" t="s">
-        <v>1192</v>
-      </c>
-      <c r="M288" s="2" t="s">
-        <v>1193</v>
-      </c>
-      <c r="N288" s="2" t="s">
-        <v>1194</v>
-      </c>
-      <c r="O288" s="4">
-        <v>3500</v>
-      </c>
-      <c r="P288" s="4">
-        <v>12.98</v>
-      </c>
-      <c r="Q288" s="5">
-        <v>45430</v>
-      </c>
-      <c r="R288" s="5">
-        <v>1476.48</v>
-      </c>
-      <c r="S288" s="5">
-        <v>46906.48</v>
-      </c>
-      <c r="T288" s="5">
+      <c r="I288" s="6" t="s">
+        <v>1236</v>
+      </c>
+      <c r="J288" s="6" t="s">
+        <v>1237</v>
+      </c>
+      <c r="K288" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="L288" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="M288" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="N288" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="O288" s="8">
+        <v>300</v>
+      </c>
+      <c r="P288" s="8">
+        <v>22.4</v>
+      </c>
+      <c r="Q288" s="9">
+        <v>6720</v>
+      </c>
+      <c r="R288" s="9">
+        <v>218.4</v>
+      </c>
+      <c r="S288" s="9">
+        <v>6938.4</v>
+      </c>
+      <c r="T288" s="9">
         <v>52150</v>
       </c>
-      <c r="U288" s="5">
-        <v>1817.2</v>
-      </c>
-      <c r="V288" s="2" t="s">
+      <c r="U288" s="9">
+        <v>806.4</v>
+      </c>
+      <c r="V288" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="W288" s="2" t="s">
+      <c r="W288" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="X288" s="2" t="s">
+      <c r="X288" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="Y288" s="2" t="s">
-        <v>1242</v>
-      </c>
-      <c r="Z288" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA288" s="2" t="s">
+      <c r="Y288" s="6" t="s">
+        <v>1240</v>
+      </c>
+      <c r="Z288" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA288" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AB288" s="2" t="s">
+      <c r="AB288" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="AC288" s="2" t="s">
+      <c r="AC288" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="AD288" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="AE288" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="AF288" s="2" t="s">
+      <c r="AD288" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="AE288" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="AF288" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="AG288" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH288" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI288" s="5">
-        <v>4</v>
-      </c>
-      <c r="AJ288" s="4">
-        <v>30421.825000000001</v>
+      <c r="AG288" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH288" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI288" s="9">
+        <v>12</v>
+      </c>
+      <c r="AJ288" s="8">
+        <v>2251.0709999999999</v>
       </c>
     </row>
     <row r="289" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A289" s="6" t="s">
+      <c r="A289" s="2" t="s">
         <v>1241</v>
       </c>
-      <c r="B289" s="6" t="s">
+      <c r="B289" s="2" t="s">
         <v>1241</v>
       </c>
-      <c r="C289" s="6" t="s">
+      <c r="C289" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D289" s="7">
-        <v>46105</v>
-      </c>
-      <c r="E289" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F289" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G289" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="H289" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="I289" s="6" t="s">
-        <v>1238</v>
-      </c>
-      <c r="J289" s="6" t="s">
-        <v>1239</v>
-      </c>
-      <c r="K289" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="L289" s="6" t="s">
-        <v>562</v>
-      </c>
-      <c r="M289" s="6" t="s">
-        <v>563</v>
-      </c>
-      <c r="N289" s="6" t="s">
-        <v>564</v>
-      </c>
-      <c r="O289" s="8">
-        <v>300</v>
-      </c>
-      <c r="P289" s="8">
-        <v>22.4</v>
-      </c>
-      <c r="Q289" s="9">
-        <v>6720</v>
-      </c>
-      <c r="R289" s="9">
-        <v>218.4</v>
-      </c>
-      <c r="S289" s="9">
-        <v>6938.4</v>
-      </c>
-      <c r="T289" s="9">
-        <v>52150</v>
-      </c>
-      <c r="U289" s="9">
-        <v>806.4</v>
-      </c>
-      <c r="V289" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="W289" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="X289" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y289" s="6" t="s">
+      <c r="D289" s="3">
+        <v>46106</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F289" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G289" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="H289" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="I289" s="2" t="s">
         <v>1242</v>
       </c>
-      <c r="Z289" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA289" s="6" t="s">
+      <c r="J289" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="K289" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="L289" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="M289" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="N289" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="O289" s="4">
+        <v>350</v>
+      </c>
+      <c r="P289" s="4">
+        <v>34.285820000000001</v>
+      </c>
+      <c r="Q289" s="5">
+        <v>12000.04</v>
+      </c>
+      <c r="R289" s="5">
+        <v>390</v>
+      </c>
+      <c r="S289" s="5">
+        <v>12390.04</v>
+      </c>
+      <c r="T289" s="5">
+        <v>12000.04</v>
+      </c>
+      <c r="U289" s="5">
+        <v>2160.0100000000002</v>
+      </c>
+      <c r="V289" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="W289" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="X289" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y289" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="Z289" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA289" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AB289" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC289" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="AD289" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="AE289" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="AF289" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="AG289" s="9">
-        <v>0</v>
-      </c>
-      <c r="AH289" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI289" s="9">
-        <v>12</v>
-      </c>
-      <c r="AJ289" s="8">
-        <v>2251.0709999999999</v>
+      <c r="AB289" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC289" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD289" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="AE289" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="AF289" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG289" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH289" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI289" s="5">
+        <v>18</v>
+      </c>
+      <c r="AJ289" s="4">
+        <v>8923.2780000000002</v>
       </c>
     </row>
     <row r="290" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A290" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="B290" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="C290" s="2" t="s">
+      <c r="A290" s="6" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B290" s="6" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C290" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D290" s="3">
+      <c r="D290" s="7">
         <v>46106</v>
       </c>
-      <c r="E290" s="2" t="s">
+      <c r="E290" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F290" s="2" t="s">
+      <c r="F290" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="G290" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="H290" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="I290" s="2" t="s">
-        <v>1244</v>
-      </c>
-      <c r="J290" s="2" t="s">
-        <v>1245</v>
-      </c>
-      <c r="K290" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="L290" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="M290" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="N290" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="O290" s="4">
-        <v>350</v>
-      </c>
-      <c r="P290" s="4">
-        <v>34.285820000000001</v>
-      </c>
-      <c r="Q290" s="5">
-        <v>12000.04</v>
-      </c>
-      <c r="R290" s="5">
-        <v>390</v>
-      </c>
-      <c r="S290" s="5">
-        <v>12390.04</v>
-      </c>
-      <c r="T290" s="5">
-        <v>12000.04</v>
-      </c>
-      <c r="U290" s="5">
-        <v>2160.0100000000002</v>
-      </c>
-      <c r="V290" s="2" t="s">
+      <c r="G290" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="H290" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="I290" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="J290" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K290" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="L290" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="M290" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="N290" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="O290" s="8">
+        <v>2980</v>
+      </c>
+      <c r="P290" s="8">
+        <v>20.349329999999998</v>
+      </c>
+      <c r="Q290" s="9">
+        <v>60641</v>
+      </c>
+      <c r="R290" s="9">
+        <v>1970.83</v>
+      </c>
+      <c r="S290" s="9">
+        <v>62611.83</v>
+      </c>
+      <c r="T290" s="9">
+        <v>61047.99</v>
+      </c>
+      <c r="U290" s="9">
+        <v>10915.38</v>
+      </c>
+      <c r="V290" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="W290" s="2" t="s">
+      <c r="W290" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="X290" s="2" t="s">
+      <c r="X290" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="Y290" s="2" t="s">
+      <c r="Y290" s="6" t="s">
         <v>1246</v>
       </c>
-      <c r="Z290" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA290" s="2" t="s">
+      <c r="Z290" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA290" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AB290" s="2" t="s">
+      <c r="AB290" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="AC290" s="2" t="s">
+      <c r="AC290" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="AD290" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="AE290" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="AF290" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="AG290" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH290" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI290" s="5">
+      <c r="AD290" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="AE290" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="AF290" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG290" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH290" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI290" s="9">
         <v>18</v>
       </c>
-      <c r="AJ290" s="4">
-        <v>8923.2780000000002</v>
+      <c r="AJ290" s="8">
+        <v>37937.932999999997</v>
       </c>
     </row>
     <row r="291" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A291" s="6" t="s">
+      <c r="A291" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C291" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D291" s="3">
+        <v>46106</v>
+      </c>
+      <c r="E291" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F291" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G291" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="H291" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="I291" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J291" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="K291" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L291" s="2" t="s">
         <v>1247</v>
       </c>
-      <c r="B291" s="6" t="s">
-        <v>1247</v>
-      </c>
-      <c r="C291" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D291" s="7">
-        <v>46106</v>
-      </c>
-      <c r="E291" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F291" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="G291" s="6" t="s">
-        <v>485</v>
-      </c>
-      <c r="H291" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="I291" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="J291" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="K291" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="L291" s="6" t="s">
-        <v>492</v>
-      </c>
-      <c r="M291" s="6" t="s">
-        <v>493</v>
-      </c>
-      <c r="N291" s="6" t="s">
-        <v>489</v>
-      </c>
-      <c r="O291" s="8">
-        <v>2980</v>
-      </c>
-      <c r="P291" s="8">
+      <c r="M291" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="N291" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="O291" s="4">
+        <v>20</v>
+      </c>
+      <c r="P291" s="4">
         <v>20.349329999999998</v>
       </c>
-      <c r="Q291" s="9">
-        <v>60641</v>
-      </c>
-      <c r="R291" s="9">
-        <v>1970.83</v>
-      </c>
-      <c r="S291" s="9">
-        <v>62611.83</v>
-      </c>
-      <c r="T291" s="9">
+      <c r="Q291" s="5">
+        <v>406.99</v>
+      </c>
+      <c r="R291" s="5">
+        <v>13.23</v>
+      </c>
+      <c r="S291" s="5">
+        <v>420.22</v>
+      </c>
+      <c r="T291" s="5">
         <v>61047.99</v>
       </c>
-      <c r="U291" s="9">
-        <v>10915.38</v>
-      </c>
-      <c r="V291" s="6" t="s">
+      <c r="U291" s="5">
+        <v>73.260000000000005</v>
+      </c>
+      <c r="V291" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="W291" s="6" t="s">
+      <c r="W291" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="X291" s="6" t="s">
+      <c r="X291" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="Y291" s="6" t="s">
-        <v>1248</v>
-      </c>
-      <c r="Z291" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA291" s="6" t="s">
+      <c r="Y291" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="Z291" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA291" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AB291" s="6" t="s">
+      <c r="AB291" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AC291" s="6" t="s">
+      <c r="AC291" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD291" s="6" t="s">
+      <c r="AD291" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="AE291" s="6" t="s">
+      <c r="AE291" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="AF291" s="6" t="s">
+      <c r="AF291" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="AG291" s="9">
-        <v>0</v>
-      </c>
-      <c r="AH291" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI291" s="9">
+      <c r="AG291" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH291" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI291" s="5">
         <v>18</v>
       </c>
-      <c r="AJ291" s="8">
-        <v>37937.932999999997</v>
+      <c r="AJ291" s="4">
+        <v>254.61699999999999</v>
       </c>
     </row>
     <row r="292" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A292" s="2" t="s">
-        <v>1247</v>
-      </c>
-      <c r="B292" s="2" t="s">
-        <v>1247</v>
-      </c>
-      <c r="C292" s="2" t="s">
+      <c r="A292" s="6" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B292" s="6" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C292" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D292" s="3">
+      <c r="D292" s="7">
         <v>46106</v>
       </c>
-      <c r="E292" s="2" t="s">
+      <c r="E292" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F292" s="2" t="s">
+      <c r="F292" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="G292" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="H292" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="I292" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="J292" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="K292" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="L292" s="2" t="s">
-        <v>1249</v>
-      </c>
-      <c r="M292" s="2" t="s">
+      <c r="G292" s="6" t="s">
         <v>1250</v>
       </c>
-      <c r="N292" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="O292" s="4">
-        <v>20</v>
-      </c>
-      <c r="P292" s="4">
-        <v>20.349329999999998</v>
-      </c>
-      <c r="Q292" s="5">
-        <v>406.99</v>
-      </c>
-      <c r="R292" s="5">
-        <v>13.23</v>
-      </c>
-      <c r="S292" s="5">
-        <v>420.22</v>
-      </c>
-      <c r="T292" s="5">
-        <v>61047.99</v>
-      </c>
-      <c r="U292" s="5">
-        <v>73.260000000000005</v>
-      </c>
-      <c r="V292" s="2" t="s">
+      <c r="H292" s="6" t="s">
+        <v>1251</v>
+      </c>
+      <c r="I292" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="J292" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="K292" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="L292" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="M292" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="N292" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="O292" s="8">
+        <v>2000</v>
+      </c>
+      <c r="P292" s="8">
+        <v>12.98</v>
+      </c>
+      <c r="Q292" s="9">
+        <v>25960</v>
+      </c>
+      <c r="R292" s="9">
+        <v>843.7</v>
+      </c>
+      <c r="S292" s="9">
+        <v>26803.7</v>
+      </c>
+      <c r="T292" s="9">
+        <v>25960</v>
+      </c>
+      <c r="U292" s="9">
+        <v>4672.8</v>
+      </c>
+      <c r="V292" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="W292" s="2" t="s">
+      <c r="W292" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="X292" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y292" s="2" t="s">
-        <v>1248</v>
-      </c>
-      <c r="Z292" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA292" s="2" t="s">
+      <c r="X292" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y292" s="6" t="s">
+        <v>1252</v>
+      </c>
+      <c r="Z292" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA292" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AB292" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AC292" s="2" t="s">
+      <c r="AB292" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC292" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="AD292" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="AE292" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="AF292" s="2" t="s">
+      <c r="AD292" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="AE292" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="AF292" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="AG292" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH292" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI292" s="5">
+      <c r="AG292" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH292" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI292" s="9">
         <v>18</v>
       </c>
-      <c r="AJ292" s="4">
-        <v>254.61699999999999</v>
+      <c r="AJ292" s="8">
+        <v>15007.14</v>
       </c>
     </row>
     <row r="293" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A293" s="6" t="s">
-        <v>1251</v>
-      </c>
-      <c r="B293" s="6" t="s">
-        <v>1251</v>
-      </c>
-      <c r="C293" s="6" t="s">
+      <c r="A293" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C293" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D293" s="7">
+      <c r="D293" s="3">
         <v>46106</v>
       </c>
-      <c r="E293" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F293" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="G293" s="6" t="s">
-        <v>1252</v>
-      </c>
-      <c r="H293" s="6" t="s">
-        <v>1253</v>
-      </c>
-      <c r="I293" s="6" t="s">
+      <c r="E293" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F293" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G293" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="H293" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="I293" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="J293" s="6" t="s">
+      <c r="J293" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="K293" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="L293" s="6" t="s">
-        <v>562</v>
-      </c>
-      <c r="M293" s="6" t="s">
-        <v>563</v>
-      </c>
-      <c r="N293" s="6" t="s">
-        <v>564</v>
-      </c>
-      <c r="O293" s="8">
-        <v>2000</v>
-      </c>
-      <c r="P293" s="8">
-        <v>12.98</v>
-      </c>
-      <c r="Q293" s="9">
-        <v>25960</v>
-      </c>
-      <c r="R293" s="9">
-        <v>843.7</v>
-      </c>
-      <c r="S293" s="9">
-        <v>26803.7</v>
-      </c>
-      <c r="T293" s="9">
-        <v>25960</v>
-      </c>
-      <c r="U293" s="9">
-        <v>4672.8</v>
-      </c>
-      <c r="V293" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="W293" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="X293" s="6" t="s">
+      <c r="K293" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="L293" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="M293" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="N293" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="O293" s="4">
+        <v>5550</v>
+      </c>
+      <c r="P293" s="4">
+        <v>28.27</v>
+      </c>
+      <c r="Q293" s="5">
+        <v>156898.5</v>
+      </c>
+      <c r="R293" s="5">
+        <v>5099.2</v>
+      </c>
+      <c r="S293" s="5">
+        <v>161997.70000000001</v>
+      </c>
+      <c r="T293" s="5">
+        <v>156898.5</v>
+      </c>
+      <c r="U293" s="5">
+        <v>6275.94</v>
+      </c>
+      <c r="V293" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="W293" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="X293" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="Y293" s="6" t="s">
+      <c r="Y293" s="2" t="s">
         <v>1254</v>
       </c>
-      <c r="Z293" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA293" s="6" t="s">
+      <c r="Z293" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA293" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AB293" s="6" t="s">
+      <c r="AB293" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="AC293" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD293" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="AE293" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="AF293" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="AG293" s="9">
-        <v>0</v>
-      </c>
-      <c r="AH293" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI293" s="9">
-        <v>18</v>
-      </c>
-      <c r="AJ293" s="8">
-        <v>15007.14</v>
+      <c r="AC293" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="AD293" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE293" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF293" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG293" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH293" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI293" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ293" s="4">
+        <v>71470.457999999999</v>
       </c>
     </row>
     <row r="294" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A294" s="2" t="s">
+      <c r="A294" s="6" t="s">
         <v>1255</v>
       </c>
-      <c r="B294" s="2" t="s">
+      <c r="B294" s="6" t="s">
         <v>1255</v>
       </c>
-      <c r="C294" s="2" t="s">
+      <c r="C294" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D294" s="3">
+      <c r="D294" s="7">
         <v>46106</v>
       </c>
-      <c r="E294" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F294" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G294" s="2" t="s">
-        <v>888</v>
-      </c>
-      <c r="H294" s="2" t="s">
-        <v>889</v>
-      </c>
-      <c r="I294" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="J294" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="K294" s="2" t="s">
-        <v>890</v>
-      </c>
-      <c r="L294" s="2" t="s">
+      <c r="E294" s="6" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F294" s="6" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G294" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="H294" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="I294" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="J294" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K294" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="L294" s="6" t="s">
         <v>891</v>
       </c>
-      <c r="M294" s="2" t="s">
+      <c r="M294" s="6" t="s">
         <v>892</v>
       </c>
-      <c r="N294" s="2" t="s">
+      <c r="N294" s="6" t="s">
         <v>893</v>
       </c>
-      <c r="O294" s="4">
-        <v>5550</v>
-      </c>
-      <c r="P294" s="4">
-        <v>28.27</v>
-      </c>
-      <c r="Q294" s="5">
-        <v>156898.5</v>
-      </c>
-      <c r="R294" s="5">
-        <v>5099.2</v>
-      </c>
-      <c r="S294" s="5">
-        <v>161997.70000000001</v>
-      </c>
-      <c r="T294" s="5">
-        <v>156898.5</v>
-      </c>
-      <c r="U294" s="5">
-        <v>6275.94</v>
-      </c>
-      <c r="V294" s="2" t="s">
-        <v>894</v>
-      </c>
-      <c r="W294" s="2" t="s">
-        <v>895</v>
-      </c>
-      <c r="X294" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y294" s="2" t="s">
-        <v>1256</v>
-      </c>
-      <c r="Z294" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA294" s="2" t="s">
+      <c r="O294" s="8">
+        <v>555</v>
+      </c>
+      <c r="P294" s="8">
+        <v>27.74</v>
+      </c>
+      <c r="Q294" s="9">
+        <v>15395.7</v>
+      </c>
+      <c r="R294" s="9">
+        <v>500.36</v>
+      </c>
+      <c r="S294" s="9">
+        <v>15896.06</v>
+      </c>
+      <c r="T294" s="9">
+        <v>87242.3</v>
+      </c>
+      <c r="U294" s="9">
+        <v>2771.23</v>
+      </c>
+      <c r="V294" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="W294" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="X294" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y294" s="6" t="s">
+        <v>1258</v>
+      </c>
+      <c r="Z294" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA294" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AB294" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC294" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="AD294" s="2" t="s">
+      <c r="AB294" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC294" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD294" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="AE294" s="2" t="s">
+      <c r="AE294" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="AF294" s="2" t="s">
+      <c r="AF294" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="AG294" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH294" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI294" s="5">
-        <v>4</v>
-      </c>
-      <c r="AJ294" s="4">
-        <v>71470.457999999999</v>
+      <c r="AG294" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH294" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI294" s="9">
+        <v>18</v>
+      </c>
+      <c r="AJ294" s="8">
+        <v>7147.0513499999997</v>
       </c>
     </row>
     <row r="295" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A295" s="6" t="s">
+      <c r="A295" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C295" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D295" s="3">
+        <v>46106</v>
+      </c>
+      <c r="E295" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F295" s="2" t="s">
         <v>1257</v>
       </c>
-      <c r="B295" s="6" t="s">
-        <v>1257</v>
-      </c>
-      <c r="C295" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D295" s="7">
-        <v>46106</v>
-      </c>
-      <c r="E295" s="6" t="s">
+      <c r="G295" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="H295" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="I295" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J295" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="K295" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="L295" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="M295" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="N295" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="O295" s="4">
+        <v>2590</v>
+      </c>
+      <c r="P295" s="4">
+        <v>27.74</v>
+      </c>
+      <c r="Q295" s="5">
+        <v>71846.600000000006</v>
+      </c>
+      <c r="R295" s="5">
+        <v>2335.0100000000002</v>
+      </c>
+      <c r="S295" s="5">
+        <v>74181.61</v>
+      </c>
+      <c r="T295" s="5">
+        <v>87242.3</v>
+      </c>
+      <c r="U295" s="5">
+        <v>12932.38</v>
+      </c>
+      <c r="V295" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="W295" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="X295" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y295" s="2" t="s">
         <v>1258</v>
       </c>
-      <c r="F295" s="6" t="s">
-        <v>1259</v>
-      </c>
-      <c r="G295" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="H295" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="I295" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="J295" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="K295" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="L295" s="6" t="s">
-        <v>891</v>
-      </c>
-      <c r="M295" s="6" t="s">
-        <v>892</v>
-      </c>
-      <c r="N295" s="6" t="s">
-        <v>893</v>
-      </c>
-      <c r="O295" s="8">
-        <v>555</v>
-      </c>
-      <c r="P295" s="8">
-        <v>27.74</v>
-      </c>
-      <c r="Q295" s="9">
-        <v>15395.7</v>
-      </c>
-      <c r="R295" s="9">
-        <v>500.36</v>
-      </c>
-      <c r="S295" s="9">
-        <v>15896.06</v>
-      </c>
-      <c r="T295" s="9">
-        <v>87242.3</v>
-      </c>
-      <c r="U295" s="9">
-        <v>2771.23</v>
-      </c>
-      <c r="V295" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="W295" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="X295" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y295" s="6" t="s">
-        <v>1260</v>
-      </c>
-      <c r="Z295" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA295" s="6" t="s">
+      <c r="Z295" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA295" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AB295" s="6" t="s">
+      <c r="AB295" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AC295" s="6" t="s">
+      <c r="AC295" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD295" s="6" t="s">
+      <c r="AD295" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="AE295" s="6" t="s">
+      <c r="AE295" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AF295" s="6" t="s">
+      <c r="AF295" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AG295" s="9">
-        <v>0</v>
-      </c>
-      <c r="AH295" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI295" s="9">
+      <c r="AG295" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH295" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI295" s="5">
         <v>18</v>
       </c>
-      <c r="AJ295" s="8">
-        <v>7147.0513499999997</v>
+      <c r="AJ295" s="4">
+        <v>33352.906300000002</v>
       </c>
     </row>
     <row r="296" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A296" s="2" t="s">
-        <v>1257</v>
-      </c>
-      <c r="B296" s="2" t="s">
-        <v>1257</v>
-      </c>
-      <c r="C296" s="2" t="s">
+      <c r="A296" s="6" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B296" s="6" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C296" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D296" s="3">
+      <c r="D296" s="7">
         <v>46106</v>
       </c>
-      <c r="E296" s="2" t="s">
-        <v>1258</v>
-      </c>
-      <c r="F296" s="2" t="s">
-        <v>1259</v>
-      </c>
-      <c r="G296" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="H296" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="I296" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="J296" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="K296" s="2" t="s">
+      <c r="E296" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="F296" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="G296" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="H296" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="I296" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="J296" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="K296" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="L296" s="2" t="s">
-        <v>1261</v>
-      </c>
-      <c r="M296" s="2" t="s">
-        <v>1262</v>
-      </c>
-      <c r="N296" s="2" t="s">
+      <c r="L296" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="M296" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="N296" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="O296" s="8">
+        <v>555</v>
+      </c>
+      <c r="P296" s="8">
+        <v>27.74</v>
+      </c>
+      <c r="Q296" s="9">
+        <v>15395.7</v>
+      </c>
+      <c r="R296" s="9">
+        <v>0</v>
+      </c>
+      <c r="S296" s="9">
+        <v>15395.7</v>
+      </c>
+      <c r="T296" s="9">
+        <v>0</v>
+      </c>
+      <c r="U296" s="9">
+        <v>0</v>
+      </c>
+      <c r="V296" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="W296" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="X296" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="Y296" s="6" t="s">
         <v>1263</v>
       </c>
-      <c r="O296" s="4">
-        <v>2590</v>
-      </c>
-      <c r="P296" s="4">
-        <v>27.74</v>
-      </c>
-      <c r="Q296" s="5">
-        <v>71846.600000000006</v>
-      </c>
-      <c r="R296" s="5">
-        <v>2335.0100000000002</v>
-      </c>
-      <c r="S296" s="5">
-        <v>74181.61</v>
-      </c>
-      <c r="T296" s="5">
-        <v>87242.3</v>
-      </c>
-      <c r="U296" s="5">
-        <v>12932.38</v>
-      </c>
-      <c r="V296" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="W296" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="X296" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y296" s="2" t="s">
-        <v>1260</v>
-      </c>
-      <c r="Z296" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA296" s="2" t="s">
+      <c r="Z296" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA296" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AB296" s="2" t="s">
+      <c r="AB296" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="AC296" s="2" t="s">
+      <c r="AC296" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="AD296" s="2" t="s">
+      <c r="AD296" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="AE296" s="2" t="s">
+      <c r="AE296" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="AF296" s="2" t="s">
+      <c r="AF296" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="AG296" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH296" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI296" s="5">
-        <v>18</v>
-      </c>
-      <c r="AJ296" s="4">
-        <v>33352.906300000002</v>
+      <c r="AG296" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH296" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI296" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ296" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="297" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A297" s="6" t="s">
-        <v>1264</v>
-      </c>
-      <c r="B297" s="6" t="s">
-        <v>1264</v>
-      </c>
-      <c r="C297" s="6" t="s">
+      <c r="A297" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B297" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C297" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D297" s="7">
+      <c r="D297" s="3">
         <v>46106</v>
       </c>
-      <c r="E297" s="6" t="s">
+      <c r="E297" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="F297" s="6" t="s">
+      <c r="F297" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="G297" s="6" t="s">
+      <c r="G297" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="H297" s="6" t="s">
+      <c r="H297" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="I297" s="6" t="s">
+      <c r="I297" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="J297" s="6" t="s">
+      <c r="J297" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="K297" s="6" t="s">
+      <c r="K297" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="L297" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="M297" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="N297" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="O297" s="8">
-        <v>555</v>
-      </c>
-      <c r="P297" s="8">
+      <c r="L297" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M297" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N297" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O297" s="4">
+        <v>2590</v>
+      </c>
+      <c r="P297" s="4">
         <v>27.74</v>
       </c>
-      <c r="Q297" s="9">
-        <v>15395.7</v>
-      </c>
-      <c r="R297" s="9">
-        <v>0</v>
-      </c>
-      <c r="S297" s="9">
-        <v>15395.7</v>
-      </c>
-      <c r="T297" s="9">
-        <v>0</v>
-      </c>
-      <c r="U297" s="9">
-        <v>0</v>
-      </c>
-      <c r="V297" s="6" t="s">
+      <c r="Q297" s="5">
+        <v>71846.600000000006</v>
+      </c>
+      <c r="R297" s="5">
+        <v>0</v>
+      </c>
+      <c r="S297" s="5">
+        <v>71846.600000000006</v>
+      </c>
+      <c r="T297" s="5">
+        <v>0</v>
+      </c>
+      <c r="U297" s="5">
+        <v>0</v>
+      </c>
+      <c r="V297" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="W297" s="6" t="s">
+      <c r="W297" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="X297" s="6" t="s">
+      <c r="X297" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="Y297" s="6" t="s">
-        <v>1265</v>
-      </c>
-      <c r="Z297" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA297" s="6" t="s">
+      <c r="Y297" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="Z297" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA297" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AB297" s="6" t="s">
+      <c r="AB297" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AC297" s="6" t="s">
+      <c r="AC297" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD297" s="6" t="s">
+      <c r="AD297" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="AE297" s="6" t="s">
+      <c r="AE297" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AF297" s="6" t="s">
+      <c r="AF297" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AG297" s="9">
-        <v>0</v>
-      </c>
-      <c r="AH297" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI297" s="9">
-        <v>0</v>
-      </c>
-      <c r="AJ297" s="8">
+      <c r="AG297" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH297" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI297" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ297" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="298" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A298" s="2" t="s">
+      <c r="A298" s="6" t="s">
         <v>1264</v>
       </c>
-      <c r="B298" s="2" t="s">
+      <c r="B298" s="6" t="s">
         <v>1264</v>
       </c>
-      <c r="C298" s="2" t="s">
+      <c r="C298" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D298" s="3">
+      <c r="D298" s="7">
         <v>46106</v>
       </c>
-      <c r="E298" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="F298" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="G298" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="H298" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="I298" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="J298" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="K298" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="L298" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="M298" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="N298" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="O298" s="4">
-        <v>2590</v>
-      </c>
-      <c r="P298" s="4">
-        <v>27.74</v>
-      </c>
-      <c r="Q298" s="5">
-        <v>71846.600000000006</v>
-      </c>
-      <c r="R298" s="5">
-        <v>0</v>
-      </c>
-      <c r="S298" s="5">
-        <v>71846.600000000006</v>
-      </c>
-      <c r="T298" s="5">
-        <v>0</v>
-      </c>
-      <c r="U298" s="5">
-        <v>0</v>
-      </c>
-      <c r="V298" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="W298" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="X298" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="Y298" s="2" t="s">
+      <c r="E298" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F298" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G298" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H298" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="I298" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="J298" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="K298" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="L298" s="6" t="s">
+        <v>859</v>
+      </c>
+      <c r="M298" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="N298" s="6" t="s">
+        <v>860</v>
+      </c>
+      <c r="O298" s="8">
+        <v>680</v>
+      </c>
+      <c r="P298" s="8">
+        <v>22.55</v>
+      </c>
+      <c r="Q298" s="9">
+        <v>15334</v>
+      </c>
+      <c r="R298" s="9">
+        <v>498.36</v>
+      </c>
+      <c r="S298" s="9">
+        <v>15832.36</v>
+      </c>
+      <c r="T298" s="9">
+        <v>15334</v>
+      </c>
+      <c r="U298" s="9">
+        <v>2760.12</v>
+      </c>
+      <c r="V298" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="W298" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="X298" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y298" s="6" t="s">
         <v>1265</v>
       </c>
-      <c r="Z298" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA298" s="2" t="s">
+      <c r="Z298" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA298" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AB298" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AC298" s="2" t="s">
+      <c r="AB298" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC298" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="AD298" s="2" t="s">
+      <c r="AD298" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="AE298" s="2" t="s">
+      <c r="AE298" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="AF298" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AG298" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH298" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI298" s="5">
-        <v>0</v>
-      </c>
-      <c r="AJ298" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="299" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A299" s="6" t="s">
-        <v>1266</v>
-      </c>
-      <c r="B299" s="6" t="s">
-        <v>1266</v>
-      </c>
-      <c r="C299" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D299" s="7">
-        <v>46106</v>
-      </c>
-      <c r="E299" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F299" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="G299" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="H299" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="I299" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="J299" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="K299" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="L299" s="6" t="s">
-        <v>859</v>
-      </c>
-      <c r="M299" s="6" t="s">
-        <v>393</v>
-      </c>
-      <c r="N299" s="6" t="s">
-        <v>860</v>
-      </c>
-      <c r="O299" s="8">
-        <v>680</v>
-      </c>
-      <c r="P299" s="8">
-        <v>22.55</v>
-      </c>
-      <c r="Q299" s="9">
-        <v>15334</v>
-      </c>
-      <c r="R299" s="9">
-        <v>498.36</v>
-      </c>
-      <c r="S299" s="9">
-        <v>15832.36</v>
-      </c>
-      <c r="T299" s="9">
-        <v>15334</v>
-      </c>
-      <c r="U299" s="9">
-        <v>2760.12</v>
-      </c>
-      <c r="V299" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="W299" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="X299" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y299" s="6" t="s">
-        <v>1267</v>
-      </c>
-      <c r="Z299" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA299" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB299" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC299" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD299" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="AE299" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF299" s="6" t="s">
+      <c r="AF298" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="AG299" s="9">
-        <v>0</v>
-      </c>
-      <c r="AH299" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI299" s="9">
+      <c r="AG298" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH298" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI298" s="9">
         <v>18</v>
       </c>
-      <c r="AJ299" s="8">
+      <c r="AJ298" s="8">
         <v>7570.2835999999998</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AJ298" xr:uid="{5B3DA891-CC25-4139-B353-C23D51C96611}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -38164,13 +38053,13 @@
     </row>
     <row r="2" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D2" s="3">
         <v>46024</v>
@@ -38182,10 +38071,10 @@
         <v>39</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>42</v>
@@ -38197,13 +38086,13 @@
         <v>440</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>1200</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="O2" s="4">
         <v>50</v>
@@ -38227,16 +38116,16 @@
         <v>39.06</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>50</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="Z2" s="2" t="s">
         <v>52</v>
@@ -38274,13 +38163,13 @@
     </row>
     <row r="3" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D3" s="7">
         <v>46027</v>
@@ -38292,10 +38181,10 @@
         <v>61</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>163</v>
@@ -38307,13 +38196,13 @@
         <v>632</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="M3" s="6" t="s">
         <v>648</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="O3" s="8">
         <v>1001</v>
@@ -38346,7 +38235,7 @@
         <v>50</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="Z3" s="6" t="s">
         <v>52</v>
@@ -38384,13 +38273,13 @@
     </row>
     <row r="4" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D4" s="3">
         <v>46027</v>
@@ -38402,10 +38291,10 @@
         <v>61</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>152</v>
@@ -38417,13 +38306,13 @@
         <v>342</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="O4" s="4">
         <v>600</v>
@@ -38447,16 +38336,16 @@
         <v>355.68</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>50</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="Z4" s="2" t="s">
         <v>52</v>
@@ -38494,13 +38383,13 @@
     </row>
     <row r="5" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D5" s="7">
         <v>46029</v>
@@ -38512,10 +38401,10 @@
         <v>212</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>139</v>
@@ -38524,7 +38413,7 @@
         <v>140</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>52</v>
@@ -38566,7 +38455,7 @@
         <v>87</v>
       </c>
       <c r="Y5" s="6" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="Z5" s="6" t="s">
         <v>52</v>
@@ -38604,13 +38493,13 @@
     </row>
     <row r="6" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D6" s="3">
         <v>46029</v>
@@ -38622,10 +38511,10 @@
         <v>212</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>139</v>
@@ -38634,7 +38523,7 @@
         <v>140</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>52</v>
@@ -38676,7 +38565,7 @@
         <v>87</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="Z6" s="2" t="s">
         <v>52</v>
@@ -38714,13 +38603,13 @@
     </row>
     <row r="7" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D7" s="7">
         <v>46029</v>
@@ -38738,22 +38627,22 @@
         <v>386</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="K7" s="6" t="s">
         <v>1058</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="O7" s="8">
         <v>1000</v>
@@ -38786,7 +38675,7 @@
         <v>50</v>
       </c>
       <c r="Y7" s="6" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="Z7" s="6" t="s">
         <v>52</v>
@@ -38824,13 +38713,13 @@
     </row>
     <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D8" s="3">
         <v>46036</v>
@@ -38842,10 +38731,10 @@
         <v>61</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>163</v>
@@ -38857,13 +38746,13 @@
         <v>632</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="O8" s="4">
         <v>1001</v>
@@ -38896,7 +38785,7 @@
         <v>50</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="Z8" s="2" t="s">
         <v>52</v>
@@ -38934,13 +38823,13 @@
     </row>
     <row r="9" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D9" s="7">
         <v>46037</v>
@@ -38952,10 +38841,10 @@
         <v>61</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>163</v>
@@ -38967,13 +38856,13 @@
         <v>417</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>1041</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="O9" s="8">
         <v>1000</v>
@@ -39006,7 +38895,7 @@
         <v>50</v>
       </c>
       <c r="Y9" s="6" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Z9" s="6" t="s">
         <v>52</v>
@@ -39044,13 +38933,13 @@
     </row>
     <row r="10" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D10" s="3">
         <v>46037</v>
@@ -39062,10 +38951,10 @@
         <v>39</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>139</v>
@@ -39077,13 +38966,13 @@
         <v>782</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="O10" s="4">
         <v>300</v>
@@ -39116,7 +39005,7 @@
         <v>50</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="Z10" s="2" t="s">
         <v>52</v>
@@ -39154,13 +39043,13 @@
     </row>
     <row r="11" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D11" s="7">
         <v>46037</v>
@@ -39172,10 +39061,10 @@
         <v>39</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>42</v>
@@ -39187,13 +39076,13 @@
         <v>300</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="O11" s="8">
         <v>25</v>
@@ -39226,7 +39115,7 @@
         <v>50</v>
       </c>
       <c r="Y11" s="6" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="Z11" s="6" t="s">
         <v>52</v>
@@ -39264,13 +39153,13 @@
     </row>
     <row r="12" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D12" s="3">
         <v>46041</v>
@@ -39282,10 +39171,10 @@
         <v>212</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>139</v>
@@ -39294,7 +39183,7 @@
         <v>140</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>52</v>
@@ -39336,7 +39225,7 @@
         <v>87</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="Z12" s="2" t="s">
         <v>52</v>
@@ -39351,10 +39240,10 @@
         <v>55</v>
       </c>
       <c r="AD12" s="2" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="AF12" s="2" t="s">
         <v>442</v>
@@ -39374,13 +39263,13 @@
     </row>
     <row r="13" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D13" s="7">
         <v>46042</v>
@@ -39398,22 +39287,22 @@
         <v>386</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>446</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="O13" s="8">
         <v>2000</v>
@@ -39446,7 +39335,7 @@
         <v>50</v>
       </c>
       <c r="Y13" s="6" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="Z13" s="6" t="s">
         <v>52</v>
@@ -39484,13 +39373,13 @@
     </row>
     <row r="14" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D14" s="3">
         <v>46042</v>
@@ -39514,16 +39403,16 @@
         <v>294</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="O14" s="4">
         <v>6000</v>
@@ -39547,16 +39436,16 @@
         <v>12873.6</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="X14" s="2" t="s">
         <v>50</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="Z14" s="2" t="s">
         <v>52</v>
@@ -39571,10 +39460,10 @@
         <v>298</v>
       </c>
       <c r="AD14" s="2" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="AE14" s="2" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="AF14" s="2" t="s">
         <v>77</v>
@@ -39594,13 +39483,13 @@
     </row>
     <row r="15" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D15" s="7">
         <v>46042</v>
@@ -39612,10 +39501,10 @@
         <v>212</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>139</v>
@@ -39666,7 +39555,7 @@
         <v>87</v>
       </c>
       <c r="Y15" s="6" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="Z15" s="6" t="s">
         <v>52</v>
@@ -39687,7 +39576,7 @@
         <v>518</v>
       </c>
       <c r="AF15" s="6" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="AG15" s="9">
         <v>0</v>
@@ -39704,13 +39593,13 @@
     </row>
     <row r="16" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D16" s="3">
         <v>46042</v>
@@ -39722,10 +39611,10 @@
         <v>212</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>139</v>
@@ -39776,7 +39665,7 @@
         <v>87</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="Z16" s="2" t="s">
         <v>52</v>
@@ -39797,7 +39686,7 @@
         <v>518</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="AG16" s="5">
         <v>0</v>
@@ -39814,13 +39703,13 @@
     </row>
     <row r="17" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D17" s="7">
         <v>46043</v>
@@ -39847,13 +39736,13 @@
         <v>417</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="O17" s="8">
         <v>1000</v>
@@ -39886,7 +39775,7 @@
         <v>50</v>
       </c>
       <c r="Y17" s="6" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="Z17" s="6" t="s">
         <v>52</v>
@@ -39924,28 +39813,28 @@
     </row>
     <row r="18" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D18" s="3">
         <v>46045</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>139</v>
@@ -39957,13 +39846,13 @@
         <v>628</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="O18" s="4">
         <v>2000</v>
@@ -39987,16 +39876,16 @@
         <v>0</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="X18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="Z18" s="2" t="s">
         <v>52</v>
@@ -40034,28 +39923,28 @@
     </row>
     <row r="19" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D19" s="7">
         <v>46045</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>139</v>
@@ -40067,13 +39956,13 @@
         <v>631</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="O19" s="8">
         <v>11725</v>
@@ -40097,16 +39986,16 @@
         <v>0</v>
       </c>
       <c r="V19" s="6" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="W19" s="6" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="X19" s="6" t="s">
         <v>87</v>
       </c>
       <c r="Y19" s="6" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="Z19" s="6" t="s">
         <v>52</v>
@@ -40144,28 +40033,28 @@
     </row>
     <row r="20" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D20" s="3">
         <v>46045</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>139</v>
@@ -40177,13 +40066,13 @@
         <v>632</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="O20" s="4">
         <v>2925</v>
@@ -40207,16 +40096,16 @@
         <v>0</v>
       </c>
       <c r="V20" s="2" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="X20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="Z20" s="2" t="s">
         <v>52</v>
@@ -40254,28 +40143,28 @@
     </row>
     <row r="21" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D21" s="7">
         <v>46045</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>139</v>
@@ -40287,13 +40176,13 @@
         <v>633</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>652</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="O21" s="8">
         <v>2925</v>
@@ -40317,16 +40206,16 @@
         <v>0</v>
       </c>
       <c r="V21" s="6" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="W21" s="6" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="X21" s="6" t="s">
         <v>87</v>
       </c>
       <c r="Y21" s="6" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="Z21" s="6" t="s">
         <v>52</v>
@@ -40364,28 +40253,28 @@
     </row>
     <row r="22" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D22" s="3">
         <v>46045</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>139</v>
@@ -40397,13 +40286,13 @@
         <v>465</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>1109</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="O22" s="4">
         <v>2400</v>
@@ -40427,16 +40316,16 @@
         <v>0</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="X22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="Z22" s="2" t="s">
         <v>52</v>
@@ -40474,28 +40363,28 @@
     </row>
     <row r="23" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D23" s="7">
         <v>46045</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="I23" s="6" t="s">
         <v>139</v>
@@ -40507,13 +40396,13 @@
         <v>465</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>1175</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="O23" s="8">
         <v>1800</v>
@@ -40537,16 +40426,16 @@
         <v>0</v>
       </c>
       <c r="V23" s="6" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="W23" s="6" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="X23" s="6" t="s">
         <v>87</v>
       </c>
       <c r="Y23" s="6" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="Z23" s="6" t="s">
         <v>52</v>
@@ -40584,28 +40473,28 @@
     </row>
     <row r="24" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D24" s="3">
         <v>46045</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>139</v>
@@ -40617,13 +40506,13 @@
         <v>634</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="O24" s="4">
         <v>1400</v>
@@ -40647,16 +40536,16 @@
         <v>0</v>
       </c>
       <c r="V24" s="2" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="X24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="Z24" s="2" t="s">
         <v>52</v>
@@ -40694,13 +40583,13 @@
     </row>
     <row r="25" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D25" s="7">
         <v>46048</v>
@@ -40727,13 +40616,13 @@
         <v>417</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="O25" s="8">
         <v>5000</v>
@@ -40766,7 +40655,7 @@
         <v>50</v>
       </c>
       <c r="Y25" s="6" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="Z25" s="6" t="s">
         <v>52</v>
@@ -40804,13 +40693,13 @@
     </row>
     <row r="26" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D26" s="3">
         <v>46048</v>
@@ -40822,10 +40711,10 @@
         <v>39</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>139</v>
@@ -40837,13 +40726,13 @@
         <v>782</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="O26" s="4">
         <v>300</v>
@@ -40876,7 +40765,7 @@
         <v>50</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="Z26" s="2" t="s">
         <v>52</v>
@@ -40914,13 +40803,13 @@
     </row>
     <row r="27" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D27" s="7">
         <v>46048</v>
@@ -40932,10 +40821,10 @@
         <v>61</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>163</v>
@@ -40947,13 +40836,13 @@
         <v>632</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>648</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="O27" s="8">
         <v>611</v>
@@ -40986,7 +40875,7 @@
         <v>50</v>
       </c>
       <c r="Y27" s="6" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="Z27" s="6" t="s">
         <v>52</v>
@@ -41024,13 +40913,13 @@
     </row>
     <row r="28" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D28" s="3">
         <v>46048</v>
@@ -41042,10 +40931,10 @@
         <v>61</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>163</v>
@@ -41054,16 +40943,16 @@
         <v>164</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="O28" s="4">
         <v>700</v>
@@ -41096,7 +40985,7 @@
         <v>50</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="Z28" s="2" t="s">
         <v>52</v>
@@ -41111,10 +41000,10 @@
         <v>55</v>
       </c>
       <c r="AD28" s="2" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="AE28" s="2" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="AF28" s="2" t="s">
         <v>77</v>
@@ -41134,13 +41023,13 @@
     </row>
     <row r="29" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D29" s="7">
         <v>46048</v>
@@ -41152,10 +41041,10 @@
         <v>212</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="I29" s="6" t="s">
         <v>139</v>
@@ -41206,7 +41095,7 @@
         <v>87</v>
       </c>
       <c r="Y29" s="6" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="Z29" s="6" t="s">
         <v>52</v>
@@ -41227,7 +41116,7 @@
         <v>57</v>
       </c>
       <c r="AF29" s="6" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="AG29" s="9">
         <v>0</v>
@@ -41244,13 +41133,13 @@
     </row>
     <row r="30" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D30" s="3">
         <v>46049</v>
@@ -41262,10 +41151,10 @@
         <v>212</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>139</v>
@@ -41316,7 +41205,7 @@
         <v>87</v>
       </c>
       <c r="Y30" s="2" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="Z30" s="2" t="s">
         <v>52</v>
@@ -41354,13 +41243,13 @@
     </row>
     <row r="31" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D31" s="7">
         <v>46049</v>
@@ -41372,10 +41261,10 @@
         <v>212</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="I31" s="6" t="s">
         <v>139</v>
@@ -41426,7 +41315,7 @@
         <v>87</v>
       </c>
       <c r="Y31" s="6" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="Z31" s="6" t="s">
         <v>52</v>
@@ -41464,13 +41353,13 @@
     </row>
     <row r="32" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D32" s="3">
         <v>46050</v>
@@ -41488,22 +41377,22 @@
         <v>386</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>446</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>448</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="O32" s="4">
         <v>1000</v>
@@ -41536,7 +41425,7 @@
         <v>50</v>
       </c>
       <c r="Y32" s="2" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="Z32" s="2" t="s">
         <v>52</v>
@@ -41574,13 +41463,13 @@
     </row>
     <row r="33" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D33" s="7">
         <v>46050</v>
@@ -41598,22 +41487,22 @@
         <v>386</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>446</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="O33" s="8">
         <v>1000</v>
@@ -41646,7 +41535,7 @@
         <v>50</v>
       </c>
       <c r="Y33" s="6" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="Z33" s="6" t="s">
         <v>52</v>
@@ -41684,13 +41573,13 @@
     </row>
     <row r="34" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D34" s="3">
         <v>46050</v>
@@ -41702,10 +41591,10 @@
         <v>212</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>139</v>
@@ -41756,7 +41645,7 @@
         <v>87</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="Z34" s="2" t="s">
         <v>52</v>
@@ -41794,13 +41683,13 @@
     </row>
     <row r="35" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D35" s="7">
         <v>46051</v>
@@ -41812,10 +41701,10 @@
         <v>39</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>42</v>
@@ -41827,13 +41716,13 @@
         <v>632</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>648</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="O35" s="8">
         <v>26</v>
@@ -41866,7 +41755,7 @@
         <v>50</v>
       </c>
       <c r="Y35" s="6" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="Z35" s="6" t="s">
         <v>52</v>
@@ -41904,13 +41793,13 @@
     </row>
     <row r="36" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D36" s="3">
         <v>46052</v>
@@ -41922,10 +41811,10 @@
         <v>61</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>163</v>
@@ -41937,13 +41826,13 @@
         <v>632</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="O36" s="4">
         <v>507</v>
@@ -41976,7 +41865,7 @@
         <v>50</v>
       </c>
       <c r="Y36" s="2" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="Z36" s="2" t="s">
         <v>52</v>
@@ -42014,13 +41903,13 @@
     </row>
     <row r="37" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D37" s="7">
         <v>46052</v>
@@ -42044,16 +41933,16 @@
         <v>164</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="O37" s="8">
         <v>500</v>
@@ -42086,7 +41975,7 @@
         <v>50</v>
       </c>
       <c r="Y37" s="6" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="Z37" s="6" t="s">
         <v>52</v>
@@ -42124,13 +42013,13 @@
     </row>
     <row r="38" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D38" s="3">
         <v>46052</v>
@@ -42142,10 +42031,10 @@
         <v>39</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>139</v>
@@ -42157,13 +42046,13 @@
         <v>782</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="O38" s="4">
         <v>300</v>
@@ -42196,7 +42085,7 @@
         <v>50</v>
       </c>
       <c r="Y38" s="2" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>52</v>
@@ -42234,13 +42123,13 @@
     </row>
     <row r="39" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D39" s="7">
         <v>46055</v>
@@ -42252,10 +42141,10 @@
         <v>212</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="I39" s="6" t="s">
         <v>139</v>
@@ -42264,7 +42153,7 @@
         <v>140</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="L39" s="6" t="s">
         <v>52</v>
@@ -42306,7 +42195,7 @@
         <v>87</v>
       </c>
       <c r="Y39" s="6" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="Z39" s="6" t="s">
         <v>52</v>
@@ -42344,13 +42233,13 @@
     </row>
     <row r="40" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D40" s="3">
         <v>46057</v>
@@ -42362,10 +42251,10 @@
         <v>61</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>163</v>
@@ -42377,13 +42266,13 @@
         <v>632</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="O40" s="4">
         <v>507</v>
@@ -42416,7 +42305,7 @@
         <v>50</v>
       </c>
       <c r="Y40" s="2" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="Z40" s="2" t="s">
         <v>52</v>
@@ -42454,13 +42343,13 @@
     </row>
     <row r="41" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D41" s="7">
         <v>46057</v>
@@ -42478,22 +42367,22 @@
         <v>386</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>446</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="N41" s="6" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="O41" s="8">
         <v>2000</v>
@@ -42526,7 +42415,7 @@
         <v>50</v>
       </c>
       <c r="Y41" s="6" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="Z41" s="6" t="s">
         <v>52</v>
@@ -42564,13 +42453,13 @@
     </row>
     <row r="42" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D42" s="3">
         <v>46058</v>
@@ -42582,10 +42471,10 @@
         <v>61</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>163</v>
@@ -42597,13 +42486,13 @@
         <v>632</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="O42" s="4">
         <v>507</v>
@@ -42636,7 +42525,7 @@
         <v>50</v>
       </c>
       <c r="Y42" s="2" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="Z42" s="2" t="s">
         <v>52</v>
@@ -42674,13 +42563,13 @@
     </row>
     <row r="43" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D43" s="7">
         <v>46058</v>
@@ -42692,10 +42581,10 @@
         <v>61</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="I43" s="6" t="s">
         <v>163</v>
@@ -42707,13 +42596,13 @@
         <v>417</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="O43" s="8">
         <v>1800</v>
@@ -42746,7 +42635,7 @@
         <v>50</v>
       </c>
       <c r="Y43" s="6" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="Z43" s="6" t="s">
         <v>52</v>
@@ -42784,13 +42673,13 @@
     </row>
     <row r="44" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D44" s="3">
         <v>46059</v>
@@ -42802,10 +42691,10 @@
         <v>39</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>42</v>
@@ -42817,13 +42706,13 @@
         <v>782</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="O44" s="4">
         <v>500</v>
@@ -42856,7 +42745,7 @@
         <v>50</v>
       </c>
       <c r="Y44" s="2" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="Z44" s="2" t="s">
         <v>52</v>
@@ -42894,13 +42783,13 @@
     </row>
     <row r="45" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D45" s="7">
         <v>46059</v>
@@ -42912,10 +42801,10 @@
         <v>39</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="I45" s="6" t="s">
         <v>42</v>
@@ -42927,13 +42816,13 @@
         <v>417</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="O45" s="8">
         <v>200</v>
@@ -42966,7 +42855,7 @@
         <v>50</v>
       </c>
       <c r="Y45" s="6" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="Z45" s="6" t="s">
         <v>52</v>
@@ -43004,28 +42893,28 @@
     </row>
     <row r="46" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D46" s="3">
         <v>46063</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>267</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>139</v>
@@ -43034,7 +42923,7 @@
         <v>140</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>52</v>
@@ -43076,7 +42965,7 @@
         <v>52</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="Z46" s="2" t="s">
         <v>52</v>
@@ -43091,10 +42980,10 @@
         <v>74</v>
       </c>
       <c r="AD46" s="2" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="AE46" s="2" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="AF46" s="2" t="s">
         <v>52</v>
@@ -43114,13 +43003,13 @@
     </row>
     <row r="47" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D47" s="7">
         <v>46064</v>
@@ -43132,10 +43021,10 @@
         <v>61</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="I47" s="6" t="s">
         <v>139</v>
@@ -43147,13 +43036,13 @@
         <v>417</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="O47" s="8">
         <v>1000</v>
@@ -43186,7 +43075,7 @@
         <v>50</v>
       </c>
       <c r="Y47" s="6" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="Z47" s="6" t="s">
         <v>52</v>
@@ -43224,13 +43113,13 @@
     </row>
     <row r="48" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D48" s="3">
         <v>46064</v>
@@ -43248,22 +43137,22 @@
         <v>386</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>446</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="O48" s="4">
         <v>1000</v>
@@ -43296,7 +43185,7 @@
         <v>50</v>
       </c>
       <c r="Y48" s="2" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="Z48" s="2" t="s">
         <v>52</v>
@@ -43334,13 +43223,13 @@
     </row>
     <row r="49" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D49" s="7">
         <v>46064</v>
@@ -43358,22 +43247,22 @@
         <v>386</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>446</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="O49" s="8">
         <v>1000</v>
@@ -43406,7 +43295,7 @@
         <v>50</v>
       </c>
       <c r="Y49" s="6" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="Z49" s="6" t="s">
         <v>52</v>
@@ -43444,13 +43333,13 @@
     </row>
     <row r="50" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D50" s="3">
         <v>46066</v>
@@ -43462,10 +43351,10 @@
         <v>61</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>163</v>
@@ -43477,13 +43366,13 @@
         <v>632</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="M50" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="O50" s="4">
         <v>507</v>
@@ -43516,7 +43405,7 @@
         <v>50</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="Z50" s="2" t="s">
         <v>52</v>
@@ -43554,13 +43443,13 @@
     </row>
     <row r="51" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D51" s="7">
         <v>46071</v>
@@ -43584,16 +43473,16 @@
         <v>164</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="N51" s="6" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="O51" s="8">
         <v>500</v>
@@ -43626,7 +43515,7 @@
         <v>50</v>
       </c>
       <c r="Y51" s="6" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="Z51" s="6" t="s">
         <v>52</v>
@@ -43641,10 +43530,10 @@
         <v>111</v>
       </c>
       <c r="AD51" s="6" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="AE51" s="6" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="AF51" s="6" t="s">
         <v>77</v>
@@ -43664,13 +43553,13 @@
     </row>
     <row r="52" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D52" s="3">
         <v>46071</v>
@@ -43682,10 +43571,10 @@
         <v>61</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>139</v>
@@ -43697,13 +43586,13 @@
         <v>446</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="O52" s="4">
         <v>200</v>
@@ -43736,7 +43625,7 @@
         <v>50</v>
       </c>
       <c r="Y52" s="2" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="Z52" s="2" t="s">
         <v>52</v>
@@ -43774,13 +43663,13 @@
     </row>
     <row r="53" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D53" s="7">
         <v>46072</v>
@@ -43792,10 +43681,10 @@
         <v>39</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="I53" s="6" t="s">
         <v>42</v>
@@ -43807,13 +43696,13 @@
         <v>440</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>1200</v>
       </c>
       <c r="N53" s="6" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="O53" s="8">
         <v>50</v>
@@ -43837,16 +43726,16 @@
         <v>0</v>
       </c>
       <c r="V53" s="6" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="W53" s="6" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="X53" s="6" t="s">
         <v>50</v>
       </c>
       <c r="Y53" s="6" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="Z53" s="6" t="s">
         <v>52</v>
@@ -43884,13 +43773,13 @@
     </row>
     <row r="54" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D54" s="3">
         <v>46072</v>
@@ -43902,10 +43791,10 @@
         <v>61</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>163</v>
@@ -43917,13 +43806,13 @@
         <v>417</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="O54" s="4">
         <v>1600</v>
@@ -43956,7 +43845,7 @@
         <v>50</v>
       </c>
       <c r="Y54" s="2" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="Z54" s="2" t="s">
         <v>52</v>
@@ -43994,13 +43883,13 @@
     </row>
     <row r="55" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D55" s="7">
         <v>46072</v>
@@ -44012,10 +43901,10 @@
         <v>39</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="I55" s="6" t="s">
         <v>42</v>
@@ -44027,13 +43916,13 @@
         <v>446</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="M55" s="6" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="N55" s="6" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="O55" s="8">
         <v>500</v>
@@ -44066,7 +43955,7 @@
         <v>50</v>
       </c>
       <c r="Y55" s="6" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="Z55" s="6" t="s">
         <v>52</v>
@@ -44104,13 +43993,13 @@
     </row>
     <row r="56" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D56" s="3">
         <v>46076</v>
@@ -44122,10 +44011,10 @@
         <v>61</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>163</v>
@@ -44137,13 +44026,13 @@
         <v>417</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="O56" s="4">
         <v>1700</v>
@@ -44176,7 +44065,7 @@
         <v>50</v>
       </c>
       <c r="Y56" s="2" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="Z56" s="2" t="s">
         <v>52</v>
@@ -44214,13 +44103,13 @@
     </row>
     <row r="57" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D57" s="7">
         <v>46077</v>
@@ -44244,16 +44133,16 @@
         <v>164</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="O57" s="8">
         <v>500</v>
@@ -44286,7 +44175,7 @@
         <v>50</v>
       </c>
       <c r="Y57" s="6" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="Z57" s="6" t="s">
         <v>52</v>
@@ -44324,13 +44213,13 @@
     </row>
     <row r="58" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D58" s="3">
         <v>46077</v>
@@ -44354,16 +44243,16 @@
         <v>164</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="O58" s="4">
         <v>500</v>
@@ -44396,7 +44285,7 @@
         <v>50</v>
       </c>
       <c r="Y58" s="2" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="Z58" s="2" t="s">
         <v>52</v>
@@ -44411,10 +44300,10 @@
         <v>111</v>
       </c>
       <c r="AD58" s="2" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="AE58" s="2" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="AF58" s="2" t="s">
         <v>77</v>
@@ -44434,13 +44323,13 @@
     </row>
     <row r="59" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D59" s="7">
         <v>46078</v>
@@ -44452,10 +44341,10 @@
         <v>39</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="I59" s="6" t="s">
         <v>139</v>
@@ -44467,13 +44356,13 @@
         <v>782</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="O59" s="8">
         <v>225</v>
@@ -44506,7 +44395,7 @@
         <v>50</v>
       </c>
       <c r="Y59" s="6" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="Z59" s="6" t="s">
         <v>52</v>
@@ -44544,13 +44433,13 @@
     </row>
     <row r="60" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D60" s="3">
         <v>46079</v>
@@ -44577,13 +44466,13 @@
         <v>417</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="O60" s="4">
         <v>5000</v>
@@ -44616,7 +44505,7 @@
         <v>50</v>
       </c>
       <c r="Y60" s="2" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="Z60" s="2" t="s">
         <v>52</v>
@@ -44654,13 +44543,13 @@
     </row>
     <row r="61" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D61" s="7">
         <v>46079</v>
@@ -44687,13 +44576,13 @@
         <v>1058</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="O61" s="8">
         <v>12000</v>
@@ -44726,7 +44615,7 @@
         <v>50</v>
       </c>
       <c r="Y61" s="6" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="Z61" s="6" t="s">
         <v>52</v>
@@ -44764,13 +44653,13 @@
     </row>
     <row r="62" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D62" s="3">
         <v>46085</v>
@@ -44797,13 +44686,13 @@
         <v>633</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>652</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="O62" s="4">
         <v>5005</v>
@@ -44836,7 +44725,7 @@
         <v>50</v>
       </c>
       <c r="Y62" s="2" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="Z62" s="2" t="s">
         <v>52</v>
@@ -44874,13 +44763,13 @@
     </row>
     <row r="63" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D63" s="7">
         <v>46085</v>
@@ -44904,16 +44793,16 @@
         <v>164</v>
       </c>
       <c r="K63" s="6" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="M63" s="6" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="O63" s="8">
         <v>500</v>
@@ -44946,7 +44835,7 @@
         <v>50</v>
       </c>
       <c r="Y63" s="6" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="Z63" s="6" t="s">
         <v>52</v>
@@ -44984,13 +44873,13 @@
     </row>
     <row r="64" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D64" s="3">
         <v>46085</v>
@@ -45014,16 +44903,16 @@
         <v>164</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="O64" s="4">
         <v>500</v>
@@ -45056,7 +44945,7 @@
         <v>50</v>
       </c>
       <c r="Y64" s="2" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="Z64" s="2" t="s">
         <v>52</v>
@@ -45071,10 +44960,10 @@
         <v>111</v>
       </c>
       <c r="AD64" s="2" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="AE64" s="2" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="AF64" s="2" t="s">
         <v>77</v>
@@ -45094,13 +44983,13 @@
     </row>
     <row r="65" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="6" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D65" s="7">
         <v>46085</v>
@@ -45112,10 +45001,10 @@
         <v>39</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="I65" s="6" t="s">
         <v>163</v>
@@ -45127,13 +45016,13 @@
         <v>154</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="O65" s="8">
         <v>3700</v>
@@ -45166,7 +45055,7 @@
         <v>50</v>
       </c>
       <c r="Y65" s="6" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="Z65" s="6" t="s">
         <v>52</v>
@@ -45204,13 +45093,13 @@
     </row>
     <row r="66" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D66" s="3">
         <v>46085</v>
@@ -45222,10 +45111,10 @@
         <v>39</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>139</v>
@@ -45234,7 +45123,7 @@
         <v>140</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>52</v>
@@ -45276,7 +45165,7 @@
         <v>52</v>
       </c>
       <c r="Y66" s="2" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="Z66" s="2" t="s">
         <v>52</v>
@@ -45291,10 +45180,10 @@
         <v>298</v>
       </c>
       <c r="AD66" s="2" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="AE66" s="2" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="AF66" s="2" t="s">
         <v>52</v>
@@ -45314,13 +45203,13 @@
     </row>
     <row r="67" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D67" s="7">
         <v>46091</v>
@@ -45347,13 +45236,13 @@
         <v>417</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="O67" s="8">
         <v>5000</v>
@@ -45386,7 +45275,7 @@
         <v>50</v>
       </c>
       <c r="Y67" s="6" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="Z67" s="6" t="s">
         <v>52</v>
@@ -45424,13 +45313,13 @@
     </row>
     <row r="68" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D68" s="3">
         <v>46091</v>
@@ -45442,10 +45331,10 @@
         <v>39</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>139</v>
@@ -45457,13 +45346,13 @@
         <v>782</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="O68" s="4">
         <v>225</v>
@@ -45496,7 +45385,7 @@
         <v>50</v>
       </c>
       <c r="Y68" s="2" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="Z68" s="2" t="s">
         <v>52</v>
@@ -45534,28 +45423,28 @@
     </row>
     <row r="69" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D69" s="7">
         <v>46092</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="I69" s="6" t="s">
         <v>139</v>
@@ -45567,13 +45456,13 @@
         <v>272</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="M69" s="6" t="s">
         <v>274</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="O69" s="8">
         <v>10000</v>
@@ -45597,16 +45486,16 @@
         <v>3312.29</v>
       </c>
       <c r="V69" s="6" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="W69" s="6" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="X69" s="6" t="s">
         <v>87</v>
       </c>
       <c r="Y69" s="6" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="Z69" s="6" t="s">
         <v>52</v>
@@ -45644,28 +45533,28 @@
     </row>
     <row r="70" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D70" s="3">
         <v>46092</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>139</v>
@@ -45677,13 +45566,13 @@
         <v>417</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="O70" s="4">
         <v>5000</v>
@@ -45707,16 +45596,16 @@
         <v>1559.15</v>
       </c>
       <c r="V70" s="2" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="W70" s="2" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="X70" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y70" s="2" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="Z70" s="2" t="s">
         <v>52</v>
@@ -45754,28 +45643,28 @@
     </row>
     <row r="71" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D71" s="7">
         <v>46092</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="I71" s="6" t="s">
         <v>139</v>
@@ -45787,13 +45676,13 @@
         <v>342</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="M71" s="6" t="s">
         <v>1193</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="O71" s="8">
         <v>8400</v>
@@ -45817,16 +45706,16 @@
         <v>2580.5300000000002</v>
       </c>
       <c r="V71" s="6" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="W71" s="6" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="X71" s="6" t="s">
         <v>87</v>
       </c>
       <c r="Y71" s="6" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="Z71" s="6" t="s">
         <v>52</v>
@@ -45864,28 +45753,28 @@
     </row>
     <row r="72" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D72" s="3">
         <v>46092</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>139</v>
@@ -45897,13 +45786,13 @@
         <v>782</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="M72" s="2" t="s">
         <v>1167</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="O72" s="4">
         <v>2400</v>
@@ -45927,16 +45816,16 @@
         <v>775.1</v>
       </c>
       <c r="V72" s="2" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="W72" s="2" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="X72" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y72" s="2" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="Z72" s="2" t="s">
         <v>52</v>
@@ -45974,13 +45863,13 @@
     </row>
     <row r="73" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="6" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D73" s="7">
         <v>46093</v>
@@ -45992,10 +45881,10 @@
         <v>61</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="I73" s="6" t="s">
         <v>163</v>
@@ -46007,13 +45896,13 @@
         <v>633</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="M73" s="6" t="s">
         <v>652</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="O73" s="8">
         <v>507</v>
@@ -46046,7 +45935,7 @@
         <v>50</v>
       </c>
       <c r="Y73" s="6" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="Z73" s="6" t="s">
         <v>52</v>
@@ -46084,13 +45973,13 @@
     </row>
     <row r="74" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D74" s="3">
         <v>46097</v>
@@ -46108,22 +45997,22 @@
         <v>386</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>446</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="O74" s="4">
         <v>3000</v>
@@ -46156,7 +46045,7 @@
         <v>50</v>
       </c>
       <c r="Y74" s="2" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="Z74" s="2" t="s">
         <v>52</v>
@@ -46194,13 +46083,13 @@
     </row>
     <row r="75" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D75" s="7">
         <v>46098</v>
@@ -46227,13 +46116,13 @@
         <v>300</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="O75" s="8">
         <v>10000</v>
@@ -46257,16 +46146,16 @@
         <v>14724</v>
       </c>
       <c r="V75" s="6" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="W75" s="6" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="X75" s="6" t="s">
         <v>50</v>
       </c>
       <c r="Y75" s="6" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="Z75" s="6" t="s">
         <v>52</v>
@@ -46304,13 +46193,13 @@
     </row>
     <row r="76" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D76" s="3">
         <v>46098</v>
@@ -46322,10 +46211,10 @@
         <v>61</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>163</v>
@@ -46337,13 +46226,13 @@
         <v>632</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="M76" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="O76" s="4">
         <v>507</v>
@@ -46376,7 +46265,7 @@
         <v>50</v>
       </c>
       <c r="Y76" s="2" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="Z76" s="2" t="s">
         <v>52</v>
@@ -46414,13 +46303,13 @@
     </row>
     <row r="77" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="6" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D77" s="7">
         <v>46100</v>
@@ -46447,13 +46336,13 @@
         <v>782</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="O77" s="8">
         <v>10000</v>
@@ -46486,7 +46375,7 @@
         <v>50</v>
       </c>
       <c r="Y77" s="6" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="Z77" s="6" t="s">
         <v>52</v>
@@ -46524,13 +46413,13 @@
     </row>
     <row r="78" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D78" s="3">
         <v>46104</v>
@@ -46557,13 +46446,13 @@
         <v>633</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="M78" s="2" t="s">
         <v>652</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="O78" s="4">
         <v>1170</v>
@@ -46596,7 +46485,7 @@
         <v>50</v>
       </c>
       <c r="Y78" s="2" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="Z78" s="2" t="s">
         <v>52</v>
@@ -46634,13 +46523,13 @@
     </row>
     <row r="79" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="6" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D79" s="7">
         <v>46104</v>
@@ -46667,13 +46556,13 @@
         <v>633</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="O79" s="8">
         <v>2834</v>
@@ -46706,7 +46595,7 @@
         <v>50</v>
       </c>
       <c r="Y79" s="6" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="Z79" s="6" t="s">
         <v>52</v>
@@ -46744,13 +46633,13 @@
     </row>
     <row r="80" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D80" s="3">
         <v>46104</v>
@@ -46774,16 +46663,16 @@
         <v>164</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="O80" s="4">
         <v>1750</v>
@@ -46816,7 +46705,7 @@
         <v>50</v>
       </c>
       <c r="Y80" s="2" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="Z80" s="2" t="s">
         <v>52</v>
@@ -46854,13 +46743,13 @@
     </row>
     <row r="81" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D81" s="7">
         <v>46104</v>
@@ -46884,16 +46773,16 @@
         <v>164</v>
       </c>
       <c r="K81" s="6" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="O81" s="8">
         <v>2000</v>
@@ -46926,7 +46815,7 @@
         <v>50</v>
       </c>
       <c r="Y81" s="6" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="Z81" s="6" t="s">
         <v>52</v>
@@ -46941,10 +46830,10 @@
         <v>111</v>
       </c>
       <c r="AD81" s="6" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="AE81" s="6" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="AF81" s="6" t="s">
         <v>77</v>
@@ -46964,13 +46853,13 @@
     </row>
     <row r="82" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D82" s="3">
         <v>46105</v>
@@ -46982,10 +46871,10 @@
         <v>39</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>42</v>
@@ -46997,13 +46886,13 @@
         <v>300</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="O82" s="4">
         <v>500</v>
@@ -47027,16 +46916,16 @@
         <v>776.4</v>
       </c>
       <c r="V82" s="2" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="W82" s="2" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="X82" s="2" t="s">
         <v>50</v>
       </c>
       <c r="Y82" s="2" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="Z82" s="2" t="s">
         <v>52</v>
@@ -47074,13 +46963,13 @@
     </row>
     <row r="83" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D83" s="7">
         <v>46106</v>
@@ -47092,10 +46981,10 @@
         <v>61</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="I83" s="6" t="s">
         <v>163</v>
@@ -47107,13 +46996,13 @@
         <v>632</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="M83" s="6" t="s">
         <v>648</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="O83" s="8">
         <v>1001</v>
@@ -47146,7 +47035,7 @@
         <v>50</v>
       </c>
       <c r="Y83" s="6" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="Z83" s="6" t="s">
         <v>52</v>
@@ -47184,13 +47073,13 @@
     </row>
     <row r="84" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D84" s="3">
         <v>46106</v>
@@ -47202,10 +47091,10 @@
         <v>39</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>293</v>
@@ -47217,13 +47106,13 @@
         <v>417</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="O84" s="4">
         <v>600</v>
@@ -47256,7 +47145,7 @@
         <v>50</v>
       </c>
       <c r="Y84" s="2" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="Z84" s="2" t="s">
         <v>52</v>
@@ -47293,6 +47182,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AJ84" xr:uid="{39F107AE-E9DE-41AA-B1D9-38E73A1F15CD}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/BASE_KEMPARTS.xlsx
+++ b/BASE_KEMPARTS.xlsx
@@ -5,20 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kempartsquimica-my.sharepoint.com/personal/gustavo_kemparts_com_br/Documents/Área de Trabalho/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dash_kp_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="8_{2A7BC25A-6575-4405-A9BB-E5E283A1D39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5D68E28-DE4D-4567-9192-7D48791FB4F0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B95F4421-11F5-496D-BEE2-C088F322D9DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CF839F49-1F72-448F-9AD3-DB64CDC568DC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{E0F48661-5987-4607-8BE2-1496201A479E}"/>
   </bookViews>
   <sheets>
     <sheet name="FSP" sheetId="1" r:id="rId1"/>
     <sheet name="FSC" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">FSC!$A$1:$AJ$86</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FSP!$A$1:$AJ$316</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">FSC!$A$1:$AJ$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FSP!$A$1:$AJ$323</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10069" uniqueCount="1586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10443" uniqueCount="1617">
   <si>
     <t>Numero</t>
   </si>
@@ -4018,6 +4018,159 @@
     <t>173951</t>
   </si>
   <si>
+    <t>000015640</t>
+  </si>
+  <si>
+    <t>2025.199.11.250615104</t>
+  </si>
+  <si>
+    <t>250615104</t>
+  </si>
+  <si>
+    <t>2025.199.11.</t>
+  </si>
+  <si>
+    <t>174008</t>
+  </si>
+  <si>
+    <t>000015643</t>
+  </si>
+  <si>
+    <t>173981</t>
+  </si>
+  <si>
+    <t>000015644</t>
+  </si>
+  <si>
+    <t>173710</t>
+  </si>
+  <si>
+    <t>000015645</t>
+  </si>
+  <si>
+    <t>173812</t>
+  </si>
+  <si>
+    <t>000015646</t>
+  </si>
+  <si>
+    <t>C00347</t>
+  </si>
+  <si>
+    <t>DACAR QUIMICA DO BRASIL S/A</t>
+  </si>
+  <si>
+    <t>174014</t>
+  </si>
+  <si>
+    <t>000015648</t>
+  </si>
+  <si>
+    <t>173900</t>
+  </si>
+  <si>
+    <t>000015649</t>
+  </si>
+  <si>
+    <t>174018</t>
+  </si>
+  <si>
+    <t>003349</t>
+  </si>
+  <si>
+    <t>2025.357.05.</t>
+  </si>
+  <si>
+    <t>250501</t>
+  </si>
+  <si>
+    <t>2025.357.05.250501</t>
+  </si>
+  <si>
+    <t>ILVA DO BRASIL IND. E COM. LTDA</t>
+  </si>
+  <si>
+    <t>C00071</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>000002528</t>
+  </si>
+  <si>
+    <t>003333</t>
+  </si>
+  <si>
+    <t>TRANS ILHEUS LTDA</t>
+  </si>
+  <si>
+    <t>T00274</t>
+  </si>
+  <si>
+    <t>2024.357.09.</t>
+  </si>
+  <si>
+    <t>241228</t>
+  </si>
+  <si>
+    <t>2024.357.09.241228</t>
+  </si>
+  <si>
+    <t>000002527</t>
+  </si>
+  <si>
+    <t>2024.357.04.</t>
+  </si>
+  <si>
+    <t>2024.357.04.240706</t>
+  </si>
+  <si>
+    <t>2024.357.03.</t>
+  </si>
+  <si>
+    <t>240707</t>
+  </si>
+  <si>
+    <t>2024.357.03.240707</t>
+  </si>
+  <si>
+    <t>003322</t>
+  </si>
+  <si>
+    <t>EXPRESSO BATISTENSE TRANSPORTES LTDA</t>
+  </si>
+  <si>
+    <t>T00223</t>
+  </si>
+  <si>
+    <t>2024.675.04.</t>
+  </si>
+  <si>
+    <t>2024.675.04.202407</t>
+  </si>
+  <si>
+    <t>BOXFLEX COMPONENTES PARA CALCADOS LTDA</t>
+  </si>
+  <si>
+    <t>C00591</t>
+  </si>
+  <si>
+    <t>000002526</t>
+  </si>
+  <si>
+    <t>003318</t>
+  </si>
+  <si>
+    <t>000002525</t>
+  </si>
+  <si>
+    <t>250106</t>
+  </si>
+  <si>
+    <t>2024.357.09.250106</t>
+  </si>
+  <si>
     <t>003328</t>
   </si>
   <si>
@@ -4036,9 +4189,6 @@
     <t>C01097</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>000002524</t>
   </si>
   <si>
@@ -4177,15 +4327,6 @@
     <t>003307</t>
   </si>
   <si>
-    <t>2024.357.09.</t>
-  </si>
-  <si>
-    <t>250106</t>
-  </si>
-  <si>
-    <t>2024.357.09.250106</t>
-  </si>
-  <si>
     <t>000002516</t>
   </si>
   <si>
@@ -4243,12 +4384,6 @@
     <t>T00258</t>
   </si>
   <si>
-    <t>2024.357.04.</t>
-  </si>
-  <si>
-    <t>2024.357.04.240706</t>
-  </si>
-  <si>
     <t>KEMPARTS COMERCIO INTERNACIONAL DE PRODU</t>
   </si>
   <si>
@@ -4264,9 +4399,6 @@
     <t>000002511</t>
   </si>
   <si>
-    <t>2025.357.05.</t>
-  </si>
-  <si>
     <t>2025.357.05.20250903</t>
   </si>
   <si>
@@ -4285,15 +4417,6 @@
     <t>003301</t>
   </si>
   <si>
-    <t>2024.357.03.</t>
-  </si>
-  <si>
-    <t>240707</t>
-  </si>
-  <si>
-    <t>2024.357.03.240707</t>
-  </si>
-  <si>
     <t>000002510</t>
   </si>
   <si>
@@ -4306,12 +4429,6 @@
     <t>003290</t>
   </si>
   <si>
-    <t>BOXFLEX COMPONENTES PARA CALCADOS LTDA</t>
-  </si>
-  <si>
-    <t>C00591</t>
-  </si>
-  <si>
     <t>000002508</t>
   </si>
   <si>
@@ -4420,18 +4537,6 @@
     <t>003274</t>
   </si>
   <si>
-    <t>EXPRESSO BATISTENSE TRANSPORTES LTDA</t>
-  </si>
-  <si>
-    <t>T00223</t>
-  </si>
-  <si>
-    <t>2024.675.04.</t>
-  </si>
-  <si>
-    <t>2024.675.04.202407</t>
-  </si>
-  <si>
     <t>000002486</t>
   </si>
   <si>
@@ -4519,12 +4624,6 @@
     <t>003251</t>
   </si>
   <si>
-    <t>DACAR QUIMICA DO BRASIL S/A</t>
-  </si>
-  <si>
-    <t>C00347</t>
-  </si>
-  <si>
     <t>000002477</t>
   </si>
   <si>
@@ -4742,12 +4841,6 @@
   </si>
   <si>
     <t>003200</t>
-  </si>
-  <si>
-    <t>250501</t>
-  </si>
-  <si>
-    <t>2025.357.05.250501</t>
   </si>
   <si>
     <t>000002437</t>
@@ -5256,48 +5349,48 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83D18634-4744-4B01-A409-8C69F6FBA3B9}">
-  <dimension ref="A1:AJ316"/>
-  <sheetFormatPr defaultColWidth="10.8984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADEADE99-9C44-4269-8B72-FB9410102EA0}">
+  <dimension ref="A1:AJ323"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="59.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="59.69921875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30.3984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="26.69921875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.8984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="13.19921875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.09765625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.09765625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.09765625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.09765625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="42.59765625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.69921875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.8984375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.8984375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.59765625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.59765625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.19921875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="29.3984375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="9.09765625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.796875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="64.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="72" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="48" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="25.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5407,7 +5500,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>36</v>
       </c>
@@ -5517,7 +5610,7 @@
         <v>5210.0477000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>59</v>
       </c>
@@ -5627,7 +5720,7 @@
         <v>35392.327499999999</v>
       </c>
     </row>
-    <row r="4" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>78</v>
       </c>
@@ -5737,7 +5830,7 @@
         <v>63318.499199999998</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>91</v>
       </c>
@@ -5847,7 +5940,7 @@
         <v>10477.219999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>105</v>
       </c>
@@ -5957,7 +6050,7 @@
         <v>5210.0477000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>112</v>
       </c>
@@ -6067,7 +6160,7 @@
         <v>10420.0954</v>
       </c>
     </row>
-    <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>119</v>
       </c>
@@ -6177,7 +6270,7 @@
         <v>20840.1908</v>
       </c>
     </row>
-    <row r="9" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>128</v>
       </c>
@@ -6287,7 +6380,7 @@
         <v>7914.8123999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>134</v>
       </c>
@@ -6397,7 +6490,7 @@
         <v>13.453620000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>149</v>
       </c>
@@ -6507,7 +6600,7 @@
         <v>36185.722500000003</v>
       </c>
     </row>
-    <row r="12" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>160</v>
       </c>
@@ -6617,7 +6710,7 @@
         <v>24123.814999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
         <v>167</v>
       </c>
@@ -6727,7 +6820,7 @@
         <v>19787.030999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>174</v>
       </c>
@@ -6837,7 +6930,7 @@
         <v>43015</v>
       </c>
     </row>
-    <row r="15" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
         <v>186</v>
       </c>
@@ -6947,7 +7040,7 @@
         <v>1978.7030999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>193</v>
       </c>
@@ -7057,7 +7150,7 @@
         <v>21711.433499999999</v>
       </c>
     </row>
-    <row r="17" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
         <v>193</v>
       </c>
@@ -7167,7 +7260,7 @@
         <v>7237.1445000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>202</v>
       </c>
@@ -7277,7 +7370,7 @@
         <v>2412.3833500000001</v>
       </c>
     </row>
-    <row r="19" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
         <v>210</v>
       </c>
@@ -7387,7 +7480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>217</v>
       </c>
@@ -7497,7 +7590,7 @@
         <v>89041.639500000005</v>
       </c>
     </row>
-    <row r="21" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
         <v>222</v>
       </c>
@@ -7607,7 +7700,7 @@
         <v>3957.4061999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>228</v>
       </c>
@@ -7717,7 +7810,7 @@
         <v>15829.6248</v>
       </c>
     </row>
-    <row r="23" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
         <v>233</v>
       </c>
@@ -7827,7 +7920,7 @@
         <v>1700.04</v>
       </c>
     </row>
-    <row r="24" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>244</v>
       </c>
@@ -7937,7 +8030,7 @@
         <v>11872.2186</v>
       </c>
     </row>
-    <row r="25" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>246</v>
       </c>
@@ -8047,7 +8140,7 @@
         <v>6566.84</v>
       </c>
     </row>
-    <row r="26" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>259</v>
       </c>
@@ -8157,7 +8250,7 @@
         <v>2511.27</v>
       </c>
     </row>
-    <row r="27" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>265</v>
       </c>
@@ -8267,7 +8360,7 @@
         <v>7092.8130000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>278</v>
       </c>
@@ -8377,7 +8470,7 @@
         <v>4824.7667000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>283</v>
       </c>
@@ -8487,7 +8580,7 @@
         <v>14474.3001</v>
       </c>
     </row>
-    <row r="30" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>290</v>
       </c>
@@ -8597,7 +8690,7 @@
         <v>10420.0954</v>
       </c>
     </row>
-    <row r="31" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>299</v>
       </c>
@@ -8707,7 +8800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>305</v>
       </c>
@@ -8817,7 +8910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
         <v>312</v>
       </c>
@@ -8927,7 +9020,7 @@
         <v>5936.1093000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>318</v>
       </c>
@@ -9037,7 +9130,7 @@
         <v>23811.614399999999</v>
       </c>
     </row>
-    <row r="35" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
         <v>328</v>
       </c>
@@ -9147,7 +9240,7 @@
         <v>41010.516949999997</v>
       </c>
     </row>
-    <row r="36" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>334</v>
       </c>
@@ -9257,7 +9350,7 @@
         <v>1978.7030999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
         <v>339</v>
       </c>
@@ -9367,7 +9460,7 @@
         <v>8.8142200000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>339</v>
       </c>
@@ -9477,7 +9570,7 @@
         <v>7.5034299999999998</v>
       </c>
     </row>
-    <row r="39" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
         <v>355</v>
       </c>
@@ -9587,7 +9680,7 @@
         <v>10.13259</v>
       </c>
     </row>
-    <row r="40" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>355</v>
       </c>
@@ -9697,7 +9790,7 @@
         <v>8.8142200000000006</v>
       </c>
     </row>
-    <row r="41" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
         <v>364</v>
       </c>
@@ -9807,7 +9900,7 @@
         <v>19787.030999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>366</v>
       </c>
@@ -9917,7 +10010,7 @@
         <v>1978.7030999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
         <v>371</v>
       </c>
@@ -10027,7 +10120,7 @@
         <v>15630.143099999999</v>
       </c>
     </row>
-    <row r="44" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>376</v>
       </c>
@@ -10137,7 +10230,7 @@
         <v>9893.5154999999995</v>
       </c>
     </row>
-    <row r="45" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>381</v>
       </c>
@@ -10247,7 +10340,7 @@
         <v>11872.2186</v>
       </c>
     </row>
-    <row r="46" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>384</v>
       </c>
@@ -10357,7 +10450,7 @@
         <v>2605.02385</v>
       </c>
     </row>
-    <row r="47" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>388</v>
       </c>
@@ -10467,7 +10560,7 @@
         <v>5478.9861000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>398</v>
       </c>
@@ -10577,7 +10670,7 @@
         <v>2605.02385</v>
       </c>
     </row>
-    <row r="49" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>404</v>
       </c>
@@ -10687,7 +10780,7 @@
         <v>26050.238499999999</v>
       </c>
     </row>
-    <row r="50" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>414</v>
       </c>
@@ -10797,7 +10890,7 @@
         <v>1979.2439999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
         <v>425</v>
       </c>
@@ -10907,7 +11000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>429</v>
       </c>
@@ -11017,7 +11110,7 @@
         <v>1275.03</v>
       </c>
     </row>
-    <row r="53" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
         <v>434</v>
       </c>
@@ -11127,7 +11220,7 @@
         <v>29680.5465</v>
       </c>
     </row>
-    <row r="54" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>439</v>
       </c>
@@ -11237,7 +11330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
         <v>443</v>
       </c>
@@ -11347,7 +11440,7 @@
         <v>258.53174999999999</v>
       </c>
     </row>
-    <row r="56" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>454</v>
       </c>
@@ -11457,7 +11550,7 @@
         <v>10315.3824</v>
       </c>
     </row>
-    <row r="57" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
         <v>454</v>
       </c>
@@ -11567,7 +11660,7 @@
         <v>98705.566000000006</v>
       </c>
     </row>
-    <row r="58" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>469</v>
       </c>
@@ -11677,7 +11770,7 @@
         <v>2605.02385</v>
       </c>
     </row>
-    <row r="59" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
         <v>478</v>
       </c>
@@ -11787,7 +11880,7 @@
         <v>4824.7667000000001</v>
       </c>
     </row>
-    <row r="60" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>484</v>
       </c>
@@ -11897,7 +11990,7 @@
         <v>37461.950400000002</v>
       </c>
     </row>
-    <row r="61" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
         <v>484</v>
       </c>
@@ -12007,7 +12100,7 @@
         <v>13506.6896</v>
       </c>
     </row>
-    <row r="62" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>494</v>
       </c>
@@ -12117,7 +12210,7 @@
         <v>1978.7030999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6" t="s">
         <v>499</v>
       </c>
@@ -12227,7 +12320,7 @@
         <v>17628.439999999999</v>
       </c>
     </row>
-    <row r="64" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>506</v>
       </c>
@@ -12337,7 +12430,7 @@
         <v>19787.030999999999</v>
       </c>
     </row>
-    <row r="65" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="6" t="s">
         <v>509</v>
       </c>
@@ -12447,7 +12540,7 @@
         <v>15167.4432</v>
       </c>
     </row>
-    <row r="66" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>509</v>
       </c>
@@ -12557,7 +12650,7 @@
         <v>13407.351000000001</v>
       </c>
     </row>
-    <row r="67" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6" t="s">
         <v>523</v>
       </c>
@@ -12667,7 +12760,7 @@
         <v>164.17099999999999</v>
       </c>
     </row>
-    <row r="68" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>529</v>
       </c>
@@ -12777,7 +12870,7 @@
         <v>1978.7030999999999</v>
       </c>
     </row>
-    <row r="69" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
         <v>532</v>
       </c>
@@ -12887,7 +12980,7 @@
         <v>1.8587499999999999</v>
       </c>
     </row>
-    <row r="70" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>540</v>
       </c>
@@ -12997,7 +13090,7 @@
         <v>6371.08</v>
       </c>
     </row>
-    <row r="71" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
         <v>542</v>
       </c>
@@ -13107,7 +13200,7 @@
         <v>4824.7667000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>548</v>
       </c>
@@ -13217,7 +13310,7 @@
         <v>20840.1908</v>
       </c>
     </row>
-    <row r="73" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="6" t="s">
         <v>550</v>
       </c>
@@ -13327,7 +13420,7 @@
         <v>4469.1170000000002</v>
       </c>
     </row>
-    <row r="74" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>555</v>
       </c>
@@ -13437,7 +13530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="s">
         <v>555</v>
       </c>
@@ -13547,7 +13640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>559</v>
       </c>
@@ -13657,7 +13750,7 @@
         <v>7503.43</v>
       </c>
     </row>
-    <row r="77" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="6" t="s">
         <v>569</v>
       </c>
@@ -13767,7 +13860,7 @@
         <v>16436.958299999998</v>
       </c>
     </row>
-    <row r="78" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>572</v>
       </c>
@@ -13877,7 +13970,7 @@
         <v>9.9359699999999993</v>
       </c>
     </row>
-    <row r="79" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="6" t="s">
         <v>588</v>
       </c>
@@ -13987,7 +14080,7 @@
         <v>2605.02385</v>
       </c>
     </row>
-    <row r="80" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>589</v>
       </c>
@@ -14097,7 +14190,7 @@
         <v>11872.2186</v>
       </c>
     </row>
-    <row r="81" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6" t="s">
         <v>590</v>
       </c>
@@ -14207,7 +14300,7 @@
         <v>18263.287</v>
       </c>
     </row>
-    <row r="82" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>592</v>
       </c>
@@ -14317,7 +14410,7 @@
         <v>25484.32</v>
       </c>
     </row>
-    <row r="83" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6" t="s">
         <v>596</v>
       </c>
@@ -14427,7 +14520,7 @@
         <v>6300.8554999999997</v>
       </c>
     </row>
-    <row r="84" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>608</v>
       </c>
@@ -14537,7 +14630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6" t="s">
         <v>610</v>
       </c>
@@ -14647,7 +14740,7 @@
         <v>63318.499199999998</v>
       </c>
     </row>
-    <row r="86" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>613</v>
       </c>
@@ -14757,7 +14850,7 @@
         <v>2826.23945</v>
       </c>
     </row>
-    <row r="87" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6" t="s">
         <v>621</v>
       </c>
@@ -14867,7 +14960,7 @@
         <v>5210.0477000000001</v>
       </c>
     </row>
-    <row r="88" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>627</v>
       </c>
@@ -14977,7 +15070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6" t="s">
         <v>627</v>
       </c>
@@ -15087,7 +15180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>627</v>
       </c>
@@ -15197,7 +15290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6" t="s">
         <v>627</v>
       </c>
@@ -15307,7 +15400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>627</v>
       </c>
@@ -15417,7 +15510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6" t="s">
         <v>627</v>
       </c>
@@ -15527,7 +15620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>627</v>
       </c>
@@ -15637,7 +15730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6" t="s">
         <v>635</v>
       </c>
@@ -15747,7 +15840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>644</v>
       </c>
@@ -15857,7 +15950,7 @@
         <v>10.925890000000001</v>
       </c>
     </row>
-    <row r="97" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="6" t="s">
         <v>644</v>
       </c>
@@ -15967,7 +16060,7 @@
         <v>14.294969999999999</v>
       </c>
     </row>
-    <row r="98" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>654</v>
       </c>
@@ -16077,7 +16170,7 @@
         <v>17628.439999999999</v>
       </c>
     </row>
-    <row r="99" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="6" t="s">
         <v>662</v>
       </c>
@@ -16187,7 +16280,7 @@
         <v>44285.405449999998</v>
       </c>
     </row>
-    <row r="100" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>666</v>
       </c>
@@ -16297,7 +16390,7 @@
         <v>9893.5154999999995</v>
       </c>
     </row>
-    <row r="101" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="6" t="s">
         <v>671</v>
       </c>
@@ -16407,7 +16500,7 @@
         <v>11905.8087</v>
       </c>
     </row>
-    <row r="102" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>671</v>
       </c>
@@ -16517,7 +16610,7 @@
         <v>2225.4047099999998</v>
       </c>
     </row>
-    <row r="103" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="6" t="s">
         <v>676</v>
       </c>
@@ -16627,7 +16720,7 @@
         <v>7092.8130000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
         <v>681</v>
       </c>
@@ -16737,7 +16830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="6" t="s">
         <v>681</v>
       </c>
@@ -16847,7 +16940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
         <v>681</v>
       </c>
@@ -16957,7 +17050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="6" t="s">
         <v>681</v>
       </c>
@@ -17067,7 +17160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
         <v>687</v>
       </c>
@@ -17177,7 +17270,7 @@
         <v>7605.05375</v>
       </c>
     </row>
-    <row r="109" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="6" t="s">
         <v>687</v>
       </c>
@@ -17287,7 +17380,7 @@
         <v>5560.3779999999997</v>
       </c>
     </row>
-    <row r="110" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
         <v>694</v>
       </c>
@@ -17397,7 +17490,7 @@
         <v>24123.833500000001</v>
       </c>
     </row>
-    <row r="111" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="6" t="s">
         <v>696</v>
       </c>
@@ -17507,7 +17600,7 @@
         <v>10.925890000000001</v>
       </c>
     </row>
-    <row r="112" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
         <v>696</v>
       </c>
@@ -17617,7 +17710,7 @@
         <v>14.294969999999999</v>
       </c>
     </row>
-    <row r="113" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="6" t="s">
         <v>700</v>
       </c>
@@ -17727,7 +17820,7 @@
         <v>25.495090000000001</v>
       </c>
     </row>
-    <row r="114" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>707</v>
       </c>
@@ -17837,7 +17930,7 @@
         <v>13025.11925</v>
       </c>
     </row>
-    <row r="115" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="6" t="s">
         <v>709</v>
       </c>
@@ -17947,7 +18040,7 @@
         <v>26442.66</v>
       </c>
     </row>
-    <row r="116" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
         <v>709</v>
       </c>
@@ -18057,7 +18150,7 @@
         <v>562.75725</v>
       </c>
     </row>
-    <row r="117" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="6" t="s">
         <v>709</v>
       </c>
@@ -18167,7 +18260,7 @@
         <v>5775.9210000000003</v>
       </c>
     </row>
-    <row r="118" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>711</v>
       </c>
@@ -18277,7 +18370,7 @@
         <v>7605.05375</v>
       </c>
     </row>
-    <row r="119" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="6" t="s">
         <v>714</v>
       </c>
@@ -18387,7 +18480,7 @@
         <v>15831.678400000001</v>
       </c>
     </row>
-    <row r="120" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>717</v>
       </c>
@@ -18497,7 +18590,7 @@
         <v>32834.199999999997</v>
       </c>
     </row>
-    <row r="121" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="6" t="s">
         <v>725</v>
       </c>
@@ -18607,7 +18700,7 @@
         <v>1484.433</v>
       </c>
     </row>
-    <row r="122" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
         <v>731</v>
       </c>
@@ -18717,7 +18810,7 @@
         <v>26008.021499999999</v>
       </c>
     </row>
-    <row r="123" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="6" t="s">
         <v>734</v>
       </c>
@@ -18827,7 +18920,7 @@
         <v>1978.6895</v>
       </c>
     </row>
-    <row r="124" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
         <v>737</v>
       </c>
@@ -18937,7 +19030,7 @@
         <v>46087.485000000001</v>
       </c>
     </row>
-    <row r="125" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="6" t="s">
         <v>744</v>
       </c>
@@ -19047,7 +19140,7 @@
         <v>2600.80215</v>
       </c>
     </row>
-    <row r="126" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
         <v>746</v>
       </c>
@@ -19157,7 +19250,7 @@
         <v>2600.80215</v>
       </c>
     </row>
-    <row r="127" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="6" t="s">
         <v>748</v>
       </c>
@@ -19267,7 +19360,7 @@
         <v>7605.05375</v>
       </c>
     </row>
-    <row r="128" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
         <v>748</v>
       </c>
@@ -19377,7 +19470,7 @@
         <v>4063.6442000000002</v>
       </c>
     </row>
-    <row r="129" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="6" t="s">
         <v>748</v>
       </c>
@@ -19487,7 +19580,7 @@
         <v>4469.1149999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
         <v>755</v>
       </c>
@@ -19597,7 +19690,7 @@
         <v>30.553940000000001</v>
       </c>
     </row>
-    <row r="131" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="6" t="s">
         <v>759</v>
       </c>
@@ -19707,7 +19800,7 @@
         <v>8.8524499999999993</v>
       </c>
     </row>
-    <row r="132" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
         <v>759</v>
       </c>
@@ -19817,7 +19910,7 @@
         <v>10.34127</v>
       </c>
     </row>
-    <row r="133" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="6" t="s">
         <v>759</v>
       </c>
@@ -19927,7 +20020,7 @@
         <v>7.5035699999999999</v>
       </c>
     </row>
-    <row r="134" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
         <v>767</v>
       </c>
@@ -20037,7 +20130,7 @@
         <v>5201.6043</v>
       </c>
     </row>
-    <row r="135" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="6" t="s">
         <v>769</v>
       </c>
@@ -20147,7 +20240,7 @@
         <v>13004.010749999999</v>
       </c>
     </row>
-    <row r="136" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
         <v>771</v>
       </c>
@@ -20257,7 +20350,7 @@
         <v>5201.6043</v>
       </c>
     </row>
-    <row r="137" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="6" t="s">
         <v>773</v>
       </c>
@@ -20367,7 +20460,7 @@
         <v>10957.9722</v>
       </c>
     </row>
-    <row r="138" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
         <v>776</v>
       </c>
@@ -20477,7 +20570,7 @@
         <v>76705.805399999997</v>
       </c>
     </row>
-    <row r="139" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="6" t="s">
         <v>779</v>
       </c>
@@ -20587,7 +20680,7 @@
         <v>1.96296</v>
       </c>
     </row>
-    <row r="140" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
         <v>787</v>
       </c>
@@ -20697,7 +20790,7 @@
         <v>9.8148</v>
       </c>
     </row>
-    <row r="141" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="6" t="s">
         <v>791</v>
       </c>
@@ -20807,7 +20900,7 @@
         <v>10957.982400000001</v>
       </c>
     </row>
-    <row r="142" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
         <v>793</v>
       </c>
@@ -20917,7 +21010,7 @@
         <v>2600.80215</v>
       </c>
     </row>
-    <row r="143" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="6" t="s">
         <v>796</v>
       </c>
@@ -21027,7 +21120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
         <v>798</v>
       </c>
@@ -21137,7 +21230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="6" t="s">
         <v>798</v>
       </c>
@@ -21247,7 +21340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
         <v>802</v>
       </c>
@@ -21357,7 +21450,7 @@
         <v>35392.327499999999</v>
       </c>
     </row>
-    <row r="147" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="6" t="s">
         <v>804</v>
       </c>
@@ -21467,7 +21560,7 @@
         <v>6532.5450000000001</v>
       </c>
     </row>
-    <row r="148" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
         <v>811</v>
       </c>
@@ -21577,7 +21670,7 @@
         <v>3598.4160000000002</v>
       </c>
     </row>
-    <row r="149" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="6" t="s">
         <v>811</v>
       </c>
@@ -21687,7 +21780,7 @@
         <v>2398.944</v>
       </c>
     </row>
-    <row r="150" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
         <v>811</v>
       </c>
@@ -21797,7 +21890,7 @@
         <v>6532.5450000000001</v>
       </c>
     </row>
-    <row r="151" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="6" t="s">
         <v>819</v>
       </c>
@@ -21907,7 +22000,7 @@
         <v>1770.49</v>
       </c>
     </row>
-    <row r="152" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
         <v>823</v>
       </c>
@@ -22017,7 +22110,7 @@
         <v>18263.304</v>
       </c>
     </row>
-    <row r="153" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="6" t="s">
         <v>826</v>
       </c>
@@ -22127,7 +22220,7 @@
         <v>10.743119999999999</v>
       </c>
     </row>
-    <row r="154" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
         <v>830</v>
       </c>
@@ -22237,7 +22330,7 @@
         <v>15.27697</v>
       </c>
     </row>
-    <row r="155" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="6" t="s">
         <v>830</v>
       </c>
@@ -22347,7 +22440,7 @@
         <v>10.743119999999999</v>
       </c>
     </row>
-    <row r="156" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
         <v>837</v>
       </c>
@@ -22457,7 +22550,7 @@
         <v>30725</v>
       </c>
     </row>
-    <row r="157" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="6" t="s">
         <v>841</v>
       </c>
@@ -22567,7 +22660,7 @@
         <v>33.119909999999997</v>
       </c>
     </row>
-    <row r="158" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
         <v>841</v>
       </c>
@@ -22677,7 +22770,7 @@
         <v>30.725000000000001</v>
       </c>
     </row>
-    <row r="159" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="6" t="s">
         <v>843</v>
       </c>
@@ -22787,7 +22880,7 @@
         <v>7092.82</v>
       </c>
     </row>
-    <row r="160" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
         <v>848</v>
       </c>
@@ -22897,7 +22990,7 @@
         <v>4713.8221999999996</v>
       </c>
     </row>
-    <row r="161" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="6" t="s">
         <v>851</v>
       </c>
@@ -23007,7 +23100,7 @@
         <v>12.747540000000001</v>
       </c>
     </row>
-    <row r="162" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
         <v>851</v>
       </c>
@@ -23117,7 +23210,7 @@
         <v>7.0950800000000003</v>
       </c>
     </row>
-    <row r="163" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="6" t="s">
         <v>855</v>
       </c>
@@ -23227,7 +23320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
         <v>858</v>
       </c>
@@ -23337,7 +23430,7 @@
         <v>1826.3304000000001</v>
       </c>
     </row>
-    <row r="165" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="6" t="s">
         <v>862</v>
       </c>
@@ -23447,7 +23540,7 @@
         <v>9.8148</v>
       </c>
     </row>
-    <row r="166" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
         <v>867</v>
       </c>
@@ -23557,7 +23650,7 @@
         <v>15210.1075</v>
       </c>
     </row>
-    <row r="167" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="6" t="s">
         <v>873</v>
       </c>
@@ -23667,7 +23760,7 @@
         <v>7914.7579999999998</v>
       </c>
     </row>
-    <row r="168" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="2" t="s">
         <v>878</v>
       </c>
@@ -23777,7 +23870,7 @@
         <v>26008.021499999999</v>
       </c>
     </row>
-    <row r="169" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="6" t="s">
         <v>881</v>
       </c>
@@ -23887,7 +23980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="2" t="s">
         <v>883</v>
       </c>
@@ -23997,7 +24090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="6" t="s">
         <v>885</v>
       </c>
@@ -24107,7 +24200,7 @@
         <v>6844.5128000000004</v>
       </c>
     </row>
-    <row r="172" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="2" t="s">
         <v>887</v>
       </c>
@@ -24217,7 +24310,7 @@
         <v>70707.277499999997</v>
       </c>
     </row>
-    <row r="173" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="6" t="s">
         <v>897</v>
       </c>
@@ -24327,7 +24420,7 @@
         <v>17111.281999999999</v>
       </c>
     </row>
-    <row r="174" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="2" t="s">
         <v>899</v>
       </c>
@@ -24437,7 +24530,7 @@
         <v>92998.406499999997</v>
       </c>
     </row>
-    <row r="175" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="6" t="s">
         <v>906</v>
       </c>
@@ -24547,7 +24640,7 @@
         <v>6844.5128000000004</v>
       </c>
     </row>
-    <row r="176" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="2" t="s">
         <v>914</v>
       </c>
@@ -24657,7 +24750,7 @@
         <v>1978.6912</v>
       </c>
     </row>
-    <row r="177" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="6" t="s">
         <v>917</v>
       </c>
@@ -24767,7 +24860,7 @@
         <v>3012.3888000000002</v>
       </c>
     </row>
-    <row r="178" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="2" t="s">
         <v>917</v>
       </c>
@@ -24877,7 +24970,7 @@
         <v>753.35</v>
       </c>
     </row>
-    <row r="179" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="6" t="s">
         <v>919</v>
       </c>
@@ -24987,7 +25080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
         <v>921</v>
       </c>
@@ -25097,7 +25190,7 @@
         <v>63318.118399999999</v>
       </c>
     </row>
-    <row r="181" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="6" t="s">
         <v>924</v>
       </c>
@@ -25207,7 +25300,7 @@
         <v>14738.4246</v>
       </c>
     </row>
-    <row r="182" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="2" t="s">
         <v>929</v>
       </c>
@@ -25317,7 +25410,7 @@
         <v>3889.0880000000002</v>
       </c>
     </row>
-    <row r="183" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="6" t="s">
         <v>929</v>
       </c>
@@ -25427,7 +25520,7 @@
         <v>35001.792000000001</v>
       </c>
     </row>
-    <row r="184" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
         <v>929</v>
       </c>
@@ -25537,7 +25630,7 @@
         <v>16681.134760000001</v>
       </c>
     </row>
-    <row r="185" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="6" t="s">
         <v>937</v>
       </c>
@@ -25647,7 +25740,7 @@
         <v>4461.6390000000001</v>
       </c>
     </row>
-    <row r="186" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="2" t="s">
         <v>943</v>
       </c>
@@ -25757,7 +25850,7 @@
         <v>10.78121</v>
       </c>
     </row>
-    <row r="187" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="6" t="s">
         <v>949</v>
       </c>
@@ -25867,7 +25960,7 @@
         <v>2916.8204999999998</v>
       </c>
     </row>
-    <row r="188" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="2" t="s">
         <v>951</v>
       </c>
@@ -25977,7 +26070,7 @@
         <v>33119.9</v>
       </c>
     </row>
-    <row r="189" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="6" t="s">
         <v>954</v>
       </c>
@@ -26087,7 +26180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="2" t="s">
         <v>956</v>
       </c>
@@ -26197,7 +26290,7 @@
         <v>30420.215</v>
       </c>
     </row>
-    <row r="191" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="6" t="s">
         <v>958</v>
       </c>
@@ -26307,7 +26400,7 @@
         <v>4.9579800000000001</v>
       </c>
     </row>
-    <row r="192" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="2" t="s">
         <v>968</v>
       </c>
@@ -26417,7 +26510,7 @@
         <v>4461.6390000000001</v>
       </c>
     </row>
-    <row r="193" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="6" t="s">
         <v>970</v>
       </c>
@@ -26527,7 +26620,7 @@
         <v>7605.05375</v>
       </c>
     </row>
-    <row r="194" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
         <v>972</v>
       </c>
@@ -26637,7 +26730,7 @@
         <v>13.99024</v>
       </c>
     </row>
-    <row r="195" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="6" t="s">
         <v>976</v>
       </c>
@@ -26747,7 +26840,7 @@
         <v>9.8148</v>
       </c>
     </row>
-    <row r="196" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
         <v>980</v>
       </c>
@@ -26857,7 +26950,7 @@
         <v>2456.4041000000002</v>
       </c>
     </row>
-    <row r="197" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="6" t="s">
         <v>982</v>
       </c>
@@ -26967,7 +27060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
         <v>982</v>
       </c>
@@ -27077,7 +27170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="6" t="s">
         <v>984</v>
       </c>
@@ -27187,7 +27280,7 @@
         <v>7605.05375</v>
       </c>
     </row>
-    <row r="200" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
         <v>984</v>
       </c>
@@ -27297,7 +27390,7 @@
         <v>3791.8685999999998</v>
       </c>
     </row>
-    <row r="201" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="6" t="s">
         <v>984</v>
       </c>
@@ -27407,7 +27500,7 @@
         <v>4461.6390000000001</v>
       </c>
     </row>
-    <row r="202" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
         <v>986</v>
       </c>
@@ -27517,7 +27610,7 @@
         <v>25881.944</v>
       </c>
     </row>
-    <row r="203" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="6" t="s">
         <v>988</v>
       </c>
@@ -27627,7 +27720,7 @@
         <v>2501.9324999999999</v>
       </c>
     </row>
-    <row r="204" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
         <v>997</v>
       </c>
@@ -27737,7 +27830,7 @@
         <v>7369.2123000000001</v>
       </c>
     </row>
-    <row r="205" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="6" t="s">
         <v>999</v>
       </c>
@@ -27847,7 +27940,7 @@
         <v>49175.693599999999</v>
       </c>
     </row>
-    <row r="206" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="2" t="s">
         <v>1001</v>
       </c>
@@ -27957,7 +28050,7 @@
         <v>1959.2873999999999</v>
       </c>
     </row>
-    <row r="207" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="6" t="s">
         <v>1003</v>
       </c>
@@ -28067,7 +28160,7 @@
         <v>7.5035699999999999</v>
       </c>
     </row>
-    <row r="208" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="2" t="s">
         <v>1010</v>
       </c>
@@ -28177,7 +28270,7 @@
         <v>21548.356800000001</v>
       </c>
     </row>
-    <row r="209" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="6" t="s">
         <v>1015</v>
       </c>
@@ -28287,7 +28380,7 @@
         <v>33.119909999999997</v>
       </c>
     </row>
-    <row r="210" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="2" t="s">
         <v>1017</v>
       </c>
@@ -28397,7 +28490,7 @@
         <v>5.8336399999999999</v>
       </c>
     </row>
-    <row r="211" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="6" t="s">
         <v>1017</v>
       </c>
@@ -28507,7 +28600,7 @@
         <v>11.511559999999999</v>
       </c>
     </row>
-    <row r="212" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="2" t="s">
         <v>1017</v>
       </c>
@@ -28617,7 +28710,7 @@
         <v>4.2570499999999996</v>
       </c>
     </row>
-    <row r="213" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="6" t="s">
         <v>1017</v>
       </c>
@@ -28727,7 +28820,7 @@
         <v>5.5413300000000003</v>
       </c>
     </row>
-    <row r="214" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
         <v>1017</v>
       </c>
@@ -28837,7 +28930,7 @@
         <v>9.1377699999999997</v>
       </c>
     </row>
-    <row r="215" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="6" t="s">
         <v>1017</v>
       </c>
@@ -28947,7 +29040,7 @@
         <v>6.1189999999999998</v>
       </c>
     </row>
-    <row r="216" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
         <v>1017</v>
       </c>
@@ -29057,7 +29150,7 @@
         <v>13.0503</v>
       </c>
     </row>
-    <row r="217" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="6" t="s">
         <v>1031</v>
       </c>
@@ -29167,7 +29260,7 @@
         <v>9825.6164000000008</v>
       </c>
     </row>
-    <row r="218" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="2" t="s">
         <v>1033</v>
       </c>
@@ -29277,7 +29370,7 @@
         <v>31058.3328</v>
       </c>
     </row>
-    <row r="219" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="6" t="s">
         <v>1035</v>
       </c>
@@ -29387,7 +29480,7 @@
         <v>17704.900000000001</v>
       </c>
     </row>
-    <row r="220" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="2" t="s">
         <v>1037</v>
       </c>
@@ -29497,7 +29590,7 @@
         <v>9897.6</v>
       </c>
     </row>
-    <row r="221" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="6" t="s">
         <v>1043</v>
       </c>
@@ -29607,7 +29700,7 @@
         <v>2456.4041000000002</v>
       </c>
     </row>
-    <row r="222" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="2" t="s">
         <v>1049</v>
       </c>
@@ -29717,7 +29810,7 @@
         <v>21765.603200000001</v>
       </c>
     </row>
-    <row r="223" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="6" t="s">
         <v>1051</v>
       </c>
@@ -29827,7 +29920,7 @@
         <v>5176.3887999999997</v>
       </c>
     </row>
-    <row r="224" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="2" t="s">
         <v>1053</v>
       </c>
@@ -29937,7 +30030,7 @@
         <v>1978.6912</v>
       </c>
     </row>
-    <row r="225" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="6" t="s">
         <v>1055</v>
       </c>
@@ -30047,7 +30140,7 @@
         <v>9.1311099999999996</v>
       </c>
     </row>
-    <row r="226" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="2" t="s">
         <v>1055</v>
       </c>
@@ -30157,7 +30250,7 @@
         <v>9.8148</v>
       </c>
     </row>
-    <row r="227" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="6" t="s">
         <v>1063</v>
       </c>
@@ -30267,7 +30360,7 @@
         <v>7503.57</v>
       </c>
     </row>
-    <row r="228" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="2" t="s">
         <v>1065</v>
       </c>
@@ -30377,7 +30470,7 @@
         <v>19786.912</v>
       </c>
     </row>
-    <row r="229" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="6" t="s">
         <v>1069</v>
       </c>
@@ -30487,7 +30580,7 @@
         <v>9.8976000000000006</v>
       </c>
     </row>
-    <row r="230" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="2" t="s">
         <v>1069</v>
       </c>
@@ -30597,7 +30690,7 @@
         <v>9.8208099999999998</v>
       </c>
     </row>
-    <row r="231" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="6" t="s">
         <v>1074</v>
       </c>
@@ -30707,7 +30800,7 @@
         <v>4912.8082000000004</v>
       </c>
     </row>
-    <row r="232" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="2" t="s">
         <v>1076</v>
       </c>
@@ -30817,7 +30910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="6" t="s">
         <v>1080</v>
       </c>
@@ -30927,7 +31020,7 @@
         <v>10341.27</v>
       </c>
     </row>
-    <row r="234" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="2" t="s">
         <v>1086</v>
       </c>
@@ -31037,7 +31130,7 @@
         <v>4912.8082000000004</v>
       </c>
     </row>
-    <row r="235" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="6" t="s">
         <v>1088</v>
       </c>
@@ -31147,7 +31240,7 @@
         <v>79487.977799999993</v>
       </c>
     </row>
-    <row r="236" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="2" t="s">
         <v>1093</v>
       </c>
@@ -31257,7 +31350,7 @@
         <v>18262.22</v>
       </c>
     </row>
-    <row r="237" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="6" t="s">
         <v>1098</v>
       </c>
@@ -31367,7 +31460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="2" t="s">
         <v>1100</v>
       </c>
@@ -31477,7 +31570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="6" t="s">
         <v>1103</v>
       </c>
@@ -31587,7 +31680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="2" t="s">
         <v>1103</v>
       </c>
@@ -31697,7 +31790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="6" t="s">
         <v>1103</v>
       </c>
@@ -31807,7 +31900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="2" t="s">
         <v>1103</v>
       </c>
@@ -31917,7 +32010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="6" t="s">
         <v>1105</v>
       </c>
@@ -32027,7 +32120,7 @@
         <v>15140.5672</v>
       </c>
     </row>
-    <row r="244" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="2" t="s">
         <v>1107</v>
       </c>
@@ -32137,7 +32230,7 @@
         <v>29776.757399999999</v>
       </c>
     </row>
-    <row r="245" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="6" t="s">
         <v>1107</v>
       </c>
@@ -32247,7 +32340,7 @@
         <v>46573.902600000001</v>
       </c>
     </row>
-    <row r="246" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="2" t="s">
         <v>1115</v>
       </c>
@@ -32357,7 +32450,7 @@
         <v>1966.3</v>
       </c>
     </row>
-    <row r="247" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="6" t="s">
         <v>1115</v>
       </c>
@@ -32467,7 +32560,7 @@
         <v>7865.2</v>
       </c>
     </row>
-    <row r="248" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="2" t="s">
         <v>1119</v>
       </c>
@@ -32577,7 +32670,7 @@
         <v>7753.1832000000004</v>
       </c>
     </row>
-    <row r="249" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="6" t="s">
         <v>1121</v>
       </c>
@@ -32687,7 +32780,7 @@
         <v>12.877560000000001</v>
       </c>
     </row>
-    <row r="250" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="2" t="s">
         <v>1125</v>
       </c>
@@ -32797,7 +32890,7 @@
         <v>775.59524999999996</v>
       </c>
     </row>
-    <row r="251" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="6" t="s">
         <v>1127</v>
       </c>
@@ -32907,7 +33000,7 @@
         <v>19663</v>
       </c>
     </row>
-    <row r="252" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="2" t="s">
         <v>1129</v>
       </c>
@@ -33017,7 +33110,7 @@
         <v>4882.1944000000003</v>
       </c>
     </row>
-    <row r="253" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="6" t="s">
         <v>1131</v>
       </c>
@@ -33127,7 +33220,7 @@
         <v>16.225290000000001</v>
       </c>
     </row>
-    <row r="254" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="2" t="s">
         <v>1136</v>
       </c>
@@ -33237,7 +33330,7 @@
         <v>4.9579800000000001</v>
       </c>
     </row>
-    <row r="255" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="6" t="s">
         <v>1138</v>
       </c>
@@ -33347,7 +33440,7 @@
         <v>9462.8544999999995</v>
       </c>
     </row>
-    <row r="256" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="2" t="s">
         <v>1140</v>
       </c>
@@ -33457,7 +33550,7 @@
         <v>62462.946000000004</v>
       </c>
     </row>
-    <row r="257" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="6" t="s">
         <v>1144</v>
       </c>
@@ -33567,7 +33660,7 @@
         <v>30281.134399999999</v>
       </c>
     </row>
-    <row r="258" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="2" t="s">
         <v>1144</v>
       </c>
@@ -33677,7 +33770,7 @@
         <v>7570.2835999999998</v>
       </c>
     </row>
-    <row r="259" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="6" t="s">
         <v>1146</v>
       </c>
@@ -33787,7 +33880,7 @@
         <v>4461.6390000000001</v>
       </c>
     </row>
-    <row r="260" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="2" t="s">
         <v>1152</v>
       </c>
@@ -33897,7 +33990,7 @@
         <v>30.725000000000001</v>
       </c>
     </row>
-    <row r="261" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="6" t="s">
         <v>1156</v>
       </c>
@@ -34007,7 +34100,7 @@
         <v>4063.6442000000002</v>
       </c>
     </row>
-    <row r="262" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="2" t="s">
         <v>1156</v>
       </c>
@@ -34117,7 +34210,7 @@
         <v>6261.2264999999998</v>
       </c>
     </row>
-    <row r="263" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="6" t="s">
         <v>1158</v>
       </c>
@@ -34227,7 +34320,7 @@
         <v>153198.864</v>
       </c>
     </row>
-    <row r="264" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="2" t="s">
         <v>1162</v>
       </c>
@@ -34337,7 +34430,7 @@
         <v>79300.053</v>
       </c>
     </row>
-    <row r="265" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="6" t="s">
         <v>1162</v>
       </c>
@@ -34447,7 +34540,7 @@
         <v>24305.589</v>
       </c>
     </row>
-    <row r="266" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="2" t="s">
         <v>1162</v>
       </c>
@@ -34557,7 +34650,7 @@
         <v>32161.940999999999</v>
       </c>
     </row>
-    <row r="267" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="6" t="s">
         <v>1162</v>
       </c>
@@ -34667,7 +34760,7 @@
         <v>5646.75875</v>
       </c>
     </row>
-    <row r="268" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="2" t="s">
         <v>1169</v>
       </c>
@@ -34777,7 +34870,7 @@
         <v>4882.1944000000003</v>
       </c>
     </row>
-    <row r="269" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="6" t="s">
         <v>1171</v>
       </c>
@@ -34887,7 +34980,7 @@
         <v>12.725110000000001</v>
       </c>
     </row>
-    <row r="270" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="2" t="s">
         <v>1178</v>
       </c>
@@ -34997,7 +35090,7 @@
         <v>2501.9324999999999</v>
       </c>
     </row>
-    <row r="271" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="6" t="s">
         <v>1182</v>
       </c>
@@ -35107,7 +35200,7 @@
         <v>15.362500000000001</v>
       </c>
     </row>
-    <row r="272" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="2" t="s">
         <v>1182</v>
       </c>
@@ -35217,7 +35310,7 @@
         <v>4.34598</v>
       </c>
     </row>
-    <row r="273" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="6" t="s">
         <v>1182</v>
       </c>
@@ -35327,7 +35420,7 @@
         <v>3.7517900000000002</v>
       </c>
     </row>
-    <row r="274" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="2" t="s">
         <v>1186</v>
       </c>
@@ -35437,7 +35530,7 @@
         <v>53403.8</v>
       </c>
     </row>
-    <row r="275" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="6" t="s">
         <v>1191</v>
       </c>
@@ -35547,7 +35640,7 @@
         <v>2607.585</v>
       </c>
     </row>
-    <row r="276" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="2" t="s">
         <v>1196</v>
       </c>
@@ -35657,7 +35750,7 @@
         <v>45630.322500000002</v>
       </c>
     </row>
-    <row r="277" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="6" t="s">
         <v>1198</v>
       </c>
@@ -35767,7 +35860,7 @@
         <v>21094.501</v>
       </c>
     </row>
-    <row r="278" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="2" t="s">
         <v>1198</v>
       </c>
@@ -35877,7 +35970,7 @@
         <v>267.01900000000001</v>
       </c>
     </row>
-    <row r="279" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="6" t="s">
         <v>1205</v>
       </c>
@@ -35987,7 +36080,7 @@
         <v>95702.2</v>
       </c>
     </row>
-    <row r="280" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="2" t="s">
         <v>1207</v>
       </c>
@@ -36097,7 +36190,7 @@
         <v>18587.041000000001</v>
       </c>
     </row>
-    <row r="281" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="6" t="s">
         <v>1211</v>
       </c>
@@ -36207,7 +36300,7 @@
         <v>2441.0972000000002</v>
       </c>
     </row>
-    <row r="282" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="2" t="s">
         <v>1213</v>
       </c>
@@ -36317,7 +36410,7 @@
         <v>166848.41376</v>
       </c>
     </row>
-    <row r="283" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="6" t="s">
         <v>1228</v>
       </c>
@@ -36346,9 +36439,7 @@
       <c r="J283" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="K283" s="6" t="s">
-        <v>1229</v>
-      </c>
+      <c r="K283" s="6"/>
       <c r="L283" s="6" t="s">
         <v>52</v>
       </c>
@@ -36423,7 +36514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="2" t="s">
         <v>1233</v>
       </c>
@@ -36533,7 +36624,7 @@
         <v>3785.1417999999999</v>
       </c>
     </row>
-    <row r="285" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="6" t="s">
         <v>1237</v>
       </c>
@@ -36643,7 +36734,7 @@
         <v>29293.166399999998</v>
       </c>
     </row>
-    <row r="286" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="2" t="s">
         <v>1237</v>
       </c>
@@ -36753,7 +36844,7 @@
         <v>16676.453150000001</v>
       </c>
     </row>
-    <row r="287" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="6" t="s">
         <v>1237</v>
       </c>
@@ -36863,7 +36954,7 @@
         <v>11911.75225</v>
       </c>
     </row>
-    <row r="288" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="2" t="s">
         <v>1241</v>
       </c>
@@ -36973,7 +37064,7 @@
         <v>30421.825000000001</v>
       </c>
     </row>
-    <row r="289" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="6" t="s">
         <v>1241</v>
       </c>
@@ -37083,7 +37174,7 @@
         <v>2251.0709999999999</v>
       </c>
     </row>
-    <row r="290" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="2" t="s">
         <v>1243</v>
       </c>
@@ -37193,7 +37284,7 @@
         <v>8923.2780000000002</v>
       </c>
     </row>
-    <row r="291" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="6" t="s">
         <v>1247</v>
       </c>
@@ -37303,7 +37394,7 @@
         <v>37937.932999999997</v>
       </c>
     </row>
-    <row r="292" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="2" t="s">
         <v>1247</v>
       </c>
@@ -37413,7 +37504,7 @@
         <v>254.61699999999999</v>
       </c>
     </row>
-    <row r="293" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="6" t="s">
         <v>1251</v>
       </c>
@@ -37523,7 +37614,7 @@
         <v>71470.457999999999</v>
       </c>
     </row>
-    <row r="294" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="2" t="s">
         <v>1253</v>
       </c>
@@ -37633,7 +37724,7 @@
         <v>7147.0513499999997</v>
       </c>
     </row>
-    <row r="295" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="6" t="s">
         <v>1253</v>
       </c>
@@ -37743,7 +37834,7 @@
         <v>33352.906300000002</v>
       </c>
     </row>
-    <row r="296" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="2" t="s">
         <v>1260</v>
       </c>
@@ -37853,7 +37944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="6" t="s">
         <v>1260</v>
       </c>
@@ -37963,7 +38054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="2" t="s">
         <v>1262</v>
       </c>
@@ -38073,7 +38164,7 @@
         <v>7570.2835999999998</v>
       </c>
     </row>
-    <row r="299" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="6" t="s">
         <v>1264</v>
       </c>
@@ -38183,7 +38274,7 @@
         <v>3751.7849999999999</v>
       </c>
     </row>
-    <row r="300" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="2" t="s">
         <v>1268</v>
       </c>
@@ -38293,7 +38384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="6" t="s">
         <v>1270</v>
       </c>
@@ -38403,7 +38494,7 @@
         <v>7323.2915999999996</v>
       </c>
     </row>
-    <row r="302" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="2" t="s">
         <v>1272</v>
       </c>
@@ -38513,7 +38604,7 @@
         <v>7147.0513499999997</v>
       </c>
     </row>
-    <row r="303" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="6" t="s">
         <v>1274</v>
       </c>
@@ -38623,7 +38714,7 @@
         <v>14646.583199999999</v>
       </c>
     </row>
-    <row r="304" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="2" t="s">
         <v>1274</v>
       </c>
@@ -38733,7 +38824,7 @@
         <v>2382.3504499999999</v>
       </c>
     </row>
-    <row r="305" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="6" t="s">
         <v>1276</v>
       </c>
@@ -38843,7 +38934,7 @@
         <v>2441.0972000000002</v>
       </c>
     </row>
-    <row r="306" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="2" t="s">
         <v>1280</v>
       </c>
@@ -38953,7 +39044,7 @@
         <v>2441.0972000000002</v>
       </c>
     </row>
-    <row r="307" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="6" t="s">
         <v>1284</v>
       </c>
@@ -39063,7 +39154,7 @@
         <v>254.61699999999999</v>
       </c>
     </row>
-    <row r="308" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="2" t="s">
         <v>1284</v>
       </c>
@@ -39173,7 +39264,7 @@
         <v>25207.082999999999</v>
       </c>
     </row>
-    <row r="309" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="6" t="s">
         <v>1289</v>
       </c>
@@ -39283,7 +39374,7 @@
         <v>83424.751199999999</v>
       </c>
     </row>
-    <row r="310" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="2" t="s">
         <v>1289</v>
       </c>
@@ -39393,7 +39484,7 @@
         <v>83424.841920000006</v>
       </c>
     </row>
-    <row r="311" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="6" t="s">
         <v>1296</v>
       </c>
@@ -39503,7 +39594,7 @@
         <v>9764.3888000000006</v>
       </c>
     </row>
-    <row r="312" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="2" t="s">
         <v>1300</v>
       </c>
@@ -39613,7 +39704,7 @@
         <v>10680.76</v>
       </c>
     </row>
-    <row r="313" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="6" t="s">
         <v>1304</v>
       </c>
@@ -39723,7 +39814,7 @@
         <v>2946.1379999999999</v>
       </c>
     </row>
-    <row r="314" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="2" t="s">
         <v>1308</v>
       </c>
@@ -39833,7 +39924,7 @@
         <v>763.851</v>
       </c>
     </row>
-    <row r="315" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="6" t="s">
         <v>1314</v>
       </c>
@@ -39943,7 +40034,7 @@
         <v>195287.77600000001</v>
       </c>
     </row>
-    <row r="316" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="2" t="s">
         <v>1323</v>
       </c>
@@ -40053,55 +40144,824 @@
         <v>41498.683850000001</v>
       </c>
     </row>
+    <row r="317" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A317" s="6" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B317" s="6" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C317" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D317" s="7">
+        <v>46108</v>
+      </c>
+      <c r="E317" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F317" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G317" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="H317" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="I317" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J317" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K317" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L317" s="6" t="s">
+        <v>1326</v>
+      </c>
+      <c r="M317" s="6" t="s">
+        <v>1327</v>
+      </c>
+      <c r="N317" s="6" t="s">
+        <v>1328</v>
+      </c>
+      <c r="O317" s="8">
+        <v>3515</v>
+      </c>
+      <c r="P317" s="8">
+        <v>26.88</v>
+      </c>
+      <c r="Q317" s="9">
+        <v>94483.199999999997</v>
+      </c>
+      <c r="R317" s="9">
+        <v>3070.7</v>
+      </c>
+      <c r="S317" s="9">
+        <v>97553.9</v>
+      </c>
+      <c r="T317" s="9">
+        <v>94483.199999999997</v>
+      </c>
+      <c r="U317" s="9">
+        <v>17006.98</v>
+      </c>
+      <c r="V317" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="W317" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="X317" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y317" s="6" t="s">
+        <v>1329</v>
+      </c>
+      <c r="Z317" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA317" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB317" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC317" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD317" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE317" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF317" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG317" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH317" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI317" s="9">
+        <v>18</v>
+      </c>
+      <c r="AJ317" s="8">
+        <v>46380.881950000003</v>
+      </c>
+    </row>
+    <row r="318" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A318" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B318" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C318" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D318" s="3">
+        <v>46111</v>
+      </c>
+      <c r="E318" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F318" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G318" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="H318" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="I318" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J318" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="K318" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="L318" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="M318" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="N318" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="O318" s="4">
+        <v>170</v>
+      </c>
+      <c r="P318" s="4">
+        <v>26.89</v>
+      </c>
+      <c r="Q318" s="5">
+        <v>4571.3</v>
+      </c>
+      <c r="R318" s="5">
+        <v>148.57</v>
+      </c>
+      <c r="S318" s="5">
+        <v>4719.87</v>
+      </c>
+      <c r="T318" s="5">
+        <v>4571.3</v>
+      </c>
+      <c r="U318" s="5">
+        <v>822.83</v>
+      </c>
+      <c r="V318" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="W318" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="X318" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y318" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="Z318" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA318" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB318" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC318" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD318" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE318" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF318" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG318" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH318" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI318" s="5">
+        <v>18</v>
+      </c>
+      <c r="AJ318" s="4">
+        <v>1892.5708999999999</v>
+      </c>
+    </row>
+    <row r="319" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A319" s="6" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B319" s="6" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C319" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D319" s="7">
+        <v>46111</v>
+      </c>
+      <c r="E319" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F319" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G319" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H319" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="I319" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="J319" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K319" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="L319" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="M319" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="N319" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="O319" s="8">
+        <v>1000</v>
+      </c>
+      <c r="P319" s="8">
+        <v>19.62</v>
+      </c>
+      <c r="Q319" s="9">
+        <v>19620</v>
+      </c>
+      <c r="R319" s="9">
+        <v>637.65</v>
+      </c>
+      <c r="S319" s="9">
+        <v>20257.650000000001</v>
+      </c>
+      <c r="T319" s="9">
+        <v>19620</v>
+      </c>
+      <c r="U319" s="9">
+        <v>3531.6</v>
+      </c>
+      <c r="V319" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="W319" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="X319" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y319" s="6" t="s">
+        <v>1333</v>
+      </c>
+      <c r="Z319" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA319" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB319" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC319" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD319" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE319" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF319" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG319" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH319" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI319" s="9">
+        <v>18</v>
+      </c>
+      <c r="AJ319" s="8">
+        <v>10477.23</v>
+      </c>
+    </row>
+    <row r="320" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A320" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C320" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D320" s="3">
+        <v>46111</v>
+      </c>
+      <c r="E320" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F320" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G320" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="H320" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="I320" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="J320" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="K320" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="L320" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="M320" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="N320" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="O320" s="4">
+        <v>680</v>
+      </c>
+      <c r="P320" s="4">
+        <v>17.45</v>
+      </c>
+      <c r="Q320" s="5">
+        <v>11866</v>
+      </c>
+      <c r="R320" s="5">
+        <v>385.65</v>
+      </c>
+      <c r="S320" s="5">
+        <v>12251.65</v>
+      </c>
+      <c r="T320" s="5">
+        <v>11866</v>
+      </c>
+      <c r="U320" s="5">
+        <v>474.64</v>
+      </c>
+      <c r="V320" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="W320" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="X320" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y320" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="Z320" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA320" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB320" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC320" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD320" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE320" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF320" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG320" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH320" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI320" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ320" s="4">
+        <v>7570.2835999999998</v>
+      </c>
+    </row>
+    <row r="321" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A321" s="6" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B321" s="6" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C321" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D321" s="7">
+        <v>46111</v>
+      </c>
+      <c r="E321" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F321" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G321" s="6" t="s">
+        <v>1337</v>
+      </c>
+      <c r="H321" s="6" t="s">
+        <v>1338</v>
+      </c>
+      <c r="I321" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J321" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K321" s="6" t="s">
+        <v>782</v>
+      </c>
+      <c r="L321" s="6" t="s">
+        <v>1166</v>
+      </c>
+      <c r="M321" s="6" t="s">
+        <v>1167</v>
+      </c>
+      <c r="N321" s="6" t="s">
+        <v>1168</v>
+      </c>
+      <c r="O321" s="8">
+        <v>500</v>
+      </c>
+      <c r="P321" s="8">
+        <v>13.18</v>
+      </c>
+      <c r="Q321" s="9">
+        <v>6590</v>
+      </c>
+      <c r="R321" s="9">
+        <v>214.18</v>
+      </c>
+      <c r="S321" s="9">
+        <v>6804.18</v>
+      </c>
+      <c r="T321" s="9">
+        <v>6590</v>
+      </c>
+      <c r="U321" s="9">
+        <v>263.60000000000002</v>
+      </c>
+      <c r="V321" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="W321" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="X321" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y321" s="6" t="s">
+        <v>1339</v>
+      </c>
+      <c r="Z321" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA321" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB321" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC321" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD321" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE321" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF321" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG321" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH321" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI321" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ321" s="8">
+        <v>4910.2299999999996</v>
+      </c>
+    </row>
+    <row r="322" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A322" s="2" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C322" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D322" s="3">
+        <v>46111</v>
+      </c>
+      <c r="E322" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F322" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G322" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="H322" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="I322" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="J322" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="K322" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="L322" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="M322" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="N322" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="O322" s="4">
+        <v>1295</v>
+      </c>
+      <c r="P322" s="4">
+        <v>21.21</v>
+      </c>
+      <c r="Q322" s="5">
+        <v>27466.95</v>
+      </c>
+      <c r="R322" s="5">
+        <v>892.68</v>
+      </c>
+      <c r="S322" s="5">
+        <v>28359.63</v>
+      </c>
+      <c r="T322" s="5">
+        <v>27466.95</v>
+      </c>
+      <c r="U322" s="5">
+        <v>4944.05</v>
+      </c>
+      <c r="V322" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="W322" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="X322" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y322" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="Z322" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA322" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB322" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC322" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD322" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE322" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF322" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG322" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH322" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI322" s="5">
+        <v>18</v>
+      </c>
+      <c r="AJ322" s="4">
+        <v>16676.453150000001</v>
+      </c>
+    </row>
+    <row r="323" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A323" s="6" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B323" s="6" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C323" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D323" s="7">
+        <v>46111</v>
+      </c>
+      <c r="E323" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F323" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G323" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H323" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="I323" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="J323" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="K323" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="L323" s="6" t="s">
+        <v>1257</v>
+      </c>
+      <c r="M323" s="6" t="s">
+        <v>1258</v>
+      </c>
+      <c r="N323" s="6" t="s">
+        <v>1259</v>
+      </c>
+      <c r="O323" s="8">
+        <v>1480</v>
+      </c>
+      <c r="P323" s="8">
+        <v>21.21</v>
+      </c>
+      <c r="Q323" s="9">
+        <v>31390.799999999999</v>
+      </c>
+      <c r="R323" s="9">
+        <v>1020.2</v>
+      </c>
+      <c r="S323" s="9">
+        <v>32411</v>
+      </c>
+      <c r="T323" s="9">
+        <v>31390.799999999999</v>
+      </c>
+      <c r="U323" s="9">
+        <v>5650.34</v>
+      </c>
+      <c r="V323" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="W323" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="X323" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y323" s="6" t="s">
+        <v>1343</v>
+      </c>
+      <c r="Z323" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA323" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB323" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC323" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD323" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE323" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF323" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG323" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH323" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI323" s="9">
+        <v>18</v>
+      </c>
+      <c r="AJ323" s="8">
+        <v>19058.803599999999</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ316" xr:uid="{83D18634-4744-4B01-A409-8C69F6FBA3B9}"/>
+  <autoFilter ref="A1:AJ323" xr:uid="{ADEADE99-9C44-4269-8B72-FB9410102EA0}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7750C0CA-A699-4DF4-84A9-3E776C737B11}">
-  <dimension ref="A1:AJ86"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42F6757A-88FA-46BC-A723-2ABE134244F9}">
+  <dimension ref="A1:AJ94"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="56.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="57.19921875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="13.19921875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.09765625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.09765625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.09765625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.09765625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="43.09765625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.69921875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.8984375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.8984375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.59765625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.59765625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.19921875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="27.3984375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.8984375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.19921875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.796875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="64.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="70.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="48" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="25.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -40211,15 +41071,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>1585</v>
+        <v>1616</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1585</v>
+        <v>1616</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D2" s="3">
         <v>46024</v>
@@ -40231,10 +41091,10 @@
         <v>39</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1422</v>
+        <v>1370</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>1421</v>
+        <v>1369</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>42</v>
@@ -40246,13 +41106,13 @@
         <v>440</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>1462</v>
+        <v>1368</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>1200</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>1461</v>
+        <v>1367</v>
       </c>
       <c r="O2" s="4">
         <v>50</v>
@@ -40276,16 +41136,16 @@
         <v>39.06</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>1460</v>
+        <v>1366</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>1459</v>
+        <v>1365</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>50</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>1584</v>
+        <v>1615</v>
       </c>
       <c r="Z2" s="2" t="s">
         <v>52</v>
@@ -40321,15 +41181,15 @@
         <v>559.65099999999995</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>1583</v>
+        <v>1614</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1583</v>
+        <v>1614</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D3" s="7">
         <v>46027</v>
@@ -40341,10 +41201,10 @@
         <v>61</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1351</v>
+        <v>1401</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>163</v>
@@ -40356,13 +41216,13 @@
         <v>632</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>1349</v>
+        <v>1399</v>
       </c>
       <c r="M3" s="6" t="s">
         <v>648</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1348</v>
+        <v>1398</v>
       </c>
       <c r="O3" s="8">
         <v>1001</v>
@@ -40395,7 +41255,7 @@
         <v>50</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>1582</v>
+        <v>1613</v>
       </c>
       <c r="Z3" s="6" t="s">
         <v>52</v>
@@ -40431,15 +41291,15 @@
         <v>10936.27535</v>
       </c>
     </row>
-    <row r="4" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>1581</v>
+        <v>1612</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1581</v>
+        <v>1612</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D4" s="3">
         <v>46027</v>
@@ -40451,10 +41311,10 @@
         <v>61</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1580</v>
+        <v>1611</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1579</v>
+        <v>1610</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>152</v>
@@ -40466,13 +41326,13 @@
         <v>342</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1578</v>
+        <v>1609</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1577</v>
+        <v>1608</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1576</v>
+        <v>1607</v>
       </c>
       <c r="O4" s="4">
         <v>600</v>
@@ -40496,16 +41356,16 @@
         <v>355.68</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>1575</v>
+        <v>1606</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>1574</v>
+        <v>1605</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>50</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>1573</v>
+        <v>1604</v>
       </c>
       <c r="Z4" s="2" t="s">
         <v>52</v>
@@ -40541,15 +41401,15 @@
         <v>5599.0079999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>1572</v>
+        <v>1603</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1572</v>
+        <v>1603</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D5" s="7">
         <v>46029</v>
@@ -40561,10 +41421,10 @@
         <v>212</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1504</v>
+        <v>1537</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1398</v>
+        <v>1445</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>139</v>
@@ -40573,7 +41433,7 @@
         <v>140</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>1571</v>
+        <v>1602</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>52</v>
@@ -40615,7 +41475,7 @@
         <v>87</v>
       </c>
       <c r="Y5" s="6" t="s">
-        <v>1570</v>
+        <v>1601</v>
       </c>
       <c r="Z5" s="6" t="s">
         <v>52</v>
@@ -40651,15 +41511,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>1572</v>
+        <v>1603</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1572</v>
+        <v>1603</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D6" s="3">
         <v>46029</v>
@@ -40671,10 +41531,10 @@
         <v>212</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1504</v>
+        <v>1537</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1398</v>
+        <v>1445</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>139</v>
@@ -40683,7 +41543,7 @@
         <v>140</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>1571</v>
+        <v>1602</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>52</v>
@@ -40725,7 +41585,7 @@
         <v>87</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>1570</v>
+        <v>1601</v>
       </c>
       <c r="Z6" s="2" t="s">
         <v>52</v>
@@ -40761,15 +41621,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>1569</v>
+        <v>1600</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1569</v>
+        <v>1600</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D7" s="7">
         <v>46029</v>
@@ -40787,22 +41647,22 @@
         <v>386</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1393</v>
+        <v>1440</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>1392</v>
+        <v>1439</v>
       </c>
       <c r="K7" s="6" t="s">
         <v>1058</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>1568</v>
+        <v>1347</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>1567</v>
+        <v>1346</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>1407</v>
+        <v>1345</v>
       </c>
       <c r="O7" s="8">
         <v>1000</v>
@@ -40835,7 +41695,7 @@
         <v>50</v>
       </c>
       <c r="Y7" s="6" t="s">
-        <v>1566</v>
+        <v>1599</v>
       </c>
       <c r="Z7" s="6" t="s">
         <v>52</v>
@@ -40871,15 +41731,15 @@
         <v>7047.1</v>
       </c>
     </row>
-    <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>1565</v>
+        <v>1598</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1565</v>
+        <v>1598</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D8" s="3">
         <v>46036</v>
@@ -40891,10 +41751,10 @@
         <v>61</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1351</v>
+        <v>1401</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>163</v>
@@ -40906,13 +41766,13 @@
         <v>632</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>1349</v>
+        <v>1399</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1348</v>
+        <v>1398</v>
       </c>
       <c r="O8" s="4">
         <v>1001</v>
@@ -40945,7 +41805,7 @@
         <v>50</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>1564</v>
+        <v>1597</v>
       </c>
       <c r="Z8" s="2" t="s">
         <v>52</v>
@@ -40981,15 +41841,15 @@
         <v>10936.27535</v>
       </c>
     </row>
-    <row r="9" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>1563</v>
+        <v>1596</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1563</v>
+        <v>1596</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D9" s="7">
         <v>46037</v>
@@ -41001,10 +41861,10 @@
         <v>61</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1330</v>
+        <v>1381</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1329</v>
+        <v>1380</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>163</v>
@@ -41016,13 +41876,13 @@
         <v>417</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>1562</v>
+        <v>1595</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>1041</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>1480</v>
+        <v>1515</v>
       </c>
       <c r="O9" s="8">
         <v>1000</v>
@@ -41055,7 +41915,7 @@
         <v>50</v>
       </c>
       <c r="Y9" s="6" t="s">
-        <v>1561</v>
+        <v>1594</v>
       </c>
       <c r="Z9" s="6" t="s">
         <v>52</v>
@@ -41091,15 +41951,15 @@
         <v>9879.4500000000007</v>
       </c>
     </row>
-    <row r="10" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>1560</v>
+        <v>1593</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1560</v>
+        <v>1593</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D10" s="3">
         <v>46037</v>
@@ -41126,13 +41986,13 @@
         <v>782</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>1416</v>
+        <v>1363</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1415</v>
+        <v>1362</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1414</v>
+        <v>1361</v>
       </c>
       <c r="O10" s="4">
         <v>300</v>
@@ -41165,7 +42025,7 @@
         <v>50</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>1559</v>
+        <v>1592</v>
       </c>
       <c r="Z10" s="2" t="s">
         <v>52</v>
@@ -41201,15 +42061,15 @@
         <v>2966.9070000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>1558</v>
+        <v>1591</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1558</v>
+        <v>1591</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D11" s="7">
         <v>46037</v>
@@ -41236,13 +42096,13 @@
         <v>300</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>1358</v>
+        <v>1408</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>1357</v>
+        <v>1407</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="O11" s="8">
         <v>25</v>
@@ -41275,7 +42135,7 @@
         <v>50</v>
       </c>
       <c r="Y11" s="6" t="s">
-        <v>1557</v>
+        <v>1590</v>
       </c>
       <c r="Z11" s="6" t="s">
         <v>52</v>
@@ -41311,15 +42171,15 @@
         <v>189.62575000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>1556</v>
+        <v>1589</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1556</v>
+        <v>1589</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D12" s="3">
         <v>46041</v>
@@ -41331,10 +42191,10 @@
         <v>212</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1504</v>
+        <v>1537</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1398</v>
+        <v>1445</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>139</v>
@@ -41343,7 +42203,7 @@
         <v>140</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>1341</v>
+        <v>1391</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>52</v>
@@ -41385,7 +42245,7 @@
         <v>87</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>1555</v>
+        <v>1588</v>
       </c>
       <c r="Z12" s="2" t="s">
         <v>52</v>
@@ -41400,10 +42260,10 @@
         <v>55</v>
       </c>
       <c r="AD12" s="2" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>1333</v>
+        <v>1383</v>
       </c>
       <c r="AF12" s="2" t="s">
         <v>442</v>
@@ -41421,15 +42281,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>1554</v>
+        <v>1587</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1554</v>
+        <v>1587</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D13" s="7">
         <v>46042</v>
@@ -41447,22 +42307,22 @@
         <v>386</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>1393</v>
+        <v>1440</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>1392</v>
+        <v>1439</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>446</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>1478</v>
+        <v>1513</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>1477</v>
+        <v>1512</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>1389</v>
+        <v>1436</v>
       </c>
       <c r="O13" s="8">
         <v>2000</v>
@@ -41495,7 +42355,7 @@
         <v>50</v>
       </c>
       <c r="Y13" s="6" t="s">
-        <v>1553</v>
+        <v>1586</v>
       </c>
       <c r="Z13" s="6" t="s">
         <v>52</v>
@@ -41531,15 +42391,15 @@
         <v>20682.54</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>1552</v>
+        <v>1585</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1552</v>
+        <v>1585</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D14" s="3">
         <v>46042</v>
@@ -41563,16 +42423,16 @@
         <v>294</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>1341</v>
+        <v>1391</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>1527</v>
+        <v>1560</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1526</v>
+        <v>1559</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1338</v>
+        <v>1388</v>
       </c>
       <c r="O14" s="4">
         <v>6000</v>
@@ -41596,16 +42456,16 @@
         <v>12873.6</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>1385</v>
+        <v>1432</v>
       </c>
       <c r="X14" s="2" t="s">
         <v>50</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>1551</v>
+        <v>1584</v>
       </c>
       <c r="Z14" s="2" t="s">
         <v>52</v>
@@ -41620,10 +42480,10 @@
         <v>298</v>
       </c>
       <c r="AD14" s="2" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="AE14" s="2" t="s">
-        <v>1333</v>
+        <v>1383</v>
       </c>
       <c r="AF14" s="2" t="s">
         <v>77</v>
@@ -41641,15 +42501,15 @@
         <v>67831.62</v>
       </c>
     </row>
-    <row r="15" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>1550</v>
+        <v>1583</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1550</v>
+        <v>1583</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D15" s="7">
         <v>46042</v>
@@ -41661,10 +42521,10 @@
         <v>212</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>1504</v>
+        <v>1537</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>1398</v>
+        <v>1445</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>139</v>
@@ -41715,7 +42575,7 @@
         <v>87</v>
       </c>
       <c r="Y15" s="6" t="s">
-        <v>1549</v>
+        <v>1582</v>
       </c>
       <c r="Z15" s="6" t="s">
         <v>52</v>
@@ -41736,7 +42596,7 @@
         <v>518</v>
       </c>
       <c r="AF15" s="6" t="s">
-        <v>1522</v>
+        <v>1555</v>
       </c>
       <c r="AG15" s="9">
         <v>0</v>
@@ -41751,15 +42611,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>1550</v>
+        <v>1583</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1550</v>
+        <v>1583</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D16" s="3">
         <v>46042</v>
@@ -41771,10 +42631,10 @@
         <v>212</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1504</v>
+        <v>1537</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1398</v>
+        <v>1445</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>139</v>
@@ -41825,7 +42685,7 @@
         <v>87</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>1549</v>
+        <v>1582</v>
       </c>
       <c r="Z16" s="2" t="s">
         <v>52</v>
@@ -41846,7 +42706,7 @@
         <v>518</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>1522</v>
+        <v>1555</v>
       </c>
       <c r="AG16" s="5">
         <v>0</v>
@@ -41861,15 +42721,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>1548</v>
+        <v>1581</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>1548</v>
+        <v>1581</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D17" s="7">
         <v>46043</v>
@@ -41896,13 +42756,13 @@
         <v>417</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>1482</v>
+        <v>1517</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>1481</v>
+        <v>1516</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>1480</v>
+        <v>1515</v>
       </c>
       <c r="O17" s="8">
         <v>1000</v>
@@ -41935,7 +42795,7 @@
         <v>50</v>
       </c>
       <c r="Y17" s="6" t="s">
-        <v>1547</v>
+        <v>1580</v>
       </c>
       <c r="Z17" s="6" t="s">
         <v>52</v>
@@ -41971,30 +42831,30 @@
         <v>9879.4500000000007</v>
       </c>
     </row>
-    <row r="18" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>1537</v>
+        <v>1570</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1537</v>
+        <v>1570</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D18" s="3">
         <v>46045</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1405</v>
+        <v>1450</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1404</v>
+        <v>1449</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1403</v>
+        <v>1448</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>1402</v>
+        <v>1447</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>139</v>
@@ -42006,13 +42866,13 @@
         <v>628</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>1546</v>
+        <v>1579</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1545</v>
+        <v>1578</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1544</v>
+        <v>1577</v>
       </c>
       <c r="O18" s="4">
         <v>2000</v>
@@ -42036,16 +42896,16 @@
         <v>0</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>1399</v>
+        <v>1446</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>1398</v>
+        <v>1445</v>
       </c>
       <c r="X18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>1533</v>
+        <v>1566</v>
       </c>
       <c r="Z18" s="2" t="s">
         <v>52</v>
@@ -42081,30 +42941,30 @@
         <v>20543.54</v>
       </c>
     </row>
-    <row r="19" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>1537</v>
+        <v>1570</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>1537</v>
+        <v>1570</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D19" s="7">
         <v>46045</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>1405</v>
+        <v>1450</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>1404</v>
+        <v>1449</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>1403</v>
+        <v>1448</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>1402</v>
+        <v>1447</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>139</v>
@@ -42116,13 +42976,13 @@
         <v>631</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>1543</v>
+        <v>1576</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>1542</v>
+        <v>1575</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>1534</v>
+        <v>1567</v>
       </c>
       <c r="O19" s="8">
         <v>11725</v>
@@ -42146,16 +43006,16 @@
         <v>0</v>
       </c>
       <c r="V19" s="6" t="s">
-        <v>1399</v>
+        <v>1446</v>
       </c>
       <c r="W19" s="6" t="s">
-        <v>1398</v>
+        <v>1445</v>
       </c>
       <c r="X19" s="6" t="s">
         <v>87</v>
       </c>
       <c r="Y19" s="6" t="s">
-        <v>1533</v>
+        <v>1566</v>
       </c>
       <c r="Z19" s="6" t="s">
         <v>52</v>
@@ -42191,30 +43051,30 @@
         <v>298929.93024999998</v>
       </c>
     </row>
-    <row r="20" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>1537</v>
+        <v>1570</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1537</v>
+        <v>1570</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D20" s="3">
         <v>46045</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1405</v>
+        <v>1450</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1404</v>
+        <v>1449</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1403</v>
+        <v>1448</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1402</v>
+        <v>1447</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>139</v>
@@ -42226,13 +43086,13 @@
         <v>632</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>1349</v>
+        <v>1399</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1348</v>
+        <v>1398</v>
       </c>
       <c r="O20" s="4">
         <v>2925</v>
@@ -42256,16 +43116,16 @@
         <v>0</v>
       </c>
       <c r="V20" s="2" t="s">
-        <v>1399</v>
+        <v>1446</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>1398</v>
+        <v>1445</v>
       </c>
       <c r="X20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>1533</v>
+        <v>1566</v>
       </c>
       <c r="Z20" s="2" t="s">
         <v>52</v>
@@ -42301,30 +43161,30 @@
         <v>31956.64875</v>
       </c>
     </row>
-    <row r="21" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>1537</v>
+        <v>1570</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1537</v>
+        <v>1570</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D21" s="7">
         <v>46045</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>1405</v>
+        <v>1450</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>1404</v>
+        <v>1449</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>1403</v>
+        <v>1448</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>1402</v>
+        <v>1447</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>139</v>
@@ -42336,13 +43196,13 @@
         <v>633</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>1376</v>
+        <v>1426</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>652</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>1375</v>
+        <v>1425</v>
       </c>
       <c r="O21" s="8">
         <v>2925</v>
@@ -42366,16 +43226,16 @@
         <v>0</v>
       </c>
       <c r="V21" s="6" t="s">
-        <v>1399</v>
+        <v>1446</v>
       </c>
       <c r="W21" s="6" t="s">
-        <v>1398</v>
+        <v>1445</v>
       </c>
       <c r="X21" s="6" t="s">
         <v>87</v>
       </c>
       <c r="Y21" s="6" t="s">
-        <v>1533</v>
+        <v>1566</v>
       </c>
       <c r="Z21" s="6" t="s">
         <v>52</v>
@@ -42411,30 +43271,30 @@
         <v>41812.787250000001</v>
       </c>
     </row>
-    <row r="22" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>1537</v>
+        <v>1570</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1537</v>
+        <v>1570</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D22" s="3">
         <v>46045</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1405</v>
+        <v>1450</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1404</v>
+        <v>1449</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1403</v>
+        <v>1448</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1402</v>
+        <v>1447</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>139</v>
@@ -42446,13 +43306,13 @@
         <v>465</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1541</v>
+        <v>1574</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>1109</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1540</v>
+        <v>1573</v>
       </c>
       <c r="O22" s="4">
         <v>2400</v>
@@ -42476,16 +43336,16 @@
         <v>0</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>1399</v>
+        <v>1446</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>1398</v>
+        <v>1445</v>
       </c>
       <c r="X22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>1533</v>
+        <v>1566</v>
       </c>
       <c r="Z22" s="2" t="s">
         <v>52</v>
@@ -42521,30 +43381,30 @@
         <v>33755.375999999997</v>
       </c>
     </row>
-    <row r="23" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>1537</v>
+        <v>1570</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>1537</v>
+        <v>1570</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D23" s="7">
         <v>46045</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>1405</v>
+        <v>1450</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>1404</v>
+        <v>1449</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>1403</v>
+        <v>1448</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>1402</v>
+        <v>1447</v>
       </c>
       <c r="I23" s="6" t="s">
         <v>139</v>
@@ -42556,13 +43416,13 @@
         <v>465</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>1539</v>
+        <v>1572</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>1175</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>1538</v>
+        <v>1571</v>
       </c>
       <c r="O23" s="8">
         <v>1800</v>
@@ -42586,16 +43446,16 @@
         <v>0</v>
       </c>
       <c r="V23" s="6" t="s">
-        <v>1399</v>
+        <v>1446</v>
       </c>
       <c r="W23" s="6" t="s">
-        <v>1398</v>
+        <v>1445</v>
       </c>
       <c r="X23" s="6" t="s">
         <v>87</v>
       </c>
       <c r="Y23" s="6" t="s">
-        <v>1533</v>
+        <v>1566</v>
       </c>
       <c r="Z23" s="6" t="s">
         <v>52</v>
@@ -42631,30 +43491,30 @@
         <v>25316.531999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>1537</v>
+        <v>1570</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1537</v>
+        <v>1570</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D24" s="3">
         <v>46045</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1405</v>
+        <v>1450</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1404</v>
+        <v>1449</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1403</v>
+        <v>1448</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1402</v>
+        <v>1447</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>139</v>
@@ -42666,13 +43526,13 @@
         <v>634</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>1536</v>
+        <v>1569</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1535</v>
+        <v>1568</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1534</v>
+        <v>1567</v>
       </c>
       <c r="O24" s="4">
         <v>1400</v>
@@ -42696,16 +43556,16 @@
         <v>0</v>
       </c>
       <c r="V24" s="2" t="s">
-        <v>1399</v>
+        <v>1446</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>1398</v>
+        <v>1445</v>
       </c>
       <c r="X24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>1533</v>
+        <v>1566</v>
       </c>
       <c r="Z24" s="2" t="s">
         <v>52</v>
@@ -42741,15 +43601,15 @@
         <v>19885.75</v>
       </c>
     </row>
-    <row r="25" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>1532</v>
+        <v>1565</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>1532</v>
+        <v>1565</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D25" s="7">
         <v>46048</v>
@@ -42776,13 +43636,13 @@
         <v>417</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>1489</v>
+        <v>1524</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>1488</v>
+        <v>1523</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>1411</v>
+        <v>1455</v>
       </c>
       <c r="O25" s="8">
         <v>5000</v>
@@ -42815,7 +43675,7 @@
         <v>50</v>
       </c>
       <c r="Y25" s="6" t="s">
-        <v>1531</v>
+        <v>1564</v>
       </c>
       <c r="Z25" s="6" t="s">
         <v>52</v>
@@ -42851,15 +43711,15 @@
         <v>49397.25</v>
       </c>
     </row>
-    <row r="26" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>1530</v>
+        <v>1563</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1530</v>
+        <v>1563</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D26" s="3">
         <v>46048</v>
@@ -42886,13 +43746,13 @@
         <v>782</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>1416</v>
+        <v>1363</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1415</v>
+        <v>1362</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1414</v>
+        <v>1361</v>
       </c>
       <c r="O26" s="4">
         <v>300</v>
@@ -42925,7 +43785,7 @@
         <v>50</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>1529</v>
+        <v>1562</v>
       </c>
       <c r="Z26" s="2" t="s">
         <v>52</v>
@@ -42961,15 +43821,15 @@
         <v>2966.9070000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>1528</v>
+        <v>1561</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>1528</v>
+        <v>1561</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D27" s="7">
         <v>46048</v>
@@ -42981,10 +43841,10 @@
         <v>61</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>1351</v>
+        <v>1401</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>163</v>
@@ -42996,13 +43856,13 @@
         <v>632</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>1349</v>
+        <v>1399</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>648</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>1348</v>
+        <v>1398</v>
       </c>
       <c r="O27" s="8">
         <v>611</v>
@@ -43035,7 +43895,7 @@
         <v>50</v>
       </c>
       <c r="Y27" s="6" t="s">
-        <v>1525</v>
+        <v>1558</v>
       </c>
       <c r="Z27" s="6" t="s">
         <v>52</v>
@@ -43071,15 +43931,15 @@
         <v>6675.3888500000003</v>
       </c>
     </row>
-    <row r="28" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>1528</v>
+        <v>1561</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1528</v>
+        <v>1561</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D28" s="3">
         <v>46048</v>
@@ -43091,10 +43951,10 @@
         <v>61</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1351</v>
+        <v>1401</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>163</v>
@@ -43103,16 +43963,16 @@
         <v>164</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>1341</v>
+        <v>1391</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>1527</v>
+        <v>1560</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1526</v>
+        <v>1559</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1338</v>
+        <v>1388</v>
       </c>
       <c r="O28" s="4">
         <v>700</v>
@@ -43145,7 +44005,7 @@
         <v>50</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>1525</v>
+        <v>1558</v>
       </c>
       <c r="Z28" s="2" t="s">
         <v>52</v>
@@ -43160,10 +44020,10 @@
         <v>55</v>
       </c>
       <c r="AD28" s="2" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="AE28" s="2" t="s">
-        <v>1333</v>
+        <v>1383</v>
       </c>
       <c r="AF28" s="2" t="s">
         <v>77</v>
@@ -43181,15 +44041,15 @@
         <v>6276.0389999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>1524</v>
+        <v>1557</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>1524</v>
+        <v>1557</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D29" s="7">
         <v>46048</v>
@@ -43201,10 +44061,10 @@
         <v>212</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>1504</v>
+        <v>1537</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>1398</v>
+        <v>1445</v>
       </c>
       <c r="I29" s="6" t="s">
         <v>139</v>
@@ -43255,7 +44115,7 @@
         <v>87</v>
       </c>
       <c r="Y29" s="6" t="s">
-        <v>1523</v>
+        <v>1556</v>
       </c>
       <c r="Z29" s="6" t="s">
         <v>52</v>
@@ -43276,7 +44136,7 @@
         <v>57</v>
       </c>
       <c r="AF29" s="6" t="s">
-        <v>1522</v>
+        <v>1555</v>
       </c>
       <c r="AG29" s="9">
         <v>0</v>
@@ -43291,15 +44151,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>1521</v>
+        <v>1554</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1521</v>
+        <v>1554</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D30" s="3">
         <v>46049</v>
@@ -43311,10 +44171,10 @@
         <v>212</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1504</v>
+        <v>1537</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1398</v>
+        <v>1445</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>139</v>
@@ -43365,7 +44225,7 @@
         <v>87</v>
       </c>
       <c r="Y30" s="2" t="s">
-        <v>1520</v>
+        <v>1553</v>
       </c>
       <c r="Z30" s="2" t="s">
         <v>52</v>
@@ -43401,15 +44261,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
-        <v>1521</v>
+        <v>1554</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>1521</v>
+        <v>1554</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D31" s="7">
         <v>46049</v>
@@ -43421,10 +44281,10 @@
         <v>212</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>1504</v>
+        <v>1537</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>1398</v>
+        <v>1445</v>
       </c>
       <c r="I31" s="6" t="s">
         <v>139</v>
@@ -43475,7 +44335,7 @@
         <v>87</v>
       </c>
       <c r="Y31" s="6" t="s">
-        <v>1520</v>
+        <v>1553</v>
       </c>
       <c r="Z31" s="6" t="s">
         <v>52</v>
@@ -43511,15 +44371,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>1517</v>
+        <v>1550</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1517</v>
+        <v>1550</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D32" s="3">
         <v>46050</v>
@@ -43537,22 +44397,22 @@
         <v>386</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>1393</v>
+        <v>1440</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>1392</v>
+        <v>1439</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>446</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>1519</v>
+        <v>1552</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>448</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1518</v>
+        <v>1551</v>
       </c>
       <c r="O32" s="4">
         <v>1000</v>
@@ -43585,7 +44445,7 @@
         <v>50</v>
       </c>
       <c r="Y32" s="2" t="s">
-        <v>1516</v>
+        <v>1549</v>
       </c>
       <c r="Z32" s="2" t="s">
         <v>52</v>
@@ -43621,15 +44481,15 @@
         <v>10341.27</v>
       </c>
     </row>
-    <row r="33" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
-        <v>1517</v>
+        <v>1550</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>1517</v>
+        <v>1550</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D33" s="7">
         <v>46050</v>
@@ -43647,22 +44507,22 @@
         <v>386</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>1393</v>
+        <v>1440</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>1392</v>
+        <v>1439</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>446</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>1478</v>
+        <v>1513</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>1477</v>
+        <v>1512</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>1389</v>
+        <v>1436</v>
       </c>
       <c r="O33" s="8">
         <v>1000</v>
@@ -43695,7 +44555,7 @@
         <v>50</v>
       </c>
       <c r="Y33" s="6" t="s">
-        <v>1516</v>
+        <v>1549</v>
       </c>
       <c r="Z33" s="6" t="s">
         <v>52</v>
@@ -43731,15 +44591,15 @@
         <v>10341.27</v>
       </c>
     </row>
-    <row r="34" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>1515</v>
+        <v>1548</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1515</v>
+        <v>1548</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D34" s="3">
         <v>46050</v>
@@ -43751,10 +44611,10 @@
         <v>212</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1504</v>
+        <v>1537</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>1398</v>
+        <v>1445</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>139</v>
@@ -43805,7 +44665,7 @@
         <v>87</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>1514</v>
+        <v>1547</v>
       </c>
       <c r="Z34" s="2" t="s">
         <v>52</v>
@@ -43841,15 +44701,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
-        <v>1513</v>
+        <v>1546</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>1513</v>
+        <v>1546</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D35" s="7">
         <v>46051</v>
@@ -43876,13 +44736,13 @@
         <v>632</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>1349</v>
+        <v>1399</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>648</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>1348</v>
+        <v>1398</v>
       </c>
       <c r="O35" s="8">
         <v>26</v>
@@ -43915,7 +44775,7 @@
         <v>50</v>
       </c>
       <c r="Y35" s="6" t="s">
-        <v>1512</v>
+        <v>1545</v>
       </c>
       <c r="Z35" s="6" t="s">
         <v>52</v>
@@ -43951,15 +44811,15 @@
         <v>284.0591</v>
       </c>
     </row>
-    <row r="36" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>1511</v>
+        <v>1544</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>1511</v>
+        <v>1544</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D36" s="3">
         <v>46052</v>
@@ -43971,10 +44831,10 @@
         <v>61</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1351</v>
+        <v>1401</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>163</v>
@@ -43986,13 +44846,13 @@
         <v>632</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>1349</v>
+        <v>1399</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1348</v>
+        <v>1398</v>
       </c>
       <c r="O36" s="4">
         <v>507</v>
@@ -44025,7 +44885,7 @@
         <v>50</v>
       </c>
       <c r="Y36" s="2" t="s">
-        <v>1510</v>
+        <v>1543</v>
       </c>
       <c r="Z36" s="2" t="s">
         <v>52</v>
@@ -44061,15 +44921,15 @@
         <v>5539.1524499999996</v>
       </c>
     </row>
-    <row r="37" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
-        <v>1509</v>
+        <v>1542</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>1509</v>
+        <v>1542</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D37" s="7">
         <v>46052</v>
@@ -44093,16 +44953,16 @@
         <v>164</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>1368</v>
+        <v>1418</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>1447</v>
+        <v>1486</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>1446</v>
+        <v>1485</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>1365</v>
+        <v>1415</v>
       </c>
       <c r="O37" s="8">
         <v>500</v>
@@ -44135,7 +44995,7 @@
         <v>50</v>
       </c>
       <c r="Y37" s="6" t="s">
-        <v>1508</v>
+        <v>1541</v>
       </c>
       <c r="Z37" s="6" t="s">
         <v>52</v>
@@ -44171,15 +45031,15 @@
         <v>4405.1099999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>1507</v>
+        <v>1540</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1507</v>
+        <v>1540</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D38" s="3">
         <v>46052</v>
@@ -44206,13 +45066,13 @@
         <v>782</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>1416</v>
+        <v>1363</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>1415</v>
+        <v>1362</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>1414</v>
+        <v>1361</v>
       </c>
       <c r="O38" s="4">
         <v>300</v>
@@ -44245,7 +45105,7 @@
         <v>50</v>
       </c>
       <c r="Y38" s="2" t="s">
-        <v>1506</v>
+        <v>1539</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>52</v>
@@ -44281,15 +45141,15 @@
         <v>2966.9070000000002</v>
       </c>
     </row>
-    <row r="39" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
-        <v>1505</v>
+        <v>1538</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>1505</v>
+        <v>1538</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D39" s="7">
         <v>46055</v>
@@ -44301,10 +45161,10 @@
         <v>212</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>1504</v>
+        <v>1537</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>1398</v>
+        <v>1445</v>
       </c>
       <c r="I39" s="6" t="s">
         <v>139</v>
@@ -44313,7 +45173,7 @@
         <v>140</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>1503</v>
+        <v>1536</v>
       </c>
       <c r="L39" s="6" t="s">
         <v>52</v>
@@ -44355,7 +45215,7 @@
         <v>87</v>
       </c>
       <c r="Y39" s="6" t="s">
-        <v>1502</v>
+        <v>1535</v>
       </c>
       <c r="Z39" s="6" t="s">
         <v>52</v>
@@ -44391,15 +45251,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>1501</v>
+        <v>1534</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1501</v>
+        <v>1534</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D40" s="3">
         <v>46057</v>
@@ -44411,10 +45271,10 @@
         <v>61</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1351</v>
+        <v>1401</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>163</v>
@@ -44426,13 +45286,13 @@
         <v>632</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>1349</v>
+        <v>1399</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>1348</v>
+        <v>1398</v>
       </c>
       <c r="O40" s="4">
         <v>507</v>
@@ -44465,7 +45325,7 @@
         <v>50</v>
       </c>
       <c r="Y40" s="2" t="s">
-        <v>1500</v>
+        <v>1533</v>
       </c>
       <c r="Z40" s="2" t="s">
         <v>52</v>
@@ -44501,15 +45361,15 @@
         <v>5539.1524499999996</v>
       </c>
     </row>
-    <row r="41" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
-        <v>1499</v>
+        <v>1532</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>1499</v>
+        <v>1532</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D41" s="7">
         <v>46057</v>
@@ -44527,22 +45387,22 @@
         <v>386</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>1393</v>
+        <v>1440</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>1392</v>
+        <v>1439</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>446</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>1478</v>
+        <v>1513</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>1477</v>
+        <v>1512</v>
       </c>
       <c r="N41" s="6" t="s">
-        <v>1389</v>
+        <v>1436</v>
       </c>
       <c r="O41" s="8">
         <v>2000</v>
@@ -44575,7 +45435,7 @@
         <v>50</v>
       </c>
       <c r="Y41" s="6" t="s">
-        <v>1475</v>
+        <v>1510</v>
       </c>
       <c r="Z41" s="6" t="s">
         <v>52</v>
@@ -44611,15 +45471,15 @@
         <v>20780.28</v>
       </c>
     </row>
-    <row r="42" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>1498</v>
+        <v>1531</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1498</v>
+        <v>1531</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D42" s="3">
         <v>46058</v>
@@ -44631,10 +45491,10 @@
         <v>61</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1351</v>
+        <v>1401</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>163</v>
@@ -44646,13 +45506,13 @@
         <v>632</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>1349</v>
+        <v>1399</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>1348</v>
+        <v>1398</v>
       </c>
       <c r="O42" s="4">
         <v>507</v>
@@ -44685,7 +45545,7 @@
         <v>50</v>
       </c>
       <c r="Y42" s="2" t="s">
-        <v>1497</v>
+        <v>1530</v>
       </c>
       <c r="Z42" s="2" t="s">
         <v>52</v>
@@ -44721,15 +45581,15 @@
         <v>5539.1524499999996</v>
       </c>
     </row>
-    <row r="43" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
-        <v>1496</v>
+        <v>1529</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>1496</v>
+        <v>1529</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D43" s="7">
         <v>46058</v>
@@ -44741,10 +45601,10 @@
         <v>61</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>1450</v>
+        <v>1489</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>1449</v>
+        <v>1488</v>
       </c>
       <c r="I43" s="6" t="s">
         <v>163</v>
@@ -44756,13 +45616,13 @@
         <v>417</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>1489</v>
+        <v>1524</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>1488</v>
+        <v>1523</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>1411</v>
+        <v>1455</v>
       </c>
       <c r="O43" s="8">
         <v>1800</v>
@@ -44795,7 +45655,7 @@
         <v>50</v>
       </c>
       <c r="Y43" s="6" t="s">
-        <v>1495</v>
+        <v>1528</v>
       </c>
       <c r="Z43" s="6" t="s">
         <v>52</v>
@@ -44831,15 +45691,15 @@
         <v>17614.835999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>1494</v>
+        <v>1527</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>1494</v>
+        <v>1527</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D44" s="3">
         <v>46059</v>
@@ -44851,10 +45711,10 @@
         <v>39</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1493</v>
+        <v>1337</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>1492</v>
+        <v>1338</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>42</v>
@@ -44866,13 +45726,13 @@
         <v>782</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>1416</v>
+        <v>1363</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>1415</v>
+        <v>1362</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>1414</v>
+        <v>1361</v>
       </c>
       <c r="O44" s="4">
         <v>500</v>
@@ -44905,7 +45765,7 @@
         <v>50</v>
       </c>
       <c r="Y44" s="2" t="s">
-        <v>1491</v>
+        <v>1526</v>
       </c>
       <c r="Z44" s="2" t="s">
         <v>52</v>
@@ -44941,15 +45801,15 @@
         <v>4944.8450000000003</v>
       </c>
     </row>
-    <row r="45" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
-        <v>1490</v>
+        <v>1525</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>1490</v>
+        <v>1525</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D45" s="7">
         <v>46059</v>
@@ -44961,10 +45821,10 @@
         <v>39</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>1345</v>
+        <v>1395</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>1344</v>
+        <v>1394</v>
       </c>
       <c r="I45" s="6" t="s">
         <v>42</v>
@@ -44976,13 +45836,13 @@
         <v>417</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>1489</v>
+        <v>1524</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>1488</v>
+        <v>1523</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>1411</v>
+        <v>1455</v>
       </c>
       <c r="O45" s="8">
         <v>200</v>
@@ -45015,7 +45875,7 @@
         <v>50</v>
       </c>
       <c r="Y45" s="6" t="s">
-        <v>1487</v>
+        <v>1522</v>
       </c>
       <c r="Z45" s="6" t="s">
         <v>52</v>
@@ -45051,28 +45911,28 @@
         <v>1957.0440000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>1486</v>
+        <v>1521</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1486</v>
+        <v>1521</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D46" s="3">
         <v>46063</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1485</v>
+        <v>1520</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
-        <v>1403</v>
+        <v>1448</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>1402</v>
+        <v>1447</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>139</v>
@@ -45121,7 +45981,7 @@
         <v>52</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>1484</v>
+        <v>1519</v>
       </c>
       <c r="Z46" s="2" t="s">
         <v>52</v>
@@ -45157,15 +46017,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
-        <v>1483</v>
+        <v>1518</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>1483</v>
+        <v>1518</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D47" s="7">
         <v>46064</v>
@@ -45177,10 +46037,10 @@
         <v>61</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>1330</v>
+        <v>1381</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>1329</v>
+        <v>1380</v>
       </c>
       <c r="I47" s="6" t="s">
         <v>139</v>
@@ -45192,13 +46052,13 @@
         <v>417</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>1482</v>
+        <v>1517</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>1481</v>
+        <v>1516</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>1480</v>
+        <v>1515</v>
       </c>
       <c r="O47" s="8">
         <v>1000</v>
@@ -45231,7 +46091,7 @@
         <v>50</v>
       </c>
       <c r="Y47" s="6" t="s">
-        <v>1479</v>
+        <v>1514</v>
       </c>
       <c r="Z47" s="6" t="s">
         <v>52</v>
@@ -45267,15 +46127,15 @@
         <v>9788.69</v>
       </c>
     </row>
-    <row r="48" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>1476</v>
+        <v>1511</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1476</v>
+        <v>1511</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D48" s="3">
         <v>46064</v>
@@ -45293,22 +46153,22 @@
         <v>386</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>1393</v>
+        <v>1440</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>1392</v>
+        <v>1439</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>446</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>1478</v>
+        <v>1513</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>1477</v>
+        <v>1512</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>1389</v>
+        <v>1436</v>
       </c>
       <c r="O48" s="4">
         <v>1000</v>
@@ -45341,7 +46201,7 @@
         <v>50</v>
       </c>
       <c r="Y48" s="2" t="s">
-        <v>1475</v>
+        <v>1510</v>
       </c>
       <c r="Z48" s="2" t="s">
         <v>52</v>
@@ -45377,15 +46237,15 @@
         <v>10390.14</v>
       </c>
     </row>
-    <row r="49" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
-        <v>1476</v>
+        <v>1511</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>1476</v>
+        <v>1511</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D49" s="7">
         <v>46064</v>
@@ -45403,22 +46263,22 @@
         <v>386</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>1393</v>
+        <v>1440</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>1392</v>
+        <v>1439</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>446</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>1391</v>
+        <v>1438</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>1390</v>
+        <v>1437</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>1389</v>
+        <v>1436</v>
       </c>
       <c r="O49" s="8">
         <v>1000</v>
@@ -45451,7 +46311,7 @@
         <v>50</v>
       </c>
       <c r="Y49" s="6" t="s">
-        <v>1475</v>
+        <v>1510</v>
       </c>
       <c r="Z49" s="6" t="s">
         <v>52</v>
@@ -45487,15 +46347,15 @@
         <v>10390.14</v>
       </c>
     </row>
-    <row r="50" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>1474</v>
+        <v>1509</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>1474</v>
+        <v>1509</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D50" s="3">
         <v>46066</v>
@@ -45507,10 +46367,10 @@
         <v>61</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1351</v>
+        <v>1401</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>163</v>
@@ -45522,13 +46382,13 @@
         <v>632</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>1349</v>
+        <v>1399</v>
       </c>
       <c r="M50" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>1348</v>
+        <v>1398</v>
       </c>
       <c r="O50" s="4">
         <v>507</v>
@@ -45561,7 +46421,7 @@
         <v>50</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>1473</v>
+        <v>1508</v>
       </c>
       <c r="Z50" s="2" t="s">
         <v>52</v>
@@ -45597,15 +46457,15 @@
         <v>5539.1575199999997</v>
       </c>
     </row>
-    <row r="51" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
-        <v>1472</v>
+        <v>1507</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>1472</v>
+        <v>1507</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D51" s="7">
         <v>46071</v>
@@ -45629,16 +46489,16 @@
         <v>164</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>1341</v>
+        <v>1391</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>1471</v>
+        <v>1506</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>1470</v>
+        <v>1505</v>
       </c>
       <c r="N51" s="6" t="s">
-        <v>1469</v>
+        <v>1504</v>
       </c>
       <c r="O51" s="8">
         <v>500</v>
@@ -45671,7 +46531,7 @@
         <v>50</v>
       </c>
       <c r="Y51" s="6" t="s">
-        <v>1468</v>
+        <v>1503</v>
       </c>
       <c r="Z51" s="6" t="s">
         <v>52</v>
@@ -45686,10 +46546,10 @@
         <v>111</v>
       </c>
       <c r="AD51" s="6" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="AE51" s="6" t="s">
-        <v>1333</v>
+        <v>1383</v>
       </c>
       <c r="AF51" s="6" t="s">
         <v>77</v>
@@ -45707,15 +46567,15 @@
         <v>4836.3900000000003</v>
       </c>
     </row>
-    <row r="52" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>1467</v>
+        <v>1502</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1467</v>
+        <v>1502</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D52" s="3">
         <v>46071</v>
@@ -45727,10 +46587,10 @@
         <v>61</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1466</v>
+        <v>1501</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>1465</v>
+        <v>1500</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>139</v>
@@ -45742,13 +46602,13 @@
         <v>446</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>1391</v>
+        <v>1438</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>1390</v>
+        <v>1437</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>1389</v>
+        <v>1436</v>
       </c>
       <c r="O52" s="4">
         <v>200</v>
@@ -45781,7 +46641,7 @@
         <v>50</v>
       </c>
       <c r="Y52" s="2" t="s">
-        <v>1464</v>
+        <v>1499</v>
       </c>
       <c r="Z52" s="2" t="s">
         <v>52</v>
@@ -45817,15 +46677,15 @@
         <v>2078.0279999999998</v>
       </c>
     </row>
-    <row r="53" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
-        <v>1463</v>
+        <v>1498</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>1463</v>
+        <v>1498</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D53" s="7">
         <v>46072</v>
@@ -45837,10 +46697,10 @@
         <v>39</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>1422</v>
+        <v>1370</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>1421</v>
+        <v>1369</v>
       </c>
       <c r="I53" s="6" t="s">
         <v>42</v>
@@ -45852,13 +46712,13 @@
         <v>440</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>1462</v>
+        <v>1368</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>1200</v>
       </c>
       <c r="N53" s="6" t="s">
-        <v>1461</v>
+        <v>1367</v>
       </c>
       <c r="O53" s="8">
         <v>50</v>
@@ -45882,16 +46742,16 @@
         <v>0</v>
       </c>
       <c r="V53" s="6" t="s">
-        <v>1460</v>
+        <v>1366</v>
       </c>
       <c r="W53" s="6" t="s">
-        <v>1459</v>
+        <v>1365</v>
       </c>
       <c r="X53" s="6" t="s">
         <v>50</v>
       </c>
       <c r="Y53" s="6" t="s">
-        <v>1458</v>
+        <v>1497</v>
       </c>
       <c r="Z53" s="6" t="s">
         <v>52</v>
@@ -45927,15 +46787,15 @@
         <v>579.30799999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>1457</v>
+        <v>1496</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1457</v>
+        <v>1496</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D54" s="3">
         <v>46072</v>
@@ -45947,10 +46807,10 @@
         <v>61</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1450</v>
+        <v>1489</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>1449</v>
+        <v>1488</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>163</v>
@@ -45962,13 +46822,13 @@
         <v>417</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>1328</v>
+        <v>1379</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>1327</v>
+        <v>1378</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>1326</v>
+        <v>1377</v>
       </c>
       <c r="O54" s="4">
         <v>1600</v>
@@ -46001,7 +46861,7 @@
         <v>50</v>
       </c>
       <c r="Y54" s="2" t="s">
-        <v>1456</v>
+        <v>1495</v>
       </c>
       <c r="Z54" s="2" t="s">
         <v>52</v>
@@ -46037,15 +46897,15 @@
         <v>15661.904</v>
       </c>
     </row>
-    <row r="55" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
-        <v>1455</v>
+        <v>1494</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>1455</v>
+        <v>1494</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D55" s="7">
         <v>46072</v>
@@ -46057,10 +46917,10 @@
         <v>39</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>1454</v>
+        <v>1493</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>1453</v>
+        <v>1492</v>
       </c>
       <c r="I55" s="6" t="s">
         <v>42</v>
@@ -46072,13 +46932,13 @@
         <v>446</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>1391</v>
+        <v>1438</v>
       </c>
       <c r="M55" s="6" t="s">
-        <v>1390</v>
+        <v>1437</v>
       </c>
       <c r="N55" s="6" t="s">
-        <v>1389</v>
+        <v>1436</v>
       </c>
       <c r="O55" s="8">
         <v>500</v>
@@ -46111,7 +46971,7 @@
         <v>50</v>
       </c>
       <c r="Y55" s="6" t="s">
-        <v>1452</v>
+        <v>1491</v>
       </c>
       <c r="Z55" s="6" t="s">
         <v>52</v>
@@ -46147,15 +47007,15 @@
         <v>5195.07</v>
       </c>
     </row>
-    <row r="56" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>1451</v>
+        <v>1490</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1451</v>
+        <v>1490</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D56" s="3">
         <v>46076</v>
@@ -46167,10 +47027,10 @@
         <v>61</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1450</v>
+        <v>1489</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>1449</v>
+        <v>1488</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>163</v>
@@ -46182,13 +47042,13 @@
         <v>417</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>1328</v>
+        <v>1379</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>1327</v>
+        <v>1378</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>1326</v>
+        <v>1377</v>
       </c>
       <c r="O56" s="4">
         <v>1700</v>
@@ -46221,7 +47081,7 @@
         <v>50</v>
       </c>
       <c r="Y56" s="2" t="s">
-        <v>1448</v>
+        <v>1487</v>
       </c>
       <c r="Z56" s="2" t="s">
         <v>52</v>
@@ -46257,15 +47117,15 @@
         <v>16640.773000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
-        <v>1445</v>
+        <v>1484</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>1445</v>
+        <v>1484</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D57" s="7">
         <v>46077</v>
@@ -46289,16 +47149,16 @@
         <v>164</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>1368</v>
+        <v>1418</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>1447</v>
+        <v>1486</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>1446</v>
+        <v>1485</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>1365</v>
+        <v>1415</v>
       </c>
       <c r="O57" s="8">
         <v>500</v>
@@ -46331,7 +47191,7 @@
         <v>50</v>
       </c>
       <c r="Y57" s="6" t="s">
-        <v>1444</v>
+        <v>1483</v>
       </c>
       <c r="Z57" s="6" t="s">
         <v>52</v>
@@ -46367,15 +47227,15 @@
         <v>4405.1099999999997</v>
       </c>
     </row>
-    <row r="58" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>1445</v>
+        <v>1484</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1445</v>
+        <v>1484</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D58" s="3">
         <v>46077</v>
@@ -46399,16 +47259,16 @@
         <v>164</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>1341</v>
+        <v>1391</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>1340</v>
+        <v>1390</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>1339</v>
+        <v>1389</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>1338</v>
+        <v>1388</v>
       </c>
       <c r="O58" s="4">
         <v>500</v>
@@ -46441,7 +47301,7 @@
         <v>50</v>
       </c>
       <c r="Y58" s="2" t="s">
-        <v>1444</v>
+        <v>1483</v>
       </c>
       <c r="Z58" s="2" t="s">
         <v>52</v>
@@ -46456,10 +47316,10 @@
         <v>111</v>
       </c>
       <c r="AD58" s="2" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="AE58" s="2" t="s">
-        <v>1333</v>
+        <v>1383</v>
       </c>
       <c r="AF58" s="2" t="s">
         <v>77</v>
@@ -46477,15 +47337,15 @@
         <v>4836.3900000000003</v>
       </c>
     </row>
-    <row r="59" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
-        <v>1443</v>
+        <v>1482</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>1443</v>
+        <v>1482</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D59" s="7">
         <v>46078</v>
@@ -46512,13 +47372,13 @@
         <v>782</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>1416</v>
+        <v>1363</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>1415</v>
+        <v>1362</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>1414</v>
+        <v>1361</v>
       </c>
       <c r="O59" s="8">
         <v>225</v>
@@ -46551,7 +47411,7 @@
         <v>50</v>
       </c>
       <c r="Y59" s="6" t="s">
-        <v>1442</v>
+        <v>1481</v>
       </c>
       <c r="Z59" s="6" t="s">
         <v>52</v>
@@ -46587,15 +47447,15 @@
         <v>2225.1802499999999</v>
       </c>
     </row>
-    <row r="60" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>1441</v>
+        <v>1480</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1441</v>
+        <v>1480</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D60" s="3">
         <v>46079</v>
@@ -46622,13 +47482,13 @@
         <v>417</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>1328</v>
+        <v>1379</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>1327</v>
+        <v>1378</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>1326</v>
+        <v>1377</v>
       </c>
       <c r="O60" s="4">
         <v>5000</v>
@@ -46661,7 +47521,7 @@
         <v>50</v>
       </c>
       <c r="Y60" s="2" t="s">
-        <v>1440</v>
+        <v>1479</v>
       </c>
       <c r="Z60" s="2" t="s">
         <v>52</v>
@@ -46697,15 +47557,15 @@
         <v>48943.45</v>
       </c>
     </row>
-    <row r="61" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
-        <v>1439</v>
+        <v>1478</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>1439</v>
+        <v>1478</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D61" s="7">
         <v>46079</v>
@@ -46732,13 +47592,13 @@
         <v>1058</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>1438</v>
+        <v>1477</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>1437</v>
+        <v>1476</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>1436</v>
+        <v>1475</v>
       </c>
       <c r="O61" s="8">
         <v>12000</v>
@@ -46771,7 +47631,7 @@
         <v>50</v>
       </c>
       <c r="Y61" s="6" t="s">
-        <v>1435</v>
+        <v>1474</v>
       </c>
       <c r="Z61" s="6" t="s">
         <v>52</v>
@@ -46807,15 +47667,15 @@
         <v>84565.56</v>
       </c>
     </row>
-    <row r="62" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>1434</v>
+        <v>1473</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1434</v>
+        <v>1473</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D62" s="3">
         <v>46085</v>
@@ -46842,13 +47702,13 @@
         <v>633</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>1376</v>
+        <v>1426</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>652</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>1375</v>
+        <v>1425</v>
       </c>
       <c r="O62" s="4">
         <v>5005</v>
@@ -46881,7 +47741,7 @@
         <v>50</v>
       </c>
       <c r="Y62" s="2" t="s">
-        <v>1433</v>
+        <v>1472</v>
       </c>
       <c r="Z62" s="2" t="s">
         <v>52</v>
@@ -46917,15 +47777,15 @@
         <v>71699.37775</v>
       </c>
     </row>
-    <row r="63" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6" t="s">
-        <v>1432</v>
+        <v>1471</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>1432</v>
+        <v>1471</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D63" s="7">
         <v>46085</v>
@@ -46949,16 +47809,16 @@
         <v>164</v>
       </c>
       <c r="K63" s="6" t="s">
-        <v>1368</v>
+        <v>1418</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>1367</v>
+        <v>1417</v>
       </c>
       <c r="M63" s="6" t="s">
-        <v>1366</v>
+        <v>1416</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>1365</v>
+        <v>1415</v>
       </c>
       <c r="O63" s="8">
         <v>500</v>
@@ -46991,7 +47851,7 @@
         <v>50</v>
       </c>
       <c r="Y63" s="6" t="s">
-        <v>1431</v>
+        <v>1470</v>
       </c>
       <c r="Z63" s="6" t="s">
         <v>52</v>
@@ -47027,15 +47887,15 @@
         <v>4405.1099999999997</v>
       </c>
     </row>
-    <row r="64" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>1432</v>
+        <v>1471</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1432</v>
+        <v>1471</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D64" s="3">
         <v>46085</v>
@@ -47059,16 +47919,16 @@
         <v>164</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>1341</v>
+        <v>1391</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>1340</v>
+        <v>1390</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>1339</v>
+        <v>1389</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>1338</v>
+        <v>1388</v>
       </c>
       <c r="O64" s="4">
         <v>500</v>
@@ -47101,7 +47961,7 @@
         <v>50</v>
       </c>
       <c r="Y64" s="2" t="s">
-        <v>1431</v>
+        <v>1470</v>
       </c>
       <c r="Z64" s="2" t="s">
         <v>52</v>
@@ -47116,10 +47976,10 @@
         <v>111</v>
       </c>
       <c r="AD64" s="2" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="AE64" s="2" t="s">
-        <v>1333</v>
+        <v>1383</v>
       </c>
       <c r="AF64" s="2" t="s">
         <v>77</v>
@@ -47137,15 +47997,15 @@
         <v>4836.3900000000003</v>
       </c>
     </row>
-    <row r="65" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="6" t="s">
-        <v>1430</v>
+        <v>1469</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>1430</v>
+        <v>1469</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D65" s="7">
         <v>46085</v>
@@ -47157,10 +48017,10 @@
         <v>39</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>1429</v>
+        <v>1468</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>1428</v>
+        <v>1467</v>
       </c>
       <c r="I65" s="6" t="s">
         <v>163</v>
@@ -47172,13 +48032,13 @@
         <v>154</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>1427</v>
+        <v>1466</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>1426</v>
+        <v>1465</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>1425</v>
+        <v>1464</v>
       </c>
       <c r="O65" s="8">
         <v>3700</v>
@@ -47211,7 +48071,7 @@
         <v>50</v>
       </c>
       <c r="Y65" s="6" t="s">
-        <v>1424</v>
+        <v>1463</v>
       </c>
       <c r="Z65" s="6" t="s">
         <v>52</v>
@@ -47247,15 +48107,15 @@
         <v>51373.093999999997</v>
       </c>
     </row>
-    <row r="66" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>1423</v>
+        <v>1462</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1423</v>
+        <v>1462</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D66" s="3">
         <v>46085</v>
@@ -47265,10 +48125,10 @@
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2" t="s">
-        <v>1422</v>
+        <v>1370</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>1421</v>
+        <v>1369</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>139</v>
@@ -47317,7 +48177,7 @@
         <v>52</v>
       </c>
       <c r="Y66" s="2" t="s">
-        <v>1420</v>
+        <v>1461</v>
       </c>
       <c r="Z66" s="2" t="s">
         <v>52</v>
@@ -47353,15 +48213,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6" t="s">
-        <v>1419</v>
+        <v>1460</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>1419</v>
+        <v>1460</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D67" s="7">
         <v>46091</v>
@@ -47388,13 +48248,13 @@
         <v>417</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>1410</v>
+        <v>1454</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>1409</v>
+        <v>1453</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>1326</v>
+        <v>1377</v>
       </c>
       <c r="O67" s="8">
         <v>5000</v>
@@ -47427,7 +48287,7 @@
         <v>50</v>
       </c>
       <c r="Y67" s="6" t="s">
-        <v>1418</v>
+        <v>1459</v>
       </c>
       <c r="Z67" s="6" t="s">
         <v>52</v>
@@ -47463,15 +48323,15 @@
         <v>48943.45</v>
       </c>
     </row>
-    <row r="68" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>1417</v>
+        <v>1458</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1417</v>
+        <v>1458</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D68" s="3">
         <v>46091</v>
@@ -47498,13 +48358,13 @@
         <v>782</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>1416</v>
+        <v>1363</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>1415</v>
+        <v>1362</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>1414</v>
+        <v>1361</v>
       </c>
       <c r="O68" s="4">
         <v>225</v>
@@ -47537,7 +48397,7 @@
         <v>50</v>
       </c>
       <c r="Y68" s="2" t="s">
-        <v>1413</v>
+        <v>1457</v>
       </c>
       <c r="Z68" s="2" t="s">
         <v>52</v>
@@ -47573,30 +48433,30 @@
         <v>2225.1802499999999</v>
       </c>
     </row>
-    <row r="69" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
-        <v>1406</v>
+        <v>1451</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>1406</v>
+        <v>1451</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D69" s="7">
         <v>46092</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>1405</v>
+        <v>1450</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>1404</v>
+        <v>1449</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>1403</v>
+        <v>1448</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>1402</v>
+        <v>1447</v>
       </c>
       <c r="I69" s="6" t="s">
         <v>139</v>
@@ -47608,13 +48468,13 @@
         <v>272</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>1412</v>
+        <v>1456</v>
       </c>
       <c r="M69" s="6" t="s">
         <v>274</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>1411</v>
+        <v>1455</v>
       </c>
       <c r="O69" s="8">
         <v>10000</v>
@@ -47638,16 +48498,16 @@
         <v>3312.29</v>
       </c>
       <c r="V69" s="6" t="s">
-        <v>1399</v>
+        <v>1446</v>
       </c>
       <c r="W69" s="6" t="s">
-        <v>1398</v>
+        <v>1445</v>
       </c>
       <c r="X69" s="6" t="s">
         <v>87</v>
       </c>
       <c r="Y69" s="6" t="s">
-        <v>1397</v>
+        <v>1444</v>
       </c>
       <c r="Z69" s="6" t="s">
         <v>52</v>
@@ -47683,30 +48543,30 @@
         <v>101325.9</v>
       </c>
     </row>
-    <row r="70" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>1406</v>
+        <v>1451</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1406</v>
+        <v>1451</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D70" s="3">
         <v>46092</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>1405</v>
+        <v>1450</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>1404</v>
+        <v>1449</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>1403</v>
+        <v>1448</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>1402</v>
+        <v>1447</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>139</v>
@@ -47718,13 +48578,13 @@
         <v>417</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>1410</v>
+        <v>1454</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>1409</v>
+        <v>1453</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>1326</v>
+        <v>1377</v>
       </c>
       <c r="O70" s="4">
         <v>5000</v>
@@ -47748,16 +48608,16 @@
         <v>1559.15</v>
       </c>
       <c r="V70" s="2" t="s">
-        <v>1399</v>
+        <v>1446</v>
       </c>
       <c r="W70" s="2" t="s">
-        <v>1398</v>
+        <v>1445</v>
       </c>
       <c r="X70" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y70" s="2" t="s">
-        <v>1397</v>
+        <v>1444</v>
       </c>
       <c r="Z70" s="2" t="s">
         <v>52</v>
@@ -47793,30 +48653,30 @@
         <v>48943.45</v>
       </c>
     </row>
-    <row r="71" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
-        <v>1406</v>
+        <v>1451</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>1406</v>
+        <v>1451</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D71" s="7">
         <v>46092</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>1405</v>
+        <v>1450</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>1404</v>
+        <v>1449</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>1403</v>
+        <v>1448</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>1402</v>
+        <v>1447</v>
       </c>
       <c r="I71" s="6" t="s">
         <v>139</v>
@@ -47828,13 +48688,13 @@
         <v>342</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>1408</v>
+        <v>1452</v>
       </c>
       <c r="M71" s="6" t="s">
         <v>1193</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>1407</v>
+        <v>1345</v>
       </c>
       <c r="O71" s="8">
         <v>8400</v>
@@ -47858,16 +48718,16 @@
         <v>2580.5300000000002</v>
       </c>
       <c r="V71" s="6" t="s">
-        <v>1399</v>
+        <v>1446</v>
       </c>
       <c r="W71" s="6" t="s">
-        <v>1398</v>
+        <v>1445</v>
       </c>
       <c r="X71" s="6" t="s">
         <v>87</v>
       </c>
       <c r="Y71" s="6" t="s">
-        <v>1397</v>
+        <v>1444</v>
       </c>
       <c r="Z71" s="6" t="s">
         <v>52</v>
@@ -47903,30 +48763,30 @@
         <v>70249.703999999998</v>
       </c>
     </row>
-    <row r="72" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>1406</v>
+        <v>1451</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1406</v>
+        <v>1451</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D72" s="3">
         <v>46092</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>1405</v>
+        <v>1450</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>1404</v>
+        <v>1449</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>1403</v>
+        <v>1448</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>1402</v>
+        <v>1447</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>139</v>
@@ -47938,13 +48798,13 @@
         <v>782</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>1401</v>
+        <v>1360</v>
       </c>
       <c r="M72" s="2" t="s">
         <v>1167</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>1400</v>
+        <v>1359</v>
       </c>
       <c r="O72" s="4">
         <v>2400</v>
@@ -47968,16 +48828,16 @@
         <v>775.1</v>
       </c>
       <c r="V72" s="2" t="s">
-        <v>1399</v>
+        <v>1446</v>
       </c>
       <c r="W72" s="2" t="s">
-        <v>1398</v>
+        <v>1445</v>
       </c>
       <c r="X72" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y72" s="2" t="s">
-        <v>1397</v>
+        <v>1444</v>
       </c>
       <c r="Z72" s="2" t="s">
         <v>52</v>
@@ -48013,15 +48873,15 @@
         <v>23735.256000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="6" t="s">
-        <v>1396</v>
+        <v>1443</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>1396</v>
+        <v>1443</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D73" s="7">
         <v>46093</v>
@@ -48033,10 +48893,10 @@
         <v>61</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>1351</v>
+        <v>1401</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="I73" s="6" t="s">
         <v>163</v>
@@ -48048,13 +48908,13 @@
         <v>633</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>1376</v>
+        <v>1426</v>
       </c>
       <c r="M73" s="6" t="s">
         <v>652</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>1375</v>
+        <v>1425</v>
       </c>
       <c r="O73" s="8">
         <v>507</v>
@@ -48087,7 +48947,7 @@
         <v>50</v>
       </c>
       <c r="Y73" s="6" t="s">
-        <v>1395</v>
+        <v>1442</v>
       </c>
       <c r="Z73" s="6" t="s">
         <v>52</v>
@@ -48123,15 +48983,15 @@
         <v>7263.0538500000002</v>
       </c>
     </row>
-    <row r="74" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>1394</v>
+        <v>1441</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1394</v>
+        <v>1441</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D74" s="3">
         <v>46097</v>
@@ -48149,22 +49009,22 @@
         <v>386</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>1393</v>
+        <v>1440</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>1392</v>
+        <v>1439</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>446</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>1391</v>
+        <v>1438</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>1390</v>
+        <v>1437</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>1389</v>
+        <v>1436</v>
       </c>
       <c r="O74" s="4">
         <v>3000</v>
@@ -48197,7 +49057,7 @@
         <v>50</v>
       </c>
       <c r="Y74" s="2" t="s">
-        <v>1388</v>
+        <v>1435</v>
       </c>
       <c r="Z74" s="2" t="s">
         <v>52</v>
@@ -48233,15 +49093,15 @@
         <v>31170.42</v>
       </c>
     </row>
-    <row r="75" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="s">
-        <v>1387</v>
+        <v>1434</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>1387</v>
+        <v>1434</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D75" s="7">
         <v>46098</v>
@@ -48268,13 +49128,13 @@
         <v>300</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>1358</v>
+        <v>1408</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>1357</v>
+        <v>1407</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="O75" s="8">
         <v>10000</v>
@@ -48298,16 +49158,16 @@
         <v>14724</v>
       </c>
       <c r="V75" s="6" t="s">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="W75" s="6" t="s">
-        <v>1385</v>
+        <v>1432</v>
       </c>
       <c r="X75" s="6" t="s">
         <v>50</v>
       </c>
       <c r="Y75" s="6" t="s">
-        <v>1384</v>
+        <v>1431</v>
       </c>
       <c r="Z75" s="6" t="s">
         <v>52</v>
@@ -48343,15 +49203,15 @@
         <v>75850.3</v>
       </c>
     </row>
-    <row r="76" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>1383</v>
+        <v>1430</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1383</v>
+        <v>1430</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D76" s="3">
         <v>46098</v>
@@ -48363,10 +49223,10 @@
         <v>61</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>1351</v>
+        <v>1401</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>163</v>
@@ -48378,13 +49238,13 @@
         <v>632</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>1349</v>
+        <v>1399</v>
       </c>
       <c r="M76" s="2" t="s">
         <v>648</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>1348</v>
+        <v>1398</v>
       </c>
       <c r="O76" s="4">
         <v>507</v>
@@ -48417,7 +49277,7 @@
         <v>50</v>
       </c>
       <c r="Y76" s="2" t="s">
-        <v>1382</v>
+        <v>1429</v>
       </c>
       <c r="Z76" s="2" t="s">
         <v>52</v>
@@ -48453,15 +49313,15 @@
         <v>5539.1575199999997</v>
       </c>
     </row>
-    <row r="77" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="6" t="s">
-        <v>1381</v>
+        <v>1428</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>1381</v>
+        <v>1428</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D77" s="7">
         <v>46100</v>
@@ -48488,13 +49348,13 @@
         <v>782</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>1380</v>
+        <v>1375</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>1379</v>
+        <v>1374</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>1378</v>
+        <v>1355</v>
       </c>
       <c r="O77" s="8">
         <v>10000</v>
@@ -48527,7 +49387,7 @@
         <v>50</v>
       </c>
       <c r="Y77" s="6" t="s">
-        <v>1377</v>
+        <v>1427</v>
       </c>
       <c r="Z77" s="6" t="s">
         <v>52</v>
@@ -48563,15 +49423,15 @@
         <v>98896.9</v>
       </c>
     </row>
-    <row r="78" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>1374</v>
+        <v>1424</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1374</v>
+        <v>1424</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D78" s="3">
         <v>46104</v>
@@ -48598,13 +49458,13 @@
         <v>633</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>1376</v>
+        <v>1426</v>
       </c>
       <c r="M78" s="2" t="s">
         <v>652</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>1375</v>
+        <v>1425</v>
       </c>
       <c r="O78" s="4">
         <v>1170</v>
@@ -48637,7 +49497,7 @@
         <v>50</v>
       </c>
       <c r="Y78" s="2" t="s">
-        <v>1370</v>
+        <v>1420</v>
       </c>
       <c r="Z78" s="2" t="s">
         <v>52</v>
@@ -48673,15 +49533,15 @@
         <v>16760.893499999998</v>
       </c>
     </row>
-    <row r="79" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="6" t="s">
-        <v>1374</v>
+        <v>1424</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>1374</v>
+        <v>1424</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D79" s="7">
         <v>46104</v>
@@ -48708,13 +49568,13 @@
         <v>633</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>1373</v>
+        <v>1423</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>1372</v>
+        <v>1422</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>1371</v>
+        <v>1421</v>
       </c>
       <c r="O79" s="8">
         <v>2834</v>
@@ -48747,7 +49607,7 @@
         <v>50</v>
       </c>
       <c r="Y79" s="6" t="s">
-        <v>1370</v>
+        <v>1420</v>
       </c>
       <c r="Z79" s="6" t="s">
         <v>52</v>
@@ -48783,15 +49643,15 @@
         <v>40598.637040000001</v>
       </c>
     </row>
-    <row r="80" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>1369</v>
+        <v>1419</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1369</v>
+        <v>1419</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D80" s="3">
         <v>46104</v>
@@ -48815,16 +49675,16 @@
         <v>164</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>1368</v>
+        <v>1418</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>1367</v>
+        <v>1417</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>1366</v>
+        <v>1416</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>1365</v>
+        <v>1415</v>
       </c>
       <c r="O80" s="4">
         <v>1750</v>
@@ -48857,7 +49717,7 @@
         <v>50</v>
       </c>
       <c r="Y80" s="2" t="s">
-        <v>1364</v>
+        <v>1414</v>
       </c>
       <c r="Z80" s="2" t="s">
         <v>52</v>
@@ -48893,15 +49753,15 @@
         <v>15417.885</v>
       </c>
     </row>
-    <row r="81" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6" t="s">
-        <v>1363</v>
+        <v>1413</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>1363</v>
+        <v>1413</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D81" s="7">
         <v>46104</v>
@@ -48925,16 +49785,16 @@
         <v>164</v>
       </c>
       <c r="K81" s="6" t="s">
-        <v>1341</v>
+        <v>1391</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>1340</v>
+        <v>1390</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>1339</v>
+        <v>1389</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>1338</v>
+        <v>1388</v>
       </c>
       <c r="O81" s="8">
         <v>2000</v>
@@ -48967,7 +49827,7 @@
         <v>50</v>
       </c>
       <c r="Y81" s="6" t="s">
-        <v>1362</v>
+        <v>1412</v>
       </c>
       <c r="Z81" s="6" t="s">
         <v>52</v>
@@ -48982,10 +49842,10 @@
         <v>111</v>
       </c>
       <c r="AD81" s="6" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="AE81" s="6" t="s">
-        <v>1333</v>
+        <v>1383</v>
       </c>
       <c r="AF81" s="6" t="s">
         <v>77</v>
@@ -49003,15 +49863,15 @@
         <v>19345.560000000001</v>
       </c>
     </row>
-    <row r="82" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>1361</v>
+        <v>1411</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1361</v>
+        <v>1411</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D82" s="3">
         <v>46105</v>
@@ -49023,10 +49883,10 @@
         <v>39</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>1360</v>
+        <v>1410</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>1359</v>
+        <v>1409</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>42</v>
@@ -49038,13 +49898,13 @@
         <v>300</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>1358</v>
+        <v>1408</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>1357</v>
+        <v>1407</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>1356</v>
+        <v>1406</v>
       </c>
       <c r="O82" s="4">
         <v>500</v>
@@ -49068,16 +49928,16 @@
         <v>776.4</v>
       </c>
       <c r="V82" s="2" t="s">
-        <v>1355</v>
+        <v>1405</v>
       </c>
       <c r="W82" s="2" t="s">
-        <v>1354</v>
+        <v>1404</v>
       </c>
       <c r="X82" s="2" t="s">
         <v>50</v>
       </c>
       <c r="Y82" s="2" t="s">
-        <v>1353</v>
+        <v>1403</v>
       </c>
       <c r="Z82" s="2" t="s">
         <v>52</v>
@@ -49113,15 +49973,15 @@
         <v>3792.5149999999999</v>
       </c>
     </row>
-    <row r="83" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6" t="s">
-        <v>1352</v>
+        <v>1402</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>1352</v>
+        <v>1402</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D83" s="7">
         <v>46106</v>
@@ -49133,10 +49993,10 @@
         <v>61</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>1351</v>
+        <v>1401</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="I83" s="6" t="s">
         <v>163</v>
@@ -49148,13 +50008,13 @@
         <v>632</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>1349</v>
+        <v>1399</v>
       </c>
       <c r="M83" s="6" t="s">
         <v>648</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>1348</v>
+        <v>1398</v>
       </c>
       <c r="O83" s="8">
         <v>1001</v>
@@ -49187,7 +50047,7 @@
         <v>50</v>
       </c>
       <c r="Y83" s="6" t="s">
-        <v>1347</v>
+        <v>1397</v>
       </c>
       <c r="Z83" s="6" t="s">
         <v>52</v>
@@ -49223,15 +50083,15 @@
         <v>10936.28536</v>
       </c>
     </row>
-    <row r="84" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>1346</v>
+        <v>1396</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1346</v>
+        <v>1396</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D84" s="3">
         <v>46106</v>
@@ -49243,10 +50103,10 @@
         <v>39</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>1345</v>
+        <v>1395</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>1344</v>
+        <v>1394</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>293</v>
@@ -49258,13 +50118,13 @@
         <v>417</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>1328</v>
+        <v>1379</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>1327</v>
+        <v>1378</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>1326</v>
+        <v>1377</v>
       </c>
       <c r="O84" s="4">
         <v>600</v>
@@ -49297,7 +50157,7 @@
         <v>50</v>
       </c>
       <c r="Y84" s="2" t="s">
-        <v>1343</v>
+        <v>1393</v>
       </c>
       <c r="Z84" s="2" t="s">
         <v>52</v>
@@ -49333,15 +50193,15 @@
         <v>5873.2139999999999</v>
       </c>
     </row>
-    <row r="85" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6" t="s">
-        <v>1342</v>
+        <v>1392</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>1342</v>
+        <v>1392</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D85" s="7">
         <v>46108</v>
@@ -49365,16 +50225,16 @@
         <v>1302</v>
       </c>
       <c r="K85" s="6" t="s">
-        <v>1341</v>
+        <v>1391</v>
       </c>
       <c r="L85" s="6" t="s">
-        <v>1340</v>
+        <v>1390</v>
       </c>
       <c r="M85" s="6" t="s">
-        <v>1339</v>
+        <v>1389</v>
       </c>
       <c r="N85" s="6" t="s">
-        <v>1338</v>
+        <v>1388</v>
       </c>
       <c r="O85" s="8">
         <v>500</v>
@@ -49398,16 +50258,16 @@
         <v>858.6</v>
       </c>
       <c r="V85" s="6" t="s">
-        <v>1337</v>
+        <v>1387</v>
       </c>
       <c r="W85" s="6" t="s">
-        <v>1336</v>
+        <v>1386</v>
       </c>
       <c r="X85" s="6" t="s">
         <v>50</v>
       </c>
       <c r="Y85" s="6" t="s">
-        <v>1335</v>
+        <v>1385</v>
       </c>
       <c r="Z85" s="6" t="s">
         <v>52</v>
@@ -49422,10 +50282,10 @@
         <v>111</v>
       </c>
       <c r="AD85" s="6" t="s">
-        <v>1334</v>
+        <v>1384</v>
       </c>
       <c r="AE85" s="6" t="s">
-        <v>1333</v>
+        <v>1383</v>
       </c>
       <c r="AF85" s="6" t="s">
         <v>77</v>
@@ -49443,15 +50303,15 @@
         <v>4836.3900000000003</v>
       </c>
     </row>
-    <row r="86" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>1332</v>
+        <v>1382</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1332</v>
+        <v>1382</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D86" s="3">
         <v>46108</v>
@@ -49463,10 +50323,10 @@
         <v>61</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>1330</v>
+        <v>1381</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>1329</v>
+        <v>1380</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>163</v>
@@ -49478,13 +50338,13 @@
         <v>417</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>1328</v>
+        <v>1379</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>1327</v>
+        <v>1378</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>1326</v>
+        <v>1377</v>
       </c>
       <c r="O86" s="4">
         <v>1000</v>
@@ -49517,7 +50377,7 @@
         <v>50</v>
       </c>
       <c r="Y86" s="2" t="s">
-        <v>1325</v>
+        <v>1376</v>
       </c>
       <c r="Z86" s="2" t="s">
         <v>52</v>
@@ -49553,8 +50413,888 @@
         <v>9788.69</v>
       </c>
     </row>
+    <row r="87" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="6" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D87" s="7">
+        <v>46111</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="I87" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="J87" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K87" s="6" t="s">
+        <v>782</v>
+      </c>
+      <c r="L87" s="6" t="s">
+        <v>1357</v>
+      </c>
+      <c r="M87" s="6" t="s">
+        <v>1356</v>
+      </c>
+      <c r="N87" s="6" t="s">
+        <v>1355</v>
+      </c>
+      <c r="O87" s="8">
+        <v>8075</v>
+      </c>
+      <c r="P87" s="8">
+        <v>8.9</v>
+      </c>
+      <c r="Q87" s="9">
+        <v>71867.5</v>
+      </c>
+      <c r="R87" s="9">
+        <v>2335.69</v>
+      </c>
+      <c r="S87" s="9">
+        <v>74203.19</v>
+      </c>
+      <c r="T87" s="9">
+        <v>133500</v>
+      </c>
+      <c r="U87" s="9">
+        <v>2874.7</v>
+      </c>
+      <c r="V87" s="6" t="s">
+        <v>1202</v>
+      </c>
+      <c r="W87" s="6" t="s">
+        <v>1203</v>
+      </c>
+      <c r="X87" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y87" s="6" t="s">
+        <v>1372</v>
+      </c>
+      <c r="Z87" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA87" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB87" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="AC87" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="AD87" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE87" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF87" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG87" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI87" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ87" s="8">
+        <v>79859.246750000006</v>
+      </c>
+    </row>
+    <row r="88" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D88" s="3">
+        <v>46111</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="M88" s="2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="N88" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="O88" s="4">
+        <v>5000</v>
+      </c>
+      <c r="P88" s="4">
+        <v>8.9</v>
+      </c>
+      <c r="Q88" s="5">
+        <v>44500</v>
+      </c>
+      <c r="R88" s="5">
+        <v>1446.25</v>
+      </c>
+      <c r="S88" s="5">
+        <v>45946.25</v>
+      </c>
+      <c r="T88" s="5">
+        <v>133500</v>
+      </c>
+      <c r="U88" s="5">
+        <v>1780</v>
+      </c>
+      <c r="V88" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="W88" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="X88" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y88" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="Z88" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA88" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB88" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AC88" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="AD88" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE88" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF88" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG88" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI88" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ88" s="4">
+        <v>49448.5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="6" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D89" s="7">
+        <v>46111</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="J89" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K89" s="6" t="s">
+        <v>782</v>
+      </c>
+      <c r="L89" s="6" t="s">
+        <v>1360</v>
+      </c>
+      <c r="M89" s="6" t="s">
+        <v>1167</v>
+      </c>
+      <c r="N89" s="6" t="s">
+        <v>1359</v>
+      </c>
+      <c r="O89" s="8">
+        <v>1925</v>
+      </c>
+      <c r="P89" s="8">
+        <v>8.9</v>
+      </c>
+      <c r="Q89" s="9">
+        <v>17132.5</v>
+      </c>
+      <c r="R89" s="9">
+        <v>556.80999999999995</v>
+      </c>
+      <c r="S89" s="9">
+        <v>17689.310000000001</v>
+      </c>
+      <c r="T89" s="9">
+        <v>133500</v>
+      </c>
+      <c r="U89" s="9">
+        <v>685.3</v>
+      </c>
+      <c r="V89" s="6" t="s">
+        <v>1202</v>
+      </c>
+      <c r="W89" s="6" t="s">
+        <v>1203</v>
+      </c>
+      <c r="X89" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y89" s="6" t="s">
+        <v>1372</v>
+      </c>
+      <c r="Z89" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA89" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB89" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="AC89" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="AD89" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE89" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF89" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG89" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI89" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ89" s="8">
+        <v>19037.672500000001</v>
+      </c>
+    </row>
+    <row r="90" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D90" s="3">
+        <v>46111</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K90" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="L90" s="2" t="s">
+        <v>1368</v>
+      </c>
+      <c r="M90" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="N90" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="O90" s="4">
+        <v>50</v>
+      </c>
+      <c r="P90" s="4">
+        <v>19.53</v>
+      </c>
+      <c r="Q90" s="5">
+        <v>976.5</v>
+      </c>
+      <c r="R90" s="5">
+        <v>0</v>
+      </c>
+      <c r="S90" s="5">
+        <v>976.5</v>
+      </c>
+      <c r="T90" s="5">
+        <v>976.5</v>
+      </c>
+      <c r="U90" s="5">
+        <v>39.06</v>
+      </c>
+      <c r="V90" s="2" t="s">
+        <v>1366</v>
+      </c>
+      <c r="W90" s="2" t="s">
+        <v>1365</v>
+      </c>
+      <c r="X90" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y90" s="2" t="s">
+        <v>1364</v>
+      </c>
+      <c r="Z90" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA90" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB90" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AC90" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="AD90" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="AE90" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="AF90" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG90" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH90" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI90" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ90" s="4">
+        <v>579.30799999999999</v>
+      </c>
+    </row>
+    <row r="91" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="6" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D91" s="7">
+        <v>46111</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>838</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>839</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="J91" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K91" s="6" t="s">
+        <v>782</v>
+      </c>
+      <c r="L91" s="6" t="s">
+        <v>1363</v>
+      </c>
+      <c r="M91" s="6" t="s">
+        <v>1362</v>
+      </c>
+      <c r="N91" s="6" t="s">
+        <v>1361</v>
+      </c>
+      <c r="O91" s="8">
+        <v>725</v>
+      </c>
+      <c r="P91" s="8">
+        <v>9.18</v>
+      </c>
+      <c r="Q91" s="9">
+        <v>6655.5</v>
+      </c>
+      <c r="R91" s="9">
+        <v>216.3</v>
+      </c>
+      <c r="S91" s="9">
+        <v>6871.8</v>
+      </c>
+      <c r="T91" s="9">
+        <v>82620</v>
+      </c>
+      <c r="U91" s="9">
+        <v>266.22000000000003</v>
+      </c>
+      <c r="V91" s="6" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W91" s="6" t="s">
+        <v>1353</v>
+      </c>
+      <c r="X91" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y91" s="6" t="s">
+        <v>1352</v>
+      </c>
+      <c r="Z91" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA91" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB91" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC91" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="AD91" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE91" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF91" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG91" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI91" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ91" s="8">
+        <v>7170.0325000000003</v>
+      </c>
+    </row>
+    <row r="92" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D92" s="3">
+        <v>46111</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="L92" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="M92" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="N92" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="O92" s="4">
+        <v>7675</v>
+      </c>
+      <c r="P92" s="4">
+        <v>9.18</v>
+      </c>
+      <c r="Q92" s="5">
+        <v>70456.5</v>
+      </c>
+      <c r="R92" s="5">
+        <v>2289.84</v>
+      </c>
+      <c r="S92" s="5">
+        <v>72746.34</v>
+      </c>
+      <c r="T92" s="5">
+        <v>82620</v>
+      </c>
+      <c r="U92" s="5">
+        <v>2818.26</v>
+      </c>
+      <c r="V92" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W92" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="X92" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y92" s="2" t="s">
+        <v>1352</v>
+      </c>
+      <c r="Z92" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA92" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB92" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC92" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="AD92" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE92" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF92" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG92" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI92" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ92" s="4">
+        <v>75903.447499999995</v>
+      </c>
+    </row>
+    <row r="93" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="6" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D93" s="7">
+        <v>46111</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>838</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>839</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="J93" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K93" s="6" t="s">
+        <v>782</v>
+      </c>
+      <c r="L93" s="6" t="s">
+        <v>1357</v>
+      </c>
+      <c r="M93" s="6" t="s">
+        <v>1356</v>
+      </c>
+      <c r="N93" s="6" t="s">
+        <v>1355</v>
+      </c>
+      <c r="O93" s="8">
+        <v>600</v>
+      </c>
+      <c r="P93" s="8">
+        <v>9.18</v>
+      </c>
+      <c r="Q93" s="9">
+        <v>5508</v>
+      </c>
+      <c r="R93" s="9">
+        <v>179.01</v>
+      </c>
+      <c r="S93" s="9">
+        <v>5687.01</v>
+      </c>
+      <c r="T93" s="9">
+        <v>82620</v>
+      </c>
+      <c r="U93" s="9">
+        <v>220.32</v>
+      </c>
+      <c r="V93" s="6" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W93" s="6" t="s">
+        <v>1353</v>
+      </c>
+      <c r="X93" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y93" s="6" t="s">
+        <v>1352</v>
+      </c>
+      <c r="Z93" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA93" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB93" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC93" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="AD93" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE93" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF93" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG93" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI93" s="9">
+        <v>4</v>
+      </c>
+      <c r="AJ93" s="8">
+        <v>5933.8320000000003</v>
+      </c>
+    </row>
+    <row r="94" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D94" s="3">
+        <v>46111</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>1349</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K94" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="L94" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="M94" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="N94" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="O94" s="4">
+        <v>75</v>
+      </c>
+      <c r="P94" s="4">
+        <v>14.65</v>
+      </c>
+      <c r="Q94" s="5">
+        <v>1098.75</v>
+      </c>
+      <c r="R94" s="5">
+        <v>35.71</v>
+      </c>
+      <c r="S94" s="5">
+        <v>1134.46</v>
+      </c>
+      <c r="T94" s="5">
+        <v>1098.75</v>
+      </c>
+      <c r="U94" s="5">
+        <v>43.95</v>
+      </c>
+      <c r="V94" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="W94" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="X94" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y94" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="Z94" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA94" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB94" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC94" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD94" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE94" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF94" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG94" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI94" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ94" s="4">
+        <v>528.53475000000003</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ86" xr:uid="{7750C0CA-A699-4DF4-84A9-3E776C737B11}"/>
+  <autoFilter ref="A1:AJ94" xr:uid="{42F6757A-88FA-46BC-A723-2ABE134244F9}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>